--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Curtis Garage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{96416574-545E-4D98-8601-2E5DE15F6AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="5475" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId4"/>
+    <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="235">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -62,29 +67,678 @@
     <t>Coaching Completed At</t>
   </si>
   <si>
-    <t>No drive alerts found for the selected period.</t>
+    <t>02/15/26 11:46 EST</t>
+  </si>
+  <si>
+    <t>Matt Roberts</t>
+  </si>
+  <si>
+    <t>SPEEDING-VIOLATIONS</t>
+  </si>
+  <si>
+    <t>8mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>Coachable</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>Tammy Thompson</t>
+  </si>
+  <si>
+    <t>03/17/26 10:47 EDT</t>
+  </si>
+  <si>
+    <t>02/15/26 12:01 EST</t>
+  </si>
+  <si>
+    <t>5.3mi S of Speedway IN</t>
+  </si>
+  <si>
+    <t>02/15/26 12:08 EST</t>
+  </si>
+  <si>
+    <t>FOLLOWING-DISTANCE</t>
+  </si>
+  <si>
+    <t>0.5mi S of Indianapolis IN</t>
+  </si>
+  <si>
+    <t>02/17/26 05:35 EST</t>
+  </si>
+  <si>
+    <t>Jeremy Schultz</t>
+  </si>
+  <si>
+    <t>4.5mi S of Speedway IN</t>
+  </si>
+  <si>
+    <t>02/17/26 05:38 EST</t>
+  </si>
+  <si>
+    <t>3.4mi SW of Indianapolis IN</t>
+  </si>
+  <si>
+    <t>02/17/26 05:47 EST</t>
+  </si>
+  <si>
+    <t>4.9mi NE of Indianapolis IN</t>
+  </si>
+  <si>
+    <t>02/17/26 07:20 EST</t>
+  </si>
+  <si>
+    <t>SIGN-VIOLATIONS</t>
+  </si>
+  <si>
+    <t>3.1mi E of Richmond IN</t>
+  </si>
+  <si>
+    <t>02/17/26 07:35 EST</t>
+  </si>
+  <si>
+    <t>9.5mi NW of Martinsville IN</t>
+  </si>
+  <si>
+    <t>02/17/26 07:38 EST</t>
+  </si>
+  <si>
+    <t>11.3mi NW of Martinsville IN</t>
+  </si>
+  <si>
+    <t>02/17/26 18:06 EST</t>
+  </si>
+  <si>
+    <t>Greg Brewer</t>
+  </si>
+  <si>
+    <t>TRAFFIC-LIGHT-VIOLATION</t>
+  </si>
+  <si>
+    <t>8.1mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>02/18/26 06:42 EST</t>
+  </si>
+  <si>
+    <t>8.4mi NE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>02/18/26 06:54 EST</t>
+  </si>
+  <si>
+    <t>1.2mi NE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>02/18/26 17:54 EST</t>
+  </si>
+  <si>
+    <t>Sam Friend</t>
+  </si>
+  <si>
+    <t>4.9mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>02/19/26 17:12 EST</t>
+  </si>
+  <si>
+    <t>9.2mi E of Greencastle IN</t>
+  </si>
+  <si>
+    <t>02/19/26 20:01 EST</t>
+  </si>
+  <si>
+    <t>02/19/26 21:33 EST</t>
+  </si>
+  <si>
+    <t>DRIVER-DISTRACTION</t>
+  </si>
+  <si>
+    <t>0.6mi E of Avon IN</t>
+  </si>
+  <si>
+    <t>02/20/26 06:33 EST</t>
+  </si>
+  <si>
+    <t>9.5mi W of Danville IN</t>
+  </si>
+  <si>
+    <t>03/17/26 10:46 EDT</t>
+  </si>
+  <si>
+    <t>02/20/26 06:36 EST</t>
+  </si>
+  <si>
+    <t>9.9mi E of Greencastle IN</t>
+  </si>
+  <si>
+    <t>02/20/26 06:51 EST</t>
+  </si>
+  <si>
+    <t>12.2mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>02/20/26 06:55 EST</t>
+  </si>
+  <si>
+    <t>12.3mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>02/20/26 07:03 EST</t>
+  </si>
+  <si>
+    <t>8.4mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>02/20/26 07:07 EST</t>
+  </si>
+  <si>
+    <t>8.3mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>02/20/26 07:17 EST</t>
+  </si>
+  <si>
+    <t>10.2mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>02/20/26 07:52 EST</t>
+  </si>
+  <si>
+    <t>10.3mi E of Greencastle IN</t>
+  </si>
+  <si>
+    <t>02/20/26 13:40 EST</t>
+  </si>
+  <si>
+    <t>Doug Phillippo</t>
+  </si>
+  <si>
+    <t>11.9mi E of Greencastle IN</t>
+  </si>
+  <si>
+    <t>02/21/26 10:20 EST</t>
+  </si>
+  <si>
+    <t>02/21/26 10:22 EST</t>
+  </si>
+  <si>
+    <t>9.7mi E of Greencastle IN</t>
+  </si>
+  <si>
+    <t>02/21/26 10:44 EST</t>
+  </si>
+  <si>
+    <t>Walker Sims</t>
+  </si>
+  <si>
+    <t>10.8mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>SEATBELT-COMPLIANCE</t>
+  </si>
+  <si>
+    <t>11.1mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>02/21/26 16:53 EST</t>
+  </si>
+  <si>
+    <t>9.2mi NE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>02/21/26 18:31 EST</t>
+  </si>
+  <si>
+    <t>13.6mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/01/26 12:11 EST</t>
+  </si>
+  <si>
+    <t>8.2mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>03/17/26 10:48 EDT</t>
+  </si>
+  <si>
+    <t>03/01/26 12:18 EST</t>
+  </si>
+  <si>
+    <t>03/03/26 07:29 EST</t>
+  </si>
+  <si>
+    <t>1.9mi S of Plainfield IN</t>
+  </si>
+  <si>
+    <t>03/03/26 21:07 EST</t>
+  </si>
+  <si>
+    <t>7.9mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/17/26 10:53 EDT</t>
+  </si>
+  <si>
+    <t>03/03/26 21:11 EST</t>
+  </si>
+  <si>
+    <t>03/03/26 21:25 EST</t>
+  </si>
+  <si>
+    <t>12.1mi E of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/04/26 07:24 EST</t>
+  </si>
+  <si>
+    <t>13mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/04/26 07:40 EST</t>
+  </si>
+  <si>
+    <t>LANE-CONDUCT</t>
+  </si>
+  <si>
+    <t>12.8mi W of Martinsville IN</t>
+  </si>
+  <si>
+    <t>03/04/26 07:55 EST</t>
+  </si>
+  <si>
+    <t>13.5mi NW of Martinsville IN</t>
+  </si>
+  <si>
+    <t>03/04/26 08:17 EST</t>
+  </si>
+  <si>
+    <t>12.4mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/17/26 10:51 EDT</t>
+  </si>
+  <si>
+    <t>03/04/26 13:17 EST</t>
+  </si>
+  <si>
+    <t>12.5mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/04/26 14:04 EST</t>
+  </si>
+  <si>
+    <t>2.2mi SW of Danville IN</t>
+  </si>
+  <si>
+    <t>03/04/26 16:53 EST</t>
+  </si>
+  <si>
+    <t>12mi E of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/05/26 07:52 EST</t>
+  </si>
+  <si>
+    <t>10.2mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/05/26 09:37 EST</t>
+  </si>
+  <si>
+    <t>03/05/26 10:33 EST</t>
+  </si>
+  <si>
+    <t>BACKING</t>
+  </si>
+  <si>
+    <t>03/05/26 11:13 EST</t>
+  </si>
+  <si>
+    <t>13.3mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/05/26 17:22 EST</t>
+  </si>
+  <si>
+    <t>9.6mi E of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/05/26 22:17 EST</t>
+  </si>
+  <si>
+    <t>03/06/26 07:32 EST</t>
+  </si>
+  <si>
+    <t>DRIVER-STAR</t>
+  </si>
+  <si>
+    <t>8mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/06/26 07:40 EST</t>
+  </si>
+  <si>
+    <t>03/06/26 08:40 EST</t>
+  </si>
+  <si>
+    <t>Mike Cline</t>
+  </si>
+  <si>
+    <t>03/06/26 15:54 EST</t>
+  </si>
+  <si>
+    <t>3.6mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/06/26 16:27 EST</t>
+  </si>
+  <si>
+    <t>03/06/26 17:49 EST</t>
+  </si>
+  <si>
+    <t>6.8mi E of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/07/26 01:18 EST</t>
+  </si>
+  <si>
+    <t>11.4mi W of Martinsville IN</t>
+  </si>
+  <si>
+    <t>03/07/26 15:25 EST</t>
+  </si>
+  <si>
+    <t>03/17/26 10:52 EDT</t>
+  </si>
+  <si>
+    <t>03/07/26 15:28 EST</t>
+  </si>
+  <si>
+    <t>03/07/26 18:09 EST</t>
+  </si>
+  <si>
+    <t>03/07/26 20:23 EST</t>
+  </si>
+  <si>
+    <t>03/07/26 20:50 EST</t>
+  </si>
+  <si>
+    <t>12.7mi NW of Martinsville IN</t>
+  </si>
+  <si>
+    <t>03/08/26 09:42 EDT</t>
+  </si>
+  <si>
+    <t>7.5mi NE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/09/26 07:03 EDT</t>
+  </si>
+  <si>
+    <t>03/09/26 07:33 EDT</t>
+  </si>
+  <si>
+    <t>03/09/26 11:42 EDT</t>
+  </si>
+  <si>
+    <t>9.9mi SW of Danville IN</t>
+  </si>
+  <si>
+    <t>03/09/26 17:14 EDT</t>
+  </si>
+  <si>
+    <t>03/09/26 20:20 EDT</t>
+  </si>
+  <si>
+    <t>6.3mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>03/09/26 21:30 EDT</t>
+  </si>
+  <si>
+    <t>2.9mi SE of Terre Haute IN</t>
+  </si>
+  <si>
+    <t>03/10/26 14:11 EDT</t>
+  </si>
+  <si>
+    <t>6mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>03/10/26 14:46 EDT</t>
+  </si>
+  <si>
+    <t>8.9mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/10/26 16:48 EDT</t>
+  </si>
+  <si>
+    <t>12.1mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>03/11/26 06:50 EDT</t>
+  </si>
+  <si>
+    <t>03/11/26 10:30 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 10:54 EDT</t>
+  </si>
+  <si>
+    <t>03/11/26 10:57 EDT</t>
+  </si>
+  <si>
+    <t>03/11/26 13:57 EDT</t>
+  </si>
+  <si>
+    <t>03/11/26 18:09 EDT</t>
+  </si>
+  <si>
+    <t>6.1mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>03/11/26 19:51 EDT</t>
+  </si>
+  <si>
+    <t>03/12/26 06:50 EDT</t>
+  </si>
+  <si>
+    <t>03/12/26 15:37 EDT</t>
+  </si>
+  <si>
+    <t>03/12/26 16:08 EDT</t>
+  </si>
+  <si>
+    <t>03/12/26 16:44 EDT</t>
+  </si>
+  <si>
+    <t>4.9mi S of Brazil IN</t>
+  </si>
+  <si>
+    <t>03/12/26 17:05 EDT</t>
+  </si>
+  <si>
+    <t>03/13/26 06:37 EDT</t>
+  </si>
+  <si>
+    <t>8.7mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/13/26 07:37 EDT</t>
+  </si>
+  <si>
+    <t>1mi N of Plainfield IN</t>
+  </si>
+  <si>
+    <t>Driver Education Network Service user</t>
+  </si>
+  <si>
+    <t>03/16/26 11:16 EDT</t>
+  </si>
+  <si>
+    <t>03/13/26 08:46 EDT</t>
+  </si>
+  <si>
+    <t>4.5mi SE of Martinsville IN</t>
+  </si>
+  <si>
+    <t>03/13/26 08:48 EDT</t>
+  </si>
+  <si>
+    <t>2.9mi SE of Martinsville IN</t>
+  </si>
+  <si>
+    <t>03/13/26 17:01 EDT</t>
+  </si>
+  <si>
+    <t>7.6mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/14/26 01:42 EDT</t>
+  </si>
+  <si>
+    <t>Non-Coachable</t>
+  </si>
+  <si>
+    <t>03/14/26 14:02 EDT</t>
+  </si>
+  <si>
+    <t>8.2mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/16/26 11:15 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 17:23 EDT</t>
+  </si>
+  <si>
+    <t>3mi NW of Martinsville IN</t>
+  </si>
+  <si>
+    <t>03/15/26 09:23 EDT</t>
+  </si>
+  <si>
+    <t>8.9mi NW of Martinsville IN</t>
+  </si>
+  <si>
+    <t>03/15/26 12:41 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 11:14 EDT</t>
+  </si>
+  <si>
+    <t>03/15/26 14:16 EDT</t>
+  </si>
+  <si>
+    <t>10.8mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/16/26 11:13 EDT</t>
+  </si>
+  <si>
+    <t>03/15/26 14:25 EDT</t>
+  </si>
+  <si>
+    <t>6.7mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>03/16/26 11:11 EDT</t>
+  </si>
+  <si>
+    <t>03/15/26 17:23 EDT</t>
+  </si>
+  <si>
+    <t>9.3mi NW of Martinsville IN</t>
+  </si>
+  <si>
+    <t>03/16/26 14:16 EDT</t>
+  </si>
+  <si>
+    <t>12.8mi E of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/17/26 09:28 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 19:29 EDT</t>
+  </si>
+  <si>
+    <t>11.2mi NW of Martinsville IN</t>
+  </si>
+  <si>
+    <t>03/17/26 09:27 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 21:49 EDT</t>
+  </si>
+  <si>
+    <t>11.2mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>03/17/26 10:55 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 22:32 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 22:36 EDT</t>
+  </si>
+  <si>
+    <t>8.9mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/18/26 03:02 EDT</t>
+  </si>
+  <si>
+    <t>10.2mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/18/26 09:59 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 19:01 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 08:07 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 19:02 EDT</t>
+  </si>
+  <si>
+    <t>11.7mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/20/26 11:42 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 02:16 EDT</t>
+  </si>
+  <si>
+    <t>10.3mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>03/20/26 11:20 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 11:38 EDT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -119,22 +773,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -424,87 +1085,4138 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M112"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="true" style="1"/>
-    <col min="2" max="2" width="15" customWidth="true" style="1"/>
-    <col min="3" max="3" width="15" customWidth="true" style="1"/>
-    <col min="4" max="4" width="15" customWidth="true" style="1"/>
-    <col min="5" max="5" width="15" customWidth="true" style="1"/>
-    <col min="6" max="6" width="15" customWidth="true" style="1"/>
-    <col min="7" max="7" width="15" customWidth="true" style="1"/>
-    <col min="8" max="8" width="15" customWidth="true" style="1"/>
-    <col min="9" max="9" width="15" customWidth="true" style="1"/>
-    <col min="10" max="10" width="15" customWidth="true" style="1"/>
-    <col min="11" max="11" width="15" customWidth="true" style="1"/>
-    <col min="12" max="12" width="15" customWidth="true" style="1"/>
-    <col min="13" max="13" width="15" customWidth="true" style="1"/>
+    <col min="1" max="13" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3">
+        <v>31</v>
+      </c>
+      <c r="D4" s="3">
+        <v>5241548237</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="3">
+        <v>56</v>
+      </c>
+      <c r="I4" s="3">
+        <v>40</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3">
+        <v>31</v>
+      </c>
+      <c r="D5" s="3">
+        <v>5241620514</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="3">
+        <v>73</v>
+      </c>
+      <c r="I5" s="3">
+        <v>60</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" s="3"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3">
+        <v>31</v>
+      </c>
+      <c r="D6" s="3">
+        <v>5241654466</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="3">
+        <v>63</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" s="3"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="3">
+        <v>31</v>
+      </c>
+      <c r="D7" s="3">
+        <v>5250674247</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="3">
+        <v>74</v>
+      </c>
+      <c r="I7" s="3">
+        <v>60</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" s="3"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="3">
+        <v>31</v>
+      </c>
+      <c r="D8" s="3">
+        <v>5250679100</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="3">
+        <v>75</v>
+      </c>
+      <c r="I8" s="3">
+        <v>60</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="3">
+        <v>31</v>
+      </c>
+      <c r="D9" s="3">
+        <v>5250695317</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="3">
+        <v>74</v>
+      </c>
+      <c r="I9" s="3">
+        <v>60</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="3">
+        <v>31</v>
+      </c>
+      <c r="D10" s="3">
+        <v>5250958207</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="3">
+        <v>9</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3">
+        <v>5251013717</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3">
+        <v>5251030165</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="3">
+        <v>65</v>
+      </c>
+      <c r="I12" s="3">
+        <v>50</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="3">
+        <v>28</v>
+      </c>
+      <c r="D13" s="3">
+        <v>5255773092</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="3">
+        <v>41</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="3">
+        <v>31</v>
+      </c>
+      <c r="D14" s="3">
+        <v>5257499444</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="3">
+        <v>38</v>
+      </c>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="3">
+        <v>31</v>
+      </c>
+      <c r="D15" s="3">
+        <v>5257538496</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="3">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="3">
+        <v>28</v>
+      </c>
+      <c r="D16" s="3">
+        <v>5262452548</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="3">
+        <v>56</v>
+      </c>
+      <c r="I16" s="3">
+        <v>50</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="3">
+        <v>31</v>
+      </c>
+      <c r="D17" s="3">
+        <v>5268779144</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="3">
+        <v>49</v>
+      </c>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="3">
+        <v>31</v>
+      </c>
+      <c r="D18" s="3">
+        <v>5269729774</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="3">
+        <v>35</v>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="3">
+        <v>31</v>
+      </c>
+      <c r="D19" s="3">
+        <v>5269967732</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="3">
+        <v>10</v>
+      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="3">
+        <v>31</v>
+      </c>
+      <c r="D20" s="3">
+        <v>5270847223</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="3">
+        <v>21</v>
+      </c>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="3">
+        <v>31</v>
+      </c>
+      <c r="D21" s="3">
+        <v>5270855569</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="3">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="3">
+        <v>31</v>
+      </c>
+      <c r="D22" s="3">
+        <v>5270902053</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="3">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="3">
+        <v>31</v>
+      </c>
+      <c r="D23" s="3">
+        <v>5270912076</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="3">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="3">
+        <v>28</v>
+      </c>
+      <c r="D24" s="3">
+        <v>5270940183</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="3">
+        <v>30</v>
+      </c>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="3">
+        <v>28</v>
+      </c>
+      <c r="D25" s="3">
+        <v>5270954580</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="3">
+        <v>69</v>
+      </c>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="3">
+        <v>28</v>
+      </c>
+      <c r="D26" s="3">
+        <v>5270991446</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" s="3">
+        <v>69</v>
+      </c>
+      <c r="I26" s="3">
+        <v>70</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="3">
+        <v>28</v>
+      </c>
+      <c r="D27" s="3">
+        <v>5271130088</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="3">
+        <v>59</v>
+      </c>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="3">
+        <v>2</v>
+      </c>
+      <c r="D28" s="3">
+        <v>5273430243</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" s="3">
+        <v>56</v>
+      </c>
+      <c r="I28" s="3">
+        <v>50</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="3">
+        <v>31</v>
+      </c>
+      <c r="D29" s="3">
+        <v>5277684634</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" s="3">
+        <v>35</v>
+      </c>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="3">
+        <v>31</v>
+      </c>
+      <c r="D30" s="3">
+        <v>5277692552</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" s="3">
+        <v>18</v>
+      </c>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" s="3">
+        <v>28</v>
+      </c>
+      <c r="D31" s="3">
+        <v>5277782983</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" s="3">
+        <v>33</v>
+      </c>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="3">
+        <v>28</v>
+      </c>
+      <c r="D32" s="3">
+        <v>5277782987</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" s="3">
+        <v>33</v>
+      </c>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="3">
+        <v>31</v>
+      </c>
+      <c r="D33" s="3">
+        <v>5279963411</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" s="3">
+        <v>5</v>
+      </c>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="3">
+        <v>28</v>
+      </c>
+      <c r="D34" s="3">
+        <v>5280441719</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" s="3">
+        <v>81</v>
+      </c>
+      <c r="I34" s="3">
+        <v>60</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="3">
+        <v>31</v>
+      </c>
+      <c r="D35" s="3">
+        <v>5323241476</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="3">
+        <v>57</v>
+      </c>
+      <c r="I35" s="3">
+        <v>45</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="3">
+        <v>31</v>
+      </c>
+      <c r="D36" s="3">
+        <v>5323277949</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" s="3">
+        <v>68</v>
+      </c>
+      <c r="I36" s="3">
+        <v>50</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M36" s="3"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="3">
+        <v>27</v>
+      </c>
+      <c r="D37" s="3">
+        <v>5333611175</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" s="3">
+        <v>76</v>
+      </c>
+      <c r="I37" s="3">
+        <v>70</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M37" s="3"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="3">
+        <v>28</v>
+      </c>
+      <c r="D38" s="3">
+        <v>5339352352</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" s="3">
+        <v>47</v>
+      </c>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M38" s="3"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="3">
+        <v>31</v>
+      </c>
+      <c r="D39" s="3">
+        <v>5339362853</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" s="3">
+        <v>35</v>
+      </c>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="3">
+        <v>31</v>
+      </c>
+      <c r="D40" s="3">
+        <v>5339395931</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" s="3">
+        <v>65</v>
+      </c>
+      <c r="I40" s="3">
+        <v>50</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="3">
+        <v>28</v>
+      </c>
+      <c r="D41" s="3">
+        <v>5340445223</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" s="3">
+        <v>16</v>
+      </c>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="3">
+        <v>28</v>
+      </c>
+      <c r="D42" s="3">
+        <v>5340521868</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" s="3">
+        <v>6</v>
+      </c>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="3">
+        <v>28</v>
+      </c>
+      <c r="D43" s="3">
+        <v>5340592888</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" s="3">
+        <v>50</v>
+      </c>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" s="3">
+        <v>27</v>
+      </c>
+      <c r="D44" s="3">
+        <v>5340699213</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" s="3">
+        <v>25</v>
+      </c>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="3">
+        <v>27</v>
+      </c>
+      <c r="D45" s="3">
+        <v>5340699214</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" s="3">
+        <v>9</v>
+      </c>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C46" s="3">
+        <v>28</v>
+      </c>
+      <c r="D46" s="3">
+        <v>5342879118</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" s="3">
+        <v>28</v>
+      </c>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47" s="3">
+        <v>31</v>
+      </c>
+      <c r="D47" s="3">
+        <v>5343325081</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" s="3">
+        <v>14</v>
+      </c>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C48" s="3">
+        <v>31</v>
+      </c>
+      <c r="D48" s="3">
+        <v>5344913024</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" s="3">
+        <v>2</v>
+      </c>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C49" s="3">
+        <v>28</v>
+      </c>
+      <c r="D49" s="3">
+        <v>5347612221</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" s="3">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C50" s="3">
+        <v>28</v>
+      </c>
+      <c r="D50" s="3">
+        <v>5348146982</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" s="3">
+        <v>54</v>
+      </c>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="3">
+        <v>31</v>
+      </c>
+      <c r="D51" s="3">
+        <v>5348496323</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" s="3">
+        <v>11</v>
+      </c>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" s="3">
+        <v>31</v>
+      </c>
+      <c r="D52" s="3">
+        <v>5348791102</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" s="3">
+        <v>28</v>
+      </c>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C53" s="3">
+        <v>31</v>
+      </c>
+      <c r="D53" s="3">
+        <v>5352069586</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" s="3">
+        <v>41</v>
+      </c>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C54" s="3">
+        <v>31</v>
+      </c>
+      <c r="D54" s="3">
+        <v>5353358807</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" s="3">
+        <v>20</v>
+      </c>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55" s="3">
+        <v>28</v>
+      </c>
+      <c r="D55" s="3">
+        <v>5354399128</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" s="3">
+        <v>52</v>
+      </c>
+      <c r="I55" s="3">
+        <v>70</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C56" s="3">
+        <v>28</v>
+      </c>
+      <c r="D56" s="3">
+        <v>5354434178</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C57" s="3">
+        <v>26</v>
+      </c>
+      <c r="D57" s="3">
+        <v>5354715817</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" s="3">
+        <v>11</v>
+      </c>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C58" s="3">
+        <v>28</v>
+      </c>
+      <c r="D58" s="3">
+        <v>5358089136</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" s="3">
+        <v>32</v>
+      </c>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C59" s="3">
+        <v>28</v>
+      </c>
+      <c r="D59" s="3">
+        <v>5358364377</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" s="3">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60" s="3">
+        <v>31</v>
+      </c>
+      <c r="D60" s="3">
+        <v>5358970915</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" s="3">
+        <v>53</v>
+      </c>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C61" s="3">
+        <v>28</v>
+      </c>
+      <c r="D61" s="3">
+        <v>5360224794</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" s="3">
+        <v>43</v>
+      </c>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C62" s="3">
+        <v>31</v>
+      </c>
+      <c r="D62" s="3">
+        <v>5362956191</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" s="3">
+        <v>35</v>
+      </c>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C63" s="3">
+        <v>31</v>
+      </c>
+      <c r="D63" s="3">
+        <v>5362975118</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H63" s="3">
+        <v>27</v>
+      </c>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C64" s="3">
+        <v>31</v>
+      </c>
+      <c r="D64" s="3">
+        <v>5363876089</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H64" s="3">
+        <v>38</v>
+      </c>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C65" s="3">
+        <v>28</v>
+      </c>
+      <c r="D65" s="3">
+        <v>5364325334</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65" s="3">
+        <v>31</v>
+      </c>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C66" s="3">
+        <v>28</v>
+      </c>
+      <c r="D66" s="3">
+        <v>5364325337</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66" s="3">
+        <v>14</v>
+      </c>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C67" s="3">
+        <v>28</v>
+      </c>
+      <c r="D67" s="3">
+        <v>5364384519</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" s="3">
+        <v>43</v>
+      </c>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C68" s="3">
+        <v>31</v>
+      </c>
+      <c r="D68" s="3">
+        <v>5365236523</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" s="3">
+        <v>31</v>
+      </c>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C69" s="3">
+        <v>31</v>
+      </c>
+      <c r="D69" s="3">
+        <v>5369314463</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H69" s="3">
+        <v>26</v>
+      </c>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C70" s="3">
+        <v>28</v>
+      </c>
+      <c r="D70" s="3">
+        <v>5369410516</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H70" s="3">
+        <v>26</v>
+      </c>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C71" s="3">
+        <v>31</v>
+      </c>
+      <c r="D71" s="3">
+        <v>5370806842</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H71" s="3">
+        <v>29</v>
+      </c>
+      <c r="I71" s="3"/>
+      <c r="J71" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" s="3">
+        <v>31</v>
+      </c>
+      <c r="D72" s="3">
+        <v>5373812527</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H72" s="3">
+        <v>73</v>
+      </c>
+      <c r="I72" s="3">
+        <v>60</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C73" s="3">
+        <v>28</v>
+      </c>
+      <c r="D73" s="3">
+        <v>5375031791</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H73" s="3">
+        <v>59</v>
+      </c>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C74" s="3">
+        <v>28</v>
+      </c>
+      <c r="D74" s="3">
+        <v>5375244354</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H74" s="3">
+        <v>5</v>
+      </c>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C75" s="3">
+        <v>28</v>
+      </c>
+      <c r="D75" s="3">
+        <v>5379169291</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" s="3">
+        <v>49</v>
+      </c>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C76" s="3">
+        <v>31</v>
+      </c>
+      <c r="D76" s="3">
+        <v>5379510721</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H76" s="3">
+        <v>33</v>
+      </c>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C77" s="3">
+        <v>26</v>
+      </c>
+      <c r="D77" s="3">
+        <v>5380670088</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" s="3">
+        <v>17</v>
+      </c>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C78" s="3">
+        <v>28</v>
+      </c>
+      <c r="D78" s="3">
+        <v>5383332104</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78" s="3">
+        <v>31</v>
+      </c>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L78" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M78" s="3"/>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C79" s="3">
+        <v>31</v>
+      </c>
+      <c r="D79" s="3">
+        <v>5384307655</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79" s="3">
+        <v>10</v>
+      </c>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="M79" s="3"/>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C80" s="3">
+        <v>31</v>
+      </c>
+      <c r="D80" s="3">
+        <v>5384491132</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" s="3">
+        <v>10</v>
+      </c>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L80" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M80" s="3"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C81" s="3">
+        <v>26</v>
+      </c>
+      <c r="D81" s="3">
+        <v>5386032759</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" s="3">
+        <v>6</v>
+      </c>
+      <c r="I81" s="3"/>
+      <c r="J81" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C82" s="3">
+        <v>31</v>
+      </c>
+      <c r="D82" s="3">
+        <v>5388257868</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82" s="3">
+        <v>33</v>
+      </c>
+      <c r="I82" s="3">
+        <v>30</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L82" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C83" s="3">
+        <v>28</v>
+      </c>
+      <c r="D83" s="3">
+        <v>5388881329</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" s="3">
+        <v>10</v>
+      </c>
+      <c r="I83" s="3"/>
+      <c r="J83" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C84" s="3">
+        <v>31</v>
+      </c>
+      <c r="D84" s="3">
+        <v>5390211280</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H84" s="3">
+        <v>48</v>
+      </c>
+      <c r="I84" s="3"/>
+      <c r="J84" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L84" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C85" s="3">
+        <v>31</v>
+      </c>
+      <c r="D85" s="3">
+        <v>5393727241</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85" s="3">
+        <v>2</v>
+      </c>
+      <c r="I85" s="3"/>
+      <c r="J85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L85" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C86" s="3">
+        <v>31</v>
+      </c>
+      <c r="D86" s="3">
+        <v>5393995016</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H86" s="3"/>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L86" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C87" s="3">
+        <v>31</v>
+      </c>
+      <c r="D87" s="3">
+        <v>5394289312</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H87" s="3">
+        <v>18</v>
+      </c>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L87" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C88" s="3">
+        <v>28</v>
+      </c>
+      <c r="D88" s="3">
+        <v>5394452073</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H88" s="3">
+        <v>6</v>
+      </c>
+      <c r="I88" s="3"/>
+      <c r="J88" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L88" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C89" s="3">
+        <v>28</v>
+      </c>
+      <c r="D89" s="3">
+        <v>5396813731</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H89" s="3">
+        <v>23</v>
+      </c>
+      <c r="I89" s="3"/>
+      <c r="J89" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C90" s="3">
+        <v>31</v>
+      </c>
+      <c r="D90" s="3">
+        <v>5396984370</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" s="3">
+        <v>10</v>
+      </c>
+      <c r="I90" s="3"/>
+      <c r="J90" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="L90" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C91" s="3">
+        <v>31</v>
+      </c>
+      <c r="D91" s="3">
+        <v>5397263222</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H91" s="3">
+        <v>31</v>
+      </c>
+      <c r="I91" s="3"/>
+      <c r="J91" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C92" s="3">
+        <v>31</v>
+      </c>
+      <c r="D92" s="3">
+        <v>5397276418</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H92" s="3">
+        <v>58</v>
+      </c>
+      <c r="I92" s="3">
+        <v>50</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L92" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C93" s="3">
+        <v>31</v>
+      </c>
+      <c r="D93" s="3">
+        <v>5400999961</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H93" s="3">
+        <v>42</v>
+      </c>
+      <c r="I93" s="3"/>
+      <c r="J93" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L93" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C94" s="3">
+        <v>28</v>
+      </c>
+      <c r="D94" s="3">
+        <v>5402803646</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="H94" s="3">
+        <v>20</v>
+      </c>
+      <c r="I94" s="3"/>
+      <c r="J94" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" s="3">
+        <v>31</v>
+      </c>
+      <c r="D95" s="3">
+        <v>5404865035</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H95" s="3">
+        <v>74</v>
+      </c>
+      <c r="I95" s="3"/>
+      <c r="J95" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K95" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L95" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" s="3">
+        <v>31</v>
+      </c>
+      <c r="D96" s="3">
+        <v>5404865042</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H96" s="3">
+        <v>75</v>
+      </c>
+      <c r="I96" s="3"/>
+      <c r="J96" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" s="3">
+        <v>31</v>
+      </c>
+      <c r="D97" s="3">
+        <v>5406119683</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H97" s="3">
+        <v>48</v>
+      </c>
+      <c r="I97" s="3">
+        <v>40</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L97" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" s="3">
+        <v>31</v>
+      </c>
+      <c r="D98" s="3">
+        <v>5407857090</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H98" s="3">
+        <v>57</v>
+      </c>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L98" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" s="3">
+        <v>31</v>
+      </c>
+      <c r="D99" s="3">
+        <v>5408580900</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H99" s="3">
+        <v>52</v>
+      </c>
+      <c r="I99" s="3"/>
+      <c r="J99" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="L99" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C100" s="3">
+        <v>28</v>
+      </c>
+      <c r="D100" s="3">
+        <v>5409118941</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H100" s="3">
+        <v>48</v>
+      </c>
+      <c r="I100" s="3"/>
+      <c r="J100" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C101" s="3">
+        <v>28</v>
+      </c>
+      <c r="D101" s="3">
+        <v>5409172955</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H101" s="3">
+        <v>63</v>
+      </c>
+      <c r="I101" s="3"/>
+      <c r="J101" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" s="3">
+        <v>31</v>
+      </c>
+      <c r="D102" s="3">
+        <v>5410176732</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H102" s="3">
+        <v>47</v>
+      </c>
+      <c r="I102" s="3"/>
+      <c r="J102" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="M102" s="3"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C103" s="3">
+        <v>31</v>
+      </c>
+      <c r="D103" s="3">
+        <v>5414460487</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H103" s="3">
+        <v>58</v>
+      </c>
+      <c r="I103" s="3">
+        <v>70</v>
+      </c>
+      <c r="J103" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K103" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="L103" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="M103" s="3"/>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" s="3">
+        <v>31</v>
+      </c>
+      <c r="D104" s="3">
+        <v>5416498836</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H104" s="3">
+        <v>64</v>
+      </c>
+      <c r="I104" s="3">
+        <v>50</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K104" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="L104" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="M104" s="3"/>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C105" s="3">
+        <v>27</v>
+      </c>
+      <c r="D105" s="3">
+        <v>5416886090</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H105" s="3">
+        <v>20</v>
+      </c>
+      <c r="I105" s="3"/>
+      <c r="J105" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K105" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L105" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="M105" s="3"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C106" s="3">
+        <v>27</v>
+      </c>
+      <c r="D106" s="3">
+        <v>5416967709</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H106" s="3">
+        <v>20</v>
+      </c>
+      <c r="I106" s="3"/>
+      <c r="J106" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K106" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L106" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="M106" s="3"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C107" s="3">
+        <v>28</v>
+      </c>
+      <c r="D107" s="3">
+        <v>5416974389</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H107" s="3">
+        <v>25</v>
+      </c>
+      <c r="I107" s="3"/>
+      <c r="J107" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K107" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L107" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="M107" s="3"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C108" s="3">
+        <v>31</v>
+      </c>
+      <c r="D108" s="3">
+        <v>5423554659</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H108" s="3">
+        <v>43</v>
+      </c>
+      <c r="I108" s="3"/>
+      <c r="J108" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K108" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="L108" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="M108" s="3"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C109" s="3">
+        <v>31</v>
+      </c>
+      <c r="D109" s="3">
+        <v>5428808883</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H109" s="3">
+        <v>75</v>
+      </c>
+      <c r="I109" s="3">
+        <v>60</v>
+      </c>
+      <c r="J109" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K109" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="L109" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="M109" s="3"/>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C110" s="3">
+        <v>31</v>
+      </c>
+      <c r="D110" s="3">
+        <v>5428814384</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H110" s="3">
+        <v>71</v>
+      </c>
+      <c r="I110" s="3">
+        <v>60</v>
+      </c>
+      <c r="J110" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K110" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L110" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="M110" s="3"/>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C111" s="3">
+        <v>28</v>
+      </c>
+      <c r="D111" s="3">
+        <v>5436082182</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H111" s="3">
+        <v>69</v>
+      </c>
+      <c r="I111" s="3"/>
+      <c r="J111" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K111" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L111" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="M111" s="3"/>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C112" s="3">
+        <v>28</v>
+      </c>
+      <c r="D112" s="3">
+        <v>5437793902</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H112" s="3">
+        <v>34</v>
+      </c>
+      <c r="I112" s="3"/>
+      <c r="J112" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K112" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L112" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="M112" s="3"/>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Curtis Garage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6B6E2D0-D6CB-4EE7-89A5-69967D97E693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B772A497-AB05-4308-BBA5-3A70319364DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4087" uniqueCount="1308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4439" uniqueCount="1408">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -3778,9 +3778,15 @@
     <t>04/03/26 03:48 EDT</t>
   </si>
   <si>
+    <t>04/06/26 10:29 EDT</t>
+  </si>
+  <si>
     <t>04/03/26 06:34 EDT</t>
   </si>
   <si>
+    <t>04/06/26 10:30 EDT</t>
+  </si>
+  <si>
     <t>04/03/26 06:40 EDT</t>
   </si>
   <si>
@@ -3790,12 +3796,18 @@
     <t>04/03/26 08:26 EDT</t>
   </si>
   <si>
+    <t>04/06/26 10:34 EDT</t>
+  </si>
+  <si>
     <t>04/03/26 10:10 EDT</t>
   </si>
   <si>
     <t>04/03/26 14:26 EDT</t>
   </si>
   <si>
+    <t>04/06/26 10:31 EDT</t>
+  </si>
+  <si>
     <t>04/03/26 14:50 EDT</t>
   </si>
   <si>
@@ -3835,6 +3847,9 @@
     <t>2.6mi S of Plainfield IN</t>
   </si>
   <si>
+    <t>04/06/26 10:35 EDT</t>
+  </si>
+  <si>
     <t>04/03/26 17:59 EDT</t>
   </si>
   <si>
@@ -3850,6 +3865,9 @@
     <t>6.1mi S of Mooresville IN</t>
   </si>
   <si>
+    <t>04/06/26 10:36 EDT</t>
+  </si>
+  <si>
     <t>04/03/26 21:40 EDT</t>
   </si>
   <si>
@@ -3868,6 +3886,9 @@
     <t>04/04/26 18:19 EDT</t>
   </si>
   <si>
+    <t>04/06/26 10:32 EDT</t>
+  </si>
+  <si>
     <t>04/04/26 18:30 EDT</t>
   </si>
   <si>
@@ -3886,6 +3907,9 @@
     <t>04/04/26 22:55 EDT</t>
   </si>
   <si>
+    <t>04/06/26 10:37 EDT</t>
+  </si>
+  <si>
     <t>04/04/26 22:57 EDT</t>
   </si>
   <si>
@@ -3944,6 +3968,282 @@
   </si>
   <si>
     <t>9.3mi S of Danville IN</t>
+  </si>
+  <si>
+    <t>04/06/26 13:02 EDT</t>
+  </si>
+  <si>
+    <t>10.6mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>04/06/26 18:56 EDT</t>
+  </si>
+  <si>
+    <t>04/06/26 14:09 EDT</t>
+  </si>
+  <si>
+    <t>7.9mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>04/07/26 09:19 EDT</t>
+  </si>
+  <si>
+    <t>04/06/26 14:18 EDT</t>
+  </si>
+  <si>
+    <t>04/06/26 15:29 EDT</t>
+  </si>
+  <si>
+    <t>04/06/26 15:38 EDT</t>
+  </si>
+  <si>
+    <t>10.7mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>04/07/26 09:20 EDT</t>
+  </si>
+  <si>
+    <t>10.9mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>04/06/26 22:49 EDT</t>
+  </si>
+  <si>
+    <t>04/06/26 22:55 EDT</t>
+  </si>
+  <si>
+    <t>04/07/26 00:31 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 10:41 EDT</t>
+  </si>
+  <si>
+    <t>04/07/26 14:47 EDT</t>
+  </si>
+  <si>
+    <t>04/07/26 16:32 EDT</t>
+  </si>
+  <si>
+    <t>12.7mi E of Greencastle IN</t>
+  </si>
+  <si>
+    <t>04/07/26 16:51 EDT</t>
+  </si>
+  <si>
+    <t>04/07/26 19:16 EDT</t>
+  </si>
+  <si>
+    <t>04/07/26 21:58 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 01:55 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 02:08 EDT</t>
+  </si>
+  <si>
+    <t>2.6mi SW of Indianapolis IN</t>
+  </si>
+  <si>
+    <t>04/08/26 02:10 EDT</t>
+  </si>
+  <si>
+    <t>3.1mi SE of Speedway IN</t>
+  </si>
+  <si>
+    <t>04/08/26 02:42 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 05:31 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 05:56 EDT</t>
+  </si>
+  <si>
+    <t>4.3mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>04/09/26 10:38 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 07:04 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 07:21 EDT</t>
+  </si>
+  <si>
+    <t>12.6mi W of Terre Haute IN</t>
+  </si>
+  <si>
+    <t>04/09/26 10:37 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 08:07 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 10:17 EDT</t>
+  </si>
+  <si>
+    <t>5.4mi SW of Brazil IN</t>
+  </si>
+  <si>
+    <t>04/08/26 11:46 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 11:47 EDT</t>
+  </si>
+  <si>
+    <t>04/08/26 15:02 EDT</t>
+  </si>
+  <si>
+    <t>04/09/26 07:50 EDT</t>
+  </si>
+  <si>
+    <t>04/09/26 08:09 EDT</t>
+  </si>
+  <si>
+    <t>04/09/26 12:26 EDT</t>
+  </si>
+  <si>
+    <t>8.2mi NW of Ellettsville IN</t>
+  </si>
+  <si>
+    <t>04/10/26 07:18 EDT</t>
+  </si>
+  <si>
+    <t>04/10/26 07:21 EDT</t>
+  </si>
+  <si>
+    <t>04/10/26 11:38 EDT</t>
+  </si>
+  <si>
+    <t>04/10/26 12:30 EDT</t>
+  </si>
+  <si>
+    <t>8.4mi S of Danville IN</t>
+  </si>
+  <si>
+    <t>04/10/26 12:32 EDT</t>
+  </si>
+  <si>
+    <t>9.4mi S of Danville IN</t>
+  </si>
+  <si>
+    <t>04/10/26 12:35 EDT</t>
+  </si>
+  <si>
+    <t>9.1mi S of Danville IN</t>
+  </si>
+  <si>
+    <t>04/10/26 13:23 EDT</t>
+  </si>
+  <si>
+    <t>04/10/26 13:58 EDT</t>
+  </si>
+  <si>
+    <t>4mi N of Martinsville IN</t>
+  </si>
+  <si>
+    <t>04/10/26 14:16 EDT</t>
+  </si>
+  <si>
+    <t>04/10/26 15:45 EDT</t>
+  </si>
+  <si>
+    <t>12.9mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>04/10/26 15:52 EDT</t>
+  </si>
+  <si>
+    <t>04/10/26 18:06 EDT</t>
+  </si>
+  <si>
+    <t>04/10/26 18:08 EDT</t>
+  </si>
+  <si>
+    <t>04/10/26 18:12 EDT</t>
+  </si>
+  <si>
+    <t>04/10/26 18:14 EDT</t>
+  </si>
+  <si>
+    <t>4.7mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>04/10/26 18:17 EDT</t>
+  </si>
+  <si>
+    <t>2mi NW of Mooresville IN</t>
+  </si>
+  <si>
+    <t>04/10/26 20:40 EDT</t>
+  </si>
+  <si>
+    <t>04/11/26 06:31 EDT</t>
+  </si>
+  <si>
+    <t>04/11/26 06:40 EDT</t>
+  </si>
+  <si>
+    <t>04/11/26 08:19 EDT</t>
+  </si>
+  <si>
+    <t>04/11/26 12:38 EDT</t>
+  </si>
+  <si>
+    <t>04/11/26 12:54 EDT</t>
+  </si>
+  <si>
+    <t>04/11/26 13:22 EDT</t>
+  </si>
+  <si>
+    <t>04/11/26 13:38 EDT</t>
+  </si>
+  <si>
+    <t>04/11/26 13:44 EDT</t>
+  </si>
+  <si>
+    <t>04/12/26 12:26 EDT</t>
+  </si>
+  <si>
+    <t>04/12/26 12:30 EDT</t>
+  </si>
+  <si>
+    <t>04/12/26 12:48 EDT</t>
+  </si>
+  <si>
+    <t>04/12/26 16:12 EDT</t>
+  </si>
+  <si>
+    <t>04/12/26 18:09 EDT</t>
+  </si>
+  <si>
+    <t>04/12/26 18:12 EDT</t>
+  </si>
+  <si>
+    <t>04/12/26 18:15 EDT</t>
+  </si>
+  <si>
+    <t>04/12/26 19:54 EDT</t>
+  </si>
+  <si>
+    <t>04/12/26 19:58 EDT</t>
+  </si>
+  <si>
+    <t>04/12/26 20:00 EDT</t>
+  </si>
+  <si>
+    <t>04/12/26 21:33 EDT</t>
+  </si>
+  <si>
+    <t>6.4mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>04/13/26 07:46 EDT</t>
+  </si>
+  <si>
+    <t>04/13/26 07:47 EDT</t>
   </si>
 </sst>
 </file>
@@ -4305,7 +4605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M813"/>
+  <dimension ref="A1:M884"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="13" width="15" customWidth="1"/>
@@ -28438,21 +28738,27 @@
       <c r="F765" s="3" t="s">
         <v>998</v>
       </c>
-      <c r="G765" s="3"/>
+      <c r="G765" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="H765" s="3">
         <v>61</v>
       </c>
       <c r="I765" s="3"/>
       <c r="J765" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K765" s="3"/>
-      <c r="L765" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K765" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L765" s="3" t="s">
+        <v>1252</v>
+      </c>
       <c r="M765" s="3"/>
     </row>
     <row r="766" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A766" s="3" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B766" s="3"/>
       <c r="C766" s="3">
@@ -28467,19 +28773,25 @@
       <c r="F766" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G766" s="3"/>
+      <c r="G766" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="H766" s="3"/>
       <c r="I766" s="3"/>
       <c r="J766" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K766" s="3"/>
-      <c r="L766" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K766" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L766" s="3" t="s">
+        <v>1254</v>
+      </c>
       <c r="M766" s="3"/>
     </row>
     <row r="767" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A767" s="3" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="B767" s="3"/>
       <c r="C767" s="3">
@@ -28492,25 +28804,33 @@
         <v>114</v>
       </c>
       <c r="F767" s="3" t="s">
-        <v>1254</v>
-      </c>
-      <c r="G767" s="3"/>
+        <v>1256</v>
+      </c>
+      <c r="G767" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="H767" s="3">
         <v>63</v>
       </c>
       <c r="I767" s="3"/>
       <c r="J767" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K767" s="3"/>
-      <c r="L767" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K767" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L767" s="3" t="s">
+        <v>1254</v>
+      </c>
       <c r="M767" s="3"/>
     </row>
     <row r="768" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A768" s="3" t="s">
-        <v>1255</v>
-      </c>
-      <c r="B768" s="3"/>
+        <v>1257</v>
+      </c>
+      <c r="B768" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="C768" s="3">
         <v>28</v>
       </c>
@@ -28523,21 +28843,27 @@
       <c r="F768" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="G768" s="3"/>
+      <c r="G768" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="H768" s="3">
         <v>70</v>
       </c>
       <c r="I768" s="3"/>
       <c r="J768" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K768" s="3"/>
-      <c r="L768" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K768" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L768" s="3" t="s">
+        <v>1258</v>
+      </c>
       <c r="M768" s="3"/>
     </row>
     <row r="769" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A769" s="3" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="B769" s="3"/>
       <c r="C769" s="3">
@@ -28566,7 +28892,7 @@
     </row>
     <row r="770" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A770" s="3" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="B770" s="3"/>
       <c r="C770" s="3">
@@ -28581,21 +28907,27 @@
       <c r="F770" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="G770" s="3"/>
+      <c r="G770" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="H770" s="3">
         <v>64</v>
       </c>
       <c r="I770" s="3"/>
       <c r="J770" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K770" s="3"/>
-      <c r="L770" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K770" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L770" s="3" t="s">
+        <v>1261</v>
+      </c>
       <c r="M770" s="3"/>
     </row>
     <row r="771" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A771" s="3" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="B771" s="3"/>
       <c r="C771" s="3">
@@ -28624,7 +28956,7 @@
     </row>
     <row r="772" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A772" s="3" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="B772" s="3"/>
       <c r="C772" s="3">
@@ -28653,7 +28985,7 @@
     </row>
     <row r="773" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A773" s="3" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="B773" s="3"/>
       <c r="C773" s="3">
@@ -28682,7 +29014,7 @@
     </row>
     <row r="774" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A774" s="3" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="B774" s="3"/>
       <c r="C774" s="3">
@@ -28695,7 +29027,7 @@
         <v>39</v>
       </c>
       <c r="F774" s="3" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="G774" s="3"/>
       <c r="H774" s="3">
@@ -28711,7 +29043,7 @@
     </row>
     <row r="775" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A775" s="3" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="B775" s="3"/>
       <c r="C775" s="3">
@@ -28724,7 +29056,7 @@
         <v>39</v>
       </c>
       <c r="F775" s="3" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="G775" s="3"/>
       <c r="H775" s="3">
@@ -28740,7 +29072,7 @@
     </row>
     <row r="776" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A776" s="3" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
       <c r="B776" s="3"/>
       <c r="C776" s="3">
@@ -28771,7 +29103,7 @@
     </row>
     <row r="777" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A777" s="3" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="B777" s="3"/>
       <c r="C777" s="3">
@@ -28784,7 +29116,7 @@
         <v>32</v>
       </c>
       <c r="F777" s="3" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="G777" s="3"/>
       <c r="H777" s="3">
@@ -28802,7 +29134,7 @@
     </row>
     <row r="778" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A778" s="3" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="B778" s="3"/>
       <c r="C778" s="3">
@@ -28815,21 +29147,27 @@
         <v>114</v>
       </c>
       <c r="F778" s="3" t="s">
-        <v>1267</v>
-      </c>
-      <c r="G778" s="3"/>
+        <v>1271</v>
+      </c>
+      <c r="G778" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="H778" s="3"/>
       <c r="I778" s="3"/>
       <c r="J778" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K778" s="3"/>
-      <c r="L778" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K778" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L778" s="3" t="s">
+        <v>1261</v>
+      </c>
       <c r="M778" s="3"/>
     </row>
     <row r="779" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A779" s="3" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="B779" s="3"/>
       <c r="C779" s="3">
@@ -28858,9 +29196,11 @@
     </row>
     <row r="780" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A780" s="3" t="s">
-        <v>1269</v>
-      </c>
-      <c r="B780" s="3"/>
+        <v>1273</v>
+      </c>
+      <c r="B780" s="3" t="s">
+        <v>167</v>
+      </c>
       <c r="C780" s="3">
         <v>31</v>
       </c>
@@ -28871,23 +29211,29 @@
         <v>39</v>
       </c>
       <c r="F780" s="3" t="s">
-        <v>1270</v>
-      </c>
-      <c r="G780" s="3"/>
+        <v>1274</v>
+      </c>
+      <c r="G780" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="H780" s="3">
         <v>16</v>
       </c>
       <c r="I780" s="3"/>
       <c r="J780" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K780" s="3"/>
-      <c r="L780" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K780" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L780" s="3" t="s">
+        <v>1275</v>
+      </c>
       <c r="M780" s="3"/>
     </row>
     <row r="781" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A781" s="3" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="B781" s="3"/>
       <c r="C781" s="3">
@@ -28916,7 +29262,7 @@
     </row>
     <row r="782" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A782" s="3" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="B782" s="3"/>
       <c r="C782" s="3">
@@ -28945,7 +29291,7 @@
     </row>
     <row r="783" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A783" s="3" t="s">
-        <v>1273</v>
+        <v>1278</v>
       </c>
       <c r="B783" s="3"/>
       <c r="C783" s="3">
@@ -28974,9 +29320,11 @@
     </row>
     <row r="784" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A784" s="3" t="s">
-        <v>1274</v>
-      </c>
-      <c r="B784" s="3"/>
+        <v>1279</v>
+      </c>
+      <c r="B784" s="3" t="s">
+        <v>167</v>
+      </c>
       <c r="C784" s="3">
         <v>31</v>
       </c>
@@ -28987,9 +29335,11 @@
         <v>32</v>
       </c>
       <c r="F784" s="3" t="s">
-        <v>1275</v>
-      </c>
-      <c r="G784" s="3"/>
+        <v>1280</v>
+      </c>
+      <c r="G784" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="H784" s="3">
         <v>60</v>
       </c>
@@ -28997,15 +29347,19 @@
         <v>50</v>
       </c>
       <c r="J784" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K784" s="3"/>
-      <c r="L784" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K784" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L784" s="3" t="s">
+        <v>1281</v>
+      </c>
       <c r="M784" s="3"/>
     </row>
     <row r="785" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A785" s="3" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B785" s="3"/>
       <c r="C785" s="3">
@@ -29032,7 +29386,7 @@
     </row>
     <row r="786" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A786" s="3" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="B786" s="3"/>
       <c r="C786" s="3">
@@ -29045,7 +29399,7 @@
         <v>32</v>
       </c>
       <c r="F786" s="3" t="s">
-        <v>1277</v>
+        <v>1283</v>
       </c>
       <c r="G786" s="3"/>
       <c r="H786" s="3">
@@ -29063,7 +29417,7 @@
     </row>
     <row r="787" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A787" s="3" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="B787" s="3"/>
       <c r="C787" s="3">
@@ -29092,7 +29446,7 @@
     </row>
     <row r="788" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A788" s="3" t="s">
-        <v>1279</v>
+        <v>1285</v>
       </c>
       <c r="B788" s="3"/>
       <c r="C788" s="3">
@@ -29121,7 +29475,7 @@
     </row>
     <row r="789" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A789" s="3" t="s">
-        <v>1280</v>
+        <v>1286</v>
       </c>
       <c r="B789" s="3"/>
       <c r="C789" s="3">
@@ -29148,7 +29502,7 @@
     </row>
     <row r="790" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A790" s="3" t="s">
-        <v>1281</v>
+        <v>1287</v>
       </c>
       <c r="B790" s="3"/>
       <c r="C790" s="3">
@@ -29163,21 +29517,27 @@
       <c r="F790" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="G790" s="3"/>
+      <c r="G790" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="H790" s="3">
         <v>28</v>
       </c>
       <c r="I790" s="3"/>
       <c r="J790" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K790" s="3"/>
-      <c r="L790" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K790" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L790" s="3" t="s">
+        <v>1288</v>
+      </c>
       <c r="M790" s="3"/>
     </row>
     <row r="791" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A791" s="3" t="s">
-        <v>1282</v>
+        <v>1289</v>
       </c>
       <c r="B791" s="3"/>
       <c r="C791" s="3">
@@ -29206,7 +29566,7 @@
     </row>
     <row r="792" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A792" s="3" t="s">
-        <v>1283</v>
+        <v>1290</v>
       </c>
       <c r="B792" s="3"/>
       <c r="C792" s="3">
@@ -29235,7 +29595,7 @@
     </row>
     <row r="793" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A793" s="3" t="s">
-        <v>1284</v>
+        <v>1291</v>
       </c>
       <c r="B793" s="3"/>
       <c r="C793" s="3">
@@ -29248,7 +29608,7 @@
         <v>32</v>
       </c>
       <c r="F793" s="3" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="G793" s="3"/>
       <c r="H793" s="3">
@@ -29266,7 +29626,7 @@
     </row>
     <row r="794" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A794" s="3" t="s">
-        <v>1285</v>
+        <v>1292</v>
       </c>
       <c r="B794" s="3"/>
       <c r="C794" s="3">
@@ -29281,21 +29641,27 @@
       <c r="F794" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="G794" s="3"/>
+      <c r="G794" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="H794" s="3">
         <v>11</v>
       </c>
       <c r="I794" s="3"/>
       <c r="J794" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K794" s="3"/>
-      <c r="L794" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K794" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L794" s="3" t="s">
+        <v>1288</v>
+      </c>
       <c r="M794" s="3"/>
     </row>
     <row r="795" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A795" s="3" t="s">
-        <v>1286</v>
+        <v>1293</v>
       </c>
       <c r="B795" s="3"/>
       <c r="C795" s="3">
@@ -29324,9 +29690,11 @@
     </row>
     <row r="796" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A796" s="3" t="s">
-        <v>1287</v>
-      </c>
-      <c r="B796" s="3"/>
+        <v>1294</v>
+      </c>
+      <c r="B796" s="3" t="s">
+        <v>167</v>
+      </c>
       <c r="C796" s="3">
         <v>31</v>
       </c>
@@ -29339,21 +29707,27 @@
       <c r="F796" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="G796" s="3"/>
+      <c r="G796" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="H796" s="3">
         <v>33</v>
       </c>
       <c r="I796" s="3"/>
       <c r="J796" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K796" s="3"/>
-      <c r="L796" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K796" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L796" s="3" t="s">
+        <v>1295</v>
+      </c>
       <c r="M796" s="3"/>
     </row>
     <row r="797" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A797" s="3" t="s">
-        <v>1287</v>
+        <v>1294</v>
       </c>
       <c r="B797" s="3"/>
       <c r="C797" s="3">
@@ -29368,21 +29742,27 @@
       <c r="F797" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="G797" s="3"/>
+      <c r="G797" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="H797" s="3">
         <v>19</v>
       </c>
       <c r="I797" s="3"/>
       <c r="J797" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K797" s="3"/>
-      <c r="L797" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K797" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L797" s="3" t="s">
+        <v>1288</v>
+      </c>
       <c r="M797" s="3"/>
     </row>
     <row r="798" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A798" s="3" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="B798" s="3"/>
       <c r="C798" s="3">
@@ -29395,7 +29775,7 @@
         <v>32</v>
       </c>
       <c r="F798" s="3" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
       <c r="G798" s="3"/>
       <c r="H798" s="3">
@@ -29413,7 +29793,7 @@
     </row>
     <row r="799" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A799" s="3" t="s">
-        <v>1290</v>
+        <v>1298</v>
       </c>
       <c r="B799" s="3"/>
       <c r="C799" s="3">
@@ -29426,7 +29806,7 @@
         <v>32</v>
       </c>
       <c r="F799" s="3" t="s">
-        <v>1291</v>
+        <v>1299</v>
       </c>
       <c r="G799" s="3"/>
       <c r="H799" s="3">
@@ -29444,7 +29824,7 @@
     </row>
     <row r="800" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A800" s="3" t="s">
-        <v>1292</v>
+        <v>1300</v>
       </c>
       <c r="B800" s="3"/>
       <c r="C800" s="3">
@@ -29457,7 +29837,7 @@
         <v>32</v>
       </c>
       <c r="F800" s="3" t="s">
-        <v>1293</v>
+        <v>1301</v>
       </c>
       <c r="G800" s="3"/>
       <c r="H800" s="3">
@@ -29475,7 +29855,7 @@
     </row>
     <row r="801" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A801" s="3" t="s">
-        <v>1294</v>
+        <v>1302</v>
       </c>
       <c r="B801" s="3"/>
       <c r="C801" s="3">
@@ -29504,7 +29884,7 @@
     </row>
     <row r="802" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A802" s="3" t="s">
-        <v>1295</v>
+        <v>1303</v>
       </c>
       <c r="B802" s="3"/>
       <c r="C802" s="3">
@@ -29517,7 +29897,7 @@
         <v>32</v>
       </c>
       <c r="F802" s="3" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="G802" s="3"/>
       <c r="H802" s="3">
@@ -29535,7 +29915,7 @@
     </row>
     <row r="803" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A803" s="3" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="B803" s="3"/>
       <c r="C803" s="3">
@@ -29566,7 +29946,7 @@
     </row>
     <row r="804" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A804" s="3" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="B804" s="3"/>
       <c r="C804" s="3">
@@ -29595,7 +29975,7 @@
     </row>
     <row r="805" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A805" s="3" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="B805" s="3"/>
       <c r="C805" s="3">
@@ -29608,7 +29988,7 @@
         <v>32</v>
       </c>
       <c r="F805" s="3" t="s">
-        <v>1277</v>
+        <v>1283</v>
       </c>
       <c r="G805" s="3"/>
       <c r="H805" s="3">
@@ -29626,7 +30006,7 @@
     </row>
     <row r="806" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A806" s="3" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
       <c r="B806" s="3"/>
       <c r="C806" s="3">
@@ -29655,7 +30035,7 @@
     </row>
     <row r="807" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A807" s="3" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
       <c r="B807" s="3"/>
       <c r="C807" s="3">
@@ -29668,7 +30048,7 @@
         <v>16</v>
       </c>
       <c r="F807" s="3" t="s">
-        <v>1301</v>
+        <v>1309</v>
       </c>
       <c r="G807" s="3"/>
       <c r="H807" s="3">
@@ -29684,7 +30064,7 @@
     </row>
     <row r="808" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A808" s="3" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
       <c r="B808" s="3"/>
       <c r="C808" s="3">
@@ -29713,7 +30093,7 @@
     </row>
     <row r="809" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A809" s="3" t="s">
-        <v>1303</v>
+        <v>1311</v>
       </c>
       <c r="B809" s="3"/>
       <c r="C809" s="3">
@@ -29742,7 +30122,7 @@
     </row>
     <row r="810" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A810" s="3" t="s">
-        <v>1304</v>
+        <v>1312</v>
       </c>
       <c r="B810" s="3"/>
       <c r="C810" s="3">
@@ -29771,7 +30151,7 @@
     </row>
     <row r="811" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A811" s="3" t="s">
-        <v>1304</v>
+        <v>1312</v>
       </c>
       <c r="B811" s="3"/>
       <c r="C811" s="3">
@@ -29800,7 +30180,7 @@
     </row>
     <row r="812" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A812" s="3" t="s">
-        <v>1305</v>
+        <v>1313</v>
       </c>
       <c r="B812" s="3"/>
       <c r="C812" s="3">
@@ -29829,7 +30209,7 @@
     </row>
     <row r="813" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A813" s="3" t="s">
-        <v>1306</v>
+        <v>1314</v>
       </c>
       <c r="B813" s="3"/>
       <c r="C813" s="3">
@@ -29842,7 +30222,7 @@
         <v>32</v>
       </c>
       <c r="F813" s="3" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="G813" s="3"/>
       <c r="H813" s="3">
@@ -29857,6 +30237,2175 @@
       <c r="K813" s="3"/>
       <c r="L813" s="3"/>
       <c r="M813" s="3"/>
+    </row>
+    <row r="814" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A814" s="3" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B814" s="3"/>
+      <c r="C814" s="3">
+        <v>31</v>
+      </c>
+      <c r="D814" s="3">
+        <v>5530856377</v>
+      </c>
+      <c r="E814" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="F814" s="3" t="s">
+        <v>1317</v>
+      </c>
+      <c r="G814" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H814" s="3"/>
+      <c r="I814" s="3"/>
+      <c r="J814" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K814" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L814" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="M814" s="3"/>
+    </row>
+    <row r="815" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A815" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B815" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C815" s="3">
+        <v>31</v>
+      </c>
+      <c r="D815" s="3">
+        <v>5531376442</v>
+      </c>
+      <c r="E815" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F815" s="3" t="s">
+        <v>1320</v>
+      </c>
+      <c r="G815" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H815" s="3">
+        <v>72</v>
+      </c>
+      <c r="I815" s="3"/>
+      <c r="J815" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K815" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L815" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="M815" s="3"/>
+    </row>
+    <row r="816" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A816" s="3" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B816" s="3"/>
+      <c r="C816" s="3">
+        <v>31</v>
+      </c>
+      <c r="D816" s="3">
+        <v>5531447257</v>
+      </c>
+      <c r="E816" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F816" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="G816" s="3"/>
+      <c r="H816" s="3">
+        <v>76</v>
+      </c>
+      <c r="I816" s="3">
+        <v>70</v>
+      </c>
+      <c r="J816" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K816" s="3"/>
+      <c r="L816" s="3"/>
+      <c r="M816" s="3"/>
+    </row>
+    <row r="817" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A817" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B817" s="3"/>
+      <c r="C817" s="3">
+        <v>31</v>
+      </c>
+      <c r="D817" s="3">
+        <v>5531999618</v>
+      </c>
+      <c r="E817" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F817" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G817" s="3"/>
+      <c r="H817" s="3">
+        <v>54</v>
+      </c>
+      <c r="I817" s="3"/>
+      <c r="J817" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K817" s="3"/>
+      <c r="L817" s="3"/>
+      <c r="M817" s="3"/>
+    </row>
+    <row r="818" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A818" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B818" s="3"/>
+      <c r="C818" s="3">
+        <v>31</v>
+      </c>
+      <c r="D818" s="3">
+        <v>5532068077</v>
+      </c>
+      <c r="E818" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F818" s="3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="G818" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H818" s="3">
+        <v>76</v>
+      </c>
+      <c r="I818" s="3"/>
+      <c r="J818" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K818" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L818" s="3" t="s">
+        <v>1326</v>
+      </c>
+      <c r="M818" s="3"/>
+    </row>
+    <row r="819" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A819" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B819" s="3"/>
+      <c r="C819" s="3">
+        <v>31</v>
+      </c>
+      <c r="D819" s="3">
+        <v>5532068080</v>
+      </c>
+      <c r="E819" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F819" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G819" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H819" s="3">
+        <v>64</v>
+      </c>
+      <c r="I819" s="3"/>
+      <c r="J819" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K819" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L819" s="3" t="s">
+        <v>1326</v>
+      </c>
+      <c r="M819" s="3"/>
+    </row>
+    <row r="820" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A820" s="3" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B820" s="3"/>
+      <c r="C820" s="3">
+        <v>31</v>
+      </c>
+      <c r="D820" s="3">
+        <v>5534121791</v>
+      </c>
+      <c r="E820" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F820" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="G820" s="3"/>
+      <c r="H820" s="3">
+        <v>66</v>
+      </c>
+      <c r="I820" s="3">
+        <v>60</v>
+      </c>
+      <c r="J820" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K820" s="3"/>
+      <c r="L820" s="3"/>
+      <c r="M820" s="3"/>
+    </row>
+    <row r="821" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A821" s="3" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B821" s="3"/>
+      <c r="C821" s="3">
+        <v>31</v>
+      </c>
+      <c r="D821" s="3">
+        <v>5534129074</v>
+      </c>
+      <c r="E821" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F821" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G821" s="3"/>
+      <c r="H821" s="3">
+        <v>56</v>
+      </c>
+      <c r="I821" s="3">
+        <v>50</v>
+      </c>
+      <c r="J821" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K821" s="3"/>
+      <c r="L821" s="3"/>
+      <c r="M821" s="3"/>
+    </row>
+    <row r="822" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A822" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B822" s="3"/>
+      <c r="C822" s="3">
+        <v>28</v>
+      </c>
+      <c r="D822" s="3">
+        <v>5534293221</v>
+      </c>
+      <c r="E822" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F822" s="3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="G822" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H822" s="3">
+        <v>69</v>
+      </c>
+      <c r="I822" s="3"/>
+      <c r="J822" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K822" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L822" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="M822" s="3"/>
+    </row>
+    <row r="823" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A823" s="3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B823" s="3"/>
+      <c r="C823" s="3">
+        <v>16</v>
+      </c>
+      <c r="D823" s="3">
+        <v>5537961813</v>
+      </c>
+      <c r="E823" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F823" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G823" s="3"/>
+      <c r="H823" s="3"/>
+      <c r="I823" s="3"/>
+      <c r="J823" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K823" s="3"/>
+      <c r="L823" s="3"/>
+      <c r="M823" s="3"/>
+    </row>
+    <row r="824" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A824" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B824" s="3"/>
+      <c r="C824" s="3">
+        <v>2</v>
+      </c>
+      <c r="D824" s="3">
+        <v>5538798953</v>
+      </c>
+      <c r="E824" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F824" s="3" t="s">
+        <v>1334</v>
+      </c>
+      <c r="G824" s="3"/>
+      <c r="H824" s="3">
+        <v>70</v>
+      </c>
+      <c r="I824" s="3">
+        <v>70</v>
+      </c>
+      <c r="J824" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K824" s="3"/>
+      <c r="L824" s="3"/>
+      <c r="M824" s="3"/>
+    </row>
+    <row r="825" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A825" s="3" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B825" s="3"/>
+      <c r="C825" s="3">
+        <v>2</v>
+      </c>
+      <c r="D825" s="3">
+        <v>5538940168</v>
+      </c>
+      <c r="E825" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F825" s="3" t="s">
+        <v>912</v>
+      </c>
+      <c r="G825" s="3"/>
+      <c r="H825" s="3">
+        <v>63</v>
+      </c>
+      <c r="I825" s="3"/>
+      <c r="J825" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K825" s="3"/>
+      <c r="L825" s="3"/>
+      <c r="M825" s="3"/>
+    </row>
+    <row r="826" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A826" s="3" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B826" s="3"/>
+      <c r="C826" s="3">
+        <v>31</v>
+      </c>
+      <c r="D826" s="3">
+        <v>5539877739</v>
+      </c>
+      <c r="E826" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F826" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G826" s="3"/>
+      <c r="H826" s="3">
+        <v>48</v>
+      </c>
+      <c r="I826" s="3">
+        <v>35</v>
+      </c>
+      <c r="J826" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K826" s="3"/>
+      <c r="L826" s="3"/>
+      <c r="M826" s="3"/>
+    </row>
+    <row r="827" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A827" s="3" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B827" s="3"/>
+      <c r="C827" s="3">
+        <v>26</v>
+      </c>
+      <c r="D827" s="3">
+        <v>5540424013</v>
+      </c>
+      <c r="E827" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F827" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G827" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H827" s="3">
+        <v>71</v>
+      </c>
+      <c r="I827" s="3"/>
+      <c r="J827" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K827" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L827" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="M827" s="3"/>
+    </row>
+    <row r="828" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A828" s="3" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B828" s="3"/>
+      <c r="C828" s="3">
+        <v>26</v>
+      </c>
+      <c r="D828" s="3">
+        <v>5540831757</v>
+      </c>
+      <c r="E828" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F828" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G828" s="3"/>
+      <c r="H828" s="3">
+        <v>69</v>
+      </c>
+      <c r="I828" s="3">
+        <v>60</v>
+      </c>
+      <c r="J828" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K828" s="3"/>
+      <c r="L828" s="3"/>
+      <c r="M828" s="3"/>
+    </row>
+    <row r="829" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A829" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B829" s="3"/>
+      <c r="C829" s="3">
+        <v>26</v>
+      </c>
+      <c r="D829" s="3">
+        <v>5540851091</v>
+      </c>
+      <c r="E829" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F829" s="3" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G829" s="3"/>
+      <c r="H829" s="3">
+        <v>61</v>
+      </c>
+      <c r="I829" s="3">
+        <v>55</v>
+      </c>
+      <c r="J829" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K829" s="3"/>
+      <c r="L829" s="3"/>
+      <c r="M829" s="3"/>
+    </row>
+    <row r="830" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A830" s="3" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B830" s="3"/>
+      <c r="C830" s="3">
+        <v>26</v>
+      </c>
+      <c r="D830" s="3">
+        <v>5540854080</v>
+      </c>
+      <c r="E830" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F830" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="G830" s="3"/>
+      <c r="H830" s="3">
+        <v>67</v>
+      </c>
+      <c r="I830" s="3">
+        <v>60</v>
+      </c>
+      <c r="J830" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K830" s="3"/>
+      <c r="L830" s="3"/>
+      <c r="M830" s="3"/>
+    </row>
+    <row r="831" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A831" s="3" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B831" s="3"/>
+      <c r="C831" s="3">
+        <v>28</v>
+      </c>
+      <c r="D831" s="3">
+        <v>5540900849</v>
+      </c>
+      <c r="E831" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F831" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G831" s="3"/>
+      <c r="H831" s="3">
+        <v>43</v>
+      </c>
+      <c r="I831" s="3"/>
+      <c r="J831" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K831" s="3"/>
+      <c r="L831" s="3"/>
+      <c r="M831" s="3"/>
+    </row>
+    <row r="832" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A832" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B832" s="3"/>
+      <c r="C832" s="3">
+        <v>31</v>
+      </c>
+      <c r="D832" s="3">
+        <v>5541162574</v>
+      </c>
+      <c r="E832" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F832" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G832" s="3"/>
+      <c r="H832" s="3">
+        <v>56</v>
+      </c>
+      <c r="I832" s="3">
+        <v>50</v>
+      </c>
+      <c r="J832" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K832" s="3"/>
+      <c r="L832" s="3"/>
+      <c r="M832" s="3"/>
+    </row>
+    <row r="833" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A833" s="3" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B833" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C833" s="3">
+        <v>27</v>
+      </c>
+      <c r="D833" s="3">
+        <v>5541210732</v>
+      </c>
+      <c r="E833" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F833" s="3" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G833" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H833" s="3">
+        <v>6</v>
+      </c>
+      <c r="I833" s="3"/>
+      <c r="J833" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K833" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L833" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="M833" s="3"/>
+    </row>
+    <row r="834" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A834" s="3" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B834" s="3"/>
+      <c r="C834" s="3">
+        <v>28</v>
+      </c>
+      <c r="D834" s="3">
+        <v>5541400431</v>
+      </c>
+      <c r="E834" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F834" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G834" s="3"/>
+      <c r="H834" s="3">
+        <v>50</v>
+      </c>
+      <c r="I834" s="3"/>
+      <c r="J834" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K834" s="3"/>
+      <c r="L834" s="3"/>
+      <c r="M834" s="3"/>
+    </row>
+    <row r="835" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A835" s="3" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B835" s="3"/>
+      <c r="C835" s="3">
+        <v>27</v>
+      </c>
+      <c r="D835" s="3">
+        <v>5541464135</v>
+      </c>
+      <c r="E835" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="F835" s="3" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G835" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H835" s="3"/>
+      <c r="I835" s="3"/>
+      <c r="J835" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K835" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L835" s="3" t="s">
+        <v>1351</v>
+      </c>
+      <c r="M835" s="3"/>
+    </row>
+    <row r="836" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A836" s="3" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B836" s="3"/>
+      <c r="C836" s="3">
+        <v>31</v>
+      </c>
+      <c r="D836" s="3">
+        <v>5541662292</v>
+      </c>
+      <c r="E836" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F836" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G836" s="3"/>
+      <c r="H836" s="3">
+        <v>69</v>
+      </c>
+      <c r="I836" s="3"/>
+      <c r="J836" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K836" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L836" s="3" t="s">
+        <v>1351</v>
+      </c>
+      <c r="M836" s="3"/>
+    </row>
+    <row r="837" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A837" s="3" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B837" s="3"/>
+      <c r="C837" s="3">
+        <v>27</v>
+      </c>
+      <c r="D837" s="3">
+        <v>5542322605</v>
+      </c>
+      <c r="E837" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F837" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="G837" s="3"/>
+      <c r="H837" s="3">
+        <v>69</v>
+      </c>
+      <c r="I837" s="3"/>
+      <c r="J837" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K837" s="3"/>
+      <c r="L837" s="3"/>
+      <c r="M837" s="3"/>
+    </row>
+    <row r="838" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A838" s="3" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B838" s="3"/>
+      <c r="C838" s="3">
+        <v>27</v>
+      </c>
+      <c r="D838" s="3">
+        <v>5542328834</v>
+      </c>
+      <c r="E838" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F838" s="3" t="s">
+        <v>1354</v>
+      </c>
+      <c r="G838" s="3"/>
+      <c r="H838" s="3">
+        <v>72</v>
+      </c>
+      <c r="I838" s="3"/>
+      <c r="J838" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K838" s="3"/>
+      <c r="L838" s="3"/>
+      <c r="M838" s="3"/>
+    </row>
+    <row r="839" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A839" s="3" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B839" s="3"/>
+      <c r="C839" s="3">
+        <v>31</v>
+      </c>
+      <c r="D839" s="3">
+        <v>5542934860</v>
+      </c>
+      <c r="E839" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F839" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="G839" s="3"/>
+      <c r="H839" s="3">
+        <v>67</v>
+      </c>
+      <c r="I839" s="3"/>
+      <c r="J839" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K839" s="3"/>
+      <c r="L839" s="3"/>
+      <c r="M839" s="3"/>
+    </row>
+    <row r="840" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A840" s="3" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B840" s="3"/>
+      <c r="C840" s="3">
+        <v>31</v>
+      </c>
+      <c r="D840" s="3">
+        <v>5542942091</v>
+      </c>
+      <c r="E840" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F840" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G840" s="3"/>
+      <c r="H840" s="3">
+        <v>69</v>
+      </c>
+      <c r="I840" s="3"/>
+      <c r="J840" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K840" s="3"/>
+      <c r="L840" s="3"/>
+      <c r="M840" s="3"/>
+    </row>
+    <row r="841" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A841" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B841" s="3"/>
+      <c r="C841" s="3">
+        <v>31</v>
+      </c>
+      <c r="D841" s="3">
+        <v>5544588333</v>
+      </c>
+      <c r="E841" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F841" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G841" s="3"/>
+      <c r="H841" s="3"/>
+      <c r="I841" s="3"/>
+      <c r="J841" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K841" s="3"/>
+      <c r="L841" s="3"/>
+      <c r="M841" s="3"/>
+    </row>
+    <row r="842" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A842" s="3" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B842" s="3"/>
+      <c r="C842" s="3">
+        <v>31</v>
+      </c>
+      <c r="D842" s="3">
+        <v>5548118084</v>
+      </c>
+      <c r="E842" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F842" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G842" s="3"/>
+      <c r="H842" s="3">
+        <v>51</v>
+      </c>
+      <c r="I842" s="3"/>
+      <c r="J842" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K842" s="3"/>
+      <c r="L842" s="3"/>
+      <c r="M842" s="3"/>
+    </row>
+    <row r="843" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A843" s="3" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B843" s="3"/>
+      <c r="C843" s="3">
+        <v>31</v>
+      </c>
+      <c r="D843" s="3">
+        <v>5548205498</v>
+      </c>
+      <c r="E843" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F843" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G843" s="3"/>
+      <c r="H843" s="3">
+        <v>45</v>
+      </c>
+      <c r="I843" s="3"/>
+      <c r="J843" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K843" s="3"/>
+      <c r="L843" s="3"/>
+      <c r="M843" s="3"/>
+    </row>
+    <row r="844" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A844" s="3" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B844" s="3"/>
+      <c r="C844" s="3">
+        <v>27</v>
+      </c>
+      <c r="D844" s="3">
+        <v>5549802235</v>
+      </c>
+      <c r="E844" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F844" s="3" t="s">
+        <v>1361</v>
+      </c>
+      <c r="G844" s="3"/>
+      <c r="H844" s="3">
+        <v>43</v>
+      </c>
+      <c r="I844" s="3">
+        <v>35</v>
+      </c>
+      <c r="J844" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K844" s="3"/>
+      <c r="L844" s="3"/>
+      <c r="M844" s="3"/>
+    </row>
+    <row r="845" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A845" s="3" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B845" s="3"/>
+      <c r="C845" s="3">
+        <v>31</v>
+      </c>
+      <c r="D845" s="3">
+        <v>5554530200</v>
+      </c>
+      <c r="E845" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F845" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G845" s="3"/>
+      <c r="H845" s="3">
+        <v>61</v>
+      </c>
+      <c r="I845" s="3">
+        <v>50</v>
+      </c>
+      <c r="J845" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K845" s="3"/>
+      <c r="L845" s="3"/>
+      <c r="M845" s="3"/>
+    </row>
+    <row r="846" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A846" s="3" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B846" s="3"/>
+      <c r="C846" s="3">
+        <v>31</v>
+      </c>
+      <c r="D846" s="3">
+        <v>5554541975</v>
+      </c>
+      <c r="E846" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F846" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G846" s="3"/>
+      <c r="H846" s="3">
+        <v>7</v>
+      </c>
+      <c r="I846" s="3"/>
+      <c r="J846" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K846" s="3"/>
+      <c r="L846" s="3"/>
+      <c r="M846" s="3"/>
+    </row>
+    <row r="847" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A847" s="3" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B847" s="3"/>
+      <c r="C847" s="3">
+        <v>31</v>
+      </c>
+      <c r="D847" s="3">
+        <v>5555925302</v>
+      </c>
+      <c r="E847" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F847" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G847" s="3"/>
+      <c r="H847" s="3">
+        <v>12</v>
+      </c>
+      <c r="I847" s="3"/>
+      <c r="J847" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K847" s="3"/>
+      <c r="L847" s="3"/>
+      <c r="M847" s="3"/>
+    </row>
+    <row r="848" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A848" s="3" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B848" s="3"/>
+      <c r="C848" s="3">
+        <v>31</v>
+      </c>
+      <c r="D848" s="3">
+        <v>5556322416</v>
+      </c>
+      <c r="E848" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F848" s="3" t="s">
+        <v>1366</v>
+      </c>
+      <c r="G848" s="3"/>
+      <c r="H848" s="3">
+        <v>19</v>
+      </c>
+      <c r="I848" s="3"/>
+      <c r="J848" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K848" s="3"/>
+      <c r="L848" s="3"/>
+      <c r="M848" s="3"/>
+    </row>
+    <row r="849" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A849" s="3" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B849" s="3"/>
+      <c r="C849" s="3">
+        <v>31</v>
+      </c>
+      <c r="D849" s="3">
+        <v>5556346216</v>
+      </c>
+      <c r="E849" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F849" s="3" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G849" s="3"/>
+      <c r="H849" s="3">
+        <v>11</v>
+      </c>
+      <c r="I849" s="3"/>
+      <c r="J849" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K849" s="3"/>
+      <c r="L849" s="3"/>
+      <c r="M849" s="3"/>
+    </row>
+    <row r="850" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A850" s="3" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B850" s="3"/>
+      <c r="C850" s="3">
+        <v>31</v>
+      </c>
+      <c r="D850" s="3">
+        <v>5556362355</v>
+      </c>
+      <c r="E850" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F850" s="3" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G850" s="3"/>
+      <c r="H850" s="3">
+        <v>17</v>
+      </c>
+      <c r="I850" s="3"/>
+      <c r="J850" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K850" s="3"/>
+      <c r="L850" s="3"/>
+      <c r="M850" s="3"/>
+    </row>
+    <row r="851" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A851" s="3" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B851" s="3"/>
+      <c r="C851" s="3">
+        <v>28</v>
+      </c>
+      <c r="D851" s="3">
+        <v>5556752124</v>
+      </c>
+      <c r="E851" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F851" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G851" s="3"/>
+      <c r="H851" s="3">
+        <v>15</v>
+      </c>
+      <c r="I851" s="3"/>
+      <c r="J851" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K851" s="3"/>
+      <c r="L851" s="3"/>
+      <c r="M851" s="3"/>
+    </row>
+    <row r="852" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A852" s="3" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B852" s="3"/>
+      <c r="C852" s="3">
+        <v>31</v>
+      </c>
+      <c r="D852" s="3">
+        <v>5557044908</v>
+      </c>
+      <c r="E852" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F852" s="3" t="s">
+        <v>1373</v>
+      </c>
+      <c r="G852" s="3"/>
+      <c r="H852" s="3">
+        <v>76</v>
+      </c>
+      <c r="I852" s="3">
+        <v>65</v>
+      </c>
+      <c r="J852" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K852" s="3"/>
+      <c r="L852" s="3"/>
+      <c r="M852" s="3"/>
+    </row>
+    <row r="853" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A853" s="3" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B853" s="3"/>
+      <c r="C853" s="3">
+        <v>31</v>
+      </c>
+      <c r="D853" s="3">
+        <v>5557193400</v>
+      </c>
+      <c r="E853" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F853" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G853" s="3"/>
+      <c r="H853" s="3">
+        <v>23</v>
+      </c>
+      <c r="I853" s="3"/>
+      <c r="J853" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K853" s="3"/>
+      <c r="L853" s="3"/>
+      <c r="M853" s="3"/>
+    </row>
+    <row r="854" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A854" s="3" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B854" s="3"/>
+      <c r="C854" s="3">
+        <v>31</v>
+      </c>
+      <c r="D854" s="3">
+        <v>5557894532</v>
+      </c>
+      <c r="E854" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F854" s="3" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G854" s="3"/>
+      <c r="H854" s="3">
+        <v>66</v>
+      </c>
+      <c r="I854" s="3">
+        <v>60</v>
+      </c>
+      <c r="J854" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K854" s="3"/>
+      <c r="L854" s="3"/>
+      <c r="M854" s="3"/>
+    </row>
+    <row r="855" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A855" s="3" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B855" s="3"/>
+      <c r="C855" s="3">
+        <v>31</v>
+      </c>
+      <c r="D855" s="3">
+        <v>5557946343</v>
+      </c>
+      <c r="E855" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F855" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="G855" s="3"/>
+      <c r="H855" s="3">
+        <v>68</v>
+      </c>
+      <c r="I855" s="3">
+        <v>60</v>
+      </c>
+      <c r="J855" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K855" s="3"/>
+      <c r="L855" s="3"/>
+      <c r="M855" s="3"/>
+    </row>
+    <row r="856" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A856" s="3" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B856" s="3"/>
+      <c r="C856" s="3">
+        <v>31</v>
+      </c>
+      <c r="D856" s="3">
+        <v>5558863188</v>
+      </c>
+      <c r="E856" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F856" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G856" s="3"/>
+      <c r="H856" s="3">
+        <v>73</v>
+      </c>
+      <c r="I856" s="3">
+        <v>70</v>
+      </c>
+      <c r="J856" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K856" s="3"/>
+      <c r="L856" s="3"/>
+      <c r="M856" s="3"/>
+    </row>
+    <row r="857" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A857" s="3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B857" s="3"/>
+      <c r="C857" s="3">
+        <v>31</v>
+      </c>
+      <c r="D857" s="3">
+        <v>5558875551</v>
+      </c>
+      <c r="E857" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F857" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="G857" s="3"/>
+      <c r="H857" s="3">
+        <v>67</v>
+      </c>
+      <c r="I857" s="3"/>
+      <c r="J857" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K857" s="3"/>
+      <c r="L857" s="3"/>
+      <c r="M857" s="3"/>
+    </row>
+    <row r="858" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A858" s="3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B858" s="3"/>
+      <c r="C858" s="3">
+        <v>31</v>
+      </c>
+      <c r="D858" s="3">
+        <v>5558875558</v>
+      </c>
+      <c r="E858" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F858" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G858" s="3"/>
+      <c r="H858" s="3">
+        <v>74</v>
+      </c>
+      <c r="I858" s="3"/>
+      <c r="J858" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K858" s="3"/>
+      <c r="L858" s="3"/>
+      <c r="M858" s="3"/>
+    </row>
+    <row r="859" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A859" s="3" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B859" s="3"/>
+      <c r="C859" s="3">
+        <v>31</v>
+      </c>
+      <c r="D859" s="3">
+        <v>5558899582</v>
+      </c>
+      <c r="E859" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F859" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G859" s="3"/>
+      <c r="H859" s="3">
+        <v>36</v>
+      </c>
+      <c r="I859" s="3"/>
+      <c r="J859" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K859" s="3"/>
+      <c r="L859" s="3"/>
+      <c r="M859" s="3"/>
+    </row>
+    <row r="860" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A860" s="3" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B860" s="3"/>
+      <c r="C860" s="3">
+        <v>31</v>
+      </c>
+      <c r="D860" s="3">
+        <v>5558911690</v>
+      </c>
+      <c r="E860" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F860" s="3" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G860" s="3"/>
+      <c r="H860" s="3">
+        <v>62</v>
+      </c>
+      <c r="I860" s="3">
+        <v>50</v>
+      </c>
+      <c r="J860" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K860" s="3"/>
+      <c r="L860" s="3"/>
+      <c r="M860" s="3"/>
+    </row>
+    <row r="861" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A861" s="3" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B861" s="3"/>
+      <c r="C861" s="3">
+        <v>31</v>
+      </c>
+      <c r="D861" s="3">
+        <v>5558929883</v>
+      </c>
+      <c r="E861" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F861" s="3" t="s">
+        <v>1384</v>
+      </c>
+      <c r="G861" s="3"/>
+      <c r="H861" s="3">
+        <v>64</v>
+      </c>
+      <c r="I861" s="3">
+        <v>50</v>
+      </c>
+      <c r="J861" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K861" s="3"/>
+      <c r="L861" s="3"/>
+      <c r="M861" s="3"/>
+    </row>
+    <row r="862" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A862" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B862" s="3"/>
+      <c r="C862" s="3">
+        <v>31</v>
+      </c>
+      <c r="D862" s="3">
+        <v>5559608966</v>
+      </c>
+      <c r="E862" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F862" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G862" s="3"/>
+      <c r="H862" s="3">
+        <v>67</v>
+      </c>
+      <c r="I862" s="3">
+        <v>50</v>
+      </c>
+      <c r="J862" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K862" s="3"/>
+      <c r="L862" s="3"/>
+      <c r="M862" s="3"/>
+    </row>
+    <row r="863" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A863" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B863" s="3"/>
+      <c r="C863" s="3">
+        <v>31</v>
+      </c>
+      <c r="D863" s="3">
+        <v>5560450081</v>
+      </c>
+      <c r="E863" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F863" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G863" s="3"/>
+      <c r="H863" s="3">
+        <v>59</v>
+      </c>
+      <c r="I863" s="3">
+        <v>50</v>
+      </c>
+      <c r="J863" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K863" s="3"/>
+      <c r="L863" s="3"/>
+      <c r="M863" s="3"/>
+    </row>
+    <row r="864" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A864" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B864" s="3"/>
+      <c r="C864" s="3">
+        <v>31</v>
+      </c>
+      <c r="D864" s="3">
+        <v>5560450082</v>
+      </c>
+      <c r="E864" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F864" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="G864" s="3"/>
+      <c r="H864" s="3">
+        <v>53</v>
+      </c>
+      <c r="I864" s="3"/>
+      <c r="J864" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K864" s="3"/>
+      <c r="L864" s="3"/>
+      <c r="M864" s="3"/>
+    </row>
+    <row r="865" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A865" s="3" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B865" s="3"/>
+      <c r="C865" s="3">
+        <v>31</v>
+      </c>
+      <c r="D865" s="3">
+        <v>5560463063</v>
+      </c>
+      <c r="E865" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F865" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G865" s="3"/>
+      <c r="H865" s="3">
+        <v>12</v>
+      </c>
+      <c r="I865" s="3"/>
+      <c r="J865" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K865" s="3"/>
+      <c r="L865" s="3"/>
+      <c r="M865" s="3"/>
+    </row>
+    <row r="866" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A866" s="3" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B866" s="3"/>
+      <c r="C866" s="3">
+        <v>28</v>
+      </c>
+      <c r="D866" s="3">
+        <v>5560667173</v>
+      </c>
+      <c r="E866" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F866" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="G866" s="3"/>
+      <c r="H866" s="3">
+        <v>56</v>
+      </c>
+      <c r="I866" s="3">
+        <v>50</v>
+      </c>
+      <c r="J866" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K866" s="3"/>
+      <c r="L866" s="3"/>
+      <c r="M866" s="3"/>
+    </row>
+    <row r="867" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A867" s="3" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B867" s="3"/>
+      <c r="C867" s="3">
+        <v>26</v>
+      </c>
+      <c r="D867" s="3">
+        <v>5561597867</v>
+      </c>
+      <c r="E867" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F867" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G867" s="3"/>
+      <c r="H867" s="3">
+        <v>27</v>
+      </c>
+      <c r="I867" s="3"/>
+      <c r="J867" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K867" s="3"/>
+      <c r="L867" s="3"/>
+      <c r="M867" s="3"/>
+    </row>
+    <row r="868" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A868" s="3" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B868" s="3"/>
+      <c r="C868" s="3">
+        <v>28</v>
+      </c>
+      <c r="D868" s="3">
+        <v>5561679156</v>
+      </c>
+      <c r="E868" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F868" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G868" s="3"/>
+      <c r="H868" s="3">
+        <v>8</v>
+      </c>
+      <c r="I868" s="3"/>
+      <c r="J868" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K868" s="3"/>
+      <c r="L868" s="3"/>
+      <c r="M868" s="3"/>
+    </row>
+    <row r="869" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A869" s="3" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B869" s="3"/>
+      <c r="C869" s="3">
+        <v>26</v>
+      </c>
+      <c r="D869" s="3">
+        <v>5561828116</v>
+      </c>
+      <c r="E869" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F869" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G869" s="3"/>
+      <c r="H869" s="3">
+        <v>7</v>
+      </c>
+      <c r="I869" s="3"/>
+      <c r="J869" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K869" s="3"/>
+      <c r="L869" s="3"/>
+      <c r="M869" s="3"/>
+    </row>
+    <row r="870" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A870" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B870" s="3"/>
+      <c r="C870" s="3">
+        <v>31</v>
+      </c>
+      <c r="D870" s="3">
+        <v>5561920551</v>
+      </c>
+      <c r="E870" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F870" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G870" s="3"/>
+      <c r="H870" s="3">
+        <v>73</v>
+      </c>
+      <c r="I870" s="3">
+        <v>60</v>
+      </c>
+      <c r="J870" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K870" s="3"/>
+      <c r="L870" s="3"/>
+      <c r="M870" s="3"/>
+    </row>
+    <row r="871" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A871" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B871" s="3"/>
+      <c r="C871" s="3">
+        <v>31</v>
+      </c>
+      <c r="D871" s="3">
+        <v>5561954336</v>
+      </c>
+      <c r="E871" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F871" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G871" s="3"/>
+      <c r="H871" s="3">
+        <v>63</v>
+      </c>
+      <c r="I871" s="3">
+        <v>50</v>
+      </c>
+      <c r="J871" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K871" s="3"/>
+      <c r="L871" s="3"/>
+      <c r="M871" s="3"/>
+    </row>
+    <row r="872" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A872" s="3" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B872" s="3"/>
+      <c r="C872" s="3">
+        <v>31</v>
+      </c>
+      <c r="D872" s="3">
+        <v>5565320525</v>
+      </c>
+      <c r="E872" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F872" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G872" s="3"/>
+      <c r="H872" s="3">
+        <v>49</v>
+      </c>
+      <c r="I872" s="3">
+        <v>40</v>
+      </c>
+      <c r="J872" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K872" s="3"/>
+      <c r="L872" s="3"/>
+      <c r="M872" s="3"/>
+    </row>
+    <row r="873" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A873" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B873" s="3"/>
+      <c r="C873" s="3">
+        <v>31</v>
+      </c>
+      <c r="D873" s="3">
+        <v>5565343913</v>
+      </c>
+      <c r="E873" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F873" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G873" s="3"/>
+      <c r="H873" s="3">
+        <v>62</v>
+      </c>
+      <c r="I873" s="3">
+        <v>50</v>
+      </c>
+      <c r="J873" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K873" s="3"/>
+      <c r="L873" s="3"/>
+      <c r="M873" s="3"/>
+    </row>
+    <row r="874" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A874" s="3" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B874" s="3"/>
+      <c r="C874" s="3">
+        <v>31</v>
+      </c>
+      <c r="D874" s="3">
+        <v>5565427945</v>
+      </c>
+      <c r="E874" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F874" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="G874" s="3"/>
+      <c r="H874" s="3">
+        <v>68</v>
+      </c>
+      <c r="I874" s="3">
+        <v>60</v>
+      </c>
+      <c r="J874" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K874" s="3"/>
+      <c r="L874" s="3"/>
+      <c r="M874" s="3"/>
+    </row>
+    <row r="875" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A875" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B875" s="3"/>
+      <c r="C875" s="3">
+        <v>28</v>
+      </c>
+      <c r="D875" s="3">
+        <v>5566424203</v>
+      </c>
+      <c r="E875" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F875" s="3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="G875" s="3"/>
+      <c r="H875" s="3">
+        <v>54</v>
+      </c>
+      <c r="I875" s="3">
+        <v>45</v>
+      </c>
+      <c r="J875" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K875" s="3"/>
+      <c r="L875" s="3"/>
+      <c r="M875" s="3"/>
+    </row>
+    <row r="876" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A876" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B876" s="3"/>
+      <c r="C876" s="3">
+        <v>31</v>
+      </c>
+      <c r="D876" s="3">
+        <v>5566963797</v>
+      </c>
+      <c r="E876" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F876" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G876" s="3"/>
+      <c r="H876" s="3">
+        <v>58</v>
+      </c>
+      <c r="I876" s="3">
+        <v>45</v>
+      </c>
+      <c r="J876" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K876" s="3"/>
+      <c r="L876" s="3"/>
+      <c r="M876" s="3"/>
+    </row>
+    <row r="877" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A877" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B877" s="3"/>
+      <c r="C877" s="3">
+        <v>28</v>
+      </c>
+      <c r="D877" s="3">
+        <v>5566976023</v>
+      </c>
+      <c r="E877" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F877" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G877" s="3"/>
+      <c r="H877" s="3">
+        <v>30</v>
+      </c>
+      <c r="I877" s="3"/>
+      <c r="J877" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K877" s="3"/>
+      <c r="L877" s="3"/>
+      <c r="M877" s="3"/>
+    </row>
+    <row r="878" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A878" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B878" s="3"/>
+      <c r="C878" s="3">
+        <v>31</v>
+      </c>
+      <c r="D878" s="3">
+        <v>5566991385</v>
+      </c>
+      <c r="E878" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F878" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G878" s="3"/>
+      <c r="H878" s="3">
+        <v>2</v>
+      </c>
+      <c r="I878" s="3"/>
+      <c r="J878" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K878" s="3"/>
+      <c r="L878" s="3"/>
+      <c r="M878" s="3"/>
+    </row>
+    <row r="879" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A879" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B879" s="3"/>
+      <c r="C879" s="3">
+        <v>31</v>
+      </c>
+      <c r="D879" s="3">
+        <v>5567391518</v>
+      </c>
+      <c r="E879" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F879" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G879" s="3"/>
+      <c r="H879" s="3">
+        <v>61</v>
+      </c>
+      <c r="I879" s="3">
+        <v>50</v>
+      </c>
+      <c r="J879" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K879" s="3"/>
+      <c r="L879" s="3"/>
+      <c r="M879" s="3"/>
+    </row>
+    <row r="880" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A880" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B880" s="3"/>
+      <c r="C880" s="3">
+        <v>31</v>
+      </c>
+      <c r="D880" s="3">
+        <v>5567401370</v>
+      </c>
+      <c r="E880" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F880" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="G880" s="3"/>
+      <c r="H880" s="3">
+        <v>67</v>
+      </c>
+      <c r="I880" s="3">
+        <v>60</v>
+      </c>
+      <c r="J880" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K880" s="3"/>
+      <c r="L880" s="3"/>
+      <c r="M880" s="3"/>
+    </row>
+    <row r="881" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A881" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B881" s="3"/>
+      <c r="C881" s="3">
+        <v>31</v>
+      </c>
+      <c r="D881" s="3">
+        <v>5567407879</v>
+      </c>
+      <c r="E881" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F881" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G881" s="3"/>
+      <c r="H881" s="3">
+        <v>44</v>
+      </c>
+      <c r="I881" s="3"/>
+      <c r="J881" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K881" s="3"/>
+      <c r="L881" s="3"/>
+      <c r="M881" s="3"/>
+    </row>
+    <row r="882" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A882" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B882" s="3"/>
+      <c r="C882" s="3">
+        <v>31</v>
+      </c>
+      <c r="D882" s="3">
+        <v>5567624714</v>
+      </c>
+      <c r="E882" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F882" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="G882" s="3"/>
+      <c r="H882" s="3">
+        <v>54</v>
+      </c>
+      <c r="I882" s="3">
+        <v>45</v>
+      </c>
+      <c r="J882" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K882" s="3"/>
+      <c r="L882" s="3"/>
+      <c r="M882" s="3"/>
+    </row>
+    <row r="883" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A883" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B883" s="3"/>
+      <c r="C883" s="3">
+        <v>28</v>
+      </c>
+      <c r="D883" s="3">
+        <v>5568708283</v>
+      </c>
+      <c r="E883" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F883" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="G883" s="3"/>
+      <c r="H883" s="3">
+        <v>56</v>
+      </c>
+      <c r="I883" s="3">
+        <v>50</v>
+      </c>
+      <c r="J883" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K883" s="3"/>
+      <c r="L883" s="3"/>
+      <c r="M883" s="3"/>
+    </row>
+    <row r="884" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A884" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B884" s="3"/>
+      <c r="C884" s="3">
+        <v>28</v>
+      </c>
+      <c r="D884" s="3">
+        <v>5568708286</v>
+      </c>
+      <c r="E884" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F884" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="G884" s="3"/>
+      <c r="H884" s="3">
+        <v>32</v>
+      </c>
+      <c r="I884" s="3"/>
+      <c r="J884" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K884" s="3"/>
+      <c r="L884" s="3"/>
+      <c r="M884" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Curtis Garage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B772A497-AB05-4308-BBA5-3A70319364DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3888973B-9961-48B2-A475-9EABB0AFC9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4439" uniqueCount="1408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4820" uniqueCount="1530">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -4111,6 +4111,9 @@
     <t>04/10/26 07:18 EDT</t>
   </si>
   <si>
+    <t>04/13/26 09:40 EDT</t>
+  </si>
+  <si>
     <t>04/10/26 07:21 EDT</t>
   </si>
   <si>
@@ -4147,6 +4150,9 @@
     <t>04/10/26 14:16 EDT</t>
   </si>
   <si>
+    <t>04/13/26 09:41 EDT</t>
+  </si>
+  <si>
     <t>04/10/26 15:45 EDT</t>
   </si>
   <si>
@@ -4162,6 +4168,12 @@
     <t>04/10/26 18:08 EDT</t>
   </si>
   <si>
+    <t>04/13/26 09:42 EDT</t>
+  </si>
+  <si>
+    <t>04/13/26 09:43 EDT</t>
+  </si>
+  <si>
     <t>04/10/26 18:12 EDT</t>
   </si>
   <si>
@@ -4186,6 +4198,9 @@
     <t>04/11/26 06:40 EDT</t>
   </si>
   <si>
+    <t>04/13/26 09:44 EDT</t>
+  </si>
+  <si>
     <t>04/11/26 08:19 EDT</t>
   </si>
   <si>
@@ -4219,6 +4234,9 @@
     <t>04/12/26 18:09 EDT</t>
   </si>
   <si>
+    <t>04/13/26 09:45 EDT</t>
+  </si>
+  <si>
     <t>04/12/26 18:12 EDT</t>
   </si>
   <si>
@@ -4234,6 +4252,9 @@
     <t>04/12/26 20:00 EDT</t>
   </si>
   <si>
+    <t>04/13/26 09:46 EDT</t>
+  </si>
+  <si>
     <t>04/12/26 21:33 EDT</t>
   </si>
   <si>
@@ -4244,6 +4265,351 @@
   </si>
   <si>
     <t>04/13/26 07:47 EDT</t>
+  </si>
+  <si>
+    <t>04/13/26 13:50 EDT</t>
+  </si>
+  <si>
+    <t>0.9mi S of Plainfield IN</t>
+  </si>
+  <si>
+    <t>04/13/26 14:41 EDT</t>
+  </si>
+  <si>
+    <t>8.4mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>04/13/26 15:07 EDT</t>
+  </si>
+  <si>
+    <t>04/13/26 15:51 EDT</t>
+  </si>
+  <si>
+    <t>13.7mi S of Terre Haute IN</t>
+  </si>
+  <si>
+    <t>04/13/26 15:58 EDT</t>
+  </si>
+  <si>
+    <t>16.4mi NW of Linton IN</t>
+  </si>
+  <si>
+    <t>04/13/26 16:02 EDT</t>
+  </si>
+  <si>
+    <t>15.4mi W of Linton IN</t>
+  </si>
+  <si>
+    <t>04/13/26 16:03 EDT</t>
+  </si>
+  <si>
+    <t>15.1mi W of Linton IN</t>
+  </si>
+  <si>
+    <t>04/13/26 16:16 EDT</t>
+  </si>
+  <si>
+    <t>14.5mi W of Linton IN</t>
+  </si>
+  <si>
+    <t>04/14/26 11:33 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 11:34 EDT</t>
+  </si>
+  <si>
+    <t>04/13/26 17:20 EDT</t>
+  </si>
+  <si>
+    <t>4.9mi SE of Terre Haute IN</t>
+  </si>
+  <si>
+    <t>04/13/26 17:36 EDT</t>
+  </si>
+  <si>
+    <t>9mi E of Brazil IN</t>
+  </si>
+  <si>
+    <t>04/14/26 07:21 EDT</t>
+  </si>
+  <si>
+    <t>12.7mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>04/14/26 07:22 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 17:04 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 08:14 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 17:11 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 17:12 EDT</t>
+  </si>
+  <si>
+    <t>13.4mi NW of Martinsville IN</t>
+  </si>
+  <si>
+    <t>04/14/26 17:22 EDT</t>
+  </si>
+  <si>
+    <t>04/14/26 19:37 EDT</t>
+  </si>
+  <si>
+    <t>10.5mi SW of Danville IN</t>
+  </si>
+  <si>
+    <t>04/14/26 19:38 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 07:39 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 07:40 EDT</t>
+  </si>
+  <si>
+    <t>13.7mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>04/15/26 09:24 EDT</t>
+  </si>
+  <si>
+    <t>7.7mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>04/16/26 09:39 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 17:20 EDT</t>
+  </si>
+  <si>
+    <t>04/15/26 21:19 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 09:42 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 09:43 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 09:48 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 10:29 EDT</t>
+  </si>
+  <si>
+    <t>6.5mi W of Beech Grove IN</t>
+  </si>
+  <si>
+    <t>04/17/26 07:37 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 11:02 EDT</t>
+  </si>
+  <si>
+    <t>6.1mi NW of Columbus IN</t>
+  </si>
+  <si>
+    <t>04/16/26 11:56 EDT</t>
+  </si>
+  <si>
+    <t>7.9mi E of Columbus IN</t>
+  </si>
+  <si>
+    <t>04/16/26 12:09 EDT</t>
+  </si>
+  <si>
+    <t>4.5mi SW of Greensburg IN</t>
+  </si>
+  <si>
+    <t>04/16/26 12:13 EDT</t>
+  </si>
+  <si>
+    <t>1.1mi SW of Greensburg IN</t>
+  </si>
+  <si>
+    <t>04/16/26 14:12 EDT</t>
+  </si>
+  <si>
+    <t>2.2mi E of Beech Grove IN</t>
+  </si>
+  <si>
+    <t>04/16/26 14:17 EDT</t>
+  </si>
+  <si>
+    <t>2.5mi SW of Beech Grove IN</t>
+  </si>
+  <si>
+    <t>04/17/26 07:38 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 07:40 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 14:33 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 18:08 EDT</t>
+  </si>
+  <si>
+    <t>8.2mi E of Brazil IN</t>
+  </si>
+  <si>
+    <t>04/16/26 19:53 EDT</t>
+  </si>
+  <si>
+    <t>6.4mi S of Danville IN</t>
+  </si>
+  <si>
+    <t>04/16/26 20:16 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 07:39 EDT</t>
+  </si>
+  <si>
+    <t>04/16/26 22:14 EDT</t>
+  </si>
+  <si>
+    <t>2.6mi SW of Kokomo IN</t>
+  </si>
+  <si>
+    <t>04/17/26 06:13 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 06:14 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 10:03 EDT</t>
+  </si>
+  <si>
+    <t>10mi SE of Franklin IN</t>
+  </si>
+  <si>
+    <t>04/17/26 10:04 EDT</t>
+  </si>
+  <si>
+    <t>9.4mi SE of Franklin IN</t>
+  </si>
+  <si>
+    <t>04/17/26 10:07 EDT</t>
+  </si>
+  <si>
+    <t>5.1mi SE of Franklin IN</t>
+  </si>
+  <si>
+    <t>04/17/26 10:36 EDT</t>
+  </si>
+  <si>
+    <t>3.4mi E of Plainfield IN</t>
+  </si>
+  <si>
+    <t>04/17/26 10:55 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 11:00 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 15:42 EDT</t>
+  </si>
+  <si>
+    <t>9.4mi E of Greencastle IN</t>
+  </si>
+  <si>
+    <t>04/17/26 17:04 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 17:10 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 17:14 EDT</t>
+  </si>
+  <si>
+    <t>10.5mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>04/17/26 19:05 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 19:06 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 22:50 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 23:09 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 23:10 EDT</t>
+  </si>
+  <si>
+    <t>04/17/26 23:11 EDT</t>
+  </si>
+  <si>
+    <t>04/18/26 09:38 EDT</t>
+  </si>
+  <si>
+    <t>04/18/26 12:48 EDT</t>
+  </si>
+  <si>
+    <t>04/18/26 12:49 EDT</t>
+  </si>
+  <si>
+    <t>04/18/26 13:20 EDT</t>
+  </si>
+  <si>
+    <t>11.4mi SW of Danville IN</t>
+  </si>
+  <si>
+    <t>04/18/26 13:36 EDT</t>
+  </si>
+  <si>
+    <t>04/18/26 13:42 EDT</t>
+  </si>
+  <si>
+    <t>04/18/26 14:59 EDT</t>
+  </si>
+  <si>
+    <t>04/18/26 15:02 EDT</t>
+  </si>
+  <si>
+    <t>04/18/26 15:06 EDT</t>
+  </si>
+  <si>
+    <t>04/18/26 15:08 EDT</t>
+  </si>
+  <si>
+    <t>04/18/26 16:32 EDT</t>
+  </si>
+  <si>
+    <t>04/18/26 16:40 EDT</t>
+  </si>
+  <si>
+    <t>04/18/26 17:00 EDT</t>
+  </si>
+  <si>
+    <t>04/18/26 20:16 EDT</t>
+  </si>
+  <si>
+    <t>04/18/26 21:35 EDT</t>
+  </si>
+  <si>
+    <t>1.7mi SW of Brazil IN</t>
+  </si>
+  <si>
+    <t>04/18/26 22:33 EDT</t>
+  </si>
+  <si>
+    <t>4.9mi SE of Brazil IN</t>
+  </si>
+  <si>
+    <t>04/18/26 22:38 EDT</t>
+  </si>
+  <si>
+    <t>7.9mi E of Brazil IN</t>
   </si>
 </sst>
 </file>
@@ -4605,7 +4971,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M884"/>
+  <dimension ref="A1:M959"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="13" width="15" customWidth="1"/>
@@ -31209,7 +31575,9 @@
       <c r="A845" s="3" t="s">
         <v>1362</v>
       </c>
-      <c r="B845" s="3"/>
+      <c r="B845" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="C845" s="3">
         <v>31</v>
       </c>
@@ -31222,7 +31590,9 @@
       <c r="F845" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G845" s="3"/>
+      <c r="G845" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="H845" s="3">
         <v>61</v>
       </c>
@@ -31230,15 +31600,19 @@
         <v>50</v>
       </c>
       <c r="J845" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K845" s="3"/>
-      <c r="L845" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K845" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L845" s="3" t="s">
+        <v>1363</v>
+      </c>
       <c r="M845" s="3"/>
     </row>
     <row r="846" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A846" s="3" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B846" s="3"/>
       <c r="C846" s="3">
@@ -31253,21 +31627,27 @@
       <c r="F846" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G846" s="3"/>
+      <c r="G846" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="H846" s="3">
         <v>7</v>
       </c>
       <c r="I846" s="3"/>
       <c r="J846" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K846" s="3"/>
-      <c r="L846" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K846" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L846" s="3" t="s">
+        <v>1363</v>
+      </c>
       <c r="M846" s="3"/>
     </row>
     <row r="847" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A847" s="3" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B847" s="3"/>
       <c r="C847" s="3">
@@ -31296,7 +31676,7 @@
     </row>
     <row r="848" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A848" s="3" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B848" s="3"/>
       <c r="C848" s="3">
@@ -31309,7 +31689,7 @@
         <v>16</v>
       </c>
       <c r="F848" s="3" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="G848" s="3"/>
       <c r="H848" s="3">
@@ -31325,7 +31705,7 @@
     </row>
     <row r="849" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A849" s="3" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B849" s="3"/>
       <c r="C849" s="3">
@@ -31338,7 +31718,7 @@
         <v>16</v>
       </c>
       <c r="F849" s="3" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="G849" s="3"/>
       <c r="H849" s="3">
@@ -31354,7 +31734,7 @@
     </row>
     <row r="850" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A850" s="3" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B850" s="3"/>
       <c r="C850" s="3">
@@ -31367,7 +31747,7 @@
         <v>16</v>
       </c>
       <c r="F850" s="3" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="G850" s="3"/>
       <c r="H850" s="3">
@@ -31383,7 +31763,7 @@
     </row>
     <row r="851" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A851" s="3" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B851" s="3"/>
       <c r="C851" s="3">
@@ -31412,7 +31792,7 @@
     </row>
     <row r="852" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A852" s="3" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B852" s="3"/>
       <c r="C852" s="3">
@@ -31425,7 +31805,7 @@
         <v>32</v>
       </c>
       <c r="F852" s="3" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="G852" s="3"/>
       <c r="H852" s="3">
@@ -31443,9 +31823,11 @@
     </row>
     <row r="853" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A853" s="3" t="s">
-        <v>1374</v>
-      </c>
-      <c r="B853" s="3"/>
+        <v>1375</v>
+      </c>
+      <c r="B853" s="3" t="s">
+        <v>167</v>
+      </c>
       <c r="C853" s="3">
         <v>31</v>
       </c>
@@ -31458,21 +31840,27 @@
       <c r="F853" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="G853" s="3"/>
+      <c r="G853" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="H853" s="3">
         <v>23</v>
       </c>
       <c r="I853" s="3"/>
       <c r="J853" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K853" s="3"/>
-      <c r="L853" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K853" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L853" s="3" t="s">
+        <v>1376</v>
+      </c>
       <c r="M853" s="3"/>
     </row>
     <row r="854" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A854" s="3" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="B854" s="3"/>
       <c r="C854" s="3">
@@ -31485,7 +31873,7 @@
         <v>32</v>
       </c>
       <c r="F854" s="3" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="G854" s="3"/>
       <c r="H854" s="3">
@@ -31503,7 +31891,7 @@
     </row>
     <row r="855" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A855" s="3" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="B855" s="3"/>
       <c r="C855" s="3">
@@ -31534,7 +31922,7 @@
     </row>
     <row r="856" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A856" s="3" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="B856" s="3"/>
       <c r="C856" s="3">
@@ -31565,9 +31953,11 @@
     </row>
     <row r="857" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A857" s="3" t="s">
-        <v>1379</v>
-      </c>
-      <c r="B857" s="3"/>
+        <v>1381</v>
+      </c>
+      <c r="B857" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="C857" s="3">
         <v>31</v>
       </c>
@@ -31580,23 +31970,31 @@
       <c r="F857" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="G857" s="3"/>
+      <c r="G857" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="H857" s="3">
         <v>67</v>
       </c>
       <c r="I857" s="3"/>
       <c r="J857" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K857" s="3"/>
-      <c r="L857" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K857" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L857" s="3" t="s">
+        <v>1382</v>
+      </c>
       <c r="M857" s="3"/>
     </row>
     <row r="858" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A858" s="3" t="s">
-        <v>1379</v>
-      </c>
-      <c r="B858" s="3"/>
+        <v>1381</v>
+      </c>
+      <c r="B858" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="C858" s="3">
         <v>31</v>
       </c>
@@ -31609,21 +32007,27 @@
       <c r="F858" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="G858" s="3"/>
+      <c r="G858" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="H858" s="3">
         <v>74</v>
       </c>
       <c r="I858" s="3"/>
       <c r="J858" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K858" s="3"/>
-      <c r="L858" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K858" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L858" s="3" t="s">
+        <v>1383</v>
+      </c>
       <c r="M858" s="3"/>
     </row>
     <row r="859" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A859" s="3" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="B859" s="3"/>
       <c r="C859" s="3">
@@ -31652,7 +32056,7 @@
     </row>
     <row r="860" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A860" s="3" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="B860" s="3"/>
       <c r="C860" s="3">
@@ -31665,7 +32069,7 @@
         <v>32</v>
       </c>
       <c r="F860" s="3" t="s">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="G860" s="3"/>
       <c r="H860" s="3">
@@ -31683,7 +32087,7 @@
     </row>
     <row r="861" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A861" s="3" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="B861" s="3"/>
       <c r="C861" s="3">
@@ -31696,7 +32100,7 @@
         <v>32</v>
       </c>
       <c r="F861" s="3" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
       <c r="G861" s="3"/>
       <c r="H861" s="3">
@@ -31714,7 +32118,7 @@
     </row>
     <row r="862" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A862" s="3" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
       <c r="B862" s="3"/>
       <c r="C862" s="3">
@@ -31745,7 +32149,7 @@
     </row>
     <row r="863" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A863" s="3" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
       <c r="B863" s="3"/>
       <c r="C863" s="3">
@@ -31776,7 +32180,7 @@
     </row>
     <row r="864" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A864" s="3" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
       <c r="B864" s="3"/>
       <c r="C864" s="3">
@@ -31805,7 +32209,7 @@
     </row>
     <row r="865" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A865" s="3" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="B865" s="3"/>
       <c r="C865" s="3">
@@ -31820,21 +32224,27 @@
       <c r="F865" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G865" s="3"/>
+      <c r="G865" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="H865" s="3">
         <v>12</v>
       </c>
       <c r="I865" s="3"/>
       <c r="J865" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K865" s="3"/>
-      <c r="L865" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K865" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L865" s="3" t="s">
+        <v>1392</v>
+      </c>
       <c r="M865" s="3"/>
     </row>
     <row r="866" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A866" s="3" t="s">
-        <v>1388</v>
+        <v>1393</v>
       </c>
       <c r="B866" s="3"/>
       <c r="C866" s="3">
@@ -31849,7 +32259,9 @@
       <c r="F866" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="G866" s="3"/>
+      <c r="G866" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="H866" s="3">
         <v>56</v>
       </c>
@@ -31857,15 +32269,19 @@
         <v>50</v>
       </c>
       <c r="J866" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K866" s="3"/>
-      <c r="L866" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K866" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L866" s="3" t="s">
+        <v>1392</v>
+      </c>
       <c r="M866" s="3"/>
     </row>
     <row r="867" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A867" s="3" t="s">
-        <v>1389</v>
+        <v>1394</v>
       </c>
       <c r="B867" s="3"/>
       <c r="C867" s="3">
@@ -31894,7 +32310,7 @@
     </row>
     <row r="868" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A868" s="3" t="s">
-        <v>1390</v>
+        <v>1395</v>
       </c>
       <c r="B868" s="3"/>
       <c r="C868" s="3">
@@ -31909,21 +32325,27 @@
       <c r="F868" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G868" s="3"/>
+      <c r="G868" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="H868" s="3">
         <v>8</v>
       </c>
       <c r="I868" s="3"/>
       <c r="J868" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K868" s="3"/>
-      <c r="L868" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K868" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L868" s="3" t="s">
+        <v>1392</v>
+      </c>
       <c r="M868" s="3"/>
     </row>
     <row r="869" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A869" s="3" t="s">
-        <v>1391</v>
+        <v>1396</v>
       </c>
       <c r="B869" s="3"/>
       <c r="C869" s="3">
@@ -31938,21 +32360,27 @@
       <c r="F869" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G869" s="3"/>
+      <c r="G869" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="H869" s="3">
         <v>7</v>
       </c>
       <c r="I869" s="3"/>
       <c r="J869" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K869" s="3"/>
-      <c r="L869" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K869" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L869" s="3" t="s">
+        <v>1392</v>
+      </c>
       <c r="M869" s="3"/>
     </row>
     <row r="870" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A870" s="3" t="s">
-        <v>1392</v>
+        <v>1397</v>
       </c>
       <c r="B870" s="3"/>
       <c r="C870" s="3">
@@ -31983,7 +32411,7 @@
     </row>
     <row r="871" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A871" s="3" t="s">
-        <v>1393</v>
+        <v>1398</v>
       </c>
       <c r="B871" s="3"/>
       <c r="C871" s="3">
@@ -32014,7 +32442,7 @@
     </row>
     <row r="872" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A872" s="3" t="s">
-        <v>1394</v>
+        <v>1399</v>
       </c>
       <c r="B872" s="3"/>
       <c r="C872" s="3">
@@ -32045,7 +32473,7 @@
     </row>
     <row r="873" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A873" s="3" t="s">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="B873" s="3"/>
       <c r="C873" s="3">
@@ -32076,7 +32504,7 @@
     </row>
     <row r="874" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A874" s="3" t="s">
-        <v>1396</v>
+        <v>1401</v>
       </c>
       <c r="B874" s="3"/>
       <c r="C874" s="3">
@@ -32107,7 +32535,7 @@
     </row>
     <row r="875" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A875" s="3" t="s">
-        <v>1397</v>
+        <v>1402</v>
       </c>
       <c r="B875" s="3"/>
       <c r="C875" s="3">
@@ -32122,7 +32550,9 @@
       <c r="F875" s="3" t="s">
         <v>1325</v>
       </c>
-      <c r="G875" s="3"/>
+      <c r="G875" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="H875" s="3">
         <v>54</v>
       </c>
@@ -32130,17 +32560,23 @@
         <v>45</v>
       </c>
       <c r="J875" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K875" s="3"/>
-      <c r="L875" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K875" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L875" s="3" t="s">
+        <v>1392</v>
+      </c>
       <c r="M875" s="3"/>
     </row>
     <row r="876" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A876" s="3" t="s">
-        <v>1398</v>
-      </c>
-      <c r="B876" s="3"/>
+        <v>1403</v>
+      </c>
+      <c r="B876" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="C876" s="3">
         <v>31</v>
       </c>
@@ -32153,7 +32589,9 @@
       <c r="F876" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G876" s="3"/>
+      <c r="G876" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="H876" s="3">
         <v>58</v>
       </c>
@@ -32161,15 +32599,19 @@
         <v>45</v>
       </c>
       <c r="J876" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K876" s="3"/>
-      <c r="L876" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K876" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L876" s="3" t="s">
+        <v>1404</v>
+      </c>
       <c r="M876" s="3"/>
     </row>
     <row r="877" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A877" s="3" t="s">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="B877" s="3"/>
       <c r="C877" s="3">
@@ -32184,21 +32626,27 @@
       <c r="F877" s="3" t="s">
         <v>1327</v>
       </c>
-      <c r="G877" s="3"/>
+      <c r="G877" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="H877" s="3">
         <v>30</v>
       </c>
       <c r="I877" s="3"/>
       <c r="J877" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K877" s="3"/>
-      <c r="L877" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K877" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L877" s="3" t="s">
+        <v>1404</v>
+      </c>
       <c r="M877" s="3"/>
     </row>
     <row r="878" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A878" s="3" t="s">
-        <v>1400</v>
+        <v>1406</v>
       </c>
       <c r="B878" s="3"/>
       <c r="C878" s="3">
@@ -32227,7 +32675,7 @@
     </row>
     <row r="879" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A879" s="3" t="s">
-        <v>1401</v>
+        <v>1407</v>
       </c>
       <c r="B879" s="3"/>
       <c r="C879" s="3">
@@ -32258,7 +32706,7 @@
     </row>
     <row r="880" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A880" s="3" t="s">
-        <v>1402</v>
+        <v>1408</v>
       </c>
       <c r="B880" s="3"/>
       <c r="C880" s="3">
@@ -32289,9 +32737,11 @@
     </row>
     <row r="881" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A881" s="3" t="s">
-        <v>1403</v>
-      </c>
-      <c r="B881" s="3"/>
+        <v>1409</v>
+      </c>
+      <c r="B881" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="C881" s="3">
         <v>31</v>
       </c>
@@ -32304,21 +32754,27 @@
       <c r="F881" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G881" s="3"/>
+      <c r="G881" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="H881" s="3">
         <v>44</v>
       </c>
       <c r="I881" s="3"/>
       <c r="J881" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K881" s="3"/>
-      <c r="L881" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="K881" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L881" s="3" t="s">
+        <v>1410</v>
+      </c>
       <c r="M881" s="3"/>
     </row>
     <row r="882" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A882" s="3" t="s">
-        <v>1404</v>
+        <v>1411</v>
       </c>
       <c r="B882" s="3"/>
       <c r="C882" s="3">
@@ -32331,7 +32787,7 @@
         <v>32</v>
       </c>
       <c r="F882" s="3" t="s">
-        <v>1405</v>
+        <v>1412</v>
       </c>
       <c r="G882" s="3"/>
       <c r="H882" s="3">
@@ -32349,7 +32805,7 @@
     </row>
     <row r="883" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A883" s="3" t="s">
-        <v>1406</v>
+        <v>1413</v>
       </c>
       <c r="B883" s="3"/>
       <c r="C883" s="3">
@@ -32380,7 +32836,7 @@
     </row>
     <row r="884" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A884" s="3" t="s">
-        <v>1407</v>
+        <v>1414</v>
       </c>
       <c r="B884" s="3"/>
       <c r="C884" s="3">
@@ -32406,6 +32862,2287 @@
       <c r="K884" s="3"/>
       <c r="L884" s="3"/>
       <c r="M884" s="3"/>
+    </row>
+    <row r="885" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A885" s="3" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B885" s="3"/>
+      <c r="C885" s="3">
+        <v>31</v>
+      </c>
+      <c r="D885" s="3">
+        <v>5571092853</v>
+      </c>
+      <c r="E885" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F885" s="3" t="s">
+        <v>1416</v>
+      </c>
+      <c r="G885" s="3"/>
+      <c r="H885" s="3">
+        <v>25</v>
+      </c>
+      <c r="I885" s="3"/>
+      <c r="J885" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K885" s="3"/>
+      <c r="L885" s="3"/>
+      <c r="M885" s="3"/>
+    </row>
+    <row r="886" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A886" s="3" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B886" s="3"/>
+      <c r="C886" s="3">
+        <v>31</v>
+      </c>
+      <c r="D886" s="3">
+        <v>5571537082</v>
+      </c>
+      <c r="E886" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F886" s="3" t="s">
+        <v>1418</v>
+      </c>
+      <c r="G886" s="3"/>
+      <c r="H886" s="3">
+        <v>72</v>
+      </c>
+      <c r="I886" s="3"/>
+      <c r="J886" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K886" s="3"/>
+      <c r="L886" s="3"/>
+      <c r="M886" s="3"/>
+    </row>
+    <row r="887" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A887" s="3" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B887" s="3"/>
+      <c r="C887" s="3">
+        <v>31</v>
+      </c>
+      <c r="D887" s="3">
+        <v>5571761533</v>
+      </c>
+      <c r="E887" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F887" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G887" s="3"/>
+      <c r="H887" s="3">
+        <v>69</v>
+      </c>
+      <c r="I887" s="3"/>
+      <c r="J887" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K887" s="3"/>
+      <c r="L887" s="3"/>
+      <c r="M887" s="3"/>
+    </row>
+    <row r="888" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A888" s="3" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B888" s="3"/>
+      <c r="C888" s="3">
+        <v>31</v>
+      </c>
+      <c r="D888" s="3">
+        <v>5572127451</v>
+      </c>
+      <c r="E888" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F888" s="3" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G888" s="3"/>
+      <c r="H888" s="3">
+        <v>66</v>
+      </c>
+      <c r="I888" s="3">
+        <v>60</v>
+      </c>
+      <c r="J888" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K888" s="3"/>
+      <c r="L888" s="3"/>
+      <c r="M888" s="3"/>
+    </row>
+    <row r="889" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A889" s="3" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B889" s="3"/>
+      <c r="C889" s="3">
+        <v>31</v>
+      </c>
+      <c r="D889" s="3">
+        <v>5572183488</v>
+      </c>
+      <c r="E889" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F889" s="3" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G889" s="3"/>
+      <c r="H889" s="3">
+        <v>66</v>
+      </c>
+      <c r="I889" s="3">
+        <v>55</v>
+      </c>
+      <c r="J889" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K889" s="3"/>
+      <c r="L889" s="3"/>
+      <c r="M889" s="3"/>
+    </row>
+    <row r="890" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A890" s="3" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B890" s="3"/>
+      <c r="C890" s="3">
+        <v>31</v>
+      </c>
+      <c r="D890" s="3">
+        <v>5572215587</v>
+      </c>
+      <c r="E890" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F890" s="3" t="s">
+        <v>1425</v>
+      </c>
+      <c r="G890" s="3"/>
+      <c r="H890" s="3">
+        <v>66</v>
+      </c>
+      <c r="I890" s="3">
+        <v>60</v>
+      </c>
+      <c r="J890" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K890" s="3"/>
+      <c r="L890" s="3"/>
+      <c r="M890" s="3"/>
+    </row>
+    <row r="891" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A891" s="3" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B891" s="3"/>
+      <c r="C891" s="3">
+        <v>31</v>
+      </c>
+      <c r="D891" s="3">
+        <v>5572222890</v>
+      </c>
+      <c r="E891" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F891" s="3" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G891" s="3"/>
+      <c r="H891" s="3">
+        <v>62</v>
+      </c>
+      <c r="I891" s="3">
+        <v>55</v>
+      </c>
+      <c r="J891" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K891" s="3"/>
+      <c r="L891" s="3"/>
+      <c r="M891" s="3"/>
+    </row>
+    <row r="892" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A892" s="3" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B892" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C892" s="3">
+        <v>31</v>
+      </c>
+      <c r="D892" s="3">
+        <v>5572326311</v>
+      </c>
+      <c r="E892" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F892" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="G892" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H892" s="3">
+        <v>6</v>
+      </c>
+      <c r="I892" s="3"/>
+      <c r="J892" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K892" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L892" s="3" t="s">
+        <v>1430</v>
+      </c>
+      <c r="M892" s="3" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="893" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A893" s="3" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B893" s="3"/>
+      <c r="C893" s="3">
+        <v>31</v>
+      </c>
+      <c r="D893" s="3">
+        <v>5572807518</v>
+      </c>
+      <c r="E893" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F893" s="3" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G893" s="3"/>
+      <c r="H893" s="3">
+        <v>76</v>
+      </c>
+      <c r="I893" s="3"/>
+      <c r="J893" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K893" s="3"/>
+      <c r="L893" s="3"/>
+      <c r="M893" s="3"/>
+    </row>
+    <row r="894" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A894" s="3" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B894" s="3"/>
+      <c r="C894" s="3">
+        <v>31</v>
+      </c>
+      <c r="D894" s="3">
+        <v>5572917191</v>
+      </c>
+      <c r="E894" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F894" s="3" t="s">
+        <v>1435</v>
+      </c>
+      <c r="G894" s="3"/>
+      <c r="H894" s="3">
+        <v>71</v>
+      </c>
+      <c r="I894" s="3"/>
+      <c r="J894" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K894" s="3"/>
+      <c r="L894" s="3"/>
+      <c r="M894" s="3"/>
+    </row>
+    <row r="895" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A895" s="3" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B895" s="3"/>
+      <c r="C895" s="3">
+        <v>31</v>
+      </c>
+      <c r="D895" s="3">
+        <v>5575124805</v>
+      </c>
+      <c r="E895" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F895" s="3" t="s">
+        <v>1437</v>
+      </c>
+      <c r="G895" s="3"/>
+      <c r="H895" s="3">
+        <v>66</v>
+      </c>
+      <c r="I895" s="3">
+        <v>60</v>
+      </c>
+      <c r="J895" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K895" s="3"/>
+      <c r="L895" s="3"/>
+      <c r="M895" s="3"/>
+    </row>
+    <row r="896" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A896" s="3" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B896" s="3"/>
+      <c r="C896" s="3">
+        <v>31</v>
+      </c>
+      <c r="D896" s="3">
+        <v>5575128953</v>
+      </c>
+      <c r="E896" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F896" s="3" t="s">
+        <v>1378</v>
+      </c>
+      <c r="G896" s="3"/>
+      <c r="H896" s="3">
+        <v>67</v>
+      </c>
+      <c r="I896" s="3">
+        <v>60</v>
+      </c>
+      <c r="J896" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K896" s="3"/>
+      <c r="L896" s="3"/>
+      <c r="M896" s="3"/>
+    </row>
+    <row r="897" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A897" s="3" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B897" s="3"/>
+      <c r="C897" s="3">
+        <v>31</v>
+      </c>
+      <c r="D897" s="3">
+        <v>5579336110</v>
+      </c>
+      <c r="E897" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F897" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G897" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H897" s="3"/>
+      <c r="I897" s="3"/>
+      <c r="J897" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K897" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L897" s="3" t="s">
+        <v>1440</v>
+      </c>
+      <c r="M897" s="3"/>
+    </row>
+    <row r="898" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A898" s="3" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B898" s="3"/>
+      <c r="C898" s="3">
+        <v>31</v>
+      </c>
+      <c r="D898" s="3">
+        <v>5579388581</v>
+      </c>
+      <c r="E898" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F898" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="G898" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H898" s="3">
+        <v>50</v>
+      </c>
+      <c r="I898" s="3"/>
+      <c r="J898" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K898" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L898" s="3" t="s">
+        <v>1440</v>
+      </c>
+      <c r="M898" s="3"/>
+    </row>
+    <row r="899" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A899" s="3" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B899" s="3"/>
+      <c r="C899" s="3">
+        <v>31</v>
+      </c>
+      <c r="D899" s="3">
+        <v>5579395653</v>
+      </c>
+      <c r="E899" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F899" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="G899" s="3"/>
+      <c r="H899" s="3">
+        <v>68</v>
+      </c>
+      <c r="I899" s="3">
+        <v>60</v>
+      </c>
+      <c r="J899" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K899" s="3"/>
+      <c r="L899" s="3"/>
+      <c r="M899" s="3"/>
+    </row>
+    <row r="900" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A900" s="3" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B900" s="3"/>
+      <c r="C900" s="3">
+        <v>28</v>
+      </c>
+      <c r="D900" s="3">
+        <v>5579468826</v>
+      </c>
+      <c r="E900" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F900" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="G900" s="3"/>
+      <c r="H900" s="3">
+        <v>49</v>
+      </c>
+      <c r="I900" s="3">
+        <v>35</v>
+      </c>
+      <c r="J900" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K900" s="3"/>
+      <c r="L900" s="3"/>
+      <c r="M900" s="3"/>
+    </row>
+    <row r="901" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A901" s="3" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B901" s="3"/>
+      <c r="C901" s="3">
+        <v>2</v>
+      </c>
+      <c r="D901" s="3">
+        <v>5580343772</v>
+      </c>
+      <c r="E901" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F901" s="3" t="s">
+        <v>1446</v>
+      </c>
+      <c r="G901" s="3"/>
+      <c r="H901" s="3">
+        <v>48</v>
+      </c>
+      <c r="I901" s="3"/>
+      <c r="J901" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K901" s="3"/>
+      <c r="L901" s="3"/>
+      <c r="M901" s="3"/>
+    </row>
+    <row r="902" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A902" s="3" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B902" s="3"/>
+      <c r="C902" s="3">
+        <v>2</v>
+      </c>
+      <c r="D902" s="3">
+        <v>5580349409</v>
+      </c>
+      <c r="E902" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F902" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="G902" s="3"/>
+      <c r="H902" s="3">
+        <v>16</v>
+      </c>
+      <c r="I902" s="3"/>
+      <c r="J902" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K902" s="3"/>
+      <c r="L902" s="3"/>
+      <c r="M902" s="3"/>
+    </row>
+    <row r="903" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A903" s="3" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B903" s="3"/>
+      <c r="C903" s="3">
+        <v>31</v>
+      </c>
+      <c r="D903" s="3">
+        <v>5581952728</v>
+      </c>
+      <c r="E903" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F903" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G903" s="3"/>
+      <c r="H903" s="3">
+        <v>67</v>
+      </c>
+      <c r="I903" s="3">
+        <v>60</v>
+      </c>
+      <c r="J903" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K903" s="3"/>
+      <c r="L903" s="3"/>
+      <c r="M903" s="3"/>
+    </row>
+    <row r="904" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A904" s="3" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B904" s="3"/>
+      <c r="C904" s="3">
+        <v>31</v>
+      </c>
+      <c r="D904" s="3">
+        <v>5581952739</v>
+      </c>
+      <c r="E904" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F904" s="3" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G904" s="3"/>
+      <c r="H904" s="3">
+        <v>66</v>
+      </c>
+      <c r="I904" s="3"/>
+      <c r="J904" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K904" s="3"/>
+      <c r="L904" s="3"/>
+      <c r="M904" s="3"/>
+    </row>
+    <row r="905" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A905" s="3" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B905" s="3"/>
+      <c r="C905" s="3">
+        <v>31</v>
+      </c>
+      <c r="D905" s="3">
+        <v>5582472055</v>
+      </c>
+      <c r="E905" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F905" s="3" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G905" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H905" s="3">
+        <v>12</v>
+      </c>
+      <c r="I905" s="3"/>
+      <c r="J905" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K905" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L905" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="M905" s="3"/>
+    </row>
+    <row r="906" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A906" s="3" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B906" s="3"/>
+      <c r="C906" s="3">
+        <v>31</v>
+      </c>
+      <c r="D906" s="3">
+        <v>5586218333</v>
+      </c>
+      <c r="E906" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F906" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="G906" s="3"/>
+      <c r="H906" s="3">
+        <v>72</v>
+      </c>
+      <c r="I906" s="3">
+        <v>60</v>
+      </c>
+      <c r="J906" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K906" s="3"/>
+      <c r="L906" s="3"/>
+      <c r="M906" s="3"/>
+    </row>
+    <row r="907" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A907" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B907" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C907" s="3">
+        <v>31</v>
+      </c>
+      <c r="D907" s="3">
+        <v>5587470755</v>
+      </c>
+      <c r="E907" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F907" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="G907" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H907" s="3">
+        <v>69</v>
+      </c>
+      <c r="I907" s="3">
+        <v>60</v>
+      </c>
+      <c r="J907" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K907" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L907" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="M907" s="3" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="908" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A908" s="3" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B908" s="3"/>
+      <c r="C908" s="3">
+        <v>28</v>
+      </c>
+      <c r="D908" s="3">
+        <v>5589408066</v>
+      </c>
+      <c r="E908" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F908" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G908" s="3"/>
+      <c r="H908" s="3">
+        <v>72</v>
+      </c>
+      <c r="I908" s="3"/>
+      <c r="J908" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K908" s="3"/>
+      <c r="L908" s="3"/>
+      <c r="M908" s="3"/>
+    </row>
+    <row r="909" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A909" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B909" s="3"/>
+      <c r="C909" s="3">
+        <v>28</v>
+      </c>
+      <c r="D909" s="3">
+        <v>5589653141</v>
+      </c>
+      <c r="E909" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F909" s="3" t="s">
+        <v>1460</v>
+      </c>
+      <c r="G909" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H909" s="3">
+        <v>68</v>
+      </c>
+      <c r="I909" s="3"/>
+      <c r="J909" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K909" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L909" s="3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="M909" s="3"/>
+    </row>
+    <row r="910" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A910" s="3" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B910" s="3"/>
+      <c r="C910" s="3">
+        <v>28</v>
+      </c>
+      <c r="D910" s="3">
+        <v>5589874408</v>
+      </c>
+      <c r="E910" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F910" s="3" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G910" s="3"/>
+      <c r="H910" s="3">
+        <v>70</v>
+      </c>
+      <c r="I910" s="3"/>
+      <c r="J910" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K910" s="3"/>
+      <c r="L910" s="3"/>
+      <c r="M910" s="3"/>
+    </row>
+    <row r="911" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A911" s="3" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B911" s="3"/>
+      <c r="C911" s="3">
+        <v>28</v>
+      </c>
+      <c r="D911" s="3">
+        <v>5590286268</v>
+      </c>
+      <c r="E911" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F911" s="3" t="s">
+        <v>1465</v>
+      </c>
+      <c r="G911" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H911" s="3">
+        <v>36</v>
+      </c>
+      <c r="I911" s="3"/>
+      <c r="J911" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K911" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L911" s="3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="M911" s="3"/>
+    </row>
+    <row r="912" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A912" s="3" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B912" s="3"/>
+      <c r="C912" s="3">
+        <v>28</v>
+      </c>
+      <c r="D912" s="3">
+        <v>5590401744</v>
+      </c>
+      <c r="E912" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F912" s="3" t="s">
+        <v>1467</v>
+      </c>
+      <c r="G912" s="3"/>
+      <c r="H912" s="3">
+        <v>66</v>
+      </c>
+      <c r="I912" s="3">
+        <v>60</v>
+      </c>
+      <c r="J912" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K912" s="3"/>
+      <c r="L912" s="3"/>
+      <c r="M912" s="3"/>
+    </row>
+    <row r="913" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A913" s="3" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B913" s="3"/>
+      <c r="C913" s="3">
+        <v>28</v>
+      </c>
+      <c r="D913" s="3">
+        <v>5590434923</v>
+      </c>
+      <c r="E913" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F913" s="3" t="s">
+        <v>1469</v>
+      </c>
+      <c r="G913" s="3"/>
+      <c r="H913" s="3">
+        <v>66</v>
+      </c>
+      <c r="I913" s="3">
+        <v>60</v>
+      </c>
+      <c r="J913" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K913" s="3"/>
+      <c r="L913" s="3"/>
+      <c r="M913" s="3"/>
+    </row>
+    <row r="914" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A914" s="3" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B914" s="3"/>
+      <c r="C914" s="3">
+        <v>28</v>
+      </c>
+      <c r="D914" s="3">
+        <v>5591455504</v>
+      </c>
+      <c r="E914" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F914" s="3" t="s">
+        <v>1471</v>
+      </c>
+      <c r="G914" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H914" s="3">
+        <v>52</v>
+      </c>
+      <c r="I914" s="3"/>
+      <c r="J914" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K914" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L914" s="3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="M914" s="3"/>
+    </row>
+    <row r="915" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A915" s="3" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B915" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C915" s="3">
+        <v>28</v>
+      </c>
+      <c r="D915" s="3">
+        <v>5591501904</v>
+      </c>
+      <c r="E915" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F915" s="3" t="s">
+        <v>1473</v>
+      </c>
+      <c r="G915" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H915" s="3">
+        <v>60</v>
+      </c>
+      <c r="I915" s="3"/>
+      <c r="J915" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K915" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L915" s="3" t="s">
+        <v>1474</v>
+      </c>
+      <c r="M915" s="3" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="916" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A916" s="3" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B916" s="3"/>
+      <c r="C916" s="3">
+        <v>28</v>
+      </c>
+      <c r="D916" s="3">
+        <v>5591643218</v>
+      </c>
+      <c r="E916" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F916" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="G916" s="3"/>
+      <c r="H916" s="3">
+        <v>75</v>
+      </c>
+      <c r="I916" s="3"/>
+      <c r="J916" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K916" s="3"/>
+      <c r="L916" s="3"/>
+      <c r="M916" s="3"/>
+    </row>
+    <row r="917" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A917" s="3" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B917" s="3"/>
+      <c r="C917" s="3">
+        <v>28</v>
+      </c>
+      <c r="D917" s="3">
+        <v>5593327804</v>
+      </c>
+      <c r="E917" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F917" s="3" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G917" s="3"/>
+      <c r="H917" s="3">
+        <v>63</v>
+      </c>
+      <c r="I917" s="3"/>
+      <c r="J917" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K917" s="3"/>
+      <c r="L917" s="3"/>
+      <c r="M917" s="3"/>
+    </row>
+    <row r="918" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A918" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B918" s="3"/>
+      <c r="C918" s="3">
+        <v>31</v>
+      </c>
+      <c r="D918" s="3">
+        <v>5593943430</v>
+      </c>
+      <c r="E918" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F918" s="3" t="s">
+        <v>1480</v>
+      </c>
+      <c r="G918" s="3"/>
+      <c r="H918" s="3">
+        <v>60</v>
+      </c>
+      <c r="I918" s="3"/>
+      <c r="J918" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K918" s="3"/>
+      <c r="L918" s="3"/>
+      <c r="M918" s="3"/>
+    </row>
+    <row r="919" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A919" s="3" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B919" s="3"/>
+      <c r="C919" s="3">
+        <v>31</v>
+      </c>
+      <c r="D919" s="3">
+        <v>5594045891</v>
+      </c>
+      <c r="E919" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="F919" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G919" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H919" s="3"/>
+      <c r="I919" s="3"/>
+      <c r="J919" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K919" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L919" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M919" s="3"/>
+    </row>
+    <row r="920" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A920" s="3" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B920" s="3"/>
+      <c r="C920" s="3">
+        <v>31</v>
+      </c>
+      <c r="D920" s="3">
+        <v>5594367654</v>
+      </c>
+      <c r="E920" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F920" s="3" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G920" s="3"/>
+      <c r="H920" s="3">
+        <v>44</v>
+      </c>
+      <c r="I920" s="3"/>
+      <c r="J920" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K920" s="3"/>
+      <c r="L920" s="3"/>
+      <c r="M920" s="3"/>
+    </row>
+    <row r="921" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A921" s="3" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B921" s="3"/>
+      <c r="C921" s="3">
+        <v>31</v>
+      </c>
+      <c r="D921" s="3">
+        <v>5595186245</v>
+      </c>
+      <c r="E921" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F921" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G921" s="3"/>
+      <c r="H921" s="3">
+        <v>60</v>
+      </c>
+      <c r="I921" s="3">
+        <v>50</v>
+      </c>
+      <c r="J921" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K921" s="3"/>
+      <c r="L921" s="3"/>
+      <c r="M921" s="3"/>
+    </row>
+    <row r="922" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A922" s="3" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B922" s="3"/>
+      <c r="C922" s="3">
+        <v>31</v>
+      </c>
+      <c r="D922" s="3">
+        <v>5595188712</v>
+      </c>
+      <c r="E922" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F922" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="G922" s="3"/>
+      <c r="H922" s="3">
+        <v>58</v>
+      </c>
+      <c r="I922" s="3">
+        <v>50</v>
+      </c>
+      <c r="J922" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K922" s="3"/>
+      <c r="L922" s="3"/>
+      <c r="M922" s="3"/>
+    </row>
+    <row r="923" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A923" s="3" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B923" s="3"/>
+      <c r="C923" s="3">
+        <v>27</v>
+      </c>
+      <c r="D923" s="3">
+        <v>5596209794</v>
+      </c>
+      <c r="E923" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F923" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G923" s="3"/>
+      <c r="H923" s="3">
+        <v>65</v>
+      </c>
+      <c r="I923" s="3"/>
+      <c r="J923" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K923" s="3"/>
+      <c r="L923" s="3"/>
+      <c r="M923" s="3"/>
+    </row>
+    <row r="924" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A924" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B924" s="3"/>
+      <c r="C924" s="3">
+        <v>27</v>
+      </c>
+      <c r="D924" s="3">
+        <v>5596214789</v>
+      </c>
+      <c r="E924" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F924" s="3" t="s">
+        <v>1490</v>
+      </c>
+      <c r="G924" s="3"/>
+      <c r="H924" s="3">
+        <v>65</v>
+      </c>
+      <c r="I924" s="3"/>
+      <c r="J924" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K924" s="3"/>
+      <c r="L924" s="3"/>
+      <c r="M924" s="3"/>
+    </row>
+    <row r="925" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A925" s="3" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B925" s="3"/>
+      <c r="C925" s="3">
+        <v>27</v>
+      </c>
+      <c r="D925" s="3">
+        <v>5596231688</v>
+      </c>
+      <c r="E925" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F925" s="3" t="s">
+        <v>1492</v>
+      </c>
+      <c r="G925" s="3"/>
+      <c r="H925" s="3">
+        <v>71</v>
+      </c>
+      <c r="I925" s="3"/>
+      <c r="J925" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K925" s="3"/>
+      <c r="L925" s="3"/>
+      <c r="M925" s="3"/>
+    </row>
+    <row r="926" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A926" s="3" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B926" s="3"/>
+      <c r="C926" s="3">
+        <v>27</v>
+      </c>
+      <c r="D926" s="3">
+        <v>5596404789</v>
+      </c>
+      <c r="E926" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F926" s="3" t="s">
+        <v>1494</v>
+      </c>
+      <c r="G926" s="3"/>
+      <c r="H926" s="3">
+        <v>65</v>
+      </c>
+      <c r="I926" s="3"/>
+      <c r="J926" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K926" s="3"/>
+      <c r="L926" s="3"/>
+      <c r="M926" s="3"/>
+    </row>
+    <row r="927" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A927" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B927" s="3"/>
+      <c r="C927" s="3">
+        <v>27</v>
+      </c>
+      <c r="D927" s="3">
+        <v>5596525785</v>
+      </c>
+      <c r="E927" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F927" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="G927" s="3"/>
+      <c r="H927" s="3">
+        <v>70</v>
+      </c>
+      <c r="I927" s="3"/>
+      <c r="J927" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K927" s="3"/>
+      <c r="L927" s="3"/>
+      <c r="M927" s="3"/>
+    </row>
+    <row r="928" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A928" s="3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B928" s="3"/>
+      <c r="C928" s="3">
+        <v>27</v>
+      </c>
+      <c r="D928" s="3">
+        <v>5596559117</v>
+      </c>
+      <c r="E928" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F928" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="G928" s="3"/>
+      <c r="H928" s="3">
+        <v>75</v>
+      </c>
+      <c r="I928" s="3"/>
+      <c r="J928" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K928" s="3"/>
+      <c r="L928" s="3"/>
+      <c r="M928" s="3"/>
+    </row>
+    <row r="929" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A929" s="3" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B929" s="3"/>
+      <c r="C929" s="3">
+        <v>31</v>
+      </c>
+      <c r="D929" s="3">
+        <v>5598828119</v>
+      </c>
+      <c r="E929" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F929" s="3" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G929" s="3"/>
+      <c r="H929" s="3">
+        <v>38</v>
+      </c>
+      <c r="I929" s="3"/>
+      <c r="J929" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K929" s="3"/>
+      <c r="L929" s="3"/>
+      <c r="M929" s="3"/>
+    </row>
+    <row r="930" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A930" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B930" s="3"/>
+      <c r="C930" s="3">
+        <v>31</v>
+      </c>
+      <c r="D930" s="3">
+        <v>5599438255</v>
+      </c>
+      <c r="E930" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F930" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G930" s="3"/>
+      <c r="H930" s="3"/>
+      <c r="I930" s="3"/>
+      <c r="J930" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K930" s="3"/>
+      <c r="L930" s="3"/>
+      <c r="M930" s="3"/>
+    </row>
+    <row r="931" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A931" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B931" s="3"/>
+      <c r="C931" s="3">
+        <v>31</v>
+      </c>
+      <c r="D931" s="3">
+        <v>5599472474</v>
+      </c>
+      <c r="E931" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F931" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G931" s="3"/>
+      <c r="H931" s="3">
+        <v>48</v>
+      </c>
+      <c r="I931" s="3"/>
+      <c r="J931" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K931" s="3"/>
+      <c r="L931" s="3"/>
+      <c r="M931" s="3"/>
+    </row>
+    <row r="932" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A932" s="3" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B932" s="3"/>
+      <c r="C932" s="3">
+        <v>31</v>
+      </c>
+      <c r="D932" s="3">
+        <v>5599479731</v>
+      </c>
+      <c r="E932" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F932" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G932" s="3"/>
+      <c r="H932" s="3">
+        <v>53</v>
+      </c>
+      <c r="I932" s="3"/>
+      <c r="J932" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K932" s="3"/>
+      <c r="L932" s="3"/>
+      <c r="M932" s="3"/>
+    </row>
+    <row r="933" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A933" s="3" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B933" s="3"/>
+      <c r="C933" s="3">
+        <v>31</v>
+      </c>
+      <c r="D933" s="3">
+        <v>5599507438</v>
+      </c>
+      <c r="E933" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="F933" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="G933" s="3"/>
+      <c r="H933" s="3">
+        <v>14</v>
+      </c>
+      <c r="I933" s="3"/>
+      <c r="J933" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K933" s="3"/>
+      <c r="L933" s="3"/>
+      <c r="M933" s="3"/>
+    </row>
+    <row r="934" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A934" s="3" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B934" s="3"/>
+      <c r="C934" s="3">
+        <v>31</v>
+      </c>
+      <c r="D934" s="3">
+        <v>5600257482</v>
+      </c>
+      <c r="E934" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F934" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G934" s="3"/>
+      <c r="H934" s="3">
+        <v>24</v>
+      </c>
+      <c r="I934" s="3"/>
+      <c r="J934" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K934" s="3"/>
+      <c r="L934" s="3"/>
+      <c r="M934" s="3"/>
+    </row>
+    <row r="935" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A935" s="3" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B935" s="3"/>
+      <c r="C935" s="3">
+        <v>28</v>
+      </c>
+      <c r="D935" s="3">
+        <v>5600204569</v>
+      </c>
+      <c r="E935" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F935" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="G935" s="3"/>
+      <c r="H935" s="3">
+        <v>42</v>
+      </c>
+      <c r="I935" s="3"/>
+      <c r="J935" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K935" s="3"/>
+      <c r="L935" s="3"/>
+      <c r="M935" s="3"/>
+    </row>
+    <row r="936" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A936" s="3" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B936" s="3"/>
+      <c r="C936" s="3">
+        <v>31</v>
+      </c>
+      <c r="D936" s="3">
+        <v>5600902908</v>
+      </c>
+      <c r="E936" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F936" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G936" s="3"/>
+      <c r="H936" s="3">
+        <v>30</v>
+      </c>
+      <c r="I936" s="3"/>
+      <c r="J936" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K936" s="3"/>
+      <c r="L936" s="3"/>
+      <c r="M936" s="3"/>
+    </row>
+    <row r="937" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A937" s="3" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B937" s="3"/>
+      <c r="C937" s="3">
+        <v>26</v>
+      </c>
+      <c r="D937" s="3">
+        <v>5600936280</v>
+      </c>
+      <c r="E937" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F937" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G937" s="3"/>
+      <c r="H937" s="3">
+        <v>9</v>
+      </c>
+      <c r="I937" s="3"/>
+      <c r="J937" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K937" s="3"/>
+      <c r="L937" s="3"/>
+      <c r="M937" s="3"/>
+    </row>
+    <row r="938" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A938" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B938" s="3"/>
+      <c r="C938" s="3">
+        <v>26</v>
+      </c>
+      <c r="D938" s="3">
+        <v>5600936284</v>
+      </c>
+      <c r="E938" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F938" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G938" s="3"/>
+      <c r="H938" s="3">
+        <v>12</v>
+      </c>
+      <c r="I938" s="3"/>
+      <c r="J938" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K938" s="3"/>
+      <c r="L938" s="3"/>
+      <c r="M938" s="3"/>
+    </row>
+    <row r="939" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A939" s="3" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B939" s="3"/>
+      <c r="C939" s="3">
+        <v>26</v>
+      </c>
+      <c r="D939" s="3">
+        <v>5600938035</v>
+      </c>
+      <c r="E939" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F939" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G939" s="3"/>
+      <c r="H939" s="3">
+        <v>21</v>
+      </c>
+      <c r="I939" s="3"/>
+      <c r="J939" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K939" s="3"/>
+      <c r="L939" s="3"/>
+      <c r="M939" s="3"/>
+    </row>
+    <row r="940" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A940" s="3" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B940" s="3"/>
+      <c r="C940" s="3">
+        <v>31</v>
+      </c>
+      <c r="D940" s="3">
+        <v>5601985640</v>
+      </c>
+      <c r="E940" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F940" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G940" s="3"/>
+      <c r="H940" s="3">
+        <v>46</v>
+      </c>
+      <c r="I940" s="3"/>
+      <c r="J940" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K940" s="3"/>
+      <c r="L940" s="3"/>
+      <c r="M940" s="3"/>
+    </row>
+    <row r="941" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A941" s="3" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B941" s="3"/>
+      <c r="C941" s="3">
+        <v>31</v>
+      </c>
+      <c r="D941" s="3">
+        <v>5602798488</v>
+      </c>
+      <c r="E941" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F941" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="G941" s="3"/>
+      <c r="H941" s="3">
+        <v>76</v>
+      </c>
+      <c r="I941" s="3"/>
+      <c r="J941" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K941" s="3"/>
+      <c r="L941" s="3"/>
+      <c r="M941" s="3"/>
+    </row>
+    <row r="942" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A942" s="3" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B942" s="3"/>
+      <c r="C942" s="3">
+        <v>31</v>
+      </c>
+      <c r="D942" s="3">
+        <v>5602798494</v>
+      </c>
+      <c r="E942" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F942" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G942" s="3"/>
+      <c r="H942" s="3">
+        <v>75</v>
+      </c>
+      <c r="I942" s="3"/>
+      <c r="J942" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K942" s="3"/>
+      <c r="L942" s="3"/>
+      <c r="M942" s="3"/>
+    </row>
+    <row r="943" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A943" s="3" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B943" s="3"/>
+      <c r="C943" s="3">
+        <v>31</v>
+      </c>
+      <c r="D943" s="3">
+        <v>5602804643</v>
+      </c>
+      <c r="E943" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F943" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G943" s="3"/>
+      <c r="H943" s="3">
+        <v>77</v>
+      </c>
+      <c r="I943" s="3"/>
+      <c r="J943" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K943" s="3"/>
+      <c r="L943" s="3"/>
+      <c r="M943" s="3"/>
+    </row>
+    <row r="944" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A944" s="3" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B944" s="3"/>
+      <c r="C944" s="3">
+        <v>28</v>
+      </c>
+      <c r="D944" s="3">
+        <v>5602978365</v>
+      </c>
+      <c r="E944" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F944" s="3" t="s">
+        <v>1513</v>
+      </c>
+      <c r="G944" s="3"/>
+      <c r="H944" s="3">
+        <v>65</v>
+      </c>
+      <c r="I944" s="3">
+        <v>55</v>
+      </c>
+      <c r="J944" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K944" s="3"/>
+      <c r="L944" s="3"/>
+      <c r="M944" s="3"/>
+    </row>
+    <row r="945" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A945" s="3" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B945" s="3"/>
+      <c r="C945" s="3">
+        <v>26</v>
+      </c>
+      <c r="D945" s="3">
+        <v>5603065320</v>
+      </c>
+      <c r="E945" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F945" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G945" s="3"/>
+      <c r="H945" s="3">
+        <v>27</v>
+      </c>
+      <c r="I945" s="3"/>
+      <c r="J945" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K945" s="3"/>
+      <c r="L945" s="3"/>
+      <c r="M945" s="3"/>
+    </row>
+    <row r="946" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A946" s="3" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B946" s="3"/>
+      <c r="C946" s="3">
+        <v>26</v>
+      </c>
+      <c r="D946" s="3">
+        <v>5603099972</v>
+      </c>
+      <c r="E946" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F946" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="G946" s="3"/>
+      <c r="H946" s="3">
+        <v>74</v>
+      </c>
+      <c r="I946" s="3"/>
+      <c r="J946" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K946" s="3"/>
+      <c r="L946" s="3"/>
+      <c r="M946" s="3"/>
+    </row>
+    <row r="947" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A947" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B947" s="3"/>
+      <c r="C947" s="3">
+        <v>31</v>
+      </c>
+      <c r="D947" s="3">
+        <v>5603546259</v>
+      </c>
+      <c r="E947" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F947" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G947" s="3"/>
+      <c r="H947" s="3">
+        <v>6</v>
+      </c>
+      <c r="I947" s="3"/>
+      <c r="J947" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K947" s="3"/>
+      <c r="L947" s="3"/>
+      <c r="M947" s="3"/>
+    </row>
+    <row r="948" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A948" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B948" s="3"/>
+      <c r="C948" s="3">
+        <v>26</v>
+      </c>
+      <c r="D948" s="3">
+        <v>5603562966</v>
+      </c>
+      <c r="E948" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F948" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G948" s="3"/>
+      <c r="H948" s="3">
+        <v>61</v>
+      </c>
+      <c r="I948" s="3">
+        <v>70</v>
+      </c>
+      <c r="J948" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K948" s="3"/>
+      <c r="L948" s="3"/>
+      <c r="M948" s="3"/>
+    </row>
+    <row r="949" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A949" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B949" s="3"/>
+      <c r="C949" s="3">
+        <v>31</v>
+      </c>
+      <c r="D949" s="3">
+        <v>5603585880</v>
+      </c>
+      <c r="E949" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F949" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G949" s="3"/>
+      <c r="H949" s="3">
+        <v>23</v>
+      </c>
+      <c r="I949" s="3"/>
+      <c r="J949" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K949" s="3"/>
+      <c r="L949" s="3"/>
+      <c r="M949" s="3"/>
+    </row>
+    <row r="950" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A950" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B950" s="3"/>
+      <c r="C950" s="3">
+        <v>26</v>
+      </c>
+      <c r="D950" s="3">
+        <v>5603585214</v>
+      </c>
+      <c r="E950" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F950" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="G950" s="3"/>
+      <c r="H950" s="3">
+        <v>65</v>
+      </c>
+      <c r="I950" s="3"/>
+      <c r="J950" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K950" s="3"/>
+      <c r="L950" s="3"/>
+      <c r="M950" s="3"/>
+    </row>
+    <row r="951" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A951" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B951" s="3"/>
+      <c r="C951" s="3">
+        <v>26</v>
+      </c>
+      <c r="D951" s="3">
+        <v>5603590821</v>
+      </c>
+      <c r="E951" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F951" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="G951" s="3"/>
+      <c r="H951" s="3">
+        <v>59</v>
+      </c>
+      <c r="I951" s="3"/>
+      <c r="J951" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K951" s="3"/>
+      <c r="L951" s="3"/>
+      <c r="M951" s="3"/>
+    </row>
+    <row r="952" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A952" s="3" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B952" s="3"/>
+      <c r="C952" s="3">
+        <v>26</v>
+      </c>
+      <c r="D952" s="3">
+        <v>5603596369</v>
+      </c>
+      <c r="E952" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F952" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G952" s="3"/>
+      <c r="H952" s="3">
+        <v>63</v>
+      </c>
+      <c r="I952" s="3">
+        <v>70</v>
+      </c>
+      <c r="J952" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K952" s="3"/>
+      <c r="L952" s="3"/>
+      <c r="M952" s="3"/>
+    </row>
+    <row r="953" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A953" s="3" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B953" s="3"/>
+      <c r="C953" s="3">
+        <v>31</v>
+      </c>
+      <c r="D953" s="3">
+        <v>5604044749</v>
+      </c>
+      <c r="E953" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F953" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G953" s="3"/>
+      <c r="H953" s="3">
+        <v>21</v>
+      </c>
+      <c r="I953" s="3"/>
+      <c r="J953" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K953" s="3"/>
+      <c r="L953" s="3"/>
+      <c r="M953" s="3"/>
+    </row>
+    <row r="954" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A954" s="3" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B954" s="3"/>
+      <c r="C954" s="3">
+        <v>31</v>
+      </c>
+      <c r="D954" s="3">
+        <v>5604080354</v>
+      </c>
+      <c r="E954" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F954" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="G954" s="3"/>
+      <c r="H954" s="3">
+        <v>25</v>
+      </c>
+      <c r="I954" s="3"/>
+      <c r="J954" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K954" s="3"/>
+      <c r="L954" s="3"/>
+      <c r="M954" s="3"/>
+    </row>
+    <row r="955" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A955" s="3" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B955" s="3"/>
+      <c r="C955" s="3">
+        <v>28</v>
+      </c>
+      <c r="D955" s="3">
+        <v>5604185110</v>
+      </c>
+      <c r="E955" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F955" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G955" s="3"/>
+      <c r="H955" s="3">
+        <v>57</v>
+      </c>
+      <c r="I955" s="3">
+        <v>50</v>
+      </c>
+      <c r="J955" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K955" s="3"/>
+      <c r="L955" s="3"/>
+      <c r="M955" s="3"/>
+    </row>
+    <row r="956" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A956" s="3" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B956" s="3"/>
+      <c r="C956" s="3">
+        <v>31</v>
+      </c>
+      <c r="D956" s="3">
+        <v>5605014359</v>
+      </c>
+      <c r="E956" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F956" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G956" s="3"/>
+      <c r="H956" s="3">
+        <v>73</v>
+      </c>
+      <c r="I956" s="3">
+        <v>60</v>
+      </c>
+      <c r="J956" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K956" s="3"/>
+      <c r="L956" s="3"/>
+      <c r="M956" s="3"/>
+    </row>
+    <row r="957" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A957" s="3" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B957" s="3"/>
+      <c r="C957" s="3">
+        <v>31</v>
+      </c>
+      <c r="D957" s="3">
+        <v>5605186618</v>
+      </c>
+      <c r="E957" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F957" s="3" t="s">
+        <v>1525</v>
+      </c>
+      <c r="G957" s="3"/>
+      <c r="H957" s="3">
+        <v>30</v>
+      </c>
+      <c r="I957" s="3"/>
+      <c r="J957" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K957" s="3"/>
+      <c r="L957" s="3"/>
+      <c r="M957" s="3"/>
+    </row>
+    <row r="958" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A958" s="3" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B958" s="3"/>
+      <c r="C958" s="3">
+        <v>31</v>
+      </c>
+      <c r="D958" s="3">
+        <v>5605275160</v>
+      </c>
+      <c r="E958" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F958" s="3" t="s">
+        <v>1527</v>
+      </c>
+      <c r="G958" s="3"/>
+      <c r="H958" s="3">
+        <v>65</v>
+      </c>
+      <c r="I958" s="3"/>
+      <c r="J958" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K958" s="3"/>
+      <c r="L958" s="3"/>
+      <c r="M958" s="3"/>
+    </row>
+    <row r="959" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A959" s="3" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B959" s="3"/>
+      <c r="C959" s="3">
+        <v>31</v>
+      </c>
+      <c r="D959" s="3">
+        <v>5605281671</v>
+      </c>
+      <c r="E959" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F959" s="3" t="s">
+        <v>1529</v>
+      </c>
+      <c r="G959" s="3"/>
+      <c r="H959" s="3">
+        <v>75</v>
+      </c>
+      <c r="I959" s="3"/>
+      <c r="J959" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K959" s="3"/>
+      <c r="L959" s="3"/>
+      <c r="M959" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Curtis Garage- TS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Curtis-Garage-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EEA3C08-2F63-4C1E-8A6C-AA876B9B34EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3538CBBB-468A-4A06-848D-F0CE914019F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1215" windowWidth="21930" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3240" yWindow="3240" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9888" uniqueCount="4100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10600" uniqueCount="4363">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -12148,6 +12148,9 @@
     <t>39.703040, -86.710480</t>
   </si>
   <si>
+    <t>06/15/26 09:05 EDT</t>
+  </si>
+  <si>
     <t>06/12/26 10:48 EDT</t>
   </si>
   <si>
@@ -12301,6 +12304,12 @@
     <t>39.499443, -86.648620</t>
   </si>
   <si>
+    <t>06/15/26 09:07 EDT</t>
+  </si>
+  <si>
+    <t>06/15/26 09:08 EDT</t>
+  </si>
+  <si>
     <t>06/14/26 13:26 EDT</t>
   </si>
   <si>
@@ -12320,6 +12329,786 @@
   </si>
   <si>
     <t>39.643955, -86.850746</t>
+  </si>
+  <si>
+    <t>06/14/26 16:34 EDT</t>
+  </si>
+  <si>
+    <t>4mi SE of Plainfield IN</t>
+  </si>
+  <si>
+    <t>39.661667, -86.311160</t>
+  </si>
+  <si>
+    <t>06/14/26 16:48 EDT</t>
+  </si>
+  <si>
+    <t>2mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>39.593760, -86.403820</t>
+  </si>
+  <si>
+    <t>06/14/26 17:08 EDT</t>
+  </si>
+  <si>
+    <t>39.542877, -86.641490</t>
+  </si>
+  <si>
+    <t>06/14/26 17:09 EDT</t>
+  </si>
+  <si>
+    <t>39.557304, -86.646350</t>
+  </si>
+  <si>
+    <t>06/14/26 17:13 EDT</t>
+  </si>
+  <si>
+    <t>12.3mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>39.579200, -86.598040</t>
+  </si>
+  <si>
+    <t>06/14/26 17:52 EDT</t>
+  </si>
+  <si>
+    <t>39.608505, -86.496500</t>
+  </si>
+  <si>
+    <t>06/15/26 09:09 EDT</t>
+  </si>
+  <si>
+    <t>39.607525, -86.499520</t>
+  </si>
+  <si>
+    <t>06/14/26 18:16 EDT</t>
+  </si>
+  <si>
+    <t>39.568607, -86.633095</t>
+  </si>
+  <si>
+    <t>06/15/26 05:06 EDT</t>
+  </si>
+  <si>
+    <t>39.690994, -86.715170</t>
+  </si>
+  <si>
+    <t>06/15/26 06:05 EDT</t>
+  </si>
+  <si>
+    <t>39.539670, -86.756690</t>
+  </si>
+  <si>
+    <t>06/15/26 06:32 EDT</t>
+  </si>
+  <si>
+    <t>9mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.515057, -86.807465</t>
+  </si>
+  <si>
+    <t>06/15/26 06:33 EDT</t>
+  </si>
+  <si>
+    <t>9.3mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.513760, -86.794290</t>
+  </si>
+  <si>
+    <t>06/15/26 06:35 EDT</t>
+  </si>
+  <si>
+    <t>10.4mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.500600, -86.780250</t>
+  </si>
+  <si>
+    <t>06/15/26 06:37 EDT</t>
+  </si>
+  <si>
+    <t>39.667940, -86.370670</t>
+  </si>
+  <si>
+    <t>06/15/26 06:41 EDT</t>
+  </si>
+  <si>
+    <t>39.499370, -86.661330</t>
+  </si>
+  <si>
+    <t>06/15/26 07:06 EDT</t>
+  </si>
+  <si>
+    <t>11.6mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.561630, -86.650760</t>
+  </si>
+  <si>
+    <t>06/15/26 07:08 EDT</t>
+  </si>
+  <si>
+    <t>39.552990, -86.701270</t>
+  </si>
+  <si>
+    <t>06/15/26 07:16 EDT</t>
+  </si>
+  <si>
+    <t>39.562477, -86.647480</t>
+  </si>
+  <si>
+    <t>06/15/26 07:18 EDT</t>
+  </si>
+  <si>
+    <t>39.556230, -86.682430</t>
+  </si>
+  <si>
+    <t>06/15/26 07:44 EDT</t>
+  </si>
+  <si>
+    <t>4.7mi NW of Mooresville IN</t>
+  </si>
+  <si>
+    <t>39.629395, -86.448160</t>
+  </si>
+  <si>
+    <t>06/15/26 07:46 EDT</t>
+  </si>
+  <si>
+    <t>39.608177, -86.497370</t>
+  </si>
+  <si>
+    <t>06/16/26 08:55 EDT</t>
+  </si>
+  <si>
+    <t>06/17/26 10:00 EDT</t>
+  </si>
+  <si>
+    <t>06/15/26 07:47 EDT</t>
+  </si>
+  <si>
+    <t>39.605020, -86.506580</t>
+  </si>
+  <si>
+    <t>39.600174, -86.518810</t>
+  </si>
+  <si>
+    <t>06/15/26 07:54 EDT</t>
+  </si>
+  <si>
+    <t>39.589510, -86.558750</t>
+  </si>
+  <si>
+    <t>06/15/26 08:00 EDT</t>
+  </si>
+  <si>
+    <t>39.546234, -86.728600</t>
+  </si>
+  <si>
+    <t>06/15/26 08:47 EDT</t>
+  </si>
+  <si>
+    <t>39.699530, -86.313260</t>
+  </si>
+  <si>
+    <t>06/15/26 08:52 EDT</t>
+  </si>
+  <si>
+    <t>39.714910, -86.269730</t>
+  </si>
+  <si>
+    <t>06/15/26 11:15 EDT</t>
+  </si>
+  <si>
+    <t>39.679028, -86.368980</t>
+  </si>
+  <si>
+    <t>06/15/26 13:34 EDT</t>
+  </si>
+  <si>
+    <t>39.678810, -86.343460</t>
+  </si>
+  <si>
+    <t>06/16/26 04:44 EDT</t>
+  </si>
+  <si>
+    <t>39.535740, -86.574420</t>
+  </si>
+  <si>
+    <t>06/17/26 08:02 EDT</t>
+  </si>
+  <si>
+    <t>06/17/26 08:41 EDT</t>
+  </si>
+  <si>
+    <t>06/16/26 04:48 EDT</t>
+  </si>
+  <si>
+    <t>39.564830, -86.606310</t>
+  </si>
+  <si>
+    <t>06/16/26 07:30 EDT</t>
+  </si>
+  <si>
+    <t>06/16/26 07:33 EDT</t>
+  </si>
+  <si>
+    <t>39.572200, -86.669846</t>
+  </si>
+  <si>
+    <t>06/16/26 07:35 EDT</t>
+  </si>
+  <si>
+    <t>39.579430, -86.654030</t>
+  </si>
+  <si>
+    <t>06/16/26 07:36 EDT</t>
+  </si>
+  <si>
+    <t>11.7mi E of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.579410, -86.637580</t>
+  </si>
+  <si>
+    <t>06/16/26 08:01 EDT</t>
+  </si>
+  <si>
+    <t>39.627758, -86.449455</t>
+  </si>
+  <si>
+    <t>06/17/26 08:03 EDT</t>
+  </si>
+  <si>
+    <t>06/16/26 08:21 EDT</t>
+  </si>
+  <si>
+    <t>39.710330, -86.371090</t>
+  </si>
+  <si>
+    <t>06/16/26 08:34 EDT</t>
+  </si>
+  <si>
+    <t>1.3mi E of Plainfield IN</t>
+  </si>
+  <si>
+    <t>39.696266, -86.346500</t>
+  </si>
+  <si>
+    <t>06/16/26 09:05 EDT</t>
+  </si>
+  <si>
+    <t>39.579010, -86.479485</t>
+  </si>
+  <si>
+    <t>06/16/26 11:05 EDT</t>
+  </si>
+  <si>
+    <t>39.521313, -86.564120</t>
+  </si>
+  <si>
+    <t>06/16/26 11:31 EDT</t>
+  </si>
+  <si>
+    <t>39.439507, -86.406080</t>
+  </si>
+  <si>
+    <t>06/16/26 13:49 EDT</t>
+  </si>
+  <si>
+    <t>39.439620, -86.406200</t>
+  </si>
+  <si>
+    <t>06/16/26 14:36 EDT</t>
+  </si>
+  <si>
+    <t>39.564820, -86.605550</t>
+  </si>
+  <si>
+    <t>06/16/26 18:40 EDT</t>
+  </si>
+  <si>
+    <t>39.594055, -86.537315</t>
+  </si>
+  <si>
+    <t>06/17/26 08:05 EDT</t>
+  </si>
+  <si>
+    <t>06/16/26 18:59 EDT</t>
+  </si>
+  <si>
+    <t>39.593460, -86.626820</t>
+  </si>
+  <si>
+    <t>06/16/26 19:07 EDT</t>
+  </si>
+  <si>
+    <t>39.645480, -86.669940</t>
+  </si>
+  <si>
+    <t>06/16/26 20:54 EDT</t>
+  </si>
+  <si>
+    <t>39.717150, -86.669980</t>
+  </si>
+  <si>
+    <t>06/16/26 20:55 EDT</t>
+  </si>
+  <si>
+    <t>39.710200, -86.669830</t>
+  </si>
+  <si>
+    <t>06/16/26 21:00 EDT</t>
+  </si>
+  <si>
+    <t>39.656330, -86.669560</t>
+  </si>
+  <si>
+    <t>06/16/26 21:01 EDT</t>
+  </si>
+  <si>
+    <t>39.630463, -86.670020</t>
+  </si>
+  <si>
+    <t>06/16/26 21:02 EDT</t>
+  </si>
+  <si>
+    <t>39.628113, -86.670090</t>
+  </si>
+  <si>
+    <t>06/16/26 21:13 EDT</t>
+  </si>
+  <si>
+    <t>39.564990, -86.631940</t>
+  </si>
+  <si>
+    <t>06/16/26 23:30 EDT</t>
+  </si>
+  <si>
+    <t>39.525860, -86.809740</t>
+  </si>
+  <si>
+    <t>06/17/26 07:24 EDT</t>
+  </si>
+  <si>
+    <t>39.583740, -86.631960</t>
+  </si>
+  <si>
+    <t>06/17/26 08:06 EDT</t>
+  </si>
+  <si>
+    <t>06/17/26 07:44 EDT</t>
+  </si>
+  <si>
+    <t>39.523544, -86.810450</t>
+  </si>
+  <si>
+    <t>06/17/26 09:11 EDT</t>
+  </si>
+  <si>
+    <t>39.706093, -86.269220</t>
+  </si>
+  <si>
+    <t>06/17/26 12:05 EDT</t>
+  </si>
+  <si>
+    <t>39.556930, -86.678406</t>
+  </si>
+  <si>
+    <t>06/17/26 13:03 EDT</t>
+  </si>
+  <si>
+    <t>1.9mi NW of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.656620, -86.873840</t>
+  </si>
+  <si>
+    <t>06/17/26 15:32 EDT</t>
+  </si>
+  <si>
+    <t>06/17/26 13:24 EDT</t>
+  </si>
+  <si>
+    <t>39.557480, -86.589670</t>
+  </si>
+  <si>
+    <t>06/18/26 08:53 EDT</t>
+  </si>
+  <si>
+    <t>06/17/26 13:27 EDT</t>
+  </si>
+  <si>
+    <t>39.542923, -86.564050</t>
+  </si>
+  <si>
+    <t>06/17/26 13:39 EDT</t>
+  </si>
+  <si>
+    <t>39.556164, -86.682860</t>
+  </si>
+  <si>
+    <t>06/17/26 13:50 EDT</t>
+  </si>
+  <si>
+    <t>39.564820, -86.593980</t>
+  </si>
+  <si>
+    <t>06/18/26 08:54 EDT</t>
+  </si>
+  <si>
+    <t>06/17/26 13:51 EDT</t>
+  </si>
+  <si>
+    <t>39.630287, -86.670160</t>
+  </si>
+  <si>
+    <t>06/17/26 13:56 EDT</t>
+  </si>
+  <si>
+    <t>39.595688, -86.530525</t>
+  </si>
+  <si>
+    <t>06/17/26 15:33 EDT</t>
+  </si>
+  <si>
+    <t>06/17/26 13:58 EDT</t>
+  </si>
+  <si>
+    <t>9mi NW of Martinsville IN</t>
+  </si>
+  <si>
+    <t>39.518010, -86.534110</t>
+  </si>
+  <si>
+    <t>06/17/26 14:10 EDT</t>
+  </si>
+  <si>
+    <t>06/17/26 14:11 EDT</t>
+  </si>
+  <si>
+    <t>39.572144, -86.617775</t>
+  </si>
+  <si>
+    <t>06/17/26 14:13 EDT</t>
+  </si>
+  <si>
+    <t>39.572113, -86.589676</t>
+  </si>
+  <si>
+    <t>06/17/26 14:16 EDT</t>
+  </si>
+  <si>
+    <t>3.1mi SW of Bloomington IN</t>
+  </si>
+  <si>
+    <t>39.137440, -86.572860</t>
+  </si>
+  <si>
+    <t>06/17/26 14:17 EDT</t>
+  </si>
+  <si>
+    <t>8.7mi NW of Martinsville IN</t>
+  </si>
+  <si>
+    <t>39.519250, -86.523350</t>
+  </si>
+  <si>
+    <t>06/17/26 14:25 EDT</t>
+  </si>
+  <si>
+    <t>39.564735, -86.589590</t>
+  </si>
+  <si>
+    <t>06/17/26 14:27 EDT</t>
+  </si>
+  <si>
+    <t>39.564870, -86.617540</t>
+  </si>
+  <si>
+    <t>06/17/26 14:49 EDT</t>
+  </si>
+  <si>
+    <t>06/17/26 14:50 EDT</t>
+  </si>
+  <si>
+    <t>39.564840, -86.618550</t>
+  </si>
+  <si>
+    <t>06/18/26 08:55 EDT</t>
+  </si>
+  <si>
+    <t>06/17/26 14:54 EDT</t>
+  </si>
+  <si>
+    <t>39.535670, -86.583050</t>
+  </si>
+  <si>
+    <t>06/17/26 14:56 EDT</t>
+  </si>
+  <si>
+    <t>39.525200, -86.564080</t>
+  </si>
+  <si>
+    <t>06/17/26 15:00 EDT</t>
+  </si>
+  <si>
+    <t>39.491430, -86.575380</t>
+  </si>
+  <si>
+    <t>6.3mi N of Martinsville IN</t>
+  </si>
+  <si>
+    <t>39.505190, -86.420300</t>
+  </si>
+  <si>
+    <t>06/17/26 16:30 EDT</t>
+  </si>
+  <si>
+    <t>39.578995, -86.479485</t>
+  </si>
+  <si>
+    <t>06/18/26 08:56 EDT</t>
+  </si>
+  <si>
+    <t>06/17/26 16:32 EDT</t>
+  </si>
+  <si>
+    <t>39.578990, -86.500470</t>
+  </si>
+  <si>
+    <t>06/17/26 16:35 EDT</t>
+  </si>
+  <si>
+    <t>39.579320, -86.561930</t>
+  </si>
+  <si>
+    <t>06/17/26 21:42 EDT</t>
+  </si>
+  <si>
+    <t>39.572110, -86.706250</t>
+  </si>
+  <si>
+    <t>06/18/26 08:24 EDT</t>
+  </si>
+  <si>
+    <t>39.579440, -86.659110</t>
+  </si>
+  <si>
+    <t>06/18/26 08:25 EDT</t>
+  </si>
+  <si>
+    <t>39.579420, -86.642380</t>
+  </si>
+  <si>
+    <t>06/18/26 11:18 EDT</t>
+  </si>
+  <si>
+    <t>39.538890, -86.762720</t>
+  </si>
+  <si>
+    <t>06/18/26 13:15 EDT</t>
+  </si>
+  <si>
+    <t>39.557583, -86.646410</t>
+  </si>
+  <si>
+    <t>06/19/26 08:34 EDT</t>
+  </si>
+  <si>
+    <t>06/18/26 13:27 EDT</t>
+  </si>
+  <si>
+    <t>39.533200, -86.641490</t>
+  </si>
+  <si>
+    <t>06/19/26 08:36 EDT</t>
+  </si>
+  <si>
+    <t>06/18/26 13:31 EDT</t>
+  </si>
+  <si>
+    <t>39.521328, -86.641400</t>
+  </si>
+  <si>
+    <t>06/18/26 15:52 EDT</t>
+  </si>
+  <si>
+    <t>39.731277, -86.523544</t>
+  </si>
+  <si>
+    <t>06/18/26 16:01 EDT</t>
+  </si>
+  <si>
+    <t>39.533775, -86.788160</t>
+  </si>
+  <si>
+    <t>06/19/26 08:37 EDT</t>
+  </si>
+  <si>
+    <t>06/19/26 08:38 EDT</t>
+  </si>
+  <si>
+    <t>06/18/26 16:11 EDT</t>
+  </si>
+  <si>
+    <t>39.486990, -86.998830</t>
+  </si>
+  <si>
+    <t>06/18/26 16:13 EDT</t>
+  </si>
+  <si>
+    <t>5.4mi SE of Brazil IN</t>
+  </si>
+  <si>
+    <t>39.466150, -87.055176</t>
+  </si>
+  <si>
+    <t>06/19/26 08:40 EDT</t>
+  </si>
+  <si>
+    <t>06/18/26 16:15 EDT</t>
+  </si>
+  <si>
+    <t>4.8mi SE of Brazil IN</t>
+  </si>
+  <si>
+    <t>39.459250, -87.086360</t>
+  </si>
+  <si>
+    <t>06/18/26 18:24 EDT</t>
+  </si>
+  <si>
+    <t>39.689518, -86.666120</t>
+  </si>
+  <si>
+    <t>06/18/26 19:29 EDT</t>
+  </si>
+  <si>
+    <t>39.678967, -86.369000</t>
+  </si>
+  <si>
+    <t>06/18/26 20:28 EDT</t>
+  </si>
+  <si>
+    <t>3.2mi W of Plainfield IN</t>
+  </si>
+  <si>
+    <t>39.692608, -86.431520</t>
+  </si>
+  <si>
+    <t>06/19/26 05:20 EDT</t>
+  </si>
+  <si>
+    <t>39.523525, -86.810090</t>
+  </si>
+  <si>
+    <t>06/19/26 07:23 EDT</t>
+  </si>
+  <si>
+    <t>39.717247, -86.682976</t>
+  </si>
+  <si>
+    <t>06/19/26 09:52 EDT</t>
+  </si>
+  <si>
+    <t>39.588272, -86.563440</t>
+  </si>
+  <si>
+    <t>06/19/26 17:27 EDT</t>
+  </si>
+  <si>
+    <t>39.564860, -86.620670</t>
+  </si>
+  <si>
+    <t>06/19/26 17:28 EDT</t>
+  </si>
+  <si>
+    <t>39.564810, -86.598630</t>
+  </si>
+  <si>
+    <t>06/19/26 17:32 EDT</t>
+  </si>
+  <si>
+    <t>39.535720, -86.568670</t>
+  </si>
+  <si>
+    <t>06/19/26 17:33 EDT</t>
+  </si>
+  <si>
+    <t>39.530600, -86.564040</t>
+  </si>
+  <si>
+    <t>06/19/26 19:35 EDT</t>
+  </si>
+  <si>
+    <t>39.535690, -86.578450</t>
+  </si>
+  <si>
+    <t>06/20/26 09:46 EDT</t>
+  </si>
+  <si>
+    <t>39.568615, -86.632840</t>
+  </si>
+  <si>
+    <t>06/20/26 21:27 EDT</t>
+  </si>
+  <si>
+    <t>7.2mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.558220, -86.764760</t>
+  </si>
+  <si>
+    <t>06/20/26 21:37 EDT</t>
+  </si>
+  <si>
+    <t>39.545850, -86.729060</t>
+  </si>
+  <si>
+    <t>06/20/26 21:43 EDT</t>
+  </si>
+  <si>
+    <t>39.536736, -86.773770</t>
+  </si>
+  <si>
+    <t>06/20/26 21:52 EDT</t>
+  </si>
+  <si>
+    <t>39.530563, -86.802990</t>
+  </si>
+  <si>
+    <t>06/20/26 21:54 EDT</t>
+  </si>
+  <si>
+    <t>39.532730, -86.802720</t>
+  </si>
+  <si>
+    <t>06/21/26 00:16 EDT</t>
+  </si>
+  <si>
+    <t>39.572190, -86.700300</t>
+  </si>
+  <si>
+    <t>06/21/26 01:41 EDT</t>
+  </si>
+  <si>
+    <t>39.528000, -86.877240</t>
+  </si>
+  <si>
+    <t>06/21/26 05:14 EDT</t>
+  </si>
+  <si>
+    <t>39.505913, -86.549560</t>
+  </si>
+  <si>
+    <t>06/21/26 05:15 EDT</t>
+  </si>
+  <si>
+    <t>39.506153, -86.563550</t>
   </si>
 </sst>
 </file>
@@ -12681,10 +13470,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1622"/>
+  <dimension ref="A1:N1736"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="14" width="15" customWidth="1"/>
+    <col min="1" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="14" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -68105,21 +68896,27 @@
       <c r="G1597" s="3" t="s">
         <v>4041</v>
       </c>
-      <c r="H1597" s="3"/>
+      <c r="H1597" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1597" s="3">
         <v>51</v>
       </c>
       <c r="J1597" s="3"/>
       <c r="K1597" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1597" s="3"/>
-      <c r="M1597" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1597" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1597" s="3" t="s">
+        <v>4042</v>
+      </c>
       <c r="N1597" s="3"/>
     </row>
     <row r="1598" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1598" s="3" t="s">
-        <v>4042</v>
+        <v>4043</v>
       </c>
       <c r="B1598" s="3"/>
       <c r="C1598" s="3">
@@ -68132,10 +68929,10 @@
         <v>17</v>
       </c>
       <c r="F1598" s="3" t="s">
-        <v>4043</v>
+        <v>4044</v>
       </c>
       <c r="G1598" s="3" t="s">
-        <v>4044</v>
+        <v>4045</v>
       </c>
       <c r="H1598" s="3"/>
       <c r="I1598" s="3">
@@ -68153,7 +68950,7 @@
     </row>
     <row r="1599" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1599" s="3" t="s">
-        <v>4045</v>
+        <v>4046</v>
       </c>
       <c r="B1599" s="3"/>
       <c r="C1599" s="3">
@@ -68166,10 +68963,10 @@
         <v>17</v>
       </c>
       <c r="F1599" s="3" t="s">
-        <v>4046</v>
+        <v>4047</v>
       </c>
       <c r="G1599" s="3" t="s">
-        <v>4047</v>
+        <v>4048</v>
       </c>
       <c r="H1599" s="3"/>
       <c r="I1599" s="3">
@@ -68187,7 +68984,7 @@
     </row>
     <row r="1600" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1600" s="3" t="s">
-        <v>4048</v>
+        <v>4049</v>
       </c>
       <c r="B1600" s="3"/>
       <c r="C1600" s="3">
@@ -68200,10 +68997,10 @@
         <v>46</v>
       </c>
       <c r="F1600" s="3" t="s">
-        <v>4049</v>
+        <v>4050</v>
       </c>
       <c r="G1600" s="3" t="s">
-        <v>4050</v>
+        <v>4051</v>
       </c>
       <c r="H1600" s="3"/>
       <c r="I1600" s="3">
@@ -68219,7 +69016,7 @@
     </row>
     <row r="1601" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1601" s="3" t="s">
-        <v>4051</v>
+        <v>4052</v>
       </c>
       <c r="B1601" s="3"/>
       <c r="C1601" s="3">
@@ -68232,10 +69029,10 @@
         <v>17</v>
       </c>
       <c r="F1601" s="3" t="s">
-        <v>4052</v>
+        <v>4053</v>
       </c>
       <c r="G1601" s="3" t="s">
-        <v>4053</v>
+        <v>4054</v>
       </c>
       <c r="H1601" s="3"/>
       <c r="I1601" s="3">
@@ -68253,7 +69050,7 @@
     </row>
     <row r="1602" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1602" s="3" t="s">
-        <v>4054</v>
+        <v>4055</v>
       </c>
       <c r="B1602" s="3"/>
       <c r="C1602" s="3">
@@ -68269,7 +69066,7 @@
         <v>253</v>
       </c>
       <c r="G1602" s="3" t="s">
-        <v>4055</v>
+        <v>4056</v>
       </c>
       <c r="H1602" s="3"/>
       <c r="I1602" s="3">
@@ -68287,7 +69084,7 @@
     </row>
     <row r="1603" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1603" s="3" t="s">
-        <v>4056</v>
+        <v>4057</v>
       </c>
       <c r="B1603" s="3"/>
       <c r="C1603" s="3">
@@ -68303,7 +69100,7 @@
         <v>40</v>
       </c>
       <c r="G1603" s="3" t="s">
-        <v>4057</v>
+        <v>4058</v>
       </c>
       <c r="H1603" s="3"/>
       <c r="I1603" s="3">
@@ -68319,7 +69116,7 @@
     </row>
     <row r="1604" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1604" s="3" t="s">
-        <v>4058</v>
+        <v>4059</v>
       </c>
       <c r="B1604" s="3"/>
       <c r="C1604" s="3">
@@ -68335,7 +69132,7 @@
         <v>557</v>
       </c>
       <c r="G1604" s="3" t="s">
-        <v>4059</v>
+        <v>4060</v>
       </c>
       <c r="H1604" s="3"/>
       <c r="I1604" s="3">
@@ -68351,7 +69148,7 @@
     </row>
     <row r="1605" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1605" s="3" t="s">
-        <v>4060</v>
+        <v>4061</v>
       </c>
       <c r="B1605" s="3"/>
       <c r="C1605" s="3">
@@ -68367,23 +69164,29 @@
         <v>319</v>
       </c>
       <c r="G1605" s="3" t="s">
-        <v>4061</v>
-      </c>
-      <c r="H1605" s="3"/>
+        <v>4062</v>
+      </c>
+      <c r="H1605" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1605" s="3">
         <v>52</v>
       </c>
       <c r="J1605" s="3"/>
       <c r="K1605" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1605" s="3"/>
-      <c r="M1605" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1605" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1605" s="3" t="s">
+        <v>4042</v>
+      </c>
       <c r="N1605" s="3"/>
     </row>
     <row r="1606" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1606" s="3" t="s">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="B1606" s="3"/>
       <c r="C1606" s="3">
@@ -68399,7 +69202,7 @@
         <v>681</v>
       </c>
       <c r="G1606" s="3" t="s">
-        <v>4063</v>
+        <v>4064</v>
       </c>
       <c r="H1606" s="3"/>
       <c r="I1606" s="3">
@@ -68417,7 +69220,7 @@
     </row>
     <row r="1607" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1607" s="3" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="B1607" s="3"/>
       <c r="C1607" s="3">
@@ -68433,7 +69236,7 @@
         <v>3281</v>
       </c>
       <c r="G1607" s="3" t="s">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="H1607" s="3"/>
       <c r="I1607" s="3">
@@ -68451,7 +69254,7 @@
     </row>
     <row r="1608" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1608" s="3" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="B1608" s="3"/>
       <c r="C1608" s="3">
@@ -68467,7 +69270,7 @@
         <v>2197</v>
       </c>
       <c r="G1608" s="3" t="s">
-        <v>4067</v>
+        <v>4068</v>
       </c>
       <c r="H1608" s="3"/>
       <c r="I1608" s="3">
@@ -68485,9 +69288,11 @@
     </row>
     <row r="1609" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1609" s="3" t="s">
-        <v>4068</v>
-      </c>
-      <c r="B1609" s="3"/>
+        <v>4069</v>
+      </c>
+      <c r="B1609" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="C1609" s="3">
         <v>31</v>
       </c>
@@ -68498,12 +69303,14 @@
         <v>17</v>
       </c>
       <c r="F1609" s="3" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
       <c r="G1609" s="3" t="s">
-        <v>4070</v>
-      </c>
-      <c r="H1609" s="3"/>
+        <v>4071</v>
+      </c>
+      <c r="H1609" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1609" s="3">
         <v>65</v>
       </c>
@@ -68511,15 +69318,19 @@
         <v>50</v>
       </c>
       <c r="K1609" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1609" s="3"/>
-      <c r="M1609" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1609" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1609" s="3" t="s">
+        <v>4042</v>
+      </c>
       <c r="N1609" s="3"/>
     </row>
     <row r="1610" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1610" s="3" t="s">
-        <v>4071</v>
+        <v>4072</v>
       </c>
       <c r="B1610" s="3"/>
       <c r="C1610" s="3">
@@ -68532,10 +69343,10 @@
         <v>17</v>
       </c>
       <c r="F1610" s="3" t="s">
-        <v>4072</v>
+        <v>4073</v>
       </c>
       <c r="G1610" s="3" t="s">
-        <v>4073</v>
+        <v>4074</v>
       </c>
       <c r="H1610" s="3"/>
       <c r="I1610" s="3">
@@ -68553,7 +69364,7 @@
     </row>
     <row r="1611" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1611" s="3" t="s">
-        <v>4074</v>
+        <v>4075</v>
       </c>
       <c r="B1611" s="3"/>
       <c r="C1611" s="3">
@@ -68566,10 +69377,10 @@
         <v>17</v>
       </c>
       <c r="F1611" s="3" t="s">
-        <v>4075</v>
+        <v>4076</v>
       </c>
       <c r="G1611" s="3" t="s">
-        <v>4076</v>
+        <v>4077</v>
       </c>
       <c r="H1611" s="3"/>
       <c r="I1611" s="3">
@@ -68587,7 +69398,7 @@
     </row>
     <row r="1612" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1612" s="3" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
       <c r="B1612" s="3"/>
       <c r="C1612" s="3">
@@ -68603,7 +69414,7 @@
         <v>412</v>
       </c>
       <c r="G1612" s="3" t="s">
-        <v>4078</v>
+        <v>4079</v>
       </c>
       <c r="H1612" s="3"/>
       <c r="I1612" s="3">
@@ -68619,7 +69430,7 @@
     </row>
     <row r="1613" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1613" s="3" t="s">
-        <v>4079</v>
+        <v>4080</v>
       </c>
       <c r="B1613" s="3"/>
       <c r="C1613" s="3">
@@ -68635,7 +69446,7 @@
         <v>428</v>
       </c>
       <c r="G1613" s="3" t="s">
-        <v>4080</v>
+        <v>4081</v>
       </c>
       <c r="H1613" s="3"/>
       <c r="I1613" s="3">
@@ -68651,7 +69462,7 @@
     </row>
     <row r="1614" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1614" s="3" t="s">
-        <v>4081</v>
+        <v>4082</v>
       </c>
       <c r="B1614" s="3"/>
       <c r="C1614" s="3">
@@ -68667,7 +69478,7 @@
         <v>221</v>
       </c>
       <c r="G1614" s="3" t="s">
-        <v>4082</v>
+        <v>4083</v>
       </c>
       <c r="H1614" s="3"/>
       <c r="I1614" s="3">
@@ -68683,7 +69494,7 @@
     </row>
     <row r="1615" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1615" s="3" t="s">
-        <v>4083</v>
+        <v>4084</v>
       </c>
       <c r="B1615" s="3"/>
       <c r="C1615" s="3">
@@ -68699,7 +69510,7 @@
         <v>210</v>
       </c>
       <c r="G1615" s="3" t="s">
-        <v>4084</v>
+        <v>4085</v>
       </c>
       <c r="H1615" s="3"/>
       <c r="I1615" s="3">
@@ -68715,7 +69526,7 @@
     </row>
     <row r="1616" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1616" s="3" t="s">
-        <v>4085</v>
+        <v>4086</v>
       </c>
       <c r="B1616" s="3"/>
       <c r="C1616" s="3">
@@ -68731,21 +69542,27 @@
         <v>2161</v>
       </c>
       <c r="G1616" s="3" t="s">
-        <v>4086</v>
-      </c>
-      <c r="H1616" s="3"/>
+        <v>4087</v>
+      </c>
+      <c r="H1616" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1616" s="3"/>
       <c r="J1616" s="3"/>
       <c r="K1616" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1616" s="3"/>
-      <c r="M1616" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1616" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1616" s="3" t="s">
+        <v>4042</v>
+      </c>
       <c r="N1616" s="3"/>
     </row>
     <row r="1617" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1617" s="3" t="s">
-        <v>4087</v>
+        <v>4088</v>
       </c>
       <c r="B1617" s="3"/>
       <c r="C1617" s="3">
@@ -68761,7 +69578,7 @@
         <v>612</v>
       </c>
       <c r="G1617" s="3" t="s">
-        <v>4088</v>
+        <v>4089</v>
       </c>
       <c r="H1617" s="3"/>
       <c r="I1617" s="3">
@@ -68777,7 +69594,7 @@
     </row>
     <row r="1618" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1618" s="3" t="s">
-        <v>4089</v>
+        <v>4090</v>
       </c>
       <c r="B1618" s="3"/>
       <c r="C1618" s="3">
@@ -68793,7 +69610,7 @@
         <v>1933</v>
       </c>
       <c r="G1618" s="3" t="s">
-        <v>4090</v>
+        <v>4091</v>
       </c>
       <c r="H1618" s="3"/>
       <c r="I1618" s="3">
@@ -68809,9 +69626,11 @@
     </row>
     <row r="1619" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1619" s="3" t="s">
-        <v>4091</v>
-      </c>
-      <c r="B1619" s="3"/>
+        <v>4092</v>
+      </c>
+      <c r="B1619" s="3" t="s">
+        <v>273</v>
+      </c>
       <c r="C1619" s="3">
         <v>28</v>
       </c>
@@ -68825,23 +69644,31 @@
         <v>1626</v>
       </c>
       <c r="G1619" s="3" t="s">
-        <v>4092</v>
-      </c>
-      <c r="H1619" s="3"/>
+        <v>4093</v>
+      </c>
+      <c r="H1619" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="I1619" s="3">
         <v>57</v>
       </c>
       <c r="J1619" s="3"/>
       <c r="K1619" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1619" s="3"/>
-      <c r="M1619" s="3"/>
-      <c r="N1619" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1619" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1619" s="3" t="s">
+        <v>4094</v>
+      </c>
+      <c r="N1619" s="3" t="s">
+        <v>4095</v>
+      </c>
     </row>
     <row r="1620" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1620" s="3" t="s">
-        <v>4093</v>
+        <v>4096</v>
       </c>
       <c r="B1620" s="3"/>
       <c r="C1620" s="3">
@@ -68857,23 +69684,29 @@
         <v>40</v>
       </c>
       <c r="G1620" s="3" t="s">
-        <v>4094</v>
-      </c>
-      <c r="H1620" s="3"/>
+        <v>4097</v>
+      </c>
+      <c r="H1620" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1620" s="3">
         <v>38</v>
       </c>
       <c r="J1620" s="3"/>
       <c r="K1620" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1620" s="3"/>
-      <c r="M1620" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1620" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1620" s="3" t="s">
+        <v>4094</v>
+      </c>
       <c r="N1620" s="3"/>
     </row>
     <row r="1621" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1621" s="3" t="s">
-        <v>4095</v>
+        <v>4098</v>
       </c>
       <c r="B1621" s="3"/>
       <c r="C1621" s="3">
@@ -68889,23 +69722,29 @@
         <v>557</v>
       </c>
       <c r="G1621" s="3" t="s">
-        <v>4096</v>
-      </c>
-      <c r="H1621" s="3"/>
+        <v>4099</v>
+      </c>
+      <c r="H1621" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1621" s="3">
         <v>34</v>
       </c>
       <c r="J1621" s="3"/>
       <c r="K1621" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1621" s="3"/>
-      <c r="M1621" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1621" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1621" s="3" t="s">
+        <v>4094</v>
+      </c>
       <c r="N1621" s="3"/>
     </row>
     <row r="1622" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1622" s="3" t="s">
-        <v>4097</v>
+        <v>4100</v>
       </c>
       <c r="B1622" s="3"/>
       <c r="C1622" s="3">
@@ -68918,22 +69757,3970 @@
         <v>28</v>
       </c>
       <c r="F1622" s="3" t="s">
-        <v>4098</v>
+        <v>4101</v>
       </c>
       <c r="G1622" s="3" t="s">
-        <v>4099</v>
-      </c>
-      <c r="H1622" s="3"/>
+        <v>4102</v>
+      </c>
+      <c r="H1622" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1622" s="3">
         <v>37</v>
       </c>
       <c r="J1622" s="3"/>
       <c r="K1622" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1622" s="3"/>
-      <c r="M1622" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1622" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1622" s="3" t="s">
+        <v>4094</v>
+      </c>
       <c r="N1622" s="3"/>
+    </row>
+    <row r="1623" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1623" s="3" t="s">
+        <v>4103</v>
+      </c>
+      <c r="B1623" s="3"/>
+      <c r="C1623" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1623" s="3">
+        <v>5947691005</v>
+      </c>
+      <c r="E1623" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1623" s="3" t="s">
+        <v>4104</v>
+      </c>
+      <c r="G1623" s="3" t="s">
+        <v>4105</v>
+      </c>
+      <c r="H1623" s="3"/>
+      <c r="I1623" s="3">
+        <v>35</v>
+      </c>
+      <c r="J1623" s="3"/>
+      <c r="K1623" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1623" s="3"/>
+      <c r="M1623" s="3"/>
+      <c r="N1623" s="3"/>
+    </row>
+    <row r="1624" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1624" s="3" t="s">
+        <v>4106</v>
+      </c>
+      <c r="B1624" s="3"/>
+      <c r="C1624" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1624" s="3">
+        <v>5947761684</v>
+      </c>
+      <c r="E1624" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1624" s="3" t="s">
+        <v>4107</v>
+      </c>
+      <c r="G1624" s="3" t="s">
+        <v>4108</v>
+      </c>
+      <c r="H1624" s="3"/>
+      <c r="I1624" s="3">
+        <v>61</v>
+      </c>
+      <c r="J1624" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1624" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1624" s="3"/>
+      <c r="M1624" s="3"/>
+      <c r="N1624" s="3"/>
+    </row>
+    <row r="1625" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1625" s="3" t="s">
+        <v>4109</v>
+      </c>
+      <c r="B1625" s="3"/>
+      <c r="C1625" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1625" s="3">
+        <v>5947863231</v>
+      </c>
+      <c r="E1625" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1625" s="3" t="s">
+        <v>1776</v>
+      </c>
+      <c r="G1625" s="3" t="s">
+        <v>4110</v>
+      </c>
+      <c r="H1625" s="3"/>
+      <c r="I1625" s="3">
+        <v>45</v>
+      </c>
+      <c r="J1625" s="3"/>
+      <c r="K1625" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1625" s="3"/>
+      <c r="M1625" s="3"/>
+      <c r="N1625" s="3"/>
+    </row>
+    <row r="1626" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1626" s="3" t="s">
+        <v>4111</v>
+      </c>
+      <c r="B1626" s="3"/>
+      <c r="C1626" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1626" s="3">
+        <v>5947868399</v>
+      </c>
+      <c r="E1626" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1626" s="3" t="s">
+        <v>1779</v>
+      </c>
+      <c r="G1626" s="3" t="s">
+        <v>4112</v>
+      </c>
+      <c r="H1626" s="3"/>
+      <c r="I1626" s="3">
+        <v>56</v>
+      </c>
+      <c r="J1626" s="3"/>
+      <c r="K1626" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1626" s="3"/>
+      <c r="M1626" s="3"/>
+      <c r="N1626" s="3"/>
+    </row>
+    <row r="1627" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1627" s="3" t="s">
+        <v>4113</v>
+      </c>
+      <c r="B1627" s="3"/>
+      <c r="C1627" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1627" s="3">
+        <v>5947889277</v>
+      </c>
+      <c r="E1627" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1627" s="3" t="s">
+        <v>4114</v>
+      </c>
+      <c r="G1627" s="3" t="s">
+        <v>4115</v>
+      </c>
+      <c r="H1627" s="3"/>
+      <c r="I1627" s="3">
+        <v>81</v>
+      </c>
+      <c r="J1627" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1627" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1627" s="3"/>
+      <c r="M1627" s="3"/>
+      <c r="N1627" s="3"/>
+    </row>
+    <row r="1628" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1628" s="3" t="s">
+        <v>4116</v>
+      </c>
+      <c r="B1628" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1628" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1628" s="3">
+        <v>5948085593</v>
+      </c>
+      <c r="E1628" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1628" s="3" t="s">
+        <v>2528</v>
+      </c>
+      <c r="G1628" s="3" t="s">
+        <v>4117</v>
+      </c>
+      <c r="H1628" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1628" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1628" s="3"/>
+      <c r="K1628" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1628" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1628" s="3" t="s">
+        <v>4095</v>
+      </c>
+      <c r="N1628" s="3" t="s">
+        <v>4118</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1629" s="3" t="s">
+        <v>4116</v>
+      </c>
+      <c r="B1629" s="3"/>
+      <c r="C1629" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1629" s="3">
+        <v>5948085594</v>
+      </c>
+      <c r="E1629" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1629" s="3" t="s">
+        <v>1868</v>
+      </c>
+      <c r="G1629" s="3" t="s">
+        <v>4119</v>
+      </c>
+      <c r="H1629" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1629" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1629" s="3"/>
+      <c r="K1629" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1629" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1629" s="3" t="s">
+        <v>4095</v>
+      </c>
+      <c r="N1629" s="3"/>
+    </row>
+    <row r="1630" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1630" s="3" t="s">
+        <v>4120</v>
+      </c>
+      <c r="B1630" s="3"/>
+      <c r="C1630" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1630" s="3">
+        <v>5948204312</v>
+      </c>
+      <c r="E1630" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1630" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1630" s="3" t="s">
+        <v>4121</v>
+      </c>
+      <c r="H1630" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1630" s="3">
+        <v>4</v>
+      </c>
+      <c r="J1630" s="3"/>
+      <c r="K1630" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1630" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1630" s="3" t="s">
+        <v>4095</v>
+      </c>
+      <c r="N1630" s="3"/>
+    </row>
+    <row r="1631" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1631" s="3" t="s">
+        <v>4122</v>
+      </c>
+      <c r="B1631" s="3"/>
+      <c r="C1631" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1631" s="3">
+        <v>5949621824</v>
+      </c>
+      <c r="E1631" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1631" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="G1631" s="3" t="s">
+        <v>4123</v>
+      </c>
+      <c r="H1631" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1631" s="3">
+        <v>10</v>
+      </c>
+      <c r="J1631" s="3"/>
+      <c r="K1631" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1631" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1631" s="3" t="s">
+        <v>4095</v>
+      </c>
+      <c r="N1631" s="3"/>
+    </row>
+    <row r="1632" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1632" s="3" t="s">
+        <v>4124</v>
+      </c>
+      <c r="B1632" s="3"/>
+      <c r="C1632" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1632" s="3">
+        <v>5949741267</v>
+      </c>
+      <c r="E1632" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1632" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="G1632" s="3" t="s">
+        <v>4125</v>
+      </c>
+      <c r="H1632" s="3"/>
+      <c r="I1632" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1632" s="3"/>
+      <c r="K1632" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1632" s="3"/>
+      <c r="M1632" s="3"/>
+      <c r="N1632" s="3"/>
+    </row>
+    <row r="1633" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1633" s="3" t="s">
+        <v>4126</v>
+      </c>
+      <c r="B1633" s="3"/>
+      <c r="C1633" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1633" s="3">
+        <v>5949823590</v>
+      </c>
+      <c r="E1633" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1633" s="3" t="s">
+        <v>4127</v>
+      </c>
+      <c r="G1633" s="3" t="s">
+        <v>4128</v>
+      </c>
+      <c r="H1633" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1633" s="3"/>
+      <c r="J1633" s="3"/>
+      <c r="K1633" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1633" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1633" s="3" t="s">
+        <v>4118</v>
+      </c>
+      <c r="N1633" s="3"/>
+    </row>
+    <row r="1634" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1634" s="3" t="s">
+        <v>4129</v>
+      </c>
+      <c r="B1634" s="3"/>
+      <c r="C1634" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1634" s="3">
+        <v>5949831185</v>
+      </c>
+      <c r="E1634" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1634" s="3" t="s">
+        <v>4130</v>
+      </c>
+      <c r="G1634" s="3" t="s">
+        <v>4131</v>
+      </c>
+      <c r="H1634" s="3"/>
+      <c r="I1634" s="3">
+        <v>42</v>
+      </c>
+      <c r="J1634" s="3">
+        <v>35</v>
+      </c>
+      <c r="K1634" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1634" s="3"/>
+      <c r="M1634" s="3"/>
+      <c r="N1634" s="3"/>
+    </row>
+    <row r="1635" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1635" s="3" t="s">
+        <v>4132</v>
+      </c>
+      <c r="B1635" s="3"/>
+      <c r="C1635" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1635" s="3">
+        <v>5949837872</v>
+      </c>
+      <c r="E1635" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1635" s="3" t="s">
+        <v>4133</v>
+      </c>
+      <c r="G1635" s="3" t="s">
+        <v>4134</v>
+      </c>
+      <c r="H1635" s="3"/>
+      <c r="I1635" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1635" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1635" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1635" s="3"/>
+      <c r="M1635" s="3"/>
+      <c r="N1635" s="3"/>
+    </row>
+    <row r="1636" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1636" s="3" t="s">
+        <v>4135</v>
+      </c>
+      <c r="B1636" s="3"/>
+      <c r="C1636" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1636" s="3">
+        <v>5949845345</v>
+      </c>
+      <c r="E1636" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1636" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="G1636" s="3" t="s">
+        <v>4136</v>
+      </c>
+      <c r="H1636" s="3"/>
+      <c r="I1636" s="3">
+        <v>77</v>
+      </c>
+      <c r="J1636" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1636" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1636" s="3"/>
+      <c r="M1636" s="3"/>
+      <c r="N1636" s="3"/>
+    </row>
+    <row r="1637" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1637" s="3" t="s">
+        <v>4137</v>
+      </c>
+      <c r="B1637" s="3"/>
+      <c r="C1637" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1637" s="3">
+        <v>5949858721</v>
+      </c>
+      <c r="E1637" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1637" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1637" s="3" t="s">
+        <v>4138</v>
+      </c>
+      <c r="H1637" s="3"/>
+      <c r="I1637" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1637" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1637" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1637" s="3"/>
+      <c r="M1637" s="3"/>
+      <c r="N1637" s="3"/>
+    </row>
+    <row r="1638" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1638" s="3" t="s">
+        <v>4139</v>
+      </c>
+      <c r="B1638" s="3"/>
+      <c r="C1638" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1638" s="3">
+        <v>5949954356</v>
+      </c>
+      <c r="E1638" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1638" s="3" t="s">
+        <v>4140</v>
+      </c>
+      <c r="G1638" s="3" t="s">
+        <v>4141</v>
+      </c>
+      <c r="H1638" s="3"/>
+      <c r="I1638" s="3">
+        <v>83</v>
+      </c>
+      <c r="J1638" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1638" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1638" s="3"/>
+      <c r="M1638" s="3"/>
+      <c r="N1638" s="3"/>
+    </row>
+    <row r="1639" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1639" s="3" t="s">
+        <v>4142</v>
+      </c>
+      <c r="B1639" s="3"/>
+      <c r="C1639" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1639" s="3">
+        <v>5949962347</v>
+      </c>
+      <c r="E1639" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1639" s="3" t="s">
+        <v>1328</v>
+      </c>
+      <c r="G1639" s="3" t="s">
+        <v>4143</v>
+      </c>
+      <c r="H1639" s="3"/>
+      <c r="I1639" s="3">
+        <v>82</v>
+      </c>
+      <c r="J1639" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1639" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1639" s="3"/>
+      <c r="M1639" s="3"/>
+      <c r="N1639" s="3"/>
+    </row>
+    <row r="1640" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1640" s="3" t="s">
+        <v>4144</v>
+      </c>
+      <c r="B1640" s="3"/>
+      <c r="C1640" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1640" s="3">
+        <v>5949993520</v>
+      </c>
+      <c r="E1640" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1640" s="3" t="s">
+        <v>1954</v>
+      </c>
+      <c r="G1640" s="3" t="s">
+        <v>4145</v>
+      </c>
+      <c r="H1640" s="3"/>
+      <c r="I1640" s="3">
+        <v>77</v>
+      </c>
+      <c r="J1640" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1640" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1640" s="3"/>
+      <c r="M1640" s="3"/>
+      <c r="N1640" s="3"/>
+    </row>
+    <row r="1641" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1641" s="3" t="s">
+        <v>4146</v>
+      </c>
+      <c r="B1641" s="3"/>
+      <c r="C1641" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1641" s="3">
+        <v>5950001708</v>
+      </c>
+      <c r="E1641" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1641" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G1641" s="3" t="s">
+        <v>4147</v>
+      </c>
+      <c r="H1641" s="3"/>
+      <c r="I1641" s="3">
+        <v>79</v>
+      </c>
+      <c r="J1641" s="3">
+        <v>-5</v>
+      </c>
+      <c r="K1641" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1641" s="3"/>
+      <c r="M1641" s="3"/>
+      <c r="N1641" s="3"/>
+    </row>
+    <row r="1642" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1642" s="3" t="s">
+        <v>4148</v>
+      </c>
+      <c r="B1642" s="3"/>
+      <c r="C1642" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1642" s="3">
+        <v>5950113701</v>
+      </c>
+      <c r="E1642" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1642" s="3" t="s">
+        <v>4149</v>
+      </c>
+      <c r="G1642" s="3" t="s">
+        <v>4150</v>
+      </c>
+      <c r="H1642" s="3"/>
+      <c r="I1642" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1642" s="3"/>
+      <c r="K1642" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1642" s="3"/>
+      <c r="M1642" s="3"/>
+      <c r="N1642" s="3"/>
+    </row>
+    <row r="1643" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1643" s="3" t="s">
+        <v>4151</v>
+      </c>
+      <c r="B1643" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1643" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1643" s="3">
+        <v>5950127904</v>
+      </c>
+      <c r="E1643" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1643" s="3" t="s">
+        <v>2528</v>
+      </c>
+      <c r="G1643" s="3" t="s">
+        <v>4152</v>
+      </c>
+      <c r="H1643" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1643" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1643" s="3"/>
+      <c r="K1643" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1643" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1643" s="3" t="s">
+        <v>4153</v>
+      </c>
+      <c r="N1643" s="3" t="s">
+        <v>4154</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1644" s="3" t="s">
+        <v>4155</v>
+      </c>
+      <c r="B1644" s="3"/>
+      <c r="C1644" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1644" s="3">
+        <v>5950127906</v>
+      </c>
+      <c r="E1644" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1644" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="G1644" s="3" t="s">
+        <v>4156</v>
+      </c>
+      <c r="H1644" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1644" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1644" s="3"/>
+      <c r="K1644" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1644" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1644" s="3" t="s">
+        <v>4153</v>
+      </c>
+      <c r="N1644" s="3"/>
+    </row>
+    <row r="1645" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1645" s="3" t="s">
+        <v>4155</v>
+      </c>
+      <c r="B1645" s="3"/>
+      <c r="C1645" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1645" s="3">
+        <v>5950132732</v>
+      </c>
+      <c r="E1645" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1645" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1645" s="3" t="s">
+        <v>4157</v>
+      </c>
+      <c r="H1645" s="3"/>
+      <c r="I1645" s="3">
+        <v>71</v>
+      </c>
+      <c r="J1645" s="3"/>
+      <c r="K1645" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1645" s="3"/>
+      <c r="M1645" s="3"/>
+      <c r="N1645" s="3"/>
+    </row>
+    <row r="1646" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1646" s="3" t="s">
+        <v>4158</v>
+      </c>
+      <c r="B1646" s="3"/>
+      <c r="C1646" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1646" s="3">
+        <v>5950163921</v>
+      </c>
+      <c r="E1646" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F1646" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G1646" s="3" t="s">
+        <v>4159</v>
+      </c>
+      <c r="H1646" s="3"/>
+      <c r="I1646" s="3">
+        <v>17</v>
+      </c>
+      <c r="J1646" s="3"/>
+      <c r="K1646" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1646" s="3"/>
+      <c r="M1646" s="3"/>
+      <c r="N1646" s="3"/>
+    </row>
+    <row r="1647" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1647" s="3" t="s">
+        <v>4160</v>
+      </c>
+      <c r="B1647" s="3"/>
+      <c r="C1647" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1647" s="3">
+        <v>5950188420</v>
+      </c>
+      <c r="E1647" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="F1647" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="G1647" s="3" t="s">
+        <v>4161</v>
+      </c>
+      <c r="H1647" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1647" s="3">
+        <v>38</v>
+      </c>
+      <c r="J1647" s="3"/>
+      <c r="K1647" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1647" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1647" s="3" t="s">
+        <v>4153</v>
+      </c>
+      <c r="N1647" s="3"/>
+    </row>
+    <row r="1648" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1648" s="3" t="s">
+        <v>4162</v>
+      </c>
+      <c r="B1648" s="3"/>
+      <c r="C1648" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1648" s="3">
+        <v>5950425026</v>
+      </c>
+      <c r="E1648" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1648" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="G1648" s="3" t="s">
+        <v>4163</v>
+      </c>
+      <c r="H1648" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1648" s="3">
+        <v>30</v>
+      </c>
+      <c r="J1648" s="3"/>
+      <c r="K1648" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1648" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1648" s="3" t="s">
+        <v>4153</v>
+      </c>
+      <c r="N1648" s="3"/>
+    </row>
+    <row r="1649" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1649" s="3" t="s">
+        <v>4164</v>
+      </c>
+      <c r="B1649" s="3"/>
+      <c r="C1649" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1649" s="3">
+        <v>5950445821</v>
+      </c>
+      <c r="E1649" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1649" s="3" t="s">
+        <v>1372</v>
+      </c>
+      <c r="G1649" s="3" t="s">
+        <v>4165</v>
+      </c>
+      <c r="H1649" s="3"/>
+      <c r="I1649" s="3">
+        <v>16</v>
+      </c>
+      <c r="J1649" s="3"/>
+      <c r="K1649" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1649" s="3"/>
+      <c r="M1649" s="3"/>
+      <c r="N1649" s="3"/>
+    </row>
+    <row r="1650" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1650" s="3" t="s">
+        <v>4166</v>
+      </c>
+      <c r="B1650" s="3"/>
+      <c r="C1650" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1650" s="3">
+        <v>5951286500</v>
+      </c>
+      <c r="E1650" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1650" s="3" t="s">
+        <v>1804</v>
+      </c>
+      <c r="G1650" s="3" t="s">
+        <v>4167</v>
+      </c>
+      <c r="H1650" s="3"/>
+      <c r="I1650" s="3">
+        <v>8</v>
+      </c>
+      <c r="J1650" s="3"/>
+      <c r="K1650" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1650" s="3"/>
+      <c r="M1650" s="3"/>
+      <c r="N1650" s="3"/>
+    </row>
+    <row r="1651" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1651" s="3" t="s">
+        <v>4168</v>
+      </c>
+      <c r="B1651" s="3"/>
+      <c r="C1651" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1651" s="3">
+        <v>5952432128</v>
+      </c>
+      <c r="E1651" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1651" s="3" t="s">
+        <v>1994</v>
+      </c>
+      <c r="G1651" s="3" t="s">
+        <v>4169</v>
+      </c>
+      <c r="H1651" s="3"/>
+      <c r="I1651" s="3">
+        <v>76</v>
+      </c>
+      <c r="J1651" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1651" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1651" s="3"/>
+      <c r="M1651" s="3"/>
+      <c r="N1651" s="3"/>
+    </row>
+    <row r="1652" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1652" s="3" t="s">
+        <v>4170</v>
+      </c>
+      <c r="B1652" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1652" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1652" s="3">
+        <v>5956532070</v>
+      </c>
+      <c r="E1652" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1652" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1652" s="3" t="s">
+        <v>4171</v>
+      </c>
+      <c r="H1652" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1652" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1652" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1652" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1652" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1652" s="3" t="s">
+        <v>4172</v>
+      </c>
+      <c r="N1652" s="3" t="s">
+        <v>4173</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1653" s="3" t="s">
+        <v>4174</v>
+      </c>
+      <c r="B1653" s="3"/>
+      <c r="C1653" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1653" s="3">
+        <v>5956538814</v>
+      </c>
+      <c r="E1653" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1653" s="3" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G1653" s="3" t="s">
+        <v>4175</v>
+      </c>
+      <c r="H1653" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1653" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1653" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1653" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1653" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1653" s="3" t="s">
+        <v>4172</v>
+      </c>
+      <c r="N1653" s="3"/>
+    </row>
+    <row r="1654" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1654" s="3" t="s">
+        <v>4176</v>
+      </c>
+      <c r="B1654" s="3"/>
+      <c r="C1654" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1654" s="3">
+        <v>5957025938</v>
+      </c>
+      <c r="E1654" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1654" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G1654" s="3" t="s">
+        <v>3884</v>
+      </c>
+      <c r="H1654" s="3"/>
+      <c r="I1654" s="3">
+        <v>52</v>
+      </c>
+      <c r="J1654" s="3"/>
+      <c r="K1654" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1654" s="3"/>
+      <c r="M1654" s="3"/>
+      <c r="N1654" s="3"/>
+    </row>
+    <row r="1655" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1655" s="3" t="s">
+        <v>4177</v>
+      </c>
+      <c r="B1655" s="3"/>
+      <c r="C1655" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1655" s="3">
+        <v>5957044718</v>
+      </c>
+      <c r="E1655" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1655" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G1655" s="3" t="s">
+        <v>4178</v>
+      </c>
+      <c r="H1655" s="3"/>
+      <c r="I1655" s="3">
+        <v>37</v>
+      </c>
+      <c r="J1655" s="3"/>
+      <c r="K1655" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1655" s="3"/>
+      <c r="M1655" s="3"/>
+      <c r="N1655" s="3"/>
+    </row>
+    <row r="1656" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1656" s="3" t="s">
+        <v>4179</v>
+      </c>
+      <c r="B1656" s="3"/>
+      <c r="C1656" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1656" s="3">
+        <v>5957054139</v>
+      </c>
+      <c r="E1656" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1656" s="3" t="s">
+        <v>2164</v>
+      </c>
+      <c r="G1656" s="3" t="s">
+        <v>4180</v>
+      </c>
+      <c r="H1656" s="3"/>
+      <c r="I1656" s="3">
+        <v>53</v>
+      </c>
+      <c r="J1656" s="3">
+        <v>45</v>
+      </c>
+      <c r="K1656" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1656" s="3"/>
+      <c r="M1656" s="3"/>
+      <c r="N1656" s="3"/>
+    </row>
+    <row r="1657" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1657" s="3" t="s">
+        <v>4181</v>
+      </c>
+      <c r="B1657" s="3"/>
+      <c r="C1657" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1657" s="3">
+        <v>5957059037</v>
+      </c>
+      <c r="E1657" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1657" s="3" t="s">
+        <v>4182</v>
+      </c>
+      <c r="G1657" s="3" t="s">
+        <v>4183</v>
+      </c>
+      <c r="H1657" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1657" s="3">
+        <v>51</v>
+      </c>
+      <c r="J1657" s="3">
+        <v>45</v>
+      </c>
+      <c r="K1657" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1657" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1657" s="3" t="s">
+        <v>4172</v>
+      </c>
+      <c r="N1657" s="3"/>
+    </row>
+    <row r="1658" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1658" s="3" t="s">
+        <v>4184</v>
+      </c>
+      <c r="B1658" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1658" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1658" s="3">
+        <v>5957173679</v>
+      </c>
+      <c r="E1658" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1658" s="3" t="s">
+        <v>2264</v>
+      </c>
+      <c r="G1658" s="3" t="s">
+        <v>4185</v>
+      </c>
+      <c r="H1658" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1658" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1658" s="3"/>
+      <c r="K1658" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1658" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1658" s="3" t="s">
+        <v>4186</v>
+      </c>
+      <c r="N1658" s="3"/>
+    </row>
+    <row r="1659" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1659" s="3" t="s">
+        <v>4187</v>
+      </c>
+      <c r="B1659" s="3"/>
+      <c r="C1659" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1659" s="3">
+        <v>5957278433</v>
+      </c>
+      <c r="E1659" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1659" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G1659" s="3" t="s">
+        <v>4188</v>
+      </c>
+      <c r="H1659" s="3"/>
+      <c r="I1659" s="3">
+        <v>13</v>
+      </c>
+      <c r="J1659" s="3"/>
+      <c r="K1659" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1659" s="3"/>
+      <c r="M1659" s="3"/>
+      <c r="N1659" s="3"/>
+    </row>
+    <row r="1660" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1660" s="3" t="s">
+        <v>4189</v>
+      </c>
+      <c r="B1660" s="3"/>
+      <c r="C1660" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1660" s="3">
+        <v>5957345628</v>
+      </c>
+      <c r="E1660" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1660" s="3" t="s">
+        <v>4190</v>
+      </c>
+      <c r="G1660" s="3" t="s">
+        <v>4191</v>
+      </c>
+      <c r="H1660" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1660" s="3">
+        <v>9</v>
+      </c>
+      <c r="J1660" s="3"/>
+      <c r="K1660" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1660" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1660" s="3" t="s">
+        <v>4186</v>
+      </c>
+      <c r="N1660" s="3"/>
+    </row>
+    <row r="1661" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1661" s="3" t="s">
+        <v>4192</v>
+      </c>
+      <c r="B1661" s="3"/>
+      <c r="C1661" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1661" s="3">
+        <v>5957505697</v>
+      </c>
+      <c r="E1661" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1661" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1661" s="3" t="s">
+        <v>4193</v>
+      </c>
+      <c r="H1661" s="3"/>
+      <c r="I1661" s="3">
+        <v>15</v>
+      </c>
+      <c r="J1661" s="3"/>
+      <c r="K1661" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1661" s="3"/>
+      <c r="M1661" s="3"/>
+      <c r="N1661" s="3"/>
+    </row>
+    <row r="1662" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1662" s="3" t="s">
+        <v>4194</v>
+      </c>
+      <c r="B1662" s="3"/>
+      <c r="C1662" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1662" s="3">
+        <v>5958235924</v>
+      </c>
+      <c r="E1662" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1662" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G1662" s="3" t="s">
+        <v>4195</v>
+      </c>
+      <c r="H1662" s="3"/>
+      <c r="I1662" s="3">
+        <v>7</v>
+      </c>
+      <c r="J1662" s="3"/>
+      <c r="K1662" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1662" s="3"/>
+      <c r="M1662" s="3"/>
+      <c r="N1662" s="3"/>
+    </row>
+    <row r="1663" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1663" s="3" t="s">
+        <v>4196</v>
+      </c>
+      <c r="B1663" s="3"/>
+      <c r="C1663" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1663" s="3">
+        <v>5958434597</v>
+      </c>
+      <c r="E1663" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1663" s="3" t="s">
+        <v>2134</v>
+      </c>
+      <c r="G1663" s="3" t="s">
+        <v>4197</v>
+      </c>
+      <c r="H1663" s="3"/>
+      <c r="I1663" s="3">
+        <v>13</v>
+      </c>
+      <c r="J1663" s="3"/>
+      <c r="K1663" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1663" s="3"/>
+      <c r="M1663" s="3"/>
+      <c r="N1663" s="3"/>
+    </row>
+    <row r="1664" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1664" s="3" t="s">
+        <v>4198</v>
+      </c>
+      <c r="B1664" s="3"/>
+      <c r="C1664" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1664" s="3">
+        <v>5959652869</v>
+      </c>
+      <c r="E1664" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1664" s="3" t="s">
+        <v>2134</v>
+      </c>
+      <c r="G1664" s="3" t="s">
+        <v>4199</v>
+      </c>
+      <c r="H1664" s="3"/>
+      <c r="I1664" s="3"/>
+      <c r="J1664" s="3"/>
+      <c r="K1664" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1664" s="3"/>
+      <c r="M1664" s="3"/>
+      <c r="N1664" s="3"/>
+    </row>
+    <row r="1665" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1665" s="3" t="s">
+        <v>4200</v>
+      </c>
+      <c r="B1665" s="3"/>
+      <c r="C1665" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1665" s="3">
+        <v>5960101166</v>
+      </c>
+      <c r="E1665" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1665" s="3" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G1665" s="3" t="s">
+        <v>4201</v>
+      </c>
+      <c r="H1665" s="3"/>
+      <c r="I1665" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1665" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1665" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1665" s="3"/>
+      <c r="M1665" s="3"/>
+      <c r="N1665" s="3"/>
+    </row>
+    <row r="1666" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1666" s="3" t="s">
+        <v>4202</v>
+      </c>
+      <c r="B1666" s="3"/>
+      <c r="C1666" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1666" s="3">
+        <v>5962067850</v>
+      </c>
+      <c r="E1666" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1666" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="G1666" s="3" t="s">
+        <v>4203</v>
+      </c>
+      <c r="H1666" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1666" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1666" s="3"/>
+      <c r="K1666" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1666" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1666" s="3" t="s">
+        <v>4204</v>
+      </c>
+      <c r="N1666" s="3"/>
+    </row>
+    <row r="1667" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1667" s="3" t="s">
+        <v>4205</v>
+      </c>
+      <c r="B1667" s="3"/>
+      <c r="C1667" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1667" s="3">
+        <v>5962192217</v>
+      </c>
+      <c r="E1667" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1667" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G1667" s="3" t="s">
+        <v>4206</v>
+      </c>
+      <c r="H1667" s="3"/>
+      <c r="I1667" s="3">
+        <v>61</v>
+      </c>
+      <c r="J1667" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1667" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1667" s="3"/>
+      <c r="M1667" s="3"/>
+      <c r="N1667" s="3"/>
+    </row>
+    <row r="1668" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1668" s="3" t="s">
+        <v>4207</v>
+      </c>
+      <c r="B1668" s="3"/>
+      <c r="C1668" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1668" s="3">
+        <v>5962243961</v>
+      </c>
+      <c r="E1668" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1668" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="G1668" s="3" t="s">
+        <v>4208</v>
+      </c>
+      <c r="H1668" s="3"/>
+      <c r="I1668" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1668" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1668" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1668" s="3"/>
+      <c r="M1668" s="3"/>
+      <c r="N1668" s="3"/>
+    </row>
+    <row r="1669" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1669" s="3" t="s">
+        <v>4209</v>
+      </c>
+      <c r="B1669" s="3"/>
+      <c r="C1669" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1669" s="3">
+        <v>5962786024</v>
+      </c>
+      <c r="E1669" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1669" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G1669" s="3" t="s">
+        <v>4210</v>
+      </c>
+      <c r="H1669" s="3"/>
+      <c r="I1669" s="3">
+        <v>34</v>
+      </c>
+      <c r="J1669" s="3"/>
+      <c r="K1669" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1669" s="3"/>
+      <c r="M1669" s="3"/>
+      <c r="N1669" s="3"/>
+    </row>
+    <row r="1670" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1670" s="3" t="s">
+        <v>4211</v>
+      </c>
+      <c r="B1670" s="3"/>
+      <c r="C1670" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1670" s="3">
+        <v>5962789604</v>
+      </c>
+      <c r="E1670" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1670" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G1670" s="3" t="s">
+        <v>4212</v>
+      </c>
+      <c r="H1670" s="3"/>
+      <c r="I1670" s="3">
+        <v>43</v>
+      </c>
+      <c r="J1670" s="3"/>
+      <c r="K1670" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1670" s="3"/>
+      <c r="M1670" s="3"/>
+      <c r="N1670" s="3"/>
+    </row>
+    <row r="1671" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1671" s="3" t="s">
+        <v>4213</v>
+      </c>
+      <c r="B1671" s="3"/>
+      <c r="C1671" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1671" s="3">
+        <v>5962807096</v>
+      </c>
+      <c r="E1671" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1671" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G1671" s="3" t="s">
+        <v>4214</v>
+      </c>
+      <c r="H1671" s="3"/>
+      <c r="I1671" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1671" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1671" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1671" s="3"/>
+      <c r="M1671" s="3"/>
+      <c r="N1671" s="3"/>
+    </row>
+    <row r="1672" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1672" s="3" t="s">
+        <v>4215</v>
+      </c>
+      <c r="B1672" s="3"/>
+      <c r="C1672" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1672" s="3">
+        <v>5962810652</v>
+      </c>
+      <c r="E1672" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1672" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G1672" s="3" t="s">
+        <v>4216</v>
+      </c>
+      <c r="H1672" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1672" s="3">
+        <v>29</v>
+      </c>
+      <c r="J1672" s="3"/>
+      <c r="K1672" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1672" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1672" s="3" t="s">
+        <v>4204</v>
+      </c>
+      <c r="N1672" s="3"/>
+    </row>
+    <row r="1673" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1673" s="3" t="s">
+        <v>4217</v>
+      </c>
+      <c r="B1673" s="3"/>
+      <c r="C1673" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1673" s="3">
+        <v>5962814169</v>
+      </c>
+      <c r="E1673" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1673" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G1673" s="3" t="s">
+        <v>4218</v>
+      </c>
+      <c r="H1673" s="3"/>
+      <c r="I1673" s="3">
+        <v>25</v>
+      </c>
+      <c r="J1673" s="3"/>
+      <c r="K1673" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1673" s="3"/>
+      <c r="M1673" s="3"/>
+      <c r="N1673" s="3"/>
+    </row>
+    <row r="1674" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1674" s="3" t="s">
+        <v>4219</v>
+      </c>
+      <c r="B1674" s="3"/>
+      <c r="C1674" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1674" s="3">
+        <v>5962848514</v>
+      </c>
+      <c r="E1674" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1674" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="G1674" s="3" t="s">
+        <v>4220</v>
+      </c>
+      <c r="H1674" s="3"/>
+      <c r="I1674" s="3">
+        <v>29</v>
+      </c>
+      <c r="J1674" s="3"/>
+      <c r="K1674" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1674" s="3"/>
+      <c r="M1674" s="3"/>
+      <c r="N1674" s="3"/>
+    </row>
+    <row r="1675" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1675" s="3" t="s">
+        <v>4221</v>
+      </c>
+      <c r="B1675" s="3"/>
+      <c r="C1675" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1675" s="3">
+        <v>5963179055</v>
+      </c>
+      <c r="E1675" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1675" s="3" t="s">
+        <v>1636</v>
+      </c>
+      <c r="G1675" s="3" t="s">
+        <v>4222</v>
+      </c>
+      <c r="H1675" s="3"/>
+      <c r="I1675" s="3">
+        <v>23</v>
+      </c>
+      <c r="J1675" s="3"/>
+      <c r="K1675" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1675" s="3"/>
+      <c r="M1675" s="3"/>
+      <c r="N1675" s="3"/>
+    </row>
+    <row r="1676" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1676" s="3" t="s">
+        <v>4223</v>
+      </c>
+      <c r="B1676" s="3"/>
+      <c r="C1676" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1676" s="3">
+        <v>5964204857</v>
+      </c>
+      <c r="E1676" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1676" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G1676" s="3" t="s">
+        <v>4224</v>
+      </c>
+      <c r="H1676" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1676" s="3">
+        <v>56</v>
+      </c>
+      <c r="J1676" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1676" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1676" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1676" s="3" t="s">
+        <v>4225</v>
+      </c>
+      <c r="N1676" s="3"/>
+    </row>
+    <row r="1677" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1677" s="3" t="s">
+        <v>4226</v>
+      </c>
+      <c r="B1677" s="3"/>
+      <c r="C1677" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1677" s="3">
+        <v>5964290067</v>
+      </c>
+      <c r="E1677" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1677" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G1677" s="3" t="s">
+        <v>4227</v>
+      </c>
+      <c r="H1677" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1677" s="3">
+        <v>7</v>
+      </c>
+      <c r="J1677" s="3"/>
+      <c r="K1677" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1677" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1677" s="3" t="s">
+        <v>4204</v>
+      </c>
+      <c r="N1677" s="3"/>
+    </row>
+    <row r="1678" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1678" s="3" t="s">
+        <v>4228</v>
+      </c>
+      <c r="B1678" s="3"/>
+      <c r="C1678" s="3">
+        <v>16</v>
+      </c>
+      <c r="D1678" s="3">
+        <v>5964738329</v>
+      </c>
+      <c r="E1678" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1678" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="G1678" s="3" t="s">
+        <v>4229</v>
+      </c>
+      <c r="H1678" s="3"/>
+      <c r="I1678" s="3">
+        <v>11</v>
+      </c>
+      <c r="J1678" s="3"/>
+      <c r="K1678" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1678" s="3"/>
+      <c r="M1678" s="3"/>
+      <c r="N1678" s="3"/>
+    </row>
+    <row r="1679" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1679" s="3" t="s">
+        <v>4230</v>
+      </c>
+      <c r="B1679" s="3"/>
+      <c r="C1679" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1679" s="3">
+        <v>5965921576</v>
+      </c>
+      <c r="E1679" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1679" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="G1679" s="3" t="s">
+        <v>4231</v>
+      </c>
+      <c r="H1679" s="3"/>
+      <c r="I1679" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1679" s="3"/>
+      <c r="K1679" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1679" s="3"/>
+      <c r="M1679" s="3"/>
+      <c r="N1679" s="3"/>
+    </row>
+    <row r="1680" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1680" s="3" t="s">
+        <v>4232</v>
+      </c>
+      <c r="B1680" s="3"/>
+      <c r="C1680" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1680" s="3">
+        <v>5966451173</v>
+      </c>
+      <c r="E1680" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1680" s="3" t="s">
+        <v>4233</v>
+      </c>
+      <c r="G1680" s="3" t="s">
+        <v>4234</v>
+      </c>
+      <c r="H1680" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1680" s="3">
+        <v>12</v>
+      </c>
+      <c r="J1680" s="3"/>
+      <c r="K1680" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1680" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1680" s="3" t="s">
+        <v>4235</v>
+      </c>
+      <c r="N1680" s="3"/>
+    </row>
+    <row r="1681" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1681" s="3" t="s">
+        <v>4236</v>
+      </c>
+      <c r="B1681" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C1681" s="3">
+        <v>26</v>
+      </c>
+      <c r="D1681" s="3">
+        <v>5966640020</v>
+      </c>
+      <c r="E1681" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1681" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1681" s="3" t="s">
+        <v>4237</v>
+      </c>
+      <c r="H1681" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1681" s="3"/>
+      <c r="J1681" s="3"/>
+      <c r="K1681" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1681" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1681" s="3" t="s">
+        <v>4238</v>
+      </c>
+      <c r="N1681" s="3"/>
+    </row>
+    <row r="1682" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1682" s="3" t="s">
+        <v>4239</v>
+      </c>
+      <c r="B1682" s="3"/>
+      <c r="C1682" s="3">
+        <v>26</v>
+      </c>
+      <c r="D1682" s="3">
+        <v>5966668822</v>
+      </c>
+      <c r="E1682" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1682" s="3" t="s">
+        <v>1472</v>
+      </c>
+      <c r="G1682" s="3" t="s">
+        <v>4240</v>
+      </c>
+      <c r="H1682" s="3"/>
+      <c r="I1682" s="3">
+        <v>42</v>
+      </c>
+      <c r="J1682" s="3"/>
+      <c r="K1682" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1682" s="3"/>
+      <c r="M1682" s="3"/>
+      <c r="N1682" s="3"/>
+    </row>
+    <row r="1683" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1683" s="3" t="s">
+        <v>4241</v>
+      </c>
+      <c r="B1683" s="3"/>
+      <c r="C1683" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1683" s="3">
+        <v>5966780459</v>
+      </c>
+      <c r="E1683" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="F1683" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G1683" s="3" t="s">
+        <v>4242</v>
+      </c>
+      <c r="H1683" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1683" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1683" s="3"/>
+      <c r="K1683" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1683" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1683" s="3" t="s">
+        <v>4235</v>
+      </c>
+      <c r="N1683" s="3"/>
+    </row>
+    <row r="1684" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1684" s="3" t="s">
+        <v>4243</v>
+      </c>
+      <c r="B1684" s="3"/>
+      <c r="C1684" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1684" s="3">
+        <v>5966883462</v>
+      </c>
+      <c r="E1684" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1684" s="3" t="s">
+        <v>4114</v>
+      </c>
+      <c r="G1684" s="3" t="s">
+        <v>4244</v>
+      </c>
+      <c r="H1684" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1684" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1684" s="3"/>
+      <c r="K1684" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1684" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1684" s="3" t="s">
+        <v>4245</v>
+      </c>
+      <c r="N1684" s="3"/>
+    </row>
+    <row r="1685" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1685" s="3" t="s">
+        <v>4246</v>
+      </c>
+      <c r="B1685" s="3"/>
+      <c r="C1685" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1685" s="3">
+        <v>5966887626</v>
+      </c>
+      <c r="E1685" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1685" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G1685" s="3" t="s">
+        <v>4247</v>
+      </c>
+      <c r="H1685" s="3"/>
+      <c r="I1685" s="3">
+        <v>22</v>
+      </c>
+      <c r="J1685" s="3"/>
+      <c r="K1685" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1685" s="3"/>
+      <c r="M1685" s="3"/>
+      <c r="N1685" s="3"/>
+    </row>
+    <row r="1686" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1686" s="3" t="s">
+        <v>4248</v>
+      </c>
+      <c r="B1686" s="3"/>
+      <c r="C1686" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1686" s="3">
+        <v>5966937918</v>
+      </c>
+      <c r="E1686" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F1686" s="3" t="s">
+        <v>1668</v>
+      </c>
+      <c r="G1686" s="3" t="s">
+        <v>4249</v>
+      </c>
+      <c r="H1686" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1686" s="3"/>
+      <c r="J1686" s="3"/>
+      <c r="K1686" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1686" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1686" s="3" t="s">
+        <v>4250</v>
+      </c>
+      <c r="N1686" s="3"/>
+    </row>
+    <row r="1687" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1687" s="3" t="s">
+        <v>4251</v>
+      </c>
+      <c r="B1687" s="3"/>
+      <c r="C1687" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1687" s="3">
+        <v>5966958780</v>
+      </c>
+      <c r="E1687" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1687" s="3" t="s">
+        <v>4252</v>
+      </c>
+      <c r="G1687" s="3" t="s">
+        <v>4253</v>
+      </c>
+      <c r="H1687" s="3"/>
+      <c r="I1687" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1687" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1687" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1687" s="3"/>
+      <c r="M1687" s="3"/>
+      <c r="N1687" s="3"/>
+    </row>
+    <row r="1688" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1688" s="3" t="s">
+        <v>4254</v>
+      </c>
+      <c r="B1688" s="3"/>
+      <c r="C1688" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1688" s="3">
+        <v>5967074375</v>
+      </c>
+      <c r="E1688" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1688" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1688" s="3" t="s">
+        <v>3491</v>
+      </c>
+      <c r="H1688" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1688" s="3">
+        <v>11</v>
+      </c>
+      <c r="J1688" s="3"/>
+      <c r="K1688" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1688" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1688" s="3" t="s">
+        <v>4250</v>
+      </c>
+      <c r="N1688" s="3"/>
+    </row>
+    <row r="1689" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1689" s="3" t="s">
+        <v>4255</v>
+      </c>
+      <c r="B1689" s="3"/>
+      <c r="C1689" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1689" s="3">
+        <v>5967083174</v>
+      </c>
+      <c r="E1689" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1689" s="3" t="s">
+        <v>3382</v>
+      </c>
+      <c r="G1689" s="3" t="s">
+        <v>4256</v>
+      </c>
+      <c r="H1689" s="3"/>
+      <c r="I1689" s="3">
+        <v>60</v>
+      </c>
+      <c r="J1689" s="3"/>
+      <c r="K1689" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1689" s="3"/>
+      <c r="M1689" s="3"/>
+      <c r="N1689" s="3"/>
+    </row>
+    <row r="1690" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1690" s="3" t="s">
+        <v>4257</v>
+      </c>
+      <c r="B1690" s="3"/>
+      <c r="C1690" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1690" s="3">
+        <v>5967102235</v>
+      </c>
+      <c r="E1690" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1690" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="G1690" s="3" t="s">
+        <v>4258</v>
+      </c>
+      <c r="H1690" s="3"/>
+      <c r="I1690" s="3">
+        <v>44</v>
+      </c>
+      <c r="J1690" s="3"/>
+      <c r="K1690" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1690" s="3"/>
+      <c r="M1690" s="3"/>
+      <c r="N1690" s="3"/>
+    </row>
+    <row r="1691" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1691" s="3" t="s">
+        <v>4259</v>
+      </c>
+      <c r="B1691" s="3"/>
+      <c r="C1691" s="3">
+        <v>26</v>
+      </c>
+      <c r="D1691" s="3">
+        <v>5967126950</v>
+      </c>
+      <c r="E1691" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F1691" s="3" t="s">
+        <v>4260</v>
+      </c>
+      <c r="G1691" s="3" t="s">
+        <v>4261</v>
+      </c>
+      <c r="H1691" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1691" s="3"/>
+      <c r="J1691" s="3"/>
+      <c r="K1691" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1691" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1691" s="3" t="s">
+        <v>4250</v>
+      </c>
+      <c r="N1691" s="3"/>
+    </row>
+    <row r="1692" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1692" s="3" t="s">
+        <v>4262</v>
+      </c>
+      <c r="B1692" s="3"/>
+      <c r="C1692" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1692" s="3">
+        <v>5967136579</v>
+      </c>
+      <c r="E1692" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1692" s="3" t="s">
+        <v>4263</v>
+      </c>
+      <c r="G1692" s="3" t="s">
+        <v>4264</v>
+      </c>
+      <c r="H1692" s="3"/>
+      <c r="I1692" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1692" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1692" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1692" s="3"/>
+      <c r="M1692" s="3"/>
+      <c r="N1692" s="3"/>
+    </row>
+    <row r="1693" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1693" s="3" t="s">
+        <v>4265</v>
+      </c>
+      <c r="B1693" s="3"/>
+      <c r="C1693" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1693" s="3">
+        <v>5967211022</v>
+      </c>
+      <c r="E1693" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1693" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="G1693" s="3" t="s">
+        <v>4266</v>
+      </c>
+      <c r="H1693" s="3"/>
+      <c r="I1693" s="3">
+        <v>15</v>
+      </c>
+      <c r="J1693" s="3"/>
+      <c r="K1693" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1693" s="3"/>
+      <c r="M1693" s="3"/>
+      <c r="N1693" s="3"/>
+    </row>
+    <row r="1694" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1694" s="3" t="s">
+        <v>4267</v>
+      </c>
+      <c r="B1694" s="3"/>
+      <c r="C1694" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1694" s="3">
+        <v>5967230493</v>
+      </c>
+      <c r="E1694" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1694" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="G1694" s="3" t="s">
+        <v>4268</v>
+      </c>
+      <c r="H1694" s="3"/>
+      <c r="I1694" s="3">
+        <v>73</v>
+      </c>
+      <c r="J1694" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1694" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1694" s="3"/>
+      <c r="M1694" s="3"/>
+      <c r="N1694" s="3"/>
+    </row>
+    <row r="1695" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1695" s="3" t="s">
+        <v>4269</v>
+      </c>
+      <c r="B1695" s="3"/>
+      <c r="C1695" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1695" s="3">
+        <v>5967434115</v>
+      </c>
+      <c r="E1695" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1695" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="G1695" s="3" t="s">
+        <v>949</v>
+      </c>
+      <c r="H1695" s="3"/>
+      <c r="I1695" s="3">
+        <v>23</v>
+      </c>
+      <c r="J1695" s="3"/>
+      <c r="K1695" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1695" s="3"/>
+      <c r="M1695" s="3"/>
+      <c r="N1695" s="3"/>
+    </row>
+    <row r="1696" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1696" s="3" t="s">
+        <v>4270</v>
+      </c>
+      <c r="B1696" s="3"/>
+      <c r="C1696" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1696" s="3">
+        <v>5967442930</v>
+      </c>
+      <c r="E1696" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1696" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="G1696" s="3" t="s">
+        <v>4271</v>
+      </c>
+      <c r="H1696" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1696" s="3">
+        <v>76</v>
+      </c>
+      <c r="J1696" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1696" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1696" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1696" s="3" t="s">
+        <v>4272</v>
+      </c>
+      <c r="N1696" s="3"/>
+    </row>
+    <row r="1697" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1697" s="3" t="s">
+        <v>4273</v>
+      </c>
+      <c r="B1697" s="3"/>
+      <c r="C1697" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1697" s="3">
+        <v>5967478692</v>
+      </c>
+      <c r="E1697" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1697" s="3" t="s">
+        <v>1909</v>
+      </c>
+      <c r="G1697" s="3" t="s">
+        <v>4274</v>
+      </c>
+      <c r="H1697" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1697" s="3">
+        <v>61</v>
+      </c>
+      <c r="J1697" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1697" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1697" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1697" s="3" t="s">
+        <v>4250</v>
+      </c>
+      <c r="N1697" s="3"/>
+    </row>
+    <row r="1698" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1698" s="3" t="s">
+        <v>4275</v>
+      </c>
+      <c r="B1698" s="3"/>
+      <c r="C1698" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1698" s="3">
+        <v>5967498055</v>
+      </c>
+      <c r="E1698" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1698" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1698" s="3" t="s">
+        <v>4276</v>
+      </c>
+      <c r="H1698" s="3"/>
+      <c r="I1698" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1698" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1698" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1698" s="3"/>
+      <c r="M1698" s="3"/>
+      <c r="N1698" s="3"/>
+    </row>
+    <row r="1699" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1699" s="3" t="s">
+        <v>4277</v>
+      </c>
+      <c r="B1699" s="3"/>
+      <c r="C1699" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1699" s="3">
+        <v>5967524795</v>
+      </c>
+      <c r="E1699" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1699" s="3" t="s">
+        <v>1419</v>
+      </c>
+      <c r="G1699" s="3" t="s">
+        <v>4278</v>
+      </c>
+      <c r="H1699" s="3"/>
+      <c r="I1699" s="3">
+        <v>23</v>
+      </c>
+      <c r="J1699" s="3"/>
+      <c r="K1699" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1699" s="3"/>
+      <c r="M1699" s="3"/>
+      <c r="N1699" s="3"/>
+    </row>
+    <row r="1700" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1700" s="3" t="s">
+        <v>4250</v>
+      </c>
+      <c r="B1700" s="3"/>
+      <c r="C1700" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1700" s="3">
+        <v>5967832770</v>
+      </c>
+      <c r="E1700" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1700" s="3" t="s">
+        <v>4279</v>
+      </c>
+      <c r="G1700" s="3" t="s">
+        <v>4280</v>
+      </c>
+      <c r="H1700" s="3"/>
+      <c r="I1700" s="3">
+        <v>71</v>
+      </c>
+      <c r="J1700" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1700" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1700" s="3"/>
+      <c r="M1700" s="3"/>
+      <c r="N1700" s="3"/>
+    </row>
+    <row r="1701" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1701" s="3" t="s">
+        <v>4281</v>
+      </c>
+      <c r="B1701" s="3"/>
+      <c r="C1701" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1701" s="3">
+        <v>5968327292</v>
+      </c>
+      <c r="E1701" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1701" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1701" s="3" t="s">
+        <v>4282</v>
+      </c>
+      <c r="H1701" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1701" s="3">
+        <v>25</v>
+      </c>
+      <c r="J1701" s="3"/>
+      <c r="K1701" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1701" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1701" s="3" t="s">
+        <v>4283</v>
+      </c>
+      <c r="N1701" s="3"/>
+    </row>
+    <row r="1702" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1702" s="3" t="s">
+        <v>4284</v>
+      </c>
+      <c r="B1702" s="3"/>
+      <c r="C1702" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1702" s="3">
+        <v>5968343529</v>
+      </c>
+      <c r="E1702" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1702" s="3" t="s">
+        <v>1654</v>
+      </c>
+      <c r="G1702" s="3" t="s">
+        <v>4285</v>
+      </c>
+      <c r="H1702" s="3"/>
+      <c r="I1702" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1702" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1702" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1702" s="3"/>
+      <c r="M1702" s="3"/>
+      <c r="N1702" s="3"/>
+    </row>
+    <row r="1703" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1703" s="3" t="s">
+        <v>4286</v>
+      </c>
+      <c r="B1703" s="3"/>
+      <c r="C1703" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1703" s="3">
+        <v>5968368203</v>
+      </c>
+      <c r="E1703" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1703" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="G1703" s="3" t="s">
+        <v>4287</v>
+      </c>
+      <c r="H1703" s="3"/>
+      <c r="I1703" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1703" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1703" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1703" s="3"/>
+      <c r="M1703" s="3"/>
+      <c r="N1703" s="3"/>
+    </row>
+    <row r="1704" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1704" s="3" t="s">
+        <v>4288</v>
+      </c>
+      <c r="B1704" s="3"/>
+      <c r="C1704" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1704" s="3">
+        <v>5970160620</v>
+      </c>
+      <c r="E1704" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1704" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="G1704" s="3" t="s">
+        <v>4289</v>
+      </c>
+      <c r="H1704" s="3"/>
+      <c r="I1704" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1704" s="3"/>
+      <c r="K1704" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1704" s="3"/>
+      <c r="M1704" s="3"/>
+      <c r="N1704" s="3"/>
+    </row>
+    <row r="1705" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1705" s="3" t="s">
+        <v>4290</v>
+      </c>
+      <c r="B1705" s="3"/>
+      <c r="C1705" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1705" s="3">
+        <v>5971734221</v>
+      </c>
+      <c r="E1705" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1705" s="3" t="s">
+        <v>2161</v>
+      </c>
+      <c r="G1705" s="3" t="s">
+        <v>4291</v>
+      </c>
+      <c r="H1705" s="3"/>
+      <c r="I1705" s="3">
+        <v>52</v>
+      </c>
+      <c r="J1705" s="3">
+        <v>45</v>
+      </c>
+      <c r="K1705" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1705" s="3"/>
+      <c r="M1705" s="3"/>
+      <c r="N1705" s="3"/>
+    </row>
+    <row r="1706" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1706" s="3" t="s">
+        <v>4292</v>
+      </c>
+      <c r="B1706" s="3"/>
+      <c r="C1706" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1706" s="3">
+        <v>5971739505</v>
+      </c>
+      <c r="E1706" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1706" s="3" t="s">
+        <v>2841</v>
+      </c>
+      <c r="G1706" s="3" t="s">
+        <v>4293</v>
+      </c>
+      <c r="H1706" s="3"/>
+      <c r="I1706" s="3">
+        <v>53</v>
+      </c>
+      <c r="J1706" s="3">
+        <v>45</v>
+      </c>
+      <c r="K1706" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1706" s="3"/>
+      <c r="M1706" s="3"/>
+      <c r="N1706" s="3"/>
+    </row>
+    <row r="1707" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1707" s="3" t="s">
+        <v>4294</v>
+      </c>
+      <c r="B1707" s="3"/>
+      <c r="C1707" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1707" s="3">
+        <v>5972780105</v>
+      </c>
+      <c r="E1707" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1707" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G1707" s="3" t="s">
+        <v>4295</v>
+      </c>
+      <c r="H1707" s="3"/>
+      <c r="I1707" s="3">
+        <v>25</v>
+      </c>
+      <c r="J1707" s="3"/>
+      <c r="K1707" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1707" s="3"/>
+      <c r="M1707" s="3"/>
+      <c r="N1707" s="3"/>
+    </row>
+    <row r="1708" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1708" s="3" t="s">
+        <v>4296</v>
+      </c>
+      <c r="B1708" s="3"/>
+      <c r="C1708" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1708" s="3">
+        <v>5973791787</v>
+      </c>
+      <c r="E1708" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1708" s="3" t="s">
+        <v>1779</v>
+      </c>
+      <c r="G1708" s="3" t="s">
+        <v>4297</v>
+      </c>
+      <c r="H1708" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1708" s="3">
+        <v>38</v>
+      </c>
+      <c r="J1708" s="3"/>
+      <c r="K1708" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1708" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1708" s="3" t="s">
+        <v>4298</v>
+      </c>
+      <c r="N1708" s="3"/>
+    </row>
+    <row r="1709" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1709" s="3" t="s">
+        <v>4299</v>
+      </c>
+      <c r="B1709" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C1709" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1709" s="3">
+        <v>5973900633</v>
+      </c>
+      <c r="E1709" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1709" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="G1709" s="3" t="s">
+        <v>4300</v>
+      </c>
+      <c r="H1709" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1709" s="3">
+        <v>53</v>
+      </c>
+      <c r="J1709" s="3"/>
+      <c r="K1709" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1709" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1709" s="3" t="s">
+        <v>4301</v>
+      </c>
+      <c r="N1709" s="3"/>
+    </row>
+    <row r="1710" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1710" s="3" t="s">
+        <v>4302</v>
+      </c>
+      <c r="B1710" s="3"/>
+      <c r="C1710" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1710" s="3">
+        <v>5973936595</v>
+      </c>
+      <c r="E1710" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1710" s="3" t="s">
+        <v>2360</v>
+      </c>
+      <c r="G1710" s="3" t="s">
+        <v>4303</v>
+      </c>
+      <c r="H1710" s="3"/>
+      <c r="I1710" s="3">
+        <v>3</v>
+      </c>
+      <c r="J1710" s="3"/>
+      <c r="K1710" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1710" s="3"/>
+      <c r="M1710" s="3"/>
+      <c r="N1710" s="3"/>
+    </row>
+    <row r="1711" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1711" s="3" t="s">
+        <v>4304</v>
+      </c>
+      <c r="B1711" s="3"/>
+      <c r="C1711" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1711" s="3">
+        <v>5975212020</v>
+      </c>
+      <c r="E1711" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1711" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="G1711" s="3" t="s">
+        <v>4305</v>
+      </c>
+      <c r="H1711" s="3"/>
+      <c r="I1711" s="3">
+        <v>18</v>
+      </c>
+      <c r="J1711" s="3"/>
+      <c r="K1711" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1711" s="3"/>
+      <c r="M1711" s="3"/>
+      <c r="N1711" s="3"/>
+    </row>
+    <row r="1712" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1712" s="3" t="s">
+        <v>4306</v>
+      </c>
+      <c r="B1712" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1712" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1712" s="3">
+        <v>5975296316</v>
+      </c>
+      <c r="E1712" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1712" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G1712" s="3" t="s">
+        <v>4307</v>
+      </c>
+      <c r="H1712" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1712" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1712" s="3"/>
+      <c r="K1712" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1712" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1712" s="3" t="s">
+        <v>4308</v>
+      </c>
+      <c r="N1712" s="3" t="s">
+        <v>4309</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1713" s="3" t="s">
+        <v>4310</v>
+      </c>
+      <c r="B1713" s="3"/>
+      <c r="C1713" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1713" s="3">
+        <v>5975382377</v>
+      </c>
+      <c r="E1713" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1713" s="3" t="s">
+        <v>1306</v>
+      </c>
+      <c r="G1713" s="3" t="s">
+        <v>4311</v>
+      </c>
+      <c r="H1713" s="3"/>
+      <c r="I1713" s="3">
+        <v>82</v>
+      </c>
+      <c r="J1713" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1713" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1713" s="3"/>
+      <c r="M1713" s="3"/>
+      <c r="N1713" s="3"/>
+    </row>
+    <row r="1714" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1714" s="3" t="s">
+        <v>4312</v>
+      </c>
+      <c r="B1714" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1714" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1714" s="3">
+        <v>5975400435</v>
+      </c>
+      <c r="E1714" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1714" s="3" t="s">
+        <v>4313</v>
+      </c>
+      <c r="G1714" s="3" t="s">
+        <v>4314</v>
+      </c>
+      <c r="H1714" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1714" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1714" s="3"/>
+      <c r="K1714" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1714" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1714" s="3" t="s">
+        <v>4309</v>
+      </c>
+      <c r="N1714" s="3" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1715" s="3" t="s">
+        <v>4316</v>
+      </c>
+      <c r="B1715" s="3"/>
+      <c r="C1715" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1715" s="3">
+        <v>5975414714</v>
+      </c>
+      <c r="E1715" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1715" s="3" t="s">
+        <v>4317</v>
+      </c>
+      <c r="G1715" s="3" t="s">
+        <v>4318</v>
+      </c>
+      <c r="H1715" s="3"/>
+      <c r="I1715" s="3">
+        <v>84</v>
+      </c>
+      <c r="J1715" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1715" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1715" s="3"/>
+      <c r="M1715" s="3"/>
+      <c r="N1715" s="3"/>
+    </row>
+    <row r="1716" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1716" s="3" t="s">
+        <v>4319</v>
+      </c>
+      <c r="B1716" s="3"/>
+      <c r="C1716" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1716" s="3">
+        <v>5976387910</v>
+      </c>
+      <c r="E1716" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1716" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="G1716" s="3" t="s">
+        <v>4320</v>
+      </c>
+      <c r="H1716" s="3"/>
+      <c r="I1716" s="3">
+        <v>25</v>
+      </c>
+      <c r="J1716" s="3"/>
+      <c r="K1716" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1716" s="3"/>
+      <c r="M1716" s="3"/>
+      <c r="N1716" s="3"/>
+    </row>
+    <row r="1717" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1717" s="3" t="s">
+        <v>4321</v>
+      </c>
+      <c r="B1717" s="3"/>
+      <c r="C1717" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1717" s="3">
+        <v>5976800463</v>
+      </c>
+      <c r="E1717" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1717" s="3" t="s">
+        <v>1804</v>
+      </c>
+      <c r="G1717" s="3" t="s">
+        <v>4322</v>
+      </c>
+      <c r="H1717" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1717" s="3">
+        <v>8</v>
+      </c>
+      <c r="J1717" s="3"/>
+      <c r="K1717" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1717" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1717" s="3" t="s">
+        <v>4309</v>
+      </c>
+      <c r="N1717" s="3"/>
+    </row>
+    <row r="1718" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1718" s="3" t="s">
+        <v>4323</v>
+      </c>
+      <c r="B1718" s="3"/>
+      <c r="C1718" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1718" s="3">
+        <v>5977098192</v>
+      </c>
+      <c r="E1718" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1718" s="3" t="s">
+        <v>4324</v>
+      </c>
+      <c r="G1718" s="3" t="s">
+        <v>4325</v>
+      </c>
+      <c r="H1718" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1718" s="3">
+        <v>7</v>
+      </c>
+      <c r="J1718" s="3"/>
+      <c r="K1718" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1718" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1718" s="3" t="s">
+        <v>4309</v>
+      </c>
+      <c r="N1718" s="3"/>
+    </row>
+    <row r="1719" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1719" s="3" t="s">
+        <v>4326</v>
+      </c>
+      <c r="B1719" s="3"/>
+      <c r="C1719" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1719" s="3">
+        <v>5978211556</v>
+      </c>
+      <c r="E1719" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1719" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G1719" s="3" t="s">
+        <v>4327</v>
+      </c>
+      <c r="H1719" s="3"/>
+      <c r="I1719" s="3"/>
+      <c r="J1719" s="3"/>
+      <c r="K1719" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1719" s="3"/>
+      <c r="M1719" s="3"/>
+      <c r="N1719" s="3"/>
+    </row>
+    <row r="1720" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1720" s="3" t="s">
+        <v>4328</v>
+      </c>
+      <c r="B1720" s="3"/>
+      <c r="C1720" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1720" s="3">
+        <v>5978580904</v>
+      </c>
+      <c r="E1720" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1720" s="3" t="s">
+        <v>3231</v>
+      </c>
+      <c r="G1720" s="3" t="s">
+        <v>4329</v>
+      </c>
+      <c r="H1720" s="3"/>
+      <c r="I1720" s="3">
+        <v>31</v>
+      </c>
+      <c r="J1720" s="3"/>
+      <c r="K1720" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1720" s="3"/>
+      <c r="M1720" s="3"/>
+      <c r="N1720" s="3"/>
+    </row>
+    <row r="1721" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1721" s="3" t="s">
+        <v>4330</v>
+      </c>
+      <c r="B1721" s="3"/>
+      <c r="C1721" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1721" s="3">
+        <v>5979280763</v>
+      </c>
+      <c r="E1721" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1721" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="G1721" s="3" t="s">
+        <v>4331</v>
+      </c>
+      <c r="H1721" s="3"/>
+      <c r="I1721" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1721" s="3"/>
+      <c r="K1721" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1721" s="3"/>
+      <c r="M1721" s="3"/>
+      <c r="N1721" s="3"/>
+    </row>
+    <row r="1722" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1722" s="3" t="s">
+        <v>4332</v>
+      </c>
+      <c r="B1722" s="3"/>
+      <c r="C1722" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1722" s="3">
+        <v>5982658953</v>
+      </c>
+      <c r="E1722" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1722" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="G1722" s="3" t="s">
+        <v>4333</v>
+      </c>
+      <c r="H1722" s="3"/>
+      <c r="I1722" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1722" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1722" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1722" s="3"/>
+      <c r="M1722" s="3"/>
+      <c r="N1722" s="3"/>
+    </row>
+    <row r="1723" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1723" s="3" t="s">
+        <v>4334</v>
+      </c>
+      <c r="B1723" s="3"/>
+      <c r="C1723" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1723" s="3">
+        <v>5982665419</v>
+      </c>
+      <c r="E1723" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1723" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="G1723" s="3" t="s">
+        <v>4335</v>
+      </c>
+      <c r="H1723" s="3"/>
+      <c r="I1723" s="3">
+        <v>71</v>
+      </c>
+      <c r="J1723" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1723" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1723" s="3"/>
+      <c r="M1723" s="3"/>
+      <c r="N1723" s="3"/>
+    </row>
+    <row r="1724" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1724" s="3" t="s">
+        <v>4336</v>
+      </c>
+      <c r="B1724" s="3"/>
+      <c r="C1724" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1724" s="3">
+        <v>5982692018</v>
+      </c>
+      <c r="E1724" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1724" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="G1724" s="3" t="s">
+        <v>4337</v>
+      </c>
+      <c r="H1724" s="3"/>
+      <c r="I1724" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1724" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1724" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1724" s="3"/>
+      <c r="M1724" s="3"/>
+      <c r="N1724" s="3"/>
+    </row>
+    <row r="1725" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1725" s="3" t="s">
+        <v>4338</v>
+      </c>
+      <c r="B1725" s="3"/>
+      <c r="C1725" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1725" s="3">
+        <v>5982698927</v>
+      </c>
+      <c r="E1725" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1725" s="3" t="s">
+        <v>3114</v>
+      </c>
+      <c r="G1725" s="3" t="s">
+        <v>4339</v>
+      </c>
+      <c r="H1725" s="3"/>
+      <c r="I1725" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1725" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1725" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1725" s="3"/>
+      <c r="M1725" s="3"/>
+      <c r="N1725" s="3"/>
+    </row>
+    <row r="1726" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1726" s="3" t="s">
+        <v>4340</v>
+      </c>
+      <c r="B1726" s="3"/>
+      <c r="C1726" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1726" s="3">
+        <v>5983417741</v>
+      </c>
+      <c r="E1726" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1726" s="3" t="s">
+        <v>1968</v>
+      </c>
+      <c r="G1726" s="3" t="s">
+        <v>4341</v>
+      </c>
+      <c r="H1726" s="3"/>
+      <c r="I1726" s="3">
+        <v>56</v>
+      </c>
+      <c r="J1726" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1726" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1726" s="3"/>
+      <c r="M1726" s="3"/>
+      <c r="N1726" s="3"/>
+    </row>
+    <row r="1727" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1727" s="3" t="s">
+        <v>4342</v>
+      </c>
+      <c r="B1727" s="3"/>
+      <c r="C1727" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1727" s="3">
+        <v>5985181341</v>
+      </c>
+      <c r="E1727" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1727" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1727" s="3" t="s">
+        <v>4343</v>
+      </c>
+      <c r="H1727" s="3"/>
+      <c r="I1727" s="3">
+        <v>28</v>
+      </c>
+      <c r="J1727" s="3"/>
+      <c r="K1727" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1727" s="3"/>
+      <c r="M1727" s="3"/>
+      <c r="N1727" s="3"/>
+    </row>
+    <row r="1728" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1728" s="3" t="s">
+        <v>4344</v>
+      </c>
+      <c r="B1728" s="3"/>
+      <c r="C1728" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1728" s="3">
+        <v>5988569759</v>
+      </c>
+      <c r="E1728" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1728" s="3" t="s">
+        <v>4345</v>
+      </c>
+      <c r="G1728" s="3" t="s">
+        <v>4346</v>
+      </c>
+      <c r="H1728" s="3"/>
+      <c r="I1728" s="3">
+        <v>56</v>
+      </c>
+      <c r="J1728" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1728" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1728" s="3"/>
+      <c r="M1728" s="3"/>
+      <c r="N1728" s="3"/>
+    </row>
+    <row r="1729" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1729" s="3" t="s">
+        <v>4347</v>
+      </c>
+      <c r="B1729" s="3"/>
+      <c r="C1729" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1729" s="3">
+        <v>5988588532</v>
+      </c>
+      <c r="E1729" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="F1729" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="G1729" s="3" t="s">
+        <v>4348</v>
+      </c>
+      <c r="H1729" s="3"/>
+      <c r="I1729" s="3">
+        <v>42</v>
+      </c>
+      <c r="J1729" s="3"/>
+      <c r="K1729" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1729" s="3"/>
+      <c r="M1729" s="3"/>
+      <c r="N1729" s="3"/>
+    </row>
+    <row r="1730" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1730" s="3" t="s">
+        <v>4349</v>
+      </c>
+      <c r="B1730" s="3"/>
+      <c r="C1730" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1730" s="3">
+        <v>5988599649</v>
+      </c>
+      <c r="E1730" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F1730" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G1730" s="3" t="s">
+        <v>4350</v>
+      </c>
+      <c r="H1730" s="3"/>
+      <c r="I1730" s="3"/>
+      <c r="J1730" s="3"/>
+      <c r="K1730" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1730" s="3"/>
+      <c r="M1730" s="3"/>
+      <c r="N1730" s="3"/>
+    </row>
+    <row r="1731" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1731" s="3" t="s">
+        <v>4351</v>
+      </c>
+      <c r="B1731" s="3"/>
+      <c r="C1731" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1731" s="3">
+        <v>5988615757</v>
+      </c>
+      <c r="E1731" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1731" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G1731" s="3" t="s">
+        <v>4352</v>
+      </c>
+      <c r="H1731" s="3"/>
+      <c r="I1731" s="3">
+        <v>8</v>
+      </c>
+      <c r="J1731" s="3"/>
+      <c r="K1731" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1731" s="3"/>
+      <c r="M1731" s="3"/>
+      <c r="N1731" s="3"/>
+    </row>
+    <row r="1732" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1732" s="3" t="s">
+        <v>4353</v>
+      </c>
+      <c r="B1732" s="3"/>
+      <c r="C1732" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1732" s="3">
+        <v>5988619573</v>
+      </c>
+      <c r="E1732" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1732" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="G1732" s="3" t="s">
+        <v>4354</v>
+      </c>
+      <c r="H1732" s="3"/>
+      <c r="I1732" s="3">
+        <v>35</v>
+      </c>
+      <c r="J1732" s="3"/>
+      <c r="K1732" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1732" s="3"/>
+      <c r="M1732" s="3"/>
+      <c r="N1732" s="3"/>
+    </row>
+    <row r="1733" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1733" s="3" t="s">
+        <v>4355</v>
+      </c>
+      <c r="B1733" s="3"/>
+      <c r="C1733" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1733" s="3">
+        <v>5988838292</v>
+      </c>
+      <c r="E1733" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1733" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="G1733" s="3" t="s">
+        <v>4356</v>
+      </c>
+      <c r="H1733" s="3"/>
+      <c r="I1733" s="3">
+        <v>41</v>
+      </c>
+      <c r="J1733" s="3"/>
+      <c r="K1733" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1733" s="3"/>
+      <c r="M1733" s="3"/>
+      <c r="N1733" s="3"/>
+    </row>
+    <row r="1734" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1734" s="3" t="s">
+        <v>4357</v>
+      </c>
+      <c r="B1734" s="3"/>
+      <c r="C1734" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1734" s="3">
+        <v>5988931206</v>
+      </c>
+      <c r="E1734" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1734" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1734" s="3" t="s">
+        <v>4358</v>
+      </c>
+      <c r="H1734" s="3"/>
+      <c r="I1734" s="3">
+        <v>32</v>
+      </c>
+      <c r="J1734" s="3"/>
+      <c r="K1734" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1734" s="3"/>
+      <c r="M1734" s="3"/>
+      <c r="N1734" s="3"/>
+    </row>
+    <row r="1735" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1735" s="3" t="s">
+        <v>4359</v>
+      </c>
+      <c r="B1735" s="3"/>
+      <c r="C1735" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1735" s="3">
+        <v>5989124583</v>
+      </c>
+      <c r="E1735" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1735" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1735" s="3" t="s">
+        <v>4360</v>
+      </c>
+      <c r="H1735" s="3"/>
+      <c r="I1735" s="3">
+        <v>33</v>
+      </c>
+      <c r="J1735" s="3"/>
+      <c r="K1735" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1735" s="3"/>
+      <c r="M1735" s="3"/>
+      <c r="N1735" s="3"/>
+    </row>
+    <row r="1736" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1736" s="3" t="s">
+        <v>4361</v>
+      </c>
+      <c r="B1736" s="3"/>
+      <c r="C1736" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1736" s="3">
+        <v>5989125536</v>
+      </c>
+      <c r="E1736" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1736" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G1736" s="3" t="s">
+        <v>4362</v>
+      </c>
+      <c r="H1736" s="3"/>
+      <c r="I1736" s="3">
+        <v>16</v>
+      </c>
+      <c r="J1736" s="3"/>
+      <c r="K1736" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1736" s="3"/>
+      <c r="M1736" s="3"/>
+      <c r="N1736" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Curtis-Garage-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3538CBBB-468A-4A06-848D-F0CE914019F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{07787563-9BCD-42E0-8032-BBAE9E4F8AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="3240" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10600" uniqueCount="4363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11035" uniqueCount="4550">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -13006,6 +13006,9 @@
     <t>39.523525, -86.810090</t>
   </si>
   <si>
+    <t>06/21/26 22:24 EDT</t>
+  </si>
+  <si>
     <t>06/19/26 07:23 EDT</t>
   </si>
   <si>
@@ -13069,6 +13072,9 @@
     <t>39.545850, -86.729060</t>
   </si>
   <si>
+    <t>06/21/26 22:25 EDT</t>
+  </si>
+  <si>
     <t>06/20/26 21:43 EDT</t>
   </si>
   <si>
@@ -13081,6 +13087,9 @@
     <t>39.530563, -86.802990</t>
   </si>
   <si>
+    <t>06/22/26 12:10 EDT</t>
+  </si>
+  <si>
     <t>06/20/26 21:54 EDT</t>
   </si>
   <si>
@@ -13099,16 +13108,568 @@
     <t>39.528000, -86.877240</t>
   </si>
   <si>
+    <t>06/21/26 22:26 EDT</t>
+  </si>
+  <si>
     <t>06/21/26 05:14 EDT</t>
   </si>
   <si>
     <t>39.505913, -86.549560</t>
   </si>
   <si>
+    <t>06/21/26 22:27 EDT</t>
+  </si>
+  <si>
     <t>06/21/26 05:15 EDT</t>
   </si>
   <si>
     <t>39.506153, -86.563550</t>
+  </si>
+  <si>
+    <t>06/22/26 05:50 EDT</t>
+  </si>
+  <si>
+    <t>39.564800, -86.608060</t>
+  </si>
+  <si>
+    <t>06/22/26 12:34 EDT</t>
+  </si>
+  <si>
+    <t>06/22/26 13:40 EDT</t>
+  </si>
+  <si>
+    <t>06/22/26 07:56 EDT</t>
+  </si>
+  <si>
+    <t>39.558025, -86.743190</t>
+  </si>
+  <si>
+    <t>06/23/26 08:28 EDT</t>
+  </si>
+  <si>
+    <t>06/22/26 08:06 EDT</t>
+  </si>
+  <si>
+    <t>39.579400, -86.638500</t>
+  </si>
+  <si>
+    <t>06/22/26 10:10 EDT</t>
+  </si>
+  <si>
+    <t>39.567978, -86.633410</t>
+  </si>
+  <si>
+    <t>06/23/26 08:38 EDT</t>
+  </si>
+  <si>
+    <t>06/22/26 11:06 EDT</t>
+  </si>
+  <si>
+    <t>39.569435, -86.632100</t>
+  </si>
+  <si>
+    <t>06/22/26 11:15 EDT</t>
+  </si>
+  <si>
+    <t>39.579086, -86.540660</t>
+  </si>
+  <si>
+    <t>06/22/26 12:12 EDT</t>
+  </si>
+  <si>
+    <t>1.5mi NE of Plainfield IN</t>
+  </si>
+  <si>
+    <t>39.712353, -86.354910</t>
+  </si>
+  <si>
+    <t>06/22/26 12:22 EDT</t>
+  </si>
+  <si>
+    <t>39.637640, -86.433650</t>
+  </si>
+  <si>
+    <t>06/22/26 13:06 EDT</t>
+  </si>
+  <si>
+    <t>11.3mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.486122, -86.785010</t>
+  </si>
+  <si>
+    <t>06/22/26 13:21 EDT</t>
+  </si>
+  <si>
+    <t>39.568027, -86.633610</t>
+  </si>
+  <si>
+    <t>06/23/26 08:29 EDT</t>
+  </si>
+  <si>
+    <t>06/22/26 15:01 EDT</t>
+  </si>
+  <si>
+    <t>39.580917, -86.591900</t>
+  </si>
+  <si>
+    <t>06/23/26 08:45 EDT</t>
+  </si>
+  <si>
+    <t>06/22/26 15:59 EDT</t>
+  </si>
+  <si>
+    <t>1.1mi N of Plainfield IN</t>
+  </si>
+  <si>
+    <t>39.711790, -86.370090</t>
+  </si>
+  <si>
+    <t>06/22/26 16:32 EDT</t>
+  </si>
+  <si>
+    <t>5.5mi SE of Brazil IN</t>
+  </si>
+  <si>
+    <t>39.466908, -87.050340</t>
+  </si>
+  <si>
+    <t>06/23/26 08:33 EDT</t>
+  </si>
+  <si>
+    <t>06/22/26 17:22 EDT</t>
+  </si>
+  <si>
+    <t>2.6mi NW of Terre Haute IN</t>
+  </si>
+  <si>
+    <t>39.496758, -87.401726</t>
+  </si>
+  <si>
+    <t>06/23/26 08:34 EDT</t>
+  </si>
+  <si>
+    <t>06/22/26 18:27 EDT</t>
+  </si>
+  <si>
+    <t>39.557335, -86.674730</t>
+  </si>
+  <si>
+    <t>06/22/26 20:19 EDT</t>
+  </si>
+  <si>
+    <t>39.564840, -86.615990</t>
+  </si>
+  <si>
+    <t>06/22/26 20:24 EDT</t>
+  </si>
+  <si>
+    <t>39.535660, -86.577260</t>
+  </si>
+  <si>
+    <t>06/23/26 08:14 EDT</t>
+  </si>
+  <si>
+    <t>39.590030, -86.628910</t>
+  </si>
+  <si>
+    <t>06/23/26 09:38 EDT</t>
+  </si>
+  <si>
+    <t>2.9mi SE of Plainfield IN</t>
+  </si>
+  <si>
+    <t>39.677710, -86.322730</t>
+  </si>
+  <si>
+    <t>06/23/26 11:06 EDT</t>
+  </si>
+  <si>
+    <t>39.647568, -86.409190</t>
+  </si>
+  <si>
+    <t>06/24/26 08:09 EDT</t>
+  </si>
+  <si>
+    <t>06/23/26 12:25 EDT</t>
+  </si>
+  <si>
+    <t>3.2mi E of Plainfield IN</t>
+  </si>
+  <si>
+    <t>39.692060, -86.310875</t>
+  </si>
+  <si>
+    <t>06/24/26 08:18 EDT</t>
+  </si>
+  <si>
+    <t>06/24/26 08:21 EDT</t>
+  </si>
+  <si>
+    <t>06/23/26 14:53 EDT</t>
+  </si>
+  <si>
+    <t>39.520927, -86.564060</t>
+  </si>
+  <si>
+    <t>06/23/26 14:57 EDT</t>
+  </si>
+  <si>
+    <t>2mi N of Greenfield IN</t>
+  </si>
+  <si>
+    <t>39.820870, -85.787420</t>
+  </si>
+  <si>
+    <t>06/23/26 15:07 EDT</t>
+  </si>
+  <si>
+    <t>3.4mi W of Cumberland IN</t>
+  </si>
+  <si>
+    <t>39.801020, -86.005430</t>
+  </si>
+  <si>
+    <t>06/23/26 15:21 EDT</t>
+  </si>
+  <si>
+    <t>1.8mi SW of Indianapolis IN</t>
+  </si>
+  <si>
+    <t>39.753600, -86.159990</t>
+  </si>
+  <si>
+    <t>06/23/26 15:22 EDT</t>
+  </si>
+  <si>
+    <t>39.754440, -86.180130</t>
+  </si>
+  <si>
+    <t>06/23/26 16:25 EDT</t>
+  </si>
+  <si>
+    <t>4.5mi NW of Mooresville IN</t>
+  </si>
+  <si>
+    <t>39.632980, -86.442340</t>
+  </si>
+  <si>
+    <t>06/23/26 18:57 EDT</t>
+  </si>
+  <si>
+    <t>5.9mi NE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.683000, -86.743390</t>
+  </si>
+  <si>
+    <t>06/24/26 06:32 EDT</t>
+  </si>
+  <si>
+    <t>39.634876, -86.649820</t>
+  </si>
+  <si>
+    <t>06/24/26 08:00 EDT</t>
+  </si>
+  <si>
+    <t>06/24/26 06:39 EDT</t>
+  </si>
+  <si>
+    <t>39.564530, -86.643040</t>
+  </si>
+  <si>
+    <t>06/24/26 06:46 EDT</t>
+  </si>
+  <si>
+    <t>39.558758, -86.666000</t>
+  </si>
+  <si>
+    <t>06/24/26 08:29 EDT</t>
+  </si>
+  <si>
+    <t>39.528008, -86.877240</t>
+  </si>
+  <si>
+    <t>06/24/26 17:31 EDT</t>
+  </si>
+  <si>
+    <t>39.557003, -86.677830</t>
+  </si>
+  <si>
+    <t>06/24/26 22:51 EDT</t>
+  </si>
+  <si>
+    <t>39.565025, -86.631980</t>
+  </si>
+  <si>
+    <t>06/25/26 00:00 EDT</t>
+  </si>
+  <si>
+    <t>39.533497, -86.804855</t>
+  </si>
+  <si>
+    <t>06/25/26 07:36 EDT</t>
+  </si>
+  <si>
+    <t>06/25/26 00:01 EDT</t>
+  </si>
+  <si>
+    <t>39.529682, -86.802280</t>
+  </si>
+  <si>
+    <t>06/25/26 07:54 EDT</t>
+  </si>
+  <si>
+    <t>39.511906, -86.641945</t>
+  </si>
+  <si>
+    <t>06/25/26 21:15 EDT</t>
+  </si>
+  <si>
+    <t>06/25/26 09:16 EDT</t>
+  </si>
+  <si>
+    <t>39.568317, -86.633630</t>
+  </si>
+  <si>
+    <t>06/25/26 21:10 EDT</t>
+  </si>
+  <si>
+    <t>06/25/26 14:45 EDT</t>
+  </si>
+  <si>
+    <t>39.571300, -86.628340</t>
+  </si>
+  <si>
+    <t>06/25/26 15:18 EDT</t>
+  </si>
+  <si>
+    <t>39.549034, -86.717790</t>
+  </si>
+  <si>
+    <t>06/25/26 15:25 EDT</t>
+  </si>
+  <si>
+    <t>39.684550, -86.462260</t>
+  </si>
+  <si>
+    <t>06/25/26 16:24 EDT</t>
+  </si>
+  <si>
+    <t>5mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>39.622900, -86.458210</t>
+  </si>
+  <si>
+    <t>06/25/26 16:30 EDT</t>
+  </si>
+  <si>
+    <t>39.585255, -86.577410</t>
+  </si>
+  <si>
+    <t>06/25/26 21:21 EDT</t>
+  </si>
+  <si>
+    <t>06/25/26 21:26 EDT</t>
+  </si>
+  <si>
+    <t>06/25/26 17:26 EDT</t>
+  </si>
+  <si>
+    <t>39.630310, -86.669716</t>
+  </si>
+  <si>
+    <t>06/26/26 06:54 EDT</t>
+  </si>
+  <si>
+    <t>39.568172, -86.632170</t>
+  </si>
+  <si>
+    <t>06/26/26 07:35 EDT</t>
+  </si>
+  <si>
+    <t>06/26/26 07:37 EDT</t>
+  </si>
+  <si>
+    <t>39.710236, -86.669850</t>
+  </si>
+  <si>
+    <t>06/26/26 07:52 EDT</t>
+  </si>
+  <si>
+    <t>39.579350, -86.631910</t>
+  </si>
+  <si>
+    <t>06/26/26 12:07 EDT</t>
+  </si>
+  <si>
+    <t>39.589073, -86.559950</t>
+  </si>
+  <si>
+    <t>2.6mi W of Plainfield IN</t>
+  </si>
+  <si>
+    <t>39.682827, -86.418470</t>
+  </si>
+  <si>
+    <t>06/26/26 12:11 EDT</t>
+  </si>
+  <si>
+    <t>39.619995, -86.462290</t>
+  </si>
+  <si>
+    <t>06/26/26 12:32 EDT</t>
+  </si>
+  <si>
+    <t>3.2mi S of Beech Grove IN</t>
+  </si>
+  <si>
+    <t>39.670200, -86.096280</t>
+  </si>
+  <si>
+    <t>06/26/26 12:49 EDT</t>
+  </si>
+  <si>
+    <t>2.7mi NE of Greenwood IN</t>
+  </si>
+  <si>
+    <t>39.633102, -86.077990</t>
+  </si>
+  <si>
+    <t>06/26/26 13:07 EDT</t>
+  </si>
+  <si>
+    <t>6.2mi E of Plainfield IN</t>
+  </si>
+  <si>
+    <t>39.696910, -86.254166</t>
+  </si>
+  <si>
+    <t>06/26/26 13:30 EDT</t>
+  </si>
+  <si>
+    <t>39.552074, -86.706970</t>
+  </si>
+  <si>
+    <t>06/26/26 13:35 EDT</t>
+  </si>
+  <si>
+    <t>39.533030, -86.819405</t>
+  </si>
+  <si>
+    <t>06/26/26 13:37 EDT</t>
+  </si>
+  <si>
+    <t>39.531006, -86.861275</t>
+  </si>
+  <si>
+    <t>06/26/26 13:38 EDT</t>
+  </si>
+  <si>
+    <t>39.529263, -86.869040</t>
+  </si>
+  <si>
+    <t>06/26/26 14:42 EDT</t>
+  </si>
+  <si>
+    <t>6.5mi W of Brazil IN</t>
+  </si>
+  <si>
+    <t>39.520927, -87.245400</t>
+  </si>
+  <si>
+    <t>06/26/26 15:22 EDT</t>
+  </si>
+  <si>
+    <t>39.569466, -86.632110</t>
+  </si>
+  <si>
+    <t>06/26/26 19:39 EDT</t>
+  </si>
+  <si>
+    <t>39.499370, -86.661660</t>
+  </si>
+  <si>
+    <t>06/27/26 12:17 EDT</t>
+  </si>
+  <si>
+    <t>5.2mi SW of Carmel IN</t>
+  </si>
+  <si>
+    <t>39.923855, -86.228430</t>
+  </si>
+  <si>
+    <t>06/27/26 12:30 EDT</t>
+  </si>
+  <si>
+    <t>6.3mi SE of Zionsville IN</t>
+  </si>
+  <si>
+    <t>39.909880, -86.260445</t>
+  </si>
+  <si>
+    <t>06/27/26 12:31 EDT</t>
+  </si>
+  <si>
+    <t>6.4mi SE of Zionsville IN</t>
+  </si>
+  <si>
+    <t>39.909160, -86.259920</t>
+  </si>
+  <si>
+    <t>06/27/26 12:56 EDT</t>
+  </si>
+  <si>
+    <t>39.533630, -86.789100</t>
+  </si>
+  <si>
+    <t>06/27/26 20:31 EDT</t>
+  </si>
+  <si>
+    <t>39.595627, -86.530780</t>
+  </si>
+  <si>
+    <t>06/27/26 20:41 EDT</t>
+  </si>
+  <si>
+    <t>39.675520, -86.351290</t>
+  </si>
+  <si>
+    <t>06/27/26 22:21 EDT</t>
+  </si>
+  <si>
+    <t>39.556526, -86.646355</t>
+  </si>
+  <si>
+    <t>06/28/26 02:50 EDT</t>
+  </si>
+  <si>
+    <t>39.525684, -86.809930</t>
+  </si>
+  <si>
+    <t>06/28/26 03:08 EDT</t>
+  </si>
+  <si>
+    <t>39.610016, -86.490870</t>
+  </si>
+  <si>
+    <t>06/28/26 04:10 EDT</t>
+  </si>
+  <si>
+    <t>4.1mi N of Terre Haute IN</t>
+  </si>
+  <si>
+    <t>39.523970, -87.360310</t>
+  </si>
+  <si>
+    <t>06/28/26 04:13 EDT</t>
+  </si>
+  <si>
+    <t>4.6mi N of Terre Haute IN</t>
+  </si>
+  <si>
+    <t>39.532330, -87.369840</t>
   </si>
 </sst>
 </file>
@@ -13470,12 +14031,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1736"/>
+  <dimension ref="A1:N1807"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="14" width="15" customWidth="1"/>
+    <col min="1" max="14" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -73158,19 +73717,25 @@
       <c r="G1719" s="3" t="s">
         <v>4327</v>
       </c>
-      <c r="H1719" s="3"/>
+      <c r="H1719" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1719" s="3"/>
       <c r="J1719" s="3"/>
       <c r="K1719" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1719" s="3"/>
-      <c r="M1719" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1719" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1719" s="3" t="s">
+        <v>4328</v>
+      </c>
       <c r="N1719" s="3"/>
     </row>
     <row r="1720" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1720" s="3" t="s">
-        <v>4328</v>
+        <v>4329</v>
       </c>
       <c r="B1720" s="3"/>
       <c r="C1720" s="3">
@@ -73186,7 +73751,7 @@
         <v>3231</v>
       </c>
       <c r="G1720" s="3" t="s">
-        <v>4329</v>
+        <v>4330</v>
       </c>
       <c r="H1720" s="3"/>
       <c r="I1720" s="3">
@@ -73202,7 +73767,7 @@
     </row>
     <row r="1721" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1721" s="3" t="s">
-        <v>4330</v>
+        <v>4331</v>
       </c>
       <c r="B1721" s="3"/>
       <c r="C1721" s="3">
@@ -73218,7 +73783,7 @@
         <v>531</v>
       </c>
       <c r="G1721" s="3" t="s">
-        <v>4331</v>
+        <v>4332</v>
       </c>
       <c r="H1721" s="3"/>
       <c r="I1721" s="3">
@@ -73234,7 +73799,7 @@
     </row>
     <row r="1722" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1722" s="3" t="s">
-        <v>4332</v>
+        <v>4333</v>
       </c>
       <c r="B1722" s="3"/>
       <c r="C1722" s="3">
@@ -73250,7 +73815,7 @@
         <v>516</v>
       </c>
       <c r="G1722" s="3" t="s">
-        <v>4333</v>
+        <v>4334</v>
       </c>
       <c r="H1722" s="3"/>
       <c r="I1722" s="3">
@@ -73268,7 +73833,7 @@
     </row>
     <row r="1723" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1723" s="3" t="s">
-        <v>4334</v>
+        <v>4335</v>
       </c>
       <c r="B1723" s="3"/>
       <c r="C1723" s="3">
@@ -73284,7 +73849,7 @@
         <v>522</v>
       </c>
       <c r="G1723" s="3" t="s">
-        <v>4335</v>
+        <v>4336</v>
       </c>
       <c r="H1723" s="3"/>
       <c r="I1723" s="3">
@@ -73302,7 +73867,7 @@
     </row>
     <row r="1724" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1724" s="3" t="s">
-        <v>4336</v>
+        <v>4337</v>
       </c>
       <c r="B1724" s="3"/>
       <c r="C1724" s="3">
@@ -73318,7 +73883,7 @@
         <v>492</v>
       </c>
       <c r="G1724" s="3" t="s">
-        <v>4337</v>
+        <v>4338</v>
       </c>
       <c r="H1724" s="3"/>
       <c r="I1724" s="3">
@@ -73336,7 +73901,7 @@
     </row>
     <row r="1725" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1725" s="3" t="s">
-        <v>4338</v>
+        <v>4339</v>
       </c>
       <c r="B1725" s="3"/>
       <c r="C1725" s="3">
@@ -73352,7 +73917,7 @@
         <v>3114</v>
       </c>
       <c r="G1725" s="3" t="s">
-        <v>4339</v>
+        <v>4340</v>
       </c>
       <c r="H1725" s="3"/>
       <c r="I1725" s="3">
@@ -73370,7 +73935,7 @@
     </row>
     <row r="1726" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1726" s="3" t="s">
-        <v>4340</v>
+        <v>4341</v>
       </c>
       <c r="B1726" s="3"/>
       <c r="C1726" s="3">
@@ -73386,7 +73951,7 @@
         <v>1968</v>
       </c>
       <c r="G1726" s="3" t="s">
-        <v>4341</v>
+        <v>4342</v>
       </c>
       <c r="H1726" s="3"/>
       <c r="I1726" s="3">
@@ -73404,7 +73969,7 @@
     </row>
     <row r="1727" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1727" s="3" t="s">
-        <v>4342</v>
+        <v>4343</v>
       </c>
       <c r="B1727" s="3"/>
       <c r="C1727" s="3">
@@ -73420,7 +73985,7 @@
         <v>274</v>
       </c>
       <c r="G1727" s="3" t="s">
-        <v>4343</v>
+        <v>4344</v>
       </c>
       <c r="H1727" s="3"/>
       <c r="I1727" s="3">
@@ -73436,7 +74001,7 @@
     </row>
     <row r="1728" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1728" s="3" t="s">
-        <v>4344</v>
+        <v>4345</v>
       </c>
       <c r="B1728" s="3"/>
       <c r="C1728" s="3">
@@ -73449,10 +74014,10 @@
         <v>17</v>
       </c>
       <c r="F1728" s="3" t="s">
-        <v>4345</v>
+        <v>4346</v>
       </c>
       <c r="G1728" s="3" t="s">
-        <v>4346</v>
+        <v>4347</v>
       </c>
       <c r="H1728" s="3"/>
       <c r="I1728" s="3">
@@ -73470,7 +74035,7 @@
     </row>
     <row r="1729" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1729" s="3" t="s">
-        <v>4347</v>
+        <v>4348</v>
       </c>
       <c r="B1729" s="3"/>
       <c r="C1729" s="3">
@@ -73486,23 +74051,29 @@
         <v>637</v>
       </c>
       <c r="G1729" s="3" t="s">
-        <v>4348</v>
-      </c>
-      <c r="H1729" s="3"/>
+        <v>4349</v>
+      </c>
+      <c r="H1729" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1729" s="3">
         <v>42</v>
       </c>
       <c r="J1729" s="3"/>
       <c r="K1729" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1729" s="3"/>
-      <c r="M1729" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1729" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1729" s="3" t="s">
+        <v>4350</v>
+      </c>
       <c r="N1729" s="3"/>
     </row>
     <row r="1730" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1730" s="3" t="s">
-        <v>4349</v>
+        <v>4351</v>
       </c>
       <c r="B1730" s="3"/>
       <c r="C1730" s="3">
@@ -73518,21 +74089,27 @@
         <v>270</v>
       </c>
       <c r="G1730" s="3" t="s">
-        <v>4350</v>
-      </c>
-      <c r="H1730" s="3"/>
+        <v>4352</v>
+      </c>
+      <c r="H1730" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1730" s="3"/>
       <c r="J1730" s="3"/>
       <c r="K1730" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1730" s="3"/>
-      <c r="M1730" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1730" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1730" s="3" t="s">
+        <v>4350</v>
+      </c>
       <c r="N1730" s="3"/>
     </row>
     <row r="1731" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1731" s="3" t="s">
-        <v>4351</v>
+        <v>4353</v>
       </c>
       <c r="B1731" s="3"/>
       <c r="C1731" s="3">
@@ -73548,23 +74125,29 @@
         <v>215</v>
       </c>
       <c r="G1731" s="3" t="s">
-        <v>4352</v>
-      </c>
-      <c r="H1731" s="3"/>
+        <v>4354</v>
+      </c>
+      <c r="H1731" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1731" s="3">
         <v>8</v>
       </c>
       <c r="J1731" s="3"/>
       <c r="K1731" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1731" s="3"/>
-      <c r="M1731" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1731" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1731" s="3" t="s">
+        <v>4355</v>
+      </c>
       <c r="N1731" s="3"/>
     </row>
     <row r="1732" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1732" s="3" t="s">
-        <v>4353</v>
+        <v>4356</v>
       </c>
       <c r="B1732" s="3"/>
       <c r="C1732" s="3">
@@ -73580,7 +74163,7 @@
         <v>745</v>
       </c>
       <c r="G1732" s="3" t="s">
-        <v>4354</v>
+        <v>4357</v>
       </c>
       <c r="H1732" s="3"/>
       <c r="I1732" s="3">
@@ -73596,7 +74179,7 @@
     </row>
     <row r="1733" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1733" s="3" t="s">
-        <v>4355</v>
+        <v>4358</v>
       </c>
       <c r="B1733" s="3"/>
       <c r="C1733" s="3">
@@ -73612,7 +74195,7 @@
         <v>637</v>
       </c>
       <c r="G1733" s="3" t="s">
-        <v>4356</v>
+        <v>4359</v>
       </c>
       <c r="H1733" s="3"/>
       <c r="I1733" s="3">
@@ -73628,7 +74211,7 @@
     </row>
     <row r="1734" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1734" s="3" t="s">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="B1734" s="3"/>
       <c r="C1734" s="3">
@@ -73644,23 +74227,29 @@
         <v>218</v>
       </c>
       <c r="G1734" s="3" t="s">
-        <v>4358</v>
-      </c>
-      <c r="H1734" s="3"/>
+        <v>4361</v>
+      </c>
+      <c r="H1734" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1734" s="3">
         <v>32</v>
       </c>
       <c r="J1734" s="3"/>
       <c r="K1734" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1734" s="3"/>
-      <c r="M1734" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1734" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1734" s="3" t="s">
+        <v>4362</v>
+      </c>
       <c r="N1734" s="3"/>
     </row>
     <row r="1735" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1735" s="3" t="s">
-        <v>4359</v>
+        <v>4363</v>
       </c>
       <c r="B1735" s="3"/>
       <c r="C1735" s="3">
@@ -73676,23 +74265,29 @@
         <v>118</v>
       </c>
       <c r="G1735" s="3" t="s">
-        <v>4360</v>
-      </c>
-      <c r="H1735" s="3"/>
+        <v>4364</v>
+      </c>
+      <c r="H1735" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1735" s="3">
         <v>33</v>
       </c>
       <c r="J1735" s="3"/>
       <c r="K1735" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1735" s="3"/>
-      <c r="M1735" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1735" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1735" s="3" t="s">
+        <v>4365</v>
+      </c>
       <c r="N1735" s="3"/>
     </row>
     <row r="1736" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1736" s="3" t="s">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="B1736" s="3"/>
       <c r="C1736" s="3">
@@ -73708,7 +74303,7 @@
         <v>159</v>
       </c>
       <c r="G1736" s="3" t="s">
-        <v>4362</v>
+        <v>4367</v>
       </c>
       <c r="H1736" s="3"/>
       <c r="I1736" s="3">
@@ -73721,6 +74316,2420 @@
       <c r="L1736" s="3"/>
       <c r="M1736" s="3"/>
       <c r="N1736" s="3"/>
+    </row>
+    <row r="1737" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1737" s="3" t="s">
+        <v>4368</v>
+      </c>
+      <c r="B1737" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1737" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1737" s="3">
+        <v>5993408319</v>
+      </c>
+      <c r="E1737" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1737" s="3" t="s">
+        <v>1483</v>
+      </c>
+      <c r="G1737" s="3" t="s">
+        <v>4369</v>
+      </c>
+      <c r="H1737" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1737" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1737" s="3">
+        <v>-5</v>
+      </c>
+      <c r="K1737" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1737" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1737" s="3" t="s">
+        <v>4370</v>
+      </c>
+      <c r="N1737" s="3" t="s">
+        <v>4371</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1738" s="3" t="s">
+        <v>4372</v>
+      </c>
+      <c r="B1738" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1738" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1738" s="3">
+        <v>5993861246</v>
+      </c>
+      <c r="E1738" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1738" s="3" t="s">
+        <v>3431</v>
+      </c>
+      <c r="G1738" s="3" t="s">
+        <v>4373</v>
+      </c>
+      <c r="H1738" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="I1738" s="3">
+        <v>15</v>
+      </c>
+      <c r="J1738" s="3"/>
+      <c r="K1738" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1738" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1738" s="3" t="s">
+        <v>4374</v>
+      </c>
+      <c r="N1738" s="3"/>
+    </row>
+    <row r="1739" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1739" s="3" t="s">
+        <v>4375</v>
+      </c>
+      <c r="B1739" s="3"/>
+      <c r="C1739" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1739" s="3">
+        <v>5993908948</v>
+      </c>
+      <c r="E1739" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1739" s="3" t="s">
+        <v>4182</v>
+      </c>
+      <c r="G1739" s="3" t="s">
+        <v>4376</v>
+      </c>
+      <c r="H1739" s="3"/>
+      <c r="I1739" s="3">
+        <v>51</v>
+      </c>
+      <c r="J1739" s="3">
+        <v>45</v>
+      </c>
+      <c r="K1739" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1739" s="3"/>
+      <c r="M1739" s="3"/>
+      <c r="N1739" s="3"/>
+    </row>
+    <row r="1740" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1740" s="3" t="s">
+        <v>4377</v>
+      </c>
+      <c r="B1740" s="3"/>
+      <c r="C1740" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1740" s="3">
+        <v>5994551829</v>
+      </c>
+      <c r="E1740" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1740" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1740" s="3" t="s">
+        <v>4378</v>
+      </c>
+      <c r="H1740" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1740" s="3">
+        <v>8</v>
+      </c>
+      <c r="J1740" s="3"/>
+      <c r="K1740" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1740" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1740" s="3" t="s">
+        <v>4379</v>
+      </c>
+      <c r="N1740" s="3"/>
+    </row>
+    <row r="1741" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1741" s="3" t="s">
+        <v>4380</v>
+      </c>
+      <c r="B1741" s="3"/>
+      <c r="C1741" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1741" s="3">
+        <v>5994912239</v>
+      </c>
+      <c r="E1741" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1741" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1741" s="3" t="s">
+        <v>4381</v>
+      </c>
+      <c r="H1741" s="3"/>
+      <c r="I1741" s="3">
+        <v>36</v>
+      </c>
+      <c r="J1741" s="3"/>
+      <c r="K1741" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1741" s="3"/>
+      <c r="M1741" s="3"/>
+      <c r="N1741" s="3"/>
+    </row>
+    <row r="1742" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1742" s="3" t="s">
+        <v>4382</v>
+      </c>
+      <c r="B1742" s="3"/>
+      <c r="C1742" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1742" s="3">
+        <v>5994976635</v>
+      </c>
+      <c r="E1742" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1742" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1742" s="3" t="s">
+        <v>4383</v>
+      </c>
+      <c r="H1742" s="3"/>
+      <c r="I1742" s="3">
+        <v>42</v>
+      </c>
+      <c r="J1742" s="3"/>
+      <c r="K1742" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1742" s="3"/>
+      <c r="M1742" s="3"/>
+      <c r="N1742" s="3"/>
+    </row>
+    <row r="1743" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1743" s="3" t="s">
+        <v>4384</v>
+      </c>
+      <c r="B1743" s="3"/>
+      <c r="C1743" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1743" s="3">
+        <v>5995431874</v>
+      </c>
+      <c r="E1743" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1743" s="3" t="s">
+        <v>4385</v>
+      </c>
+      <c r="G1743" s="3" t="s">
+        <v>4386</v>
+      </c>
+      <c r="H1743" s="3"/>
+      <c r="I1743" s="3">
+        <v>36</v>
+      </c>
+      <c r="J1743" s="3"/>
+      <c r="K1743" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1743" s="3"/>
+      <c r="M1743" s="3"/>
+      <c r="N1743" s="3"/>
+    </row>
+    <row r="1744" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1744" s="3" t="s">
+        <v>4387</v>
+      </c>
+      <c r="B1744" s="3"/>
+      <c r="C1744" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1744" s="3">
+        <v>5995522004</v>
+      </c>
+      <c r="E1744" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1744" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="G1744" s="3" t="s">
+        <v>4388</v>
+      </c>
+      <c r="H1744" s="3"/>
+      <c r="I1744" s="3">
+        <v>71</v>
+      </c>
+      <c r="J1744" s="3"/>
+      <c r="K1744" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1744" s="3"/>
+      <c r="M1744" s="3"/>
+      <c r="N1744" s="3"/>
+    </row>
+    <row r="1745" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1745" s="3" t="s">
+        <v>4389</v>
+      </c>
+      <c r="B1745" s="3"/>
+      <c r="C1745" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1745" s="3">
+        <v>5995893171</v>
+      </c>
+      <c r="E1745" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1745" s="3" t="s">
+        <v>4390</v>
+      </c>
+      <c r="G1745" s="3" t="s">
+        <v>4391</v>
+      </c>
+      <c r="H1745" s="3"/>
+      <c r="I1745" s="3"/>
+      <c r="J1745" s="3"/>
+      <c r="K1745" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1745" s="3"/>
+      <c r="M1745" s="3"/>
+      <c r="N1745" s="3"/>
+    </row>
+    <row r="1746" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1746" s="3" t="s">
+        <v>4392</v>
+      </c>
+      <c r="B1746" s="3"/>
+      <c r="C1746" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1746" s="3">
+        <v>5996022685</v>
+      </c>
+      <c r="E1746" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1746" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1746" s="3" t="s">
+        <v>4393</v>
+      </c>
+      <c r="H1746" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1746" s="3">
+        <v>8</v>
+      </c>
+      <c r="J1746" s="3"/>
+      <c r="K1746" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1746" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1746" s="3" t="s">
+        <v>4394</v>
+      </c>
+      <c r="N1746" s="3"/>
+    </row>
+    <row r="1747" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1747" s="3" t="s">
+        <v>4395</v>
+      </c>
+      <c r="B1747" s="3"/>
+      <c r="C1747" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1747" s="3">
+        <v>5996920759</v>
+      </c>
+      <c r="E1747" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1747" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="G1747" s="3" t="s">
+        <v>4396</v>
+      </c>
+      <c r="H1747" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1747" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1747" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1747" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1747" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1747" s="3" t="s">
+        <v>4397</v>
+      </c>
+      <c r="N1747" s="3"/>
+    </row>
+    <row r="1748" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1748" s="3" t="s">
+        <v>4398</v>
+      </c>
+      <c r="B1748" s="3"/>
+      <c r="C1748" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1748" s="3">
+        <v>5997423665</v>
+      </c>
+      <c r="E1748" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1748" s="3" t="s">
+        <v>4399</v>
+      </c>
+      <c r="G1748" s="3" t="s">
+        <v>4400</v>
+      </c>
+      <c r="H1748" s="3"/>
+      <c r="I1748" s="3">
+        <v>10</v>
+      </c>
+      <c r="J1748" s="3"/>
+      <c r="K1748" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1748" s="3"/>
+      <c r="M1748" s="3"/>
+      <c r="N1748" s="3"/>
+    </row>
+    <row r="1749" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1749" s="3" t="s">
+        <v>4401</v>
+      </c>
+      <c r="B1749" s="3"/>
+      <c r="C1749" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1749" s="3">
+        <v>5997695451</v>
+      </c>
+      <c r="E1749" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1749" s="3" t="s">
+        <v>4402</v>
+      </c>
+      <c r="G1749" s="3" t="s">
+        <v>4403</v>
+      </c>
+      <c r="H1749" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1749" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1749" s="3"/>
+      <c r="K1749" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1749" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1749" s="3" t="s">
+        <v>4404</v>
+      </c>
+      <c r="N1749" s="3"/>
+    </row>
+    <row r="1750" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1750" s="3" t="s">
+        <v>4405</v>
+      </c>
+      <c r="B1750" s="3"/>
+      <c r="C1750" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1750" s="3">
+        <v>5998088844</v>
+      </c>
+      <c r="E1750" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1750" s="3" t="s">
+        <v>4406</v>
+      </c>
+      <c r="G1750" s="3" t="s">
+        <v>4407</v>
+      </c>
+      <c r="H1750" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1750" s="3">
+        <v>11</v>
+      </c>
+      <c r="J1750" s="3"/>
+      <c r="K1750" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1750" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1750" s="3" t="s">
+        <v>4408</v>
+      </c>
+      <c r="N1750" s="3"/>
+    </row>
+    <row r="1751" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1751" s="3" t="s">
+        <v>4409</v>
+      </c>
+      <c r="B1751" s="3"/>
+      <c r="C1751" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1751" s="3">
+        <v>5998532627</v>
+      </c>
+      <c r="E1751" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1751" s="3" t="s">
+        <v>2161</v>
+      </c>
+      <c r="G1751" s="3" t="s">
+        <v>4410</v>
+      </c>
+      <c r="H1751" s="3"/>
+      <c r="I1751" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1751" s="3"/>
+      <c r="K1751" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1751" s="3"/>
+      <c r="M1751" s="3"/>
+      <c r="N1751" s="3"/>
+    </row>
+    <row r="1752" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1752" s="3" t="s">
+        <v>4411</v>
+      </c>
+      <c r="B1752" s="3"/>
+      <c r="C1752" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1752" s="3">
+        <v>5999156571</v>
+      </c>
+      <c r="E1752" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1752" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="G1752" s="3" t="s">
+        <v>4412</v>
+      </c>
+      <c r="H1752" s="3"/>
+      <c r="I1752" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1752" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1752" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1752" s="3"/>
+      <c r="M1752" s="3"/>
+      <c r="N1752" s="3"/>
+    </row>
+    <row r="1753" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1753" s="3" t="s">
+        <v>4413</v>
+      </c>
+      <c r="B1753" s="3"/>
+      <c r="C1753" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1753" s="3">
+        <v>5999177768</v>
+      </c>
+      <c r="E1753" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1753" s="3" t="s">
+        <v>1968</v>
+      </c>
+      <c r="G1753" s="3" t="s">
+        <v>4414</v>
+      </c>
+      <c r="H1753" s="3"/>
+      <c r="I1753" s="3">
+        <v>60</v>
+      </c>
+      <c r="J1753" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1753" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1753" s="3"/>
+      <c r="M1753" s="3"/>
+      <c r="N1753" s="3"/>
+    </row>
+    <row r="1754" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1754" s="3" t="s">
+        <v>4415</v>
+      </c>
+      <c r="B1754" s="3"/>
+      <c r="C1754" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1754" s="3">
+        <v>6000878480</v>
+      </c>
+      <c r="E1754" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1754" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G1754" s="3" t="s">
+        <v>4416</v>
+      </c>
+      <c r="H1754" s="3"/>
+      <c r="I1754" s="3">
+        <v>61</v>
+      </c>
+      <c r="J1754" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1754" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1754" s="3"/>
+      <c r="M1754" s="3"/>
+      <c r="N1754" s="3"/>
+    </row>
+    <row r="1755" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1755" s="3" t="s">
+        <v>4417</v>
+      </c>
+      <c r="B1755" s="3"/>
+      <c r="C1755" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1755" s="3">
+        <v>6001325514</v>
+      </c>
+      <c r="E1755" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1755" s="3" t="s">
+        <v>4418</v>
+      </c>
+      <c r="G1755" s="3" t="s">
+        <v>4419</v>
+      </c>
+      <c r="H1755" s="3"/>
+      <c r="I1755" s="3">
+        <v>58</v>
+      </c>
+      <c r="J1755" s="3">
+        <v>45</v>
+      </c>
+      <c r="K1755" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1755" s="3"/>
+      <c r="M1755" s="3"/>
+      <c r="N1755" s="3"/>
+    </row>
+    <row r="1756" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1756" s="3" t="s">
+        <v>4420</v>
+      </c>
+      <c r="B1756" s="3"/>
+      <c r="C1756" s="3">
+        <v>26</v>
+      </c>
+      <c r="D1756" s="3">
+        <v>6001885083</v>
+      </c>
+      <c r="E1756" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1756" s="3" t="s">
+        <v>2061</v>
+      </c>
+      <c r="G1756" s="3" t="s">
+        <v>4421</v>
+      </c>
+      <c r="H1756" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1756" s="3">
+        <v>60</v>
+      </c>
+      <c r="J1756" s="3"/>
+      <c r="K1756" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1756" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1756" s="3" t="s">
+        <v>4422</v>
+      </c>
+      <c r="N1756" s="3"/>
+    </row>
+    <row r="1757" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1757" s="3" t="s">
+        <v>4423</v>
+      </c>
+      <c r="B1757" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1757" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1757" s="3">
+        <v>6002528364</v>
+      </c>
+      <c r="E1757" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1757" s="3" t="s">
+        <v>4424</v>
+      </c>
+      <c r="G1757" s="3" t="s">
+        <v>4425</v>
+      </c>
+      <c r="H1757" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1757" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1757" s="3"/>
+      <c r="K1757" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1757" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1757" s="3" t="s">
+        <v>4426</v>
+      </c>
+      <c r="N1757" s="3" t="s">
+        <v>4427</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1758" s="3" t="s">
+        <v>4428</v>
+      </c>
+      <c r="B1758" s="3"/>
+      <c r="C1758" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1758" s="3">
+        <v>6003880110</v>
+      </c>
+      <c r="E1758" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1758" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G1758" s="3" t="s">
+        <v>4429</v>
+      </c>
+      <c r="H1758" s="3"/>
+      <c r="I1758" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1758" s="3"/>
+      <c r="K1758" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1758" s="3"/>
+      <c r="M1758" s="3"/>
+      <c r="N1758" s="3"/>
+    </row>
+    <row r="1759" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1759" s="3" t="s">
+        <v>4430</v>
+      </c>
+      <c r="B1759" s="3"/>
+      <c r="C1759" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1759" s="3">
+        <v>6003918664</v>
+      </c>
+      <c r="E1759" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1759" s="3" t="s">
+        <v>4431</v>
+      </c>
+      <c r="G1759" s="3" t="s">
+        <v>4432</v>
+      </c>
+      <c r="H1759" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1759" s="3">
+        <v>71</v>
+      </c>
+      <c r="J1759" s="3"/>
+      <c r="K1759" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1759" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1759" s="3" t="s">
+        <v>4427</v>
+      </c>
+      <c r="N1759" s="3"/>
+    </row>
+    <row r="1760" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1760" s="3" t="s">
+        <v>4433</v>
+      </c>
+      <c r="B1760" s="3"/>
+      <c r="C1760" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1760" s="3">
+        <v>6004011095</v>
+      </c>
+      <c r="E1760" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1760" s="3" t="s">
+        <v>4434</v>
+      </c>
+      <c r="G1760" s="3" t="s">
+        <v>4435</v>
+      </c>
+      <c r="H1760" s="3"/>
+      <c r="I1760" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1760" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1760" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1760" s="3"/>
+      <c r="M1760" s="3"/>
+      <c r="N1760" s="3"/>
+    </row>
+    <row r="1761" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1761" s="3" t="s">
+        <v>4436</v>
+      </c>
+      <c r="B1761" s="3"/>
+      <c r="C1761" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1761" s="3">
+        <v>6004136799</v>
+      </c>
+      <c r="E1761" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1761" s="3" t="s">
+        <v>4437</v>
+      </c>
+      <c r="G1761" s="3" t="s">
+        <v>4438</v>
+      </c>
+      <c r="H1761" s="3"/>
+      <c r="I1761" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1761" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1761" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1761" s="3"/>
+      <c r="M1761" s="3"/>
+      <c r="N1761" s="3"/>
+    </row>
+    <row r="1762" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1762" s="3" t="s">
+        <v>4439</v>
+      </c>
+      <c r="B1762" s="3"/>
+      <c r="C1762" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1762" s="3">
+        <v>6004146042</v>
+      </c>
+      <c r="E1762" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1762" s="3" t="s">
+        <v>2620</v>
+      </c>
+      <c r="G1762" s="3" t="s">
+        <v>4440</v>
+      </c>
+      <c r="H1762" s="3"/>
+      <c r="I1762" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1762" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1762" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1762" s="3"/>
+      <c r="M1762" s="3"/>
+      <c r="N1762" s="3"/>
+    </row>
+    <row r="1763" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1763" s="3" t="s">
+        <v>4441</v>
+      </c>
+      <c r="B1763" s="3"/>
+      <c r="C1763" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1763" s="3">
+        <v>6004695537</v>
+      </c>
+      <c r="E1763" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1763" s="3" t="s">
+        <v>4442</v>
+      </c>
+      <c r="G1763" s="3" t="s">
+        <v>4443</v>
+      </c>
+      <c r="H1763" s="3"/>
+      <c r="I1763" s="3">
+        <v>76</v>
+      </c>
+      <c r="J1763" s="3"/>
+      <c r="K1763" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1763" s="3"/>
+      <c r="M1763" s="3"/>
+      <c r="N1763" s="3"/>
+    </row>
+    <row r="1764" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1764" s="3" t="s">
+        <v>4444</v>
+      </c>
+      <c r="B1764" s="3"/>
+      <c r="C1764" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1764" s="3">
+        <v>6005812755</v>
+      </c>
+      <c r="E1764" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1764" s="3" t="s">
+        <v>4445</v>
+      </c>
+      <c r="G1764" s="3" t="s">
+        <v>4446</v>
+      </c>
+      <c r="H1764" s="3"/>
+      <c r="I1764" s="3">
+        <v>57</v>
+      </c>
+      <c r="J1764" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1764" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1764" s="3"/>
+      <c r="M1764" s="3"/>
+      <c r="N1764" s="3"/>
+    </row>
+    <row r="1765" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1765" s="3" t="s">
+        <v>4447</v>
+      </c>
+      <c r="B1765" s="3"/>
+      <c r="C1765" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1765" s="3">
+        <v>6007562741</v>
+      </c>
+      <c r="E1765" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1765" s="3" t="s">
+        <v>3273</v>
+      </c>
+      <c r="G1765" s="3" t="s">
+        <v>4448</v>
+      </c>
+      <c r="H1765" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1765" s="3">
+        <v>33</v>
+      </c>
+      <c r="J1765" s="3"/>
+      <c r="K1765" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1765" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1765" s="3" t="s">
+        <v>4449</v>
+      </c>
+      <c r="N1765" s="3"/>
+    </row>
+    <row r="1766" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1766" s="3" t="s">
+        <v>4450</v>
+      </c>
+      <c r="B1766" s="3"/>
+      <c r="C1766" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1766" s="3">
+        <v>6007590533</v>
+      </c>
+      <c r="E1766" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1766" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="G1766" s="3" t="s">
+        <v>4451</v>
+      </c>
+      <c r="H1766" s="3"/>
+      <c r="I1766" s="3">
+        <v>80</v>
+      </c>
+      <c r="J1766" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1766" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1766" s="3"/>
+      <c r="M1766" s="3"/>
+      <c r="N1766" s="3"/>
+    </row>
+    <row r="1767" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1767" s="3" t="s">
+        <v>4452</v>
+      </c>
+      <c r="B1767" s="3"/>
+      <c r="C1767" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1767" s="3">
+        <v>6007616594</v>
+      </c>
+      <c r="E1767" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F1767" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G1767" s="3" t="s">
+        <v>4453</v>
+      </c>
+      <c r="H1767" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1767" s="3"/>
+      <c r="J1767" s="3"/>
+      <c r="K1767" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1767" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1767" s="3" t="s">
+        <v>4449</v>
+      </c>
+      <c r="N1767" s="3"/>
+    </row>
+    <row r="1768" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1768" s="3" t="s">
+        <v>4454</v>
+      </c>
+      <c r="B1768" s="3"/>
+      <c r="C1768" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1768" s="3">
+        <v>6008078539</v>
+      </c>
+      <c r="E1768" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1768" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1768" s="3" t="s">
+        <v>4455</v>
+      </c>
+      <c r="H1768" s="3"/>
+      <c r="I1768" s="3">
+        <v>16</v>
+      </c>
+      <c r="J1768" s="3"/>
+      <c r="K1768" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1768" s="3"/>
+      <c r="M1768" s="3"/>
+      <c r="N1768" s="3"/>
+    </row>
+    <row r="1769" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1769" s="3" t="s">
+        <v>4456</v>
+      </c>
+      <c r="B1769" s="3"/>
+      <c r="C1769" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1769" s="3">
+        <v>6012425169</v>
+      </c>
+      <c r="E1769" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1769" s="3" t="s">
+        <v>2149</v>
+      </c>
+      <c r="G1769" s="3" t="s">
+        <v>4457</v>
+      </c>
+      <c r="H1769" s="3"/>
+      <c r="I1769" s="3">
+        <v>61</v>
+      </c>
+      <c r="J1769" s="3"/>
+      <c r="K1769" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1769" s="3"/>
+      <c r="M1769" s="3"/>
+      <c r="N1769" s="3"/>
+    </row>
+    <row r="1770" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1770" s="3" t="s">
+        <v>4458</v>
+      </c>
+      <c r="B1770" s="3"/>
+      <c r="C1770" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1770" s="3">
+        <v>6014015211</v>
+      </c>
+      <c r="E1770" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1770" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="G1770" s="3" t="s">
+        <v>4459</v>
+      </c>
+      <c r="H1770" s="3"/>
+      <c r="I1770" s="3">
+        <v>37</v>
+      </c>
+      <c r="J1770" s="3"/>
+      <c r="K1770" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1770" s="3"/>
+      <c r="M1770" s="3"/>
+      <c r="N1770" s="3"/>
+    </row>
+    <row r="1771" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1771" s="3" t="s">
+        <v>4460</v>
+      </c>
+      <c r="B1771" s="3"/>
+      <c r="C1771" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1771" s="3">
+        <v>6014166286</v>
+      </c>
+      <c r="E1771" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F1771" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G1771" s="3" t="s">
+        <v>4461</v>
+      </c>
+      <c r="H1771" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1771" s="3">
+        <v>11</v>
+      </c>
+      <c r="J1771" s="3"/>
+      <c r="K1771" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1771" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1771" s="3" t="s">
+        <v>4462</v>
+      </c>
+      <c r="N1771" s="3"/>
+    </row>
+    <row r="1772" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1772" s="3" t="s">
+        <v>4463</v>
+      </c>
+      <c r="B1772" s="3"/>
+      <c r="C1772" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1772" s="3">
+        <v>6014170348</v>
+      </c>
+      <c r="E1772" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1772" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G1772" s="3" t="s">
+        <v>4464</v>
+      </c>
+      <c r="H1772" s="3"/>
+      <c r="I1772" s="3">
+        <v>37</v>
+      </c>
+      <c r="J1772" s="3"/>
+      <c r="K1772" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1772" s="3"/>
+      <c r="M1772" s="3"/>
+      <c r="N1772" s="3"/>
+    </row>
+    <row r="1773" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1773" s="3" t="s">
+        <v>4465</v>
+      </c>
+      <c r="B1773" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1773" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1773" s="3">
+        <v>6015254777</v>
+      </c>
+      <c r="E1773" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F1773" s="3" t="s">
+        <v>1948</v>
+      </c>
+      <c r="G1773" s="3" t="s">
+        <v>4466</v>
+      </c>
+      <c r="H1773" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1773" s="3">
+        <v>50</v>
+      </c>
+      <c r="J1773" s="3"/>
+      <c r="K1773" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1773" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1773" s="3" t="s">
+        <v>4467</v>
+      </c>
+      <c r="N1773" s="3"/>
+    </row>
+    <row r="1774" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1774" s="3" t="s">
+        <v>4468</v>
+      </c>
+      <c r="B1774" s="3"/>
+      <c r="C1774" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1774" s="3">
+        <v>6015678766</v>
+      </c>
+      <c r="E1774" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1774" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1774" s="3" t="s">
+        <v>4469</v>
+      </c>
+      <c r="H1774" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1774" s="3">
+        <v>7</v>
+      </c>
+      <c r="J1774" s="3"/>
+      <c r="K1774" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1774" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1774" s="3" t="s">
+        <v>4470</v>
+      </c>
+      <c r="N1774" s="3"/>
+    </row>
+    <row r="1775" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1775" s="3" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B1775" s="3"/>
+      <c r="C1775" s="3">
+        <v>26</v>
+      </c>
+      <c r="D1775" s="3">
+        <v>6018308358</v>
+      </c>
+      <c r="E1775" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1775" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="G1775" s="3" t="s">
+        <v>4472</v>
+      </c>
+      <c r="H1775" s="3"/>
+      <c r="I1775" s="3"/>
+      <c r="J1775" s="3"/>
+      <c r="K1775" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1775" s="3"/>
+      <c r="M1775" s="3"/>
+      <c r="N1775" s="3"/>
+    </row>
+    <row r="1776" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1776" s="3" t="s">
+        <v>4473</v>
+      </c>
+      <c r="B1776" s="3"/>
+      <c r="C1776" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1776" s="3">
+        <v>6018621293</v>
+      </c>
+      <c r="E1776" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1776" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1776" s="3" t="s">
+        <v>4474</v>
+      </c>
+      <c r="H1776" s="3"/>
+      <c r="I1776" s="3"/>
+      <c r="J1776" s="3"/>
+      <c r="K1776" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1776" s="3"/>
+      <c r="M1776" s="3"/>
+      <c r="N1776" s="3"/>
+    </row>
+    <row r="1777" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1777" s="3" t="s">
+        <v>4475</v>
+      </c>
+      <c r="B1777" s="3"/>
+      <c r="C1777" s="3">
+        <v>26</v>
+      </c>
+      <c r="D1777" s="3">
+        <v>6018681485</v>
+      </c>
+      <c r="E1777" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1777" s="3" t="s">
+        <v>1818</v>
+      </c>
+      <c r="G1777" s="3" t="s">
+        <v>4476</v>
+      </c>
+      <c r="H1777" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1777" s="3"/>
+      <c r="J1777" s="3"/>
+      <c r="K1777" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1777" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1777" s="3" t="s">
+        <v>4470</v>
+      </c>
+      <c r="N1777" s="3"/>
+    </row>
+    <row r="1778" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1778" s="3" t="s">
+        <v>4477</v>
+      </c>
+      <c r="B1778" s="3"/>
+      <c r="C1778" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1778" s="3">
+        <v>6019207726</v>
+      </c>
+      <c r="E1778" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1778" s="3" t="s">
+        <v>4478</v>
+      </c>
+      <c r="G1778" s="3" t="s">
+        <v>4479</v>
+      </c>
+      <c r="H1778" s="3"/>
+      <c r="I1778" s="3"/>
+      <c r="J1778" s="3"/>
+      <c r="K1778" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1778" s="3"/>
+      <c r="M1778" s="3"/>
+      <c r="N1778" s="3"/>
+    </row>
+    <row r="1779" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1779" s="3" t="s">
+        <v>4480</v>
+      </c>
+      <c r="B1779" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1779" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1779" s="3">
+        <v>6019257431</v>
+      </c>
+      <c r="E1779" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1779" s="3" t="s">
+        <v>1472</v>
+      </c>
+      <c r="G1779" s="3" t="s">
+        <v>4481</v>
+      </c>
+      <c r="H1779" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1779" s="3"/>
+      <c r="J1779" s="3"/>
+      <c r="K1779" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1779" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1779" s="3" t="s">
+        <v>4482</v>
+      </c>
+      <c r="N1779" s="3" t="s">
+        <v>4483</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1780" s="3" t="s">
+        <v>4484</v>
+      </c>
+      <c r="B1780" s="3"/>
+      <c r="C1780" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1780" s="3">
+        <v>6019716450</v>
+      </c>
+      <c r="E1780" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1780" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G1780" s="3" t="s">
+        <v>4485</v>
+      </c>
+      <c r="H1780" s="3"/>
+      <c r="I1780" s="3"/>
+      <c r="J1780" s="3"/>
+      <c r="K1780" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1780" s="3"/>
+      <c r="M1780" s="3"/>
+      <c r="N1780" s="3"/>
+    </row>
+    <row r="1781" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1781" s="3" t="s">
+        <v>4486</v>
+      </c>
+      <c r="B1781" s="3"/>
+      <c r="C1781" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1781" s="3">
+        <v>6022274866</v>
+      </c>
+      <c r="E1781" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1781" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1781" s="3" t="s">
+        <v>4487</v>
+      </c>
+      <c r="H1781" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1781" s="3">
+        <v>9</v>
+      </c>
+      <c r="J1781" s="3"/>
+      <c r="K1781" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1781" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1781" s="3" t="s">
+        <v>4488</v>
+      </c>
+      <c r="N1781" s="3"/>
+    </row>
+    <row r="1782" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1782" s="3" t="s">
+        <v>4489</v>
+      </c>
+      <c r="B1782" s="3"/>
+      <c r="C1782" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1782" s="3">
+        <v>6022446607</v>
+      </c>
+      <c r="E1782" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1782" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G1782" s="3" t="s">
+        <v>4490</v>
+      </c>
+      <c r="H1782" s="3"/>
+      <c r="I1782" s="3">
+        <v>14</v>
+      </c>
+      <c r="J1782" s="3"/>
+      <c r="K1782" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1782" s="3"/>
+      <c r="M1782" s="3"/>
+      <c r="N1782" s="3"/>
+    </row>
+    <row r="1783" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1783" s="3" t="s">
+        <v>4491</v>
+      </c>
+      <c r="B1783" s="3"/>
+      <c r="C1783" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1783" s="3">
+        <v>6022519055</v>
+      </c>
+      <c r="E1783" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1783" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1783" s="3" t="s">
+        <v>4492</v>
+      </c>
+      <c r="H1783" s="3"/>
+      <c r="I1783" s="3">
+        <v>56</v>
+      </c>
+      <c r="J1783" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1783" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1783" s="3"/>
+      <c r="M1783" s="3"/>
+      <c r="N1783" s="3"/>
+    </row>
+    <row r="1784" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1784" s="3" t="s">
+        <v>4493</v>
+      </c>
+      <c r="B1784" s="3"/>
+      <c r="C1784" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1784" s="3">
+        <v>6024059951</v>
+      </c>
+      <c r="E1784" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1784" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="G1784" s="3" t="s">
+        <v>4494</v>
+      </c>
+      <c r="H1784" s="3"/>
+      <c r="I1784" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1784" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1784" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1784" s="3"/>
+      <c r="M1784" s="3"/>
+      <c r="N1784" s="3"/>
+    </row>
+    <row r="1785" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1785" s="3" t="s">
+        <v>4493</v>
+      </c>
+      <c r="B1785" s="3"/>
+      <c r="C1785" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1785" s="3">
+        <v>6024060291</v>
+      </c>
+      <c r="E1785" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1785" s="3" t="s">
+        <v>4495</v>
+      </c>
+      <c r="G1785" s="3" t="s">
+        <v>4496</v>
+      </c>
+      <c r="H1785" s="3"/>
+      <c r="I1785" s="3">
+        <v>37</v>
+      </c>
+      <c r="J1785" s="3"/>
+      <c r="K1785" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1785" s="3"/>
+      <c r="M1785" s="3"/>
+      <c r="N1785" s="3"/>
+    </row>
+    <row r="1786" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1786" s="3" t="s">
+        <v>4497</v>
+      </c>
+      <c r="B1786" s="3"/>
+      <c r="C1786" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1786" s="3">
+        <v>6024101955</v>
+      </c>
+      <c r="E1786" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1786" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="G1786" s="3" t="s">
+        <v>4498</v>
+      </c>
+      <c r="H1786" s="3"/>
+      <c r="I1786" s="3">
+        <v>71</v>
+      </c>
+      <c r="J1786" s="3"/>
+      <c r="K1786" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1786" s="3"/>
+      <c r="M1786" s="3"/>
+      <c r="N1786" s="3"/>
+    </row>
+    <row r="1787" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1787" s="3" t="s">
+        <v>4499</v>
+      </c>
+      <c r="B1787" s="3"/>
+      <c r="C1787" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1787" s="3">
+        <v>6024280818</v>
+      </c>
+      <c r="E1787" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1787" s="3" t="s">
+        <v>4500</v>
+      </c>
+      <c r="G1787" s="3" t="s">
+        <v>4501</v>
+      </c>
+      <c r="H1787" s="3"/>
+      <c r="I1787" s="3">
+        <v>76</v>
+      </c>
+      <c r="J1787" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1787" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1787" s="3"/>
+      <c r="M1787" s="3"/>
+      <c r="N1787" s="3"/>
+    </row>
+    <row r="1788" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1788" s="3" t="s">
+        <v>4502</v>
+      </c>
+      <c r="B1788" s="3"/>
+      <c r="C1788" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1788" s="3">
+        <v>6024425113</v>
+      </c>
+      <c r="E1788" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1788" s="3" t="s">
+        <v>4503</v>
+      </c>
+      <c r="G1788" s="3" t="s">
+        <v>4504</v>
+      </c>
+      <c r="H1788" s="3"/>
+      <c r="I1788" s="3">
+        <v>2</v>
+      </c>
+      <c r="J1788" s="3"/>
+      <c r="K1788" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1788" s="3"/>
+      <c r="M1788" s="3"/>
+      <c r="N1788" s="3"/>
+    </row>
+    <row r="1789" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1789" s="3" t="s">
+        <v>4505</v>
+      </c>
+      <c r="B1789" s="3"/>
+      <c r="C1789" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1789" s="3">
+        <v>6024589225</v>
+      </c>
+      <c r="E1789" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1789" s="3" t="s">
+        <v>4506</v>
+      </c>
+      <c r="G1789" s="3" t="s">
+        <v>4507</v>
+      </c>
+      <c r="H1789" s="3"/>
+      <c r="I1789" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1789" s="3"/>
+      <c r="K1789" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1789" s="3"/>
+      <c r="M1789" s="3"/>
+      <c r="N1789" s="3"/>
+    </row>
+    <row r="1790" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1790" s="3" t="s">
+        <v>4508</v>
+      </c>
+      <c r="B1790" s="3"/>
+      <c r="C1790" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1790" s="3">
+        <v>6024791252</v>
+      </c>
+      <c r="E1790" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1790" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G1790" s="3" t="s">
+        <v>4509</v>
+      </c>
+      <c r="H1790" s="3"/>
+      <c r="I1790" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1790" s="3"/>
+      <c r="K1790" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1790" s="3"/>
+      <c r="M1790" s="3"/>
+      <c r="N1790" s="3"/>
+    </row>
+    <row r="1791" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1791" s="3" t="s">
+        <v>4510</v>
+      </c>
+      <c r="B1791" s="3"/>
+      <c r="C1791" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1791" s="3">
+        <v>6024836205</v>
+      </c>
+      <c r="E1791" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1791" s="3" t="s">
+        <v>2375</v>
+      </c>
+      <c r="G1791" s="3" t="s">
+        <v>4511</v>
+      </c>
+      <c r="H1791" s="3"/>
+      <c r="I1791" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1791" s="3"/>
+      <c r="K1791" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1791" s="3"/>
+      <c r="M1791" s="3"/>
+      <c r="N1791" s="3"/>
+    </row>
+    <row r="1792" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1792" s="3" t="s">
+        <v>4512</v>
+      </c>
+      <c r="B1792" s="3"/>
+      <c r="C1792" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1792" s="3">
+        <v>6024854593</v>
+      </c>
+      <c r="E1792" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1792" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G1792" s="3" t="s">
+        <v>4513</v>
+      </c>
+      <c r="H1792" s="3"/>
+      <c r="I1792" s="3">
+        <v>76</v>
+      </c>
+      <c r="J1792" s="3"/>
+      <c r="K1792" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1792" s="3"/>
+      <c r="M1792" s="3"/>
+      <c r="N1792" s="3"/>
+    </row>
+    <row r="1793" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1793" s="3" t="s">
+        <v>4514</v>
+      </c>
+      <c r="B1793" s="3"/>
+      <c r="C1793" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1793" s="3">
+        <v>6024854598</v>
+      </c>
+      <c r="E1793" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1793" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="G1793" s="3" t="s">
+        <v>4515</v>
+      </c>
+      <c r="H1793" s="3"/>
+      <c r="I1793" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1793" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1793" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1793" s="3"/>
+      <c r="M1793" s="3"/>
+      <c r="N1793" s="3"/>
+    </row>
+    <row r="1794" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1794" s="3" t="s">
+        <v>4516</v>
+      </c>
+      <c r="B1794" s="3"/>
+      <c r="C1794" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1794" s="3">
+        <v>6025434736</v>
+      </c>
+      <c r="E1794" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1794" s="3" t="s">
+        <v>4517</v>
+      </c>
+      <c r="G1794" s="3" t="s">
+        <v>4518</v>
+      </c>
+      <c r="H1794" s="3"/>
+      <c r="I1794" s="3"/>
+      <c r="J1794" s="3"/>
+      <c r="K1794" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1794" s="3"/>
+      <c r="M1794" s="3"/>
+      <c r="N1794" s="3"/>
+    </row>
+    <row r="1795" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1795" s="3" t="s">
+        <v>4519</v>
+      </c>
+      <c r="B1795" s="3"/>
+      <c r="C1795" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1795" s="3">
+        <v>6025787949</v>
+      </c>
+      <c r="E1795" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1795" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1795" s="3" t="s">
+        <v>4520</v>
+      </c>
+      <c r="H1795" s="3"/>
+      <c r="I1795" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1795" s="3"/>
+      <c r="K1795" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1795" s="3"/>
+      <c r="M1795" s="3"/>
+      <c r="N1795" s="3"/>
+    </row>
+    <row r="1796" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1796" s="3" t="s">
+        <v>4521</v>
+      </c>
+      <c r="B1796" s="3"/>
+      <c r="C1796" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1796" s="3">
+        <v>6027673212</v>
+      </c>
+      <c r="E1796" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1796" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="G1796" s="3" t="s">
+        <v>4522</v>
+      </c>
+      <c r="H1796" s="3"/>
+      <c r="I1796" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1796" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1796" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1796" s="3"/>
+      <c r="M1796" s="3"/>
+      <c r="N1796" s="3"/>
+    </row>
+    <row r="1797" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1797" s="3" t="s">
+        <v>4523</v>
+      </c>
+      <c r="B1797" s="3"/>
+      <c r="C1797" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1797" s="3">
+        <v>6030149799</v>
+      </c>
+      <c r="E1797" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1797" s="3" t="s">
+        <v>4524</v>
+      </c>
+      <c r="G1797" s="3" t="s">
+        <v>4525</v>
+      </c>
+      <c r="H1797" s="3"/>
+      <c r="I1797" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1797" s="3"/>
+      <c r="K1797" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1797" s="3"/>
+      <c r="M1797" s="3"/>
+      <c r="N1797" s="3"/>
+    </row>
+    <row r="1798" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1798" s="3" t="s">
+        <v>4526</v>
+      </c>
+      <c r="B1798" s="3"/>
+      <c r="C1798" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1798" s="3">
+        <v>6030231305</v>
+      </c>
+      <c r="E1798" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="F1798" s="3" t="s">
+        <v>4527</v>
+      </c>
+      <c r="G1798" s="3" t="s">
+        <v>4528</v>
+      </c>
+      <c r="H1798" s="3"/>
+      <c r="I1798" s="3">
+        <v>10</v>
+      </c>
+      <c r="J1798" s="3"/>
+      <c r="K1798" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1798" s="3"/>
+      <c r="M1798" s="3"/>
+      <c r="N1798" s="3"/>
+    </row>
+    <row r="1799" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1799" s="3" t="s">
+        <v>4529</v>
+      </c>
+      <c r="B1799" s="3"/>
+      <c r="C1799" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1799" s="3">
+        <v>6030231315</v>
+      </c>
+      <c r="E1799" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1799" s="3" t="s">
+        <v>4530</v>
+      </c>
+      <c r="G1799" s="3" t="s">
+        <v>4531</v>
+      </c>
+      <c r="H1799" s="3"/>
+      <c r="I1799" s="3">
+        <v>25</v>
+      </c>
+      <c r="J1799" s="3"/>
+      <c r="K1799" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1799" s="3"/>
+      <c r="M1799" s="3"/>
+      <c r="N1799" s="3"/>
+    </row>
+    <row r="1800" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1800" s="3" t="s">
+        <v>4532</v>
+      </c>
+      <c r="B1800" s="3"/>
+      <c r="C1800" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1800" s="3">
+        <v>6030391762</v>
+      </c>
+      <c r="E1800" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1800" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G1800" s="3" t="s">
+        <v>4533</v>
+      </c>
+      <c r="H1800" s="3"/>
+      <c r="I1800" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1800" s="3"/>
+      <c r="K1800" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1800" s="3"/>
+      <c r="M1800" s="3"/>
+      <c r="N1800" s="3"/>
+    </row>
+    <row r="1801" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1801" s="3" t="s">
+        <v>4534</v>
+      </c>
+      <c r="B1801" s="3"/>
+      <c r="C1801" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1801" s="3">
+        <v>6032973603</v>
+      </c>
+      <c r="E1801" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1801" s="3" t="s">
+        <v>1668</v>
+      </c>
+      <c r="G1801" s="3" t="s">
+        <v>4535</v>
+      </c>
+      <c r="H1801" s="3"/>
+      <c r="I1801" s="3">
+        <v>4</v>
+      </c>
+      <c r="J1801" s="3"/>
+      <c r="K1801" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1801" s="3"/>
+      <c r="M1801" s="3"/>
+      <c r="N1801" s="3"/>
+    </row>
+    <row r="1802" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1802" s="3" t="s">
+        <v>4536</v>
+      </c>
+      <c r="B1802" s="3"/>
+      <c r="C1802" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1802" s="3">
+        <v>6033011911</v>
+      </c>
+      <c r="E1802" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1802" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="G1802" s="3" t="s">
+        <v>4537</v>
+      </c>
+      <c r="H1802" s="3"/>
+      <c r="I1802" s="3">
+        <v>76</v>
+      </c>
+      <c r="J1802" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1802" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1802" s="3"/>
+      <c r="M1802" s="3"/>
+      <c r="N1802" s="3"/>
+    </row>
+    <row r="1803" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1803" s="3" t="s">
+        <v>4538</v>
+      </c>
+      <c r="B1803" s="3"/>
+      <c r="C1803" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1803" s="3">
+        <v>6033245777</v>
+      </c>
+      <c r="E1803" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F1803" s="3" t="s">
+        <v>1779</v>
+      </c>
+      <c r="G1803" s="3" t="s">
+        <v>4539</v>
+      </c>
+      <c r="H1803" s="3"/>
+      <c r="I1803" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1803" s="3"/>
+      <c r="K1803" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1803" s="3"/>
+      <c r="M1803" s="3"/>
+      <c r="N1803" s="3"/>
+    </row>
+    <row r="1804" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1804" s="3" t="s">
+        <v>4540</v>
+      </c>
+      <c r="B1804" s="3"/>
+      <c r="C1804" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1804" s="3">
+        <v>6033599309</v>
+      </c>
+      <c r="E1804" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1804" s="3" t="s">
+        <v>1636</v>
+      </c>
+      <c r="G1804" s="3" t="s">
+        <v>4541</v>
+      </c>
+      <c r="H1804" s="3"/>
+      <c r="I1804" s="3">
+        <v>39</v>
+      </c>
+      <c r="J1804" s="3"/>
+      <c r="K1804" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1804" s="3"/>
+      <c r="M1804" s="3"/>
+      <c r="N1804" s="3"/>
+    </row>
+    <row r="1805" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1805" s="3" t="s">
+        <v>4542</v>
+      </c>
+      <c r="B1805" s="3"/>
+      <c r="C1805" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1805" s="3">
+        <v>6033615852</v>
+      </c>
+      <c r="E1805" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="F1805" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="G1805" s="3" t="s">
+        <v>4543</v>
+      </c>
+      <c r="H1805" s="3"/>
+      <c r="I1805" s="3">
+        <v>21</v>
+      </c>
+      <c r="J1805" s="3"/>
+      <c r="K1805" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1805" s="3"/>
+      <c r="M1805" s="3"/>
+      <c r="N1805" s="3"/>
+    </row>
+    <row r="1806" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1806" s="3" t="s">
+        <v>4544</v>
+      </c>
+      <c r="B1806" s="3"/>
+      <c r="C1806" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1806" s="3">
+        <v>6033672954</v>
+      </c>
+      <c r="E1806" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1806" s="3" t="s">
+        <v>4545</v>
+      </c>
+      <c r="G1806" s="3" t="s">
+        <v>4546</v>
+      </c>
+      <c r="H1806" s="3"/>
+      <c r="I1806" s="3">
+        <v>34</v>
+      </c>
+      <c r="J1806" s="3"/>
+      <c r="K1806" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1806" s="3"/>
+      <c r="M1806" s="3"/>
+      <c r="N1806" s="3"/>
+    </row>
+    <row r="1807" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1807" s="3" t="s">
+        <v>4547</v>
+      </c>
+      <c r="B1807" s="3"/>
+      <c r="C1807" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1807" s="3">
+        <v>6033675771</v>
+      </c>
+      <c r="E1807" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1807" s="3" t="s">
+        <v>4548</v>
+      </c>
+      <c r="G1807" s="3" t="s">
+        <v>4549</v>
+      </c>
+      <c r="H1807" s="3"/>
+      <c r="I1807" s="3">
+        <v>38</v>
+      </c>
+      <c r="J1807" s="3"/>
+      <c r="K1807" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1807" s="3"/>
+      <c r="M1807" s="3"/>
+      <c r="N1807" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Curtis-Garage-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5DB8D4C-29FC-4732-9F6C-DFAF20D0D4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B9C3761-4076-49DC-B338-4963DABF5095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11650" uniqueCount="4794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12175" uniqueCount="5000">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -14137,6 +14137,9 @@
     <t>39.542050, -86.641510</t>
   </si>
   <si>
+    <t>07/09/26 07:52 EDT</t>
+  </si>
+  <si>
     <t>07/02/26 07:47 EDT</t>
   </si>
   <si>
@@ -14173,6 +14176,9 @@
     <t>39.635273, -86.438110</t>
   </si>
   <si>
+    <t>07/06/26 09:37 EDT</t>
+  </si>
+  <si>
     <t>07/02/26 13:18 EDT</t>
   </si>
   <si>
@@ -14182,9 +14188,15 @@
     <t>39.630493, -86.446526</t>
   </si>
   <si>
+    <t>07/06/26 09:31 EDT</t>
+  </si>
+  <si>
     <t>39.628220, -86.450020</t>
   </si>
   <si>
+    <t>07/06/26 09:58 EDT</t>
+  </si>
+  <si>
     <t>07/02/26 13:19 EDT</t>
   </si>
   <si>
@@ -14224,6 +14236,9 @@
     <t>39.567562, -86.632030</t>
   </si>
   <si>
+    <t>07/09/26 07:53 EDT</t>
+  </si>
+  <si>
     <t>07/02/26 19:58 EDT</t>
   </si>
   <si>
@@ -14251,12 +14266,18 @@
     <t>39.552307, -86.810440</t>
   </si>
   <si>
+    <t>07/06/26 09:45 EDT</t>
+  </si>
+  <si>
     <t>07/03/26 08:26 EDT</t>
   </si>
   <si>
     <t>39.506077, -86.549790</t>
   </si>
   <si>
+    <t>07/06/26 09:33 EDT</t>
+  </si>
+  <si>
     <t>07/03/26 09:11 EDT</t>
   </si>
   <si>
@@ -14284,6 +14305,9 @@
     <t>39.558594, -86.668520</t>
   </si>
   <si>
+    <t>07/06/26 13:22 EDT</t>
+  </si>
+  <si>
     <t>07/03/26 12:08 EDT</t>
   </si>
   <si>
@@ -14311,6 +14335,9 @@
     <t>39.513878, -86.922430</t>
   </si>
   <si>
+    <t>07/06/26 09:50 EDT</t>
+  </si>
+  <si>
     <t>07/03/26 12:21 EDT</t>
   </si>
   <si>
@@ -14326,6 +14353,9 @@
     <t>39.564810, -86.605515</t>
   </si>
   <si>
+    <t>07/06/26 09:56 EDT</t>
+  </si>
+  <si>
     <t>07/03/26 15:07 EDT</t>
   </si>
   <si>
@@ -14392,16 +14422,604 @@
     <t>39.579490, -86.669540</t>
   </si>
   <si>
+    <t>07/06/26 09:34 EDT</t>
+  </si>
+  <si>
     <t>07/04/26 19:15 EDT</t>
   </si>
   <si>
     <t>39.563572, -86.701520</t>
   </si>
   <si>
+    <t>07/06/26 09:57 EDT</t>
+  </si>
+  <si>
     <t>07/04/26 19:18 EDT</t>
   </si>
   <si>
     <t>39.572180, -86.669860</t>
+  </si>
+  <si>
+    <t>07/05/26 15:23 EDT</t>
+  </si>
+  <si>
+    <t>39.557700, -86.714210</t>
+  </si>
+  <si>
+    <t>07/05/26 15:30 EDT</t>
+  </si>
+  <si>
+    <t>39.579440, -86.649940</t>
+  </si>
+  <si>
+    <t>07/05/26 18:23 EDT</t>
+  </si>
+  <si>
+    <t>2.7mi SE of Plainfield IN</t>
+  </si>
+  <si>
+    <t>39.679340, -86.325070</t>
+  </si>
+  <si>
+    <t>07/06/26 07:27 EDT</t>
+  </si>
+  <si>
+    <t>9.6mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.508450, -86.795555</t>
+  </si>
+  <si>
+    <t>07/06/26 07:30 EDT</t>
+  </si>
+  <si>
+    <t>39.508354, -86.795660</t>
+  </si>
+  <si>
+    <t>07/06/26 07:43 EDT</t>
+  </si>
+  <si>
+    <t>39.569424, -86.632095</t>
+  </si>
+  <si>
+    <t>07/06/26 09:35 EDT</t>
+  </si>
+  <si>
+    <t>07/06/26 09:10 EDT</t>
+  </si>
+  <si>
+    <t>6mi E of Plainfield IN</t>
+  </si>
+  <si>
+    <t>39.700695, -86.259705</t>
+  </si>
+  <si>
+    <t>07/06/26 09:36 EDT</t>
+  </si>
+  <si>
+    <t>07/06/26 10:04 EDT</t>
+  </si>
+  <si>
+    <t>7mi SW of Indianapolis IN</t>
+  </si>
+  <si>
+    <t>39.692318, -86.216680</t>
+  </si>
+  <si>
+    <t>07/06/26 10:05 EDT</t>
+  </si>
+  <si>
+    <t>39.692295, -86.227770</t>
+  </si>
+  <si>
+    <t>07/06/26 10:30 EDT</t>
+  </si>
+  <si>
+    <t>5.6mi S of Danville IN</t>
+  </si>
+  <si>
+    <t>39.677360, -86.492080</t>
+  </si>
+  <si>
+    <t>07/06/26 11:11 EDT</t>
+  </si>
+  <si>
+    <t>39.628130, -86.670074</t>
+  </si>
+  <si>
+    <t>07/06/26 12:56 EDT</t>
+  </si>
+  <si>
+    <t>39.660180, -86.715620</t>
+  </si>
+  <si>
+    <t>07/07/26 07:43 EDT</t>
+  </si>
+  <si>
+    <t>07/06/26 13:09 EDT</t>
+  </si>
+  <si>
+    <t>39.620100, -86.622820</t>
+  </si>
+  <si>
+    <t>07/06/26 13:10 EDT</t>
+  </si>
+  <si>
+    <t>39.604590, -86.622770</t>
+  </si>
+  <si>
+    <t>07/06/26 13:11 EDT</t>
+  </si>
+  <si>
+    <t>39.594140, -86.626380</t>
+  </si>
+  <si>
+    <t>07/06/26 13:28 EDT</t>
+  </si>
+  <si>
+    <t>2mi SE of Plainfield IN</t>
+  </si>
+  <si>
+    <t>39.680077, -86.340540</t>
+  </si>
+  <si>
+    <t>07/07/26 08:01 EDT</t>
+  </si>
+  <si>
+    <t>07/07/26 08:10 EDT</t>
+  </si>
+  <si>
+    <t>07/06/26 14:30 EDT</t>
+  </si>
+  <si>
+    <t>39.678993, -86.368990</t>
+  </si>
+  <si>
+    <t>07/06/26 14:31 EDT</t>
+  </si>
+  <si>
+    <t>39.678770, -86.370960</t>
+  </si>
+  <si>
+    <t>07/06/26 14:38 EDT</t>
+  </si>
+  <si>
+    <t>0.1mi NW of Plainfield IN</t>
+  </si>
+  <si>
+    <t>39.697002, -86.372940</t>
+  </si>
+  <si>
+    <t>07/06/26 14:56 EDT</t>
+  </si>
+  <si>
+    <t>39.568027, -86.633415</t>
+  </si>
+  <si>
+    <t>07/07/26 07:44 EDT</t>
+  </si>
+  <si>
+    <t>07/06/26 17:08 EDT</t>
+  </si>
+  <si>
+    <t>39.564870, -86.621670</t>
+  </si>
+  <si>
+    <t>07/06/26 17:09 EDT</t>
+  </si>
+  <si>
+    <t>39.564830, -86.600120</t>
+  </si>
+  <si>
+    <t>07/07/26 07:51 EDT</t>
+  </si>
+  <si>
+    <t>07/06/26 17:14 EDT</t>
+  </si>
+  <si>
+    <t>39.532940, -86.564030</t>
+  </si>
+  <si>
+    <t>07/07/26 00:04 EDT</t>
+  </si>
+  <si>
+    <t>39.579430, -86.632030</t>
+  </si>
+  <si>
+    <t>07/07/26 02:06 EDT</t>
+  </si>
+  <si>
+    <t>39.635864, -86.670135</t>
+  </si>
+  <si>
+    <t>07/07/26 07:59 EDT</t>
+  </si>
+  <si>
+    <t>07/07/26 08:00 EDT</t>
+  </si>
+  <si>
+    <t>07/07/26 04:27 EDT</t>
+  </si>
+  <si>
+    <t>39.579407, -86.632034</t>
+  </si>
+  <si>
+    <t>07/07/26 04:37 EDT</t>
+  </si>
+  <si>
+    <t>39.592380, -86.545240</t>
+  </si>
+  <si>
+    <t>07/07/26 07:46 EDT</t>
+  </si>
+  <si>
+    <t>07/07/26 06:30 EDT</t>
+  </si>
+  <si>
+    <t>39.535660, -86.580320</t>
+  </si>
+  <si>
+    <t>07/07/26 10:28 EDT</t>
+  </si>
+  <si>
+    <t>39.578980, -86.497460</t>
+  </si>
+  <si>
+    <t>07/07/26 10:32 EDT</t>
+  </si>
+  <si>
+    <t>3.9mi W of Mooresville IN</t>
+  </si>
+  <si>
+    <t>39.593090, -86.440030</t>
+  </si>
+  <si>
+    <t>07/07/26 10:35 EDT</t>
+  </si>
+  <si>
+    <t>39.602860, -86.387750</t>
+  </si>
+  <si>
+    <t>07/07/26 10:59 EDT</t>
+  </si>
+  <si>
+    <t>39.591743, -86.482270</t>
+  </si>
+  <si>
+    <t>07/07/26 11:25 EDT</t>
+  </si>
+  <si>
+    <t>39.602910, -86.511894</t>
+  </si>
+  <si>
+    <t>07/08/26 07:47 EDT</t>
+  </si>
+  <si>
+    <t>07/07/26 11:26 EDT</t>
+  </si>
+  <si>
+    <t>39.594425, -86.535416</t>
+  </si>
+  <si>
+    <t>07/07/26 17:09 EDT</t>
+  </si>
+  <si>
+    <t>39.499450, -86.652130</t>
+  </si>
+  <si>
+    <t>07/07/26 17:29 EDT</t>
+  </si>
+  <si>
+    <t>39.499290, -86.672730</t>
+  </si>
+  <si>
+    <t>07/07/26 21:11 EDT</t>
+  </si>
+  <si>
+    <t>39.689680, -86.669945</t>
+  </si>
+  <si>
+    <t>07/07/26 21:13 EDT</t>
+  </si>
+  <si>
+    <t>39.667740, -86.669630</t>
+  </si>
+  <si>
+    <t>07/07/26 21:14 EDT</t>
+  </si>
+  <si>
+    <t>39.651840, -86.669770</t>
+  </si>
+  <si>
+    <t>07/08/26 07:45 EDT</t>
+  </si>
+  <si>
+    <t>07/07/26 21:25 EDT</t>
+  </si>
+  <si>
+    <t>39.557617, -86.646440</t>
+  </si>
+  <si>
+    <t>07/07/26 21:30 EDT</t>
+  </si>
+  <si>
+    <t>12.3mi NW of Martinsville IN</t>
+  </si>
+  <si>
+    <t>39.521240, -86.616100</t>
+  </si>
+  <si>
+    <t>07/07/26 22:10 EDT</t>
+  </si>
+  <si>
+    <t>39.564690, -86.589610</t>
+  </si>
+  <si>
+    <t>07/07/26 23:36 EDT</t>
+  </si>
+  <si>
+    <t>39.500640, -86.781140</t>
+  </si>
+  <si>
+    <t>07/08/26 07:44 EDT</t>
+  </si>
+  <si>
+    <t>07/07/26 23:39 EDT</t>
+  </si>
+  <si>
+    <t>39.533240, -86.802800</t>
+  </si>
+  <si>
+    <t>07/08/26 00:01 EDT</t>
+  </si>
+  <si>
+    <t>39.556324, -86.680590</t>
+  </si>
+  <si>
+    <t>07/08/26 07:43 EDT</t>
+  </si>
+  <si>
+    <t>07/08/26 06:48 EDT</t>
+  </si>
+  <si>
+    <t>9.9mi W of Danville IN</t>
+  </si>
+  <si>
+    <t>39.717255, -86.680510</t>
+  </si>
+  <si>
+    <t>07/08/26 10:10 EDT</t>
+  </si>
+  <si>
+    <t>39.638750, -86.431140</t>
+  </si>
+  <si>
+    <t>07/09/26 07:55 EDT</t>
+  </si>
+  <si>
+    <t>07/08/26 16:38 EDT</t>
+  </si>
+  <si>
+    <t>39.572086, -86.701480</t>
+  </si>
+  <si>
+    <t>07/08/26 16:40 EDT</t>
+  </si>
+  <si>
+    <t>39.572210, -86.669830</t>
+  </si>
+  <si>
+    <t>07/08/26 16:44 EDT</t>
+  </si>
+  <si>
+    <t>39.579410, -86.632060</t>
+  </si>
+  <si>
+    <t>07/08/26 22:26 EDT</t>
+  </si>
+  <si>
+    <t>39.557674, -86.701760</t>
+  </si>
+  <si>
+    <t>07/08/26 22:31 EDT</t>
+  </si>
+  <si>
+    <t>39.585070, -86.669660</t>
+  </si>
+  <si>
+    <t>07/08/26 23:20 EDT</t>
+  </si>
+  <si>
+    <t>39.628100, -86.670120</t>
+  </si>
+  <si>
+    <t>07/09/26 16:45 EDT</t>
+  </si>
+  <si>
+    <t>39.678790, -86.343500</t>
+  </si>
+  <si>
+    <t>07/10/26 08:10 EDT</t>
+  </si>
+  <si>
+    <t>07/09/26 18:18 EDT</t>
+  </si>
+  <si>
+    <t>39.514470, -86.382400</t>
+  </si>
+  <si>
+    <t>07/09/26 20:08 EDT</t>
+  </si>
+  <si>
+    <t>39.525760, -86.809906</t>
+  </si>
+  <si>
+    <t>07/09/26 20:18 EDT</t>
+  </si>
+  <si>
+    <t>39.569440, -86.632080</t>
+  </si>
+  <si>
+    <t>07/10/26 06:56 EDT</t>
+  </si>
+  <si>
+    <t>39.616264, -86.720610</t>
+  </si>
+  <si>
+    <t>07/10/26 06:57 EDT</t>
+  </si>
+  <si>
+    <t>6.1mi SE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.608410, -86.736430</t>
+  </si>
+  <si>
+    <t>07/10/26 08:05 EDT</t>
+  </si>
+  <si>
+    <t>07/10/26 12:21 EDT</t>
+  </si>
+  <si>
+    <t>07/10/26 07:00 EDT</t>
+  </si>
+  <si>
+    <t>39.587910, -86.805530</t>
+  </si>
+  <si>
+    <t>07/10/26 07:03 EDT</t>
+  </si>
+  <si>
+    <t>39.575280, -86.860020</t>
+  </si>
+  <si>
+    <t>07/10/26 08:07 EDT</t>
+  </si>
+  <si>
+    <t>07/10/26 07:05 EDT</t>
+  </si>
+  <si>
+    <t>39.560940, -86.905490</t>
+  </si>
+  <si>
+    <t>07/10/26 08:08 EDT</t>
+  </si>
+  <si>
+    <t>5.8mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.562560, -86.813930</t>
+  </si>
+  <si>
+    <t>07/10/26 10:18 EDT</t>
+  </si>
+  <si>
+    <t>39.538616, -86.763916</t>
+  </si>
+  <si>
+    <t>07/10/26 11:29 EDT</t>
+  </si>
+  <si>
+    <t>39.433290, -87.292610</t>
+  </si>
+  <si>
+    <t>07/10/26 11:43 EDT</t>
+  </si>
+  <si>
+    <t>39.493080, -86.985855</t>
+  </si>
+  <si>
+    <t>07/10/26 12:05 EDT</t>
+  </si>
+  <si>
+    <t>39.499300, -86.668150</t>
+  </si>
+  <si>
+    <t>07/10/26 19:13 EDT</t>
+  </si>
+  <si>
+    <t>39.710205, -86.669850</t>
+  </si>
+  <si>
+    <t>07/10/26 19:15 EDT</t>
+  </si>
+  <si>
+    <t>39.689520, -86.666120</t>
+  </si>
+  <si>
+    <t>07/10/26 19:23 EDT</t>
+  </si>
+  <si>
+    <t>39.633070, -86.626520</t>
+  </si>
+  <si>
+    <t>07/10/26 19:25 EDT</t>
+  </si>
+  <si>
+    <t>39.614100, -86.594570</t>
+  </si>
+  <si>
+    <t>39.610405, -86.585220</t>
+  </si>
+  <si>
+    <t>07/10/26 19:32 EDT</t>
+  </si>
+  <si>
+    <t>39.535660, -86.584820</t>
+  </si>
+  <si>
+    <t>07/10/26 19:34 EDT</t>
+  </si>
+  <si>
+    <t>39.521267, -86.564110</t>
+  </si>
+  <si>
+    <t>07/10/26 20:11 EDT</t>
+  </si>
+  <si>
+    <t>39.564700, -86.589615</t>
+  </si>
+  <si>
+    <t>07/11/26 13:16 EDT</t>
+  </si>
+  <si>
+    <t>3.6mi N of Martinsville IN</t>
+  </si>
+  <si>
+    <t>39.466570, -86.442930</t>
+  </si>
+  <si>
+    <t>07/11/26 13:21 EDT</t>
+  </si>
+  <si>
+    <t>39.717160, -86.669950</t>
+  </si>
+  <si>
+    <t>07/11/26 13:37 EDT</t>
+  </si>
+  <si>
+    <t>39.585380, -86.631940</t>
+  </si>
+  <si>
+    <t>07/11/26 15:42 EDT</t>
+  </si>
+  <si>
+    <t>39.692940, -86.669890</t>
+  </si>
+  <si>
+    <t>07/11/26 16:31 EDT</t>
+  </si>
+  <si>
+    <t>39.567696, -86.637610</t>
+  </si>
+  <si>
+    <t>07/11/26 17:05 EDT</t>
+  </si>
+  <si>
+    <t>5.1mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.573490, -86.872110</t>
   </si>
 </sst>
 </file>
@@ -14763,7 +15381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1910"/>
+  <dimension ref="A1:N1991"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -79606,7 +80224,7 @@
         <v>4704</v>
       </c>
       <c r="H1868" s="3" t="s">
-        <v>276</v>
+        <v>853</v>
       </c>
       <c r="I1868" s="3">
         <v>36</v>
@@ -79619,13 +80237,13 @@
         <v>430</v>
       </c>
       <c r="M1868" s="3" t="s">
-        <v>4693</v>
+        <v>4705</v>
       </c>
       <c r="N1868" s="3"/>
     </row>
     <row r="1869" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1869" s="3" t="s">
-        <v>4705</v>
+        <v>4706</v>
       </c>
       <c r="B1869" s="3"/>
       <c r="C1869" s="3">
@@ -79638,10 +80256,10 @@
         <v>201</v>
       </c>
       <c r="F1869" s="3" t="s">
-        <v>4706</v>
+        <v>4707</v>
       </c>
       <c r="G1869" s="3" t="s">
-        <v>4707</v>
+        <v>4708</v>
       </c>
       <c r="H1869" s="3"/>
       <c r="I1869" s="3">
@@ -79657,7 +80275,7 @@
     </row>
     <row r="1870" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1870" s="3" t="s">
-        <v>4708</v>
+        <v>4709</v>
       </c>
       <c r="B1870" s="3"/>
       <c r="C1870" s="3">
@@ -79673,23 +80291,29 @@
         <v>1994</v>
       </c>
       <c r="G1870" s="3" t="s">
-        <v>4709</v>
-      </c>
-      <c r="H1870" s="3"/>
+        <v>4710</v>
+      </c>
+      <c r="H1870" s="3" t="s">
+        <v>853</v>
+      </c>
       <c r="I1870" s="3">
         <v>29</v>
       </c>
       <c r="J1870" s="3"/>
       <c r="K1870" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1870" s="3"/>
-      <c r="M1870" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1870" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1870" s="3" t="s">
+        <v>4705</v>
+      </c>
       <c r="N1870" s="3"/>
     </row>
     <row r="1871" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1871" s="3" t="s">
-        <v>4710</v>
+        <v>4711</v>
       </c>
       <c r="B1871" s="3"/>
       <c r="C1871" s="3">
@@ -79705,21 +80329,27 @@
         <v>1994</v>
       </c>
       <c r="G1871" s="3" t="s">
-        <v>4711</v>
-      </c>
-      <c r="H1871" s="3"/>
+        <v>4712</v>
+      </c>
+      <c r="H1871" s="3" t="s">
+        <v>853</v>
+      </c>
       <c r="I1871" s="3"/>
       <c r="J1871" s="3"/>
       <c r="K1871" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1871" s="3"/>
-      <c r="M1871" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1871" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1871" s="3" t="s">
+        <v>4705</v>
+      </c>
       <c r="N1871" s="3"/>
     </row>
     <row r="1872" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1872" s="3" t="s">
-        <v>4712</v>
+        <v>4713</v>
       </c>
       <c r="B1872" s="3"/>
       <c r="C1872" s="3">
@@ -79732,10 +80362,10 @@
         <v>46</v>
       </c>
       <c r="F1872" s="3" t="s">
-        <v>4713</v>
+        <v>4714</v>
       </c>
       <c r="G1872" s="3" t="s">
-        <v>4714</v>
+        <v>4715</v>
       </c>
       <c r="H1872" s="3"/>
       <c r="I1872" s="3">
@@ -79751,7 +80381,7 @@
     </row>
     <row r="1873" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1873" s="3" t="s">
-        <v>4715</v>
+        <v>4716</v>
       </c>
       <c r="B1873" s="3"/>
       <c r="C1873" s="3">
@@ -79767,23 +80397,29 @@
         <v>84</v>
       </c>
       <c r="G1873" s="3" t="s">
-        <v>4716</v>
-      </c>
-      <c r="H1873" s="3"/>
+        <v>4717</v>
+      </c>
+      <c r="H1873" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="I1873" s="3">
         <v>71</v>
       </c>
       <c r="J1873" s="3"/>
       <c r="K1873" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1873" s="3"/>
-      <c r="M1873" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1873" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1873" s="3" t="s">
+        <v>4718</v>
+      </c>
       <c r="N1873" s="3"/>
     </row>
     <row r="1874" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1874" s="3" t="s">
-        <v>4717</v>
+        <v>4719</v>
       </c>
       <c r="B1874" s="3"/>
       <c r="C1874" s="3">
@@ -79796,26 +80432,32 @@
         <v>46</v>
       </c>
       <c r="F1874" s="3" t="s">
-        <v>4718</v>
+        <v>4720</v>
       </c>
       <c r="G1874" s="3" t="s">
-        <v>4719</v>
-      </c>
-      <c r="H1874" s="3"/>
+        <v>4721</v>
+      </c>
+      <c r="H1874" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1874" s="3">
         <v>68</v>
       </c>
       <c r="J1874" s="3"/>
       <c r="K1874" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1874" s="3"/>
-      <c r="M1874" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1874" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1874" s="3" t="s">
+        <v>4722</v>
+      </c>
       <c r="N1874" s="3"/>
     </row>
     <row r="1875" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1875" s="3" t="s">
-        <v>4717</v>
+        <v>4719</v>
       </c>
       <c r="B1875" s="3"/>
       <c r="C1875" s="3">
@@ -79831,23 +80473,29 @@
         <v>2264</v>
       </c>
       <c r="G1875" s="3" t="s">
-        <v>4720</v>
-      </c>
-      <c r="H1875" s="3"/>
+        <v>4723</v>
+      </c>
+      <c r="H1875" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1875" s="3">
         <v>63</v>
       </c>
       <c r="J1875" s="3"/>
       <c r="K1875" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1875" s="3"/>
-      <c r="M1875" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1875" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1875" s="3" t="s">
+        <v>4724</v>
+      </c>
       <c r="N1875" s="3"/>
     </row>
     <row r="1876" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1876" s="3" t="s">
-        <v>4721</v>
+        <v>4725</v>
       </c>
       <c r="B1876" s="3"/>
       <c r="C1876" s="3">
@@ -79863,7 +80511,7 @@
         <v>4588</v>
       </c>
       <c r="G1876" s="3" t="s">
-        <v>4722</v>
+        <v>4726</v>
       </c>
       <c r="H1876" s="3"/>
       <c r="I1876" s="3">
@@ -79879,7 +80527,7 @@
     </row>
     <row r="1877" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1877" s="3" t="s">
-        <v>4723</v>
+        <v>4727</v>
       </c>
       <c r="B1877" s="3"/>
       <c r="C1877" s="3">
@@ -79895,7 +80543,7 @@
         <v>304</v>
       </c>
       <c r="G1877" s="3" t="s">
-        <v>4724</v>
+        <v>4728</v>
       </c>
       <c r="H1877" s="3"/>
       <c r="I1877" s="3">
@@ -79911,7 +80559,7 @@
     </row>
     <row r="1878" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1878" s="3" t="s">
-        <v>4725</v>
+        <v>4729</v>
       </c>
       <c r="B1878" s="3"/>
       <c r="C1878" s="3">
@@ -79927,7 +80575,7 @@
         <v>77</v>
       </c>
       <c r="G1878" s="3" t="s">
-        <v>4726</v>
+        <v>4730</v>
       </c>
       <c r="H1878" s="3"/>
       <c r="I1878" s="3">
@@ -79943,7 +80591,7 @@
     </row>
     <row r="1879" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1879" s="3" t="s">
-        <v>4727</v>
+        <v>4731</v>
       </c>
       <c r="B1879" s="3"/>
       <c r="C1879" s="3">
@@ -79959,7 +80607,7 @@
         <v>1668</v>
       </c>
       <c r="G1879" s="3" t="s">
-        <v>4728</v>
+        <v>4732</v>
       </c>
       <c r="H1879" s="3"/>
       <c r="I1879" s="3">
@@ -79975,7 +80623,7 @@
     </row>
     <row r="1880" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1880" s="3" t="s">
-        <v>4729</v>
+        <v>4733</v>
       </c>
       <c r="B1880" s="3"/>
       <c r="C1880" s="3">
@@ -79988,10 +80636,10 @@
         <v>46</v>
       </c>
       <c r="F1880" s="3" t="s">
-        <v>4730</v>
+        <v>4734</v>
       </c>
       <c r="G1880" s="3" t="s">
-        <v>4731</v>
+        <v>4735</v>
       </c>
       <c r="H1880" s="3"/>
       <c r="I1880" s="3">
@@ -80007,7 +80655,7 @@
     </row>
     <row r="1881" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1881" s="3" t="s">
-        <v>4732</v>
+        <v>4736</v>
       </c>
       <c r="B1881" s="3"/>
       <c r="C1881" s="3">
@@ -80023,23 +80671,29 @@
         <v>274</v>
       </c>
       <c r="G1881" s="3" t="s">
-        <v>4733</v>
-      </c>
-      <c r="H1881" s="3"/>
+        <v>4737</v>
+      </c>
+      <c r="H1881" s="3" t="s">
+        <v>853</v>
+      </c>
       <c r="I1881" s="3">
         <v>15</v>
       </c>
       <c r="J1881" s="3"/>
       <c r="K1881" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1881" s="3"/>
-      <c r="M1881" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1881" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1881" s="3" t="s">
+        <v>4738</v>
+      </c>
       <c r="N1881" s="3"/>
     </row>
     <row r="1882" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1882" s="3" t="s">
-        <v>4734</v>
+        <v>4739</v>
       </c>
       <c r="B1882" s="3"/>
       <c r="C1882" s="3">
@@ -80055,7 +80709,7 @@
         <v>3602</v>
       </c>
       <c r="G1882" s="3" t="s">
-        <v>4735</v>
+        <v>4740</v>
       </c>
       <c r="H1882" s="3"/>
       <c r="I1882" s="3">
@@ -80073,7 +80727,7 @@
     </row>
     <row r="1883" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1883" s="3" t="s">
-        <v>4736</v>
+        <v>4741</v>
       </c>
       <c r="B1883" s="3"/>
       <c r="C1883" s="3">
@@ -80089,23 +80743,29 @@
         <v>342</v>
       </c>
       <c r="G1883" s="3" t="s">
-        <v>4737</v>
-      </c>
-      <c r="H1883" s="3"/>
+        <v>4742</v>
+      </c>
+      <c r="H1883" s="3" t="s">
+        <v>853</v>
+      </c>
       <c r="I1883" s="3">
         <v>15</v>
       </c>
       <c r="J1883" s="3"/>
       <c r="K1883" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1883" s="3"/>
-      <c r="M1883" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1883" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1883" s="3" t="s">
+        <v>4738</v>
+      </c>
       <c r="N1883" s="3"/>
     </row>
     <row r="1884" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1884" s="3" t="s">
-        <v>4738</v>
+        <v>4743</v>
       </c>
       <c r="B1884" s="3"/>
       <c r="C1884" s="3">
@@ -80121,23 +80781,29 @@
         <v>1636</v>
       </c>
       <c r="G1884" s="3" t="s">
-        <v>4739</v>
-      </c>
-      <c r="H1884" s="3"/>
+        <v>4744</v>
+      </c>
+      <c r="H1884" s="3" t="s">
+        <v>853</v>
+      </c>
       <c r="I1884" s="3">
         <v>29</v>
       </c>
       <c r="J1884" s="3"/>
       <c r="K1884" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1884" s="3"/>
-      <c r="M1884" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1884" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1884" s="3" t="s">
+        <v>4738</v>
+      </c>
       <c r="N1884" s="3"/>
     </row>
     <row r="1885" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1885" s="3" t="s">
-        <v>4740</v>
+        <v>4745</v>
       </c>
       <c r="B1885" s="3"/>
       <c r="C1885" s="3">
@@ -80150,26 +80816,32 @@
         <v>194</v>
       </c>
       <c r="F1885" s="3" t="s">
-        <v>4741</v>
+        <v>4746</v>
       </c>
       <c r="G1885" s="3" t="s">
-        <v>4742</v>
-      </c>
-      <c r="H1885" s="3"/>
+        <v>4747</v>
+      </c>
+      <c r="H1885" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1885" s="3">
         <v>54</v>
       </c>
       <c r="J1885" s="3"/>
       <c r="K1885" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1885" s="3"/>
-      <c r="M1885" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1885" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1885" s="3" t="s">
+        <v>4748</v>
+      </c>
       <c r="N1885" s="3"/>
     </row>
     <row r="1886" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1886" s="3" t="s">
-        <v>4743</v>
+        <v>4749</v>
       </c>
       <c r="B1886" s="3"/>
       <c r="C1886" s="3">
@@ -80185,23 +80857,29 @@
         <v>118</v>
       </c>
       <c r="G1886" s="3" t="s">
-        <v>4744</v>
-      </c>
-      <c r="H1886" s="3"/>
+        <v>4750</v>
+      </c>
+      <c r="H1886" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1886" s="3">
         <v>35</v>
       </c>
       <c r="J1886" s="3"/>
       <c r="K1886" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1886" s="3"/>
-      <c r="M1886" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1886" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1886" s="3" t="s">
+        <v>4751</v>
+      </c>
       <c r="N1886" s="3"/>
     </row>
     <row r="1887" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1887" s="3" t="s">
-        <v>4745</v>
+        <v>4752</v>
       </c>
       <c r="B1887" s="3"/>
       <c r="C1887" s="3">
@@ -80217,7 +80895,7 @@
         <v>2250</v>
       </c>
       <c r="G1887" s="3" t="s">
-        <v>4746</v>
+        <v>4753</v>
       </c>
       <c r="H1887" s="3"/>
       <c r="I1887" s="3">
@@ -80233,7 +80911,7 @@
     </row>
     <row r="1888" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1888" s="3" t="s">
-        <v>4747</v>
+        <v>4754</v>
       </c>
       <c r="B1888" s="3"/>
       <c r="C1888" s="3">
@@ -80246,10 +80924,10 @@
         <v>33</v>
       </c>
       <c r="F1888" s="3" t="s">
-        <v>4748</v>
+        <v>4755</v>
       </c>
       <c r="G1888" s="3" t="s">
-        <v>4749</v>
+        <v>4756</v>
       </c>
       <c r="H1888" s="3"/>
       <c r="I1888" s="3">
@@ -80265,7 +80943,7 @@
     </row>
     <row r="1889" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1889" s="3" t="s">
-        <v>4750</v>
+        <v>4757</v>
       </c>
       <c r="B1889" s="3"/>
       <c r="C1889" s="3">
@@ -80281,7 +80959,7 @@
         <v>361</v>
       </c>
       <c r="G1889" s="3" t="s">
-        <v>4751</v>
+        <v>4758</v>
       </c>
       <c r="H1889" s="3"/>
       <c r="I1889" s="3">
@@ -80297,9 +80975,11 @@
     </row>
     <row r="1890" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1890" s="3" t="s">
-        <v>4752</v>
-      </c>
-      <c r="B1890" s="3"/>
+        <v>4759</v>
+      </c>
+      <c r="B1890" s="3" t="s">
+        <v>273</v>
+      </c>
       <c r="C1890" s="3">
         <v>31</v>
       </c>
@@ -80313,23 +80993,31 @@
         <v>2164</v>
       </c>
       <c r="G1890" s="3" t="s">
-        <v>4753</v>
-      </c>
-      <c r="H1890" s="3"/>
+        <v>4760</v>
+      </c>
+      <c r="H1890" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="I1890" s="3">
         <v>75</v>
       </c>
       <c r="J1890" s="3"/>
       <c r="K1890" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1890" s="3"/>
-      <c r="M1890" s="3"/>
-      <c r="N1890" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1890" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1890" s="3" t="s">
+        <v>4748</v>
+      </c>
+      <c r="N1890" s="3" t="s">
+        <v>4761</v>
+      </c>
     </row>
     <row r="1891" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1891" s="3" t="s">
-        <v>4754</v>
+        <v>4762</v>
       </c>
       <c r="B1891" s="3"/>
       <c r="C1891" s="3">
@@ -80345,7 +81033,7 @@
         <v>52</v>
       </c>
       <c r="G1891" s="3" t="s">
-        <v>4755</v>
+        <v>4763</v>
       </c>
       <c r="H1891" s="3"/>
       <c r="I1891" s="3">
@@ -80361,7 +81049,7 @@
     </row>
     <row r="1892" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1892" s="3" t="s">
-        <v>4756</v>
+        <v>4764</v>
       </c>
       <c r="B1892" s="3"/>
       <c r="C1892" s="3">
@@ -80377,7 +81065,7 @@
         <v>52</v>
       </c>
       <c r="G1892" s="3" t="s">
-        <v>4757</v>
+        <v>4765</v>
       </c>
       <c r="H1892" s="3"/>
       <c r="I1892" s="3">
@@ -80393,7 +81081,7 @@
     </row>
     <row r="1893" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1893" s="3" t="s">
-        <v>4758</v>
+        <v>4766</v>
       </c>
       <c r="B1893" s="3"/>
       <c r="C1893" s="3">
@@ -80409,7 +81097,7 @@
         <v>442</v>
       </c>
       <c r="G1893" s="3" t="s">
-        <v>4759</v>
+        <v>4767</v>
       </c>
       <c r="H1893" s="3"/>
       <c r="I1893" s="3">
@@ -80425,7 +81113,7 @@
     </row>
     <row r="1894" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1894" s="3" t="s">
-        <v>4760</v>
+        <v>4768</v>
       </c>
       <c r="B1894" s="3"/>
       <c r="C1894" s="3">
@@ -80438,26 +81126,32 @@
         <v>46</v>
       </c>
       <c r="F1894" s="3" t="s">
-        <v>4761</v>
+        <v>4769</v>
       </c>
       <c r="G1894" s="3" t="s">
-        <v>4762</v>
-      </c>
-      <c r="H1894" s="3"/>
+        <v>4770</v>
+      </c>
+      <c r="H1894" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1894" s="3">
         <v>76</v>
       </c>
       <c r="J1894" s="3"/>
       <c r="K1894" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1894" s="3"/>
-      <c r="M1894" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1894" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1894" s="3" t="s">
+        <v>4771</v>
+      </c>
       <c r="N1894" s="3"/>
     </row>
     <row r="1895" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1895" s="3" t="s">
-        <v>4763</v>
+        <v>4772</v>
       </c>
       <c r="B1895" s="3"/>
       <c r="C1895" s="3">
@@ -80470,10 +81164,10 @@
         <v>169</v>
       </c>
       <c r="F1895" s="3" t="s">
-        <v>4764</v>
+        <v>4773</v>
       </c>
       <c r="G1895" s="3" t="s">
-        <v>4765</v>
+        <v>4774</v>
       </c>
       <c r="H1895" s="3"/>
       <c r="I1895" s="3">
@@ -80489,9 +81183,11 @@
     </row>
     <row r="1896" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1896" s="3" t="s">
-        <v>4766</v>
-      </c>
-      <c r="B1896" s="3"/>
+        <v>4775</v>
+      </c>
+      <c r="B1896" s="3" t="s">
+        <v>273</v>
+      </c>
       <c r="C1896" s="3">
         <v>31</v>
       </c>
@@ -80507,7 +81203,9 @@
       <c r="G1896" s="3" t="s">
         <v>2590</v>
       </c>
-      <c r="H1896" s="3"/>
+      <c r="H1896" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="I1896" s="3">
         <v>74</v>
       </c>
@@ -80515,15 +81213,19 @@
         <v>60</v>
       </c>
       <c r="K1896" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1896" s="3"/>
-      <c r="M1896" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1896" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1896" s="3" t="s">
+        <v>4771</v>
+      </c>
       <c r="N1896" s="3"/>
     </row>
     <row r="1897" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1897" s="3" t="s">
-        <v>4766</v>
+        <v>4775</v>
       </c>
       <c r="B1897" s="3"/>
       <c r="C1897" s="3">
@@ -80539,23 +81241,29 @@
         <v>1439</v>
       </c>
       <c r="G1897" s="3" t="s">
-        <v>4767</v>
-      </c>
-      <c r="H1897" s="3"/>
+        <v>4776</v>
+      </c>
+      <c r="H1897" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1897" s="3">
         <v>74</v>
       </c>
       <c r="J1897" s="3"/>
       <c r="K1897" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1897" s="3"/>
-      <c r="M1897" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1897" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1897" s="3" t="s">
+        <v>4777</v>
+      </c>
       <c r="N1897" s="3"/>
     </row>
     <row r="1898" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1898" s="3" t="s">
-        <v>4768</v>
+        <v>4778</v>
       </c>
       <c r="B1898" s="3"/>
       <c r="C1898" s="3">
@@ -80571,7 +81279,7 @@
         <v>495</v>
       </c>
       <c r="G1898" s="3" t="s">
-        <v>4769</v>
+        <v>4779</v>
       </c>
       <c r="H1898" s="3"/>
       <c r="I1898" s="3">
@@ -80587,7 +81295,7 @@
     </row>
     <row r="1899" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1899" s="3" t="s">
-        <v>4770</v>
+        <v>4780</v>
       </c>
       <c r="B1899" s="3"/>
       <c r="C1899" s="3">
@@ -80603,7 +81311,7 @@
         <v>661</v>
       </c>
       <c r="G1899" s="3" t="s">
-        <v>4771</v>
+        <v>4781</v>
       </c>
       <c r="H1899" s="3"/>
       <c r="I1899" s="3">
@@ -80619,7 +81327,7 @@
     </row>
     <row r="1900" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1900" s="3" t="s">
-        <v>4772</v>
+        <v>4782</v>
       </c>
       <c r="B1900" s="3"/>
       <c r="C1900" s="3">
@@ -80635,7 +81343,7 @@
         <v>290</v>
       </c>
       <c r="G1900" s="3" t="s">
-        <v>4773</v>
+        <v>4783</v>
       </c>
       <c r="H1900" s="3"/>
       <c r="I1900" s="3">
@@ -80651,7 +81359,7 @@
     </row>
     <row r="1901" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1901" s="3" t="s">
-        <v>4772</v>
+        <v>4782</v>
       </c>
       <c r="B1901" s="3"/>
       <c r="C1901" s="3">
@@ -80667,7 +81375,7 @@
         <v>2264</v>
       </c>
       <c r="G1901" s="3" t="s">
-        <v>4774</v>
+        <v>4784</v>
       </c>
       <c r="H1901" s="3"/>
       <c r="I1901" s="3">
@@ -80683,7 +81391,7 @@
     </row>
     <row r="1902" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1902" s="3" t="s">
-        <v>4775</v>
+        <v>4785</v>
       </c>
       <c r="B1902" s="3"/>
       <c r="C1902" s="3">
@@ -80699,7 +81407,7 @@
         <v>1331</v>
       </c>
       <c r="G1902" s="3" t="s">
-        <v>4776</v>
+        <v>4786</v>
       </c>
       <c r="H1902" s="3"/>
       <c r="I1902" s="3">
@@ -80715,7 +81423,7 @@
     </row>
     <row r="1903" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1903" s="3" t="s">
-        <v>4777</v>
+        <v>4787</v>
       </c>
       <c r="B1903" s="3"/>
       <c r="C1903" s="3">
@@ -80728,10 +81436,10 @@
         <v>33</v>
       </c>
       <c r="F1903" s="3" t="s">
-        <v>4778</v>
+        <v>4788</v>
       </c>
       <c r="G1903" s="3" t="s">
-        <v>4779</v>
+        <v>4789</v>
       </c>
       <c r="H1903" s="3"/>
       <c r="I1903" s="3">
@@ -80747,7 +81455,7 @@
     </row>
     <row r="1904" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1904" s="3" t="s">
-        <v>4780</v>
+        <v>4790</v>
       </c>
       <c r="B1904" s="3"/>
       <c r="C1904" s="3">
@@ -80763,7 +81471,7 @@
         <v>342</v>
       </c>
       <c r="G1904" s="3" t="s">
-        <v>4781</v>
+        <v>4791</v>
       </c>
       <c r="H1904" s="3"/>
       <c r="I1904" s="3">
@@ -80779,7 +81487,7 @@
     </row>
     <row r="1905" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1905" s="3" t="s">
-        <v>4782</v>
+        <v>4792</v>
       </c>
       <c r="B1905" s="3"/>
       <c r="C1905" s="3">
@@ -80795,7 +81503,7 @@
         <v>1325</v>
       </c>
       <c r="G1905" s="3" t="s">
-        <v>4783</v>
+        <v>4793</v>
       </c>
       <c r="H1905" s="3"/>
       <c r="I1905" s="3">
@@ -80811,7 +81519,7 @@
     </row>
     <row r="1906" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1906" s="3" t="s">
-        <v>4784</v>
+        <v>4794</v>
       </c>
       <c r="B1906" s="3"/>
       <c r="C1906" s="3">
@@ -80827,7 +81535,7 @@
         <v>847</v>
       </c>
       <c r="G1906" s="3" t="s">
-        <v>4785</v>
+        <v>4795</v>
       </c>
       <c r="H1906" s="3"/>
       <c r="I1906" s="3">
@@ -80843,7 +81551,7 @@
     </row>
     <row r="1907" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1907" s="3" t="s">
-        <v>4786</v>
+        <v>4796</v>
       </c>
       <c r="B1907" s="3"/>
       <c r="C1907" s="3">
@@ -80859,7 +81567,7 @@
         <v>1331</v>
       </c>
       <c r="G1907" s="3" t="s">
-        <v>4787</v>
+        <v>4797</v>
       </c>
       <c r="H1907" s="3"/>
       <c r="I1907" s="3">
@@ -80875,7 +81583,7 @@
     </row>
     <row r="1908" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1908" s="3" t="s">
-        <v>4788</v>
+        <v>4798</v>
       </c>
       <c r="B1908" s="3"/>
       <c r="C1908" s="3">
@@ -80891,23 +81599,29 @@
         <v>847</v>
       </c>
       <c r="G1908" s="3" t="s">
-        <v>4789</v>
-      </c>
-      <c r="H1908" s="3"/>
+        <v>4799</v>
+      </c>
+      <c r="H1908" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1908" s="3">
         <v>26</v>
       </c>
       <c r="J1908" s="3"/>
       <c r="K1908" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1908" s="3"/>
-      <c r="M1908" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1908" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1908" s="3" t="s">
+        <v>4800</v>
+      </c>
       <c r="N1908" s="3"/>
     </row>
     <row r="1909" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1909" s="3" t="s">
-        <v>4790</v>
+        <v>4801</v>
       </c>
       <c r="B1909" s="3"/>
       <c r="C1909" s="3">
@@ -80923,23 +81637,29 @@
         <v>914</v>
       </c>
       <c r="G1909" s="3" t="s">
-        <v>4791</v>
-      </c>
-      <c r="H1909" s="3"/>
+        <v>4802</v>
+      </c>
+      <c r="H1909" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="I1909" s="3">
         <v>39</v>
       </c>
       <c r="J1909" s="3"/>
       <c r="K1909" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1909" s="3"/>
-      <c r="M1909" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1909" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1909" s="3" t="s">
+        <v>4803</v>
+      </c>
       <c r="N1909" s="3"/>
     </row>
     <row r="1910" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1910" s="3" t="s">
-        <v>4792</v>
+        <v>4804</v>
       </c>
       <c r="B1910" s="3"/>
       <c r="C1910" s="3">
@@ -80955,7 +81675,7 @@
         <v>1331</v>
       </c>
       <c r="G1910" s="3" t="s">
-        <v>4793</v>
+        <v>4805</v>
       </c>
       <c r="H1910" s="3"/>
       <c r="I1910" s="3"/>
@@ -80967,6 +81687,2798 @@
       <c r="M1910" s="3"/>
       <c r="N1910" s="3"/>
     </row>
+    <row r="1911" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1911" s="3" t="s">
+        <v>4806</v>
+      </c>
+      <c r="B1911" s="3"/>
+      <c r="C1911" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1911" s="3">
+        <v>6075813765</v>
+      </c>
+      <c r="E1911" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1911" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="G1911" s="3" t="s">
+        <v>4807</v>
+      </c>
+      <c r="H1911" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1911" s="3">
+        <v>56</v>
+      </c>
+      <c r="J1911" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1911" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1911" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1911" s="3" t="s">
+        <v>4800</v>
+      </c>
+      <c r="N1911" s="3"/>
+    </row>
+    <row r="1912" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1912" s="3" t="s">
+        <v>4808</v>
+      </c>
+      <c r="B1912" s="3"/>
+      <c r="C1912" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1912" s="3">
+        <v>6075848421</v>
+      </c>
+      <c r="E1912" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1912" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="G1912" s="3" t="s">
+        <v>4809</v>
+      </c>
+      <c r="H1912" s="3"/>
+      <c r="I1912" s="3">
+        <v>51</v>
+      </c>
+      <c r="J1912" s="3">
+        <v>45</v>
+      </c>
+      <c r="K1912" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1912" s="3"/>
+      <c r="M1912" s="3"/>
+      <c r="N1912" s="3"/>
+    </row>
+    <row r="1913" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1913" s="3" t="s">
+        <v>4810</v>
+      </c>
+      <c r="B1913" s="3"/>
+      <c r="C1913" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1913" s="3">
+        <v>6076665261</v>
+      </c>
+      <c r="E1913" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1913" s="3" t="s">
+        <v>4811</v>
+      </c>
+      <c r="G1913" s="3" t="s">
+        <v>4812</v>
+      </c>
+      <c r="H1913" s="3"/>
+      <c r="I1913" s="3">
+        <v>56</v>
+      </c>
+      <c r="J1913" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1913" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1913" s="3"/>
+      <c r="M1913" s="3"/>
+      <c r="N1913" s="3"/>
+    </row>
+    <row r="1914" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1914" s="3" t="s">
+        <v>4813</v>
+      </c>
+      <c r="B1914" s="3"/>
+      <c r="C1914" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1914" s="3">
+        <v>6078302199</v>
+      </c>
+      <c r="E1914" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1914" s="3" t="s">
+        <v>4814</v>
+      </c>
+      <c r="G1914" s="3" t="s">
+        <v>4815</v>
+      </c>
+      <c r="H1914" s="3"/>
+      <c r="I1914" s="3">
+        <v>16</v>
+      </c>
+      <c r="J1914" s="3"/>
+      <c r="K1914" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1914" s="3"/>
+      <c r="M1914" s="3"/>
+      <c r="N1914" s="3"/>
+    </row>
+    <row r="1915" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1915" s="3" t="s">
+        <v>4816</v>
+      </c>
+      <c r="B1915" s="3"/>
+      <c r="C1915" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1915" s="3">
+        <v>6078314747</v>
+      </c>
+      <c r="E1915" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1915" s="3" t="s">
+        <v>4814</v>
+      </c>
+      <c r="G1915" s="3" t="s">
+        <v>4817</v>
+      </c>
+      <c r="H1915" s="3"/>
+      <c r="I1915" s="3">
+        <v>13</v>
+      </c>
+      <c r="J1915" s="3"/>
+      <c r="K1915" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1915" s="3"/>
+      <c r="M1915" s="3"/>
+      <c r="N1915" s="3"/>
+    </row>
+    <row r="1916" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1916" s="3" t="s">
+        <v>4818</v>
+      </c>
+      <c r="B1916" s="3"/>
+      <c r="C1916" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1916" s="3">
+        <v>6078368894</v>
+      </c>
+      <c r="E1916" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1916" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1916" s="3" t="s">
+        <v>4819</v>
+      </c>
+      <c r="H1916" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1916" s="3">
+        <v>53</v>
+      </c>
+      <c r="J1916" s="3"/>
+      <c r="K1916" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1916" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1916" s="3" t="s">
+        <v>4820</v>
+      </c>
+      <c r="N1916" s="3"/>
+    </row>
+    <row r="1917" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1917" s="3" t="s">
+        <v>4821</v>
+      </c>
+      <c r="B1917" s="3"/>
+      <c r="C1917" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1917" s="3">
+        <v>6078773249</v>
+      </c>
+      <c r="E1917" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1917" s="3" t="s">
+        <v>4822</v>
+      </c>
+      <c r="G1917" s="3" t="s">
+        <v>4823</v>
+      </c>
+      <c r="H1917" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1917" s="3">
+        <v>58</v>
+      </c>
+      <c r="J1917" s="3"/>
+      <c r="K1917" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1917" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1917" s="3" t="s">
+        <v>4824</v>
+      </c>
+      <c r="N1917" s="3"/>
+    </row>
+    <row r="1918" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1918" s="3" t="s">
+        <v>4825</v>
+      </c>
+      <c r="B1918" s="3"/>
+      <c r="C1918" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1918" s="3">
+        <v>6079047784</v>
+      </c>
+      <c r="E1918" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1918" s="3" t="s">
+        <v>4826</v>
+      </c>
+      <c r="G1918" s="3" t="s">
+        <v>4827</v>
+      </c>
+      <c r="H1918" s="3"/>
+      <c r="I1918" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1918" s="3"/>
+      <c r="K1918" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1918" s="3"/>
+      <c r="M1918" s="3"/>
+      <c r="N1918" s="3"/>
+    </row>
+    <row r="1919" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1919" s="3" t="s">
+        <v>4828</v>
+      </c>
+      <c r="B1919" s="3"/>
+      <c r="C1919" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1919" s="3">
+        <v>6079053197</v>
+      </c>
+      <c r="E1919" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1919" s="3" t="s">
+        <v>1997</v>
+      </c>
+      <c r="G1919" s="3" t="s">
+        <v>4829</v>
+      </c>
+      <c r="H1919" s="3"/>
+      <c r="I1919" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1919" s="3"/>
+      <c r="K1919" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1919" s="3"/>
+      <c r="M1919" s="3"/>
+      <c r="N1919" s="3"/>
+    </row>
+    <row r="1920" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1920" s="3" t="s">
+        <v>4830</v>
+      </c>
+      <c r="B1920" s="3"/>
+      <c r="C1920" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1920" s="3">
+        <v>6079191518</v>
+      </c>
+      <c r="E1920" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1920" s="3" t="s">
+        <v>4831</v>
+      </c>
+      <c r="G1920" s="3" t="s">
+        <v>4832</v>
+      </c>
+      <c r="H1920" s="3"/>
+      <c r="I1920" s="3">
+        <v>17</v>
+      </c>
+      <c r="J1920" s="3"/>
+      <c r="K1920" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1920" s="3"/>
+      <c r="M1920" s="3"/>
+      <c r="N1920" s="3"/>
+    </row>
+    <row r="1921" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1921" s="3" t="s">
+        <v>4833</v>
+      </c>
+      <c r="B1921" s="3"/>
+      <c r="C1921" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1921" s="3">
+        <v>6079451986</v>
+      </c>
+      <c r="E1921" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1921" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G1921" s="3" t="s">
+        <v>4834</v>
+      </c>
+      <c r="H1921" s="3"/>
+      <c r="I1921" s="3">
+        <v>29</v>
+      </c>
+      <c r="J1921" s="3"/>
+      <c r="K1921" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1921" s="3"/>
+      <c r="M1921" s="3"/>
+      <c r="N1921" s="3"/>
+    </row>
+    <row r="1922" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1922" s="3" t="s">
+        <v>4835</v>
+      </c>
+      <c r="B1922" s="3"/>
+      <c r="C1922" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1922" s="3">
+        <v>6080272542</v>
+      </c>
+      <c r="E1922" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F1922" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G1922" s="3" t="s">
+        <v>4836</v>
+      </c>
+      <c r="H1922" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1922" s="3">
+        <v>7</v>
+      </c>
+      <c r="J1922" s="3"/>
+      <c r="K1922" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1922" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1922" s="3" t="s">
+        <v>4837</v>
+      </c>
+      <c r="N1922" s="3"/>
+    </row>
+    <row r="1923" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1923" s="3" t="s">
+        <v>4838</v>
+      </c>
+      <c r="B1923" s="3"/>
+      <c r="C1923" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1923" s="3">
+        <v>6080382945</v>
+      </c>
+      <c r="E1923" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1923" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="G1923" s="3" t="s">
+        <v>4839</v>
+      </c>
+      <c r="H1923" s="3"/>
+      <c r="I1923" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1923" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1923" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1923" s="3"/>
+      <c r="M1923" s="3"/>
+      <c r="N1923" s="3"/>
+    </row>
+    <row r="1924" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1924" s="3" t="s">
+        <v>4840</v>
+      </c>
+      <c r="B1924" s="3"/>
+      <c r="C1924" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1924" s="3">
+        <v>6080391363</v>
+      </c>
+      <c r="E1924" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1924" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1924" s="3" t="s">
+        <v>4841</v>
+      </c>
+      <c r="H1924" s="3"/>
+      <c r="I1924" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1924" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1924" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1924" s="3"/>
+      <c r="M1924" s="3"/>
+      <c r="N1924" s="3"/>
+    </row>
+    <row r="1925" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1925" s="3" t="s">
+        <v>4842</v>
+      </c>
+      <c r="B1925" s="3"/>
+      <c r="C1925" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1925" s="3">
+        <v>6080400118</v>
+      </c>
+      <c r="E1925" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1925" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1925" s="3" t="s">
+        <v>4843</v>
+      </c>
+      <c r="H1925" s="3"/>
+      <c r="I1925" s="3">
+        <v>57</v>
+      </c>
+      <c r="J1925" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1925" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1925" s="3"/>
+      <c r="M1925" s="3"/>
+      <c r="N1925" s="3"/>
+    </row>
+    <row r="1926" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1926" s="3" t="s">
+        <v>4844</v>
+      </c>
+      <c r="B1926" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1926" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1926" s="3">
+        <v>6080546706</v>
+      </c>
+      <c r="E1926" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1926" s="3" t="s">
+        <v>4845</v>
+      </c>
+      <c r="G1926" s="3" t="s">
+        <v>4846</v>
+      </c>
+      <c r="H1926" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1926" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1926" s="3"/>
+      <c r="K1926" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1926" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1926" s="3" t="s">
+        <v>4847</v>
+      </c>
+      <c r="N1926" s="3" t="s">
+        <v>4848</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1927" s="3" t="s">
+        <v>4849</v>
+      </c>
+      <c r="B1927" s="3"/>
+      <c r="C1927" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1927" s="3">
+        <v>6081076556</v>
+      </c>
+      <c r="E1927" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1927" s="3" t="s">
+        <v>1804</v>
+      </c>
+      <c r="G1927" s="3" t="s">
+        <v>4850</v>
+      </c>
+      <c r="H1927" s="3"/>
+      <c r="I1927" s="3"/>
+      <c r="J1927" s="3"/>
+      <c r="K1927" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1927" s="3"/>
+      <c r="M1927" s="3"/>
+      <c r="N1927" s="3"/>
+    </row>
+    <row r="1928" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1928" s="3" t="s">
+        <v>4851</v>
+      </c>
+      <c r="B1928" s="3"/>
+      <c r="C1928" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1928" s="3">
+        <v>6081076559</v>
+      </c>
+      <c r="E1928" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1928" s="3" t="s">
+        <v>1804</v>
+      </c>
+      <c r="G1928" s="3" t="s">
+        <v>4852</v>
+      </c>
+      <c r="H1928" s="3"/>
+      <c r="I1928" s="3">
+        <v>7</v>
+      </c>
+      <c r="J1928" s="3"/>
+      <c r="K1928" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1928" s="3"/>
+      <c r="M1928" s="3"/>
+      <c r="N1928" s="3"/>
+    </row>
+    <row r="1929" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1929" s="3" t="s">
+        <v>4853</v>
+      </c>
+      <c r="B1929" s="3"/>
+      <c r="C1929" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1929" s="3">
+        <v>6081137546</v>
+      </c>
+      <c r="E1929" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1929" s="3" t="s">
+        <v>4854</v>
+      </c>
+      <c r="G1929" s="3" t="s">
+        <v>4855</v>
+      </c>
+      <c r="H1929" s="3"/>
+      <c r="I1929" s="3"/>
+      <c r="J1929" s="3"/>
+      <c r="K1929" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1929" s="3"/>
+      <c r="M1929" s="3"/>
+      <c r="N1929" s="3"/>
+    </row>
+    <row r="1930" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1930" s="3" t="s">
+        <v>4856</v>
+      </c>
+      <c r="B1930" s="3"/>
+      <c r="C1930" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1930" s="3">
+        <v>6081301199</v>
+      </c>
+      <c r="E1930" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1930" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1930" s="3" t="s">
+        <v>4857</v>
+      </c>
+      <c r="H1930" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1930" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1930" s="3"/>
+      <c r="K1930" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1930" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1930" s="3" t="s">
+        <v>4858</v>
+      </c>
+      <c r="N1930" s="3"/>
+    </row>
+    <row r="1931" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1931" s="3" t="s">
+        <v>4859</v>
+      </c>
+      <c r="B1931" s="3"/>
+      <c r="C1931" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1931" s="3">
+        <v>6082365492</v>
+      </c>
+      <c r="E1931" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1931" s="3" t="s">
+        <v>2250</v>
+      </c>
+      <c r="G1931" s="3" t="s">
+        <v>4860</v>
+      </c>
+      <c r="H1931" s="3"/>
+      <c r="I1931" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1931" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1931" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1931" s="3"/>
+      <c r="M1931" s="3"/>
+      <c r="N1931" s="3"/>
+    </row>
+    <row r="1932" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1932" s="3" t="s">
+        <v>4861</v>
+      </c>
+      <c r="B1932" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1932" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1932" s="3">
+        <v>6082372743</v>
+      </c>
+      <c r="E1932" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1932" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G1932" s="3" t="s">
+        <v>4862</v>
+      </c>
+      <c r="H1932" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1932" s="3">
+        <v>71</v>
+      </c>
+      <c r="J1932" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1932" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1932" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1932" s="3" t="s">
+        <v>4863</v>
+      </c>
+      <c r="N1932" s="3" t="s">
+        <v>4848</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1933" s="3" t="s">
+        <v>4864</v>
+      </c>
+      <c r="B1933" s="3"/>
+      <c r="C1933" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1933" s="3">
+        <v>6082409934</v>
+      </c>
+      <c r="E1933" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1933" s="3" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G1933" s="3" t="s">
+        <v>4865</v>
+      </c>
+      <c r="H1933" s="3"/>
+      <c r="I1933" s="3">
+        <v>56</v>
+      </c>
+      <c r="J1933" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1933" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1933" s="3"/>
+      <c r="M1933" s="3"/>
+      <c r="N1933" s="3"/>
+    </row>
+    <row r="1934" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1934" s="3" t="s">
+        <v>4866</v>
+      </c>
+      <c r="B1934" s="3"/>
+      <c r="C1934" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1934" s="3">
+        <v>6084176316</v>
+      </c>
+      <c r="E1934" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1934" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1934" s="3" t="s">
+        <v>4867</v>
+      </c>
+      <c r="H1934" s="3"/>
+      <c r="I1934" s="3">
+        <v>26</v>
+      </c>
+      <c r="J1934" s="3"/>
+      <c r="K1934" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1934" s="3"/>
+      <c r="M1934" s="3"/>
+      <c r="N1934" s="3"/>
+    </row>
+    <row r="1935" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1935" s="3" t="s">
+        <v>4868</v>
+      </c>
+      <c r="B1935" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1935" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1935" s="3">
+        <v>6084375504</v>
+      </c>
+      <c r="E1935" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1935" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="G1935" s="3" t="s">
+        <v>4869</v>
+      </c>
+      <c r="H1935" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1935" s="3">
+        <v>40</v>
+      </c>
+      <c r="J1935" s="3"/>
+      <c r="K1935" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1935" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1935" s="3" t="s">
+        <v>4870</v>
+      </c>
+      <c r="N1935" s="3" t="s">
+        <v>4871</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1936" s="3" t="s">
+        <v>4872</v>
+      </c>
+      <c r="B1936" s="3"/>
+      <c r="C1936" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1936" s="3">
+        <v>6084589767</v>
+      </c>
+      <c r="E1936" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1936" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1936" s="3" t="s">
+        <v>4873</v>
+      </c>
+      <c r="H1936" s="3"/>
+      <c r="I1936" s="3">
+        <v>20</v>
+      </c>
+      <c r="J1936" s="3"/>
+      <c r="K1936" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1936" s="3"/>
+      <c r="M1936" s="3"/>
+      <c r="N1936" s="3"/>
+    </row>
+    <row r="1937" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1937" s="3" t="s">
+        <v>4874</v>
+      </c>
+      <c r="B1937" s="3"/>
+      <c r="C1937" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1937" s="3">
+        <v>6084605037</v>
+      </c>
+      <c r="E1937" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F1937" s="3" t="s">
+        <v>1782</v>
+      </c>
+      <c r="G1937" s="3" t="s">
+        <v>4875</v>
+      </c>
+      <c r="H1937" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1937" s="3"/>
+      <c r="J1937" s="3"/>
+      <c r="K1937" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1937" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1937" s="3" t="s">
+        <v>4876</v>
+      </c>
+      <c r="N1937" s="3"/>
+    </row>
+    <row r="1938" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1938" s="3" t="s">
+        <v>4877</v>
+      </c>
+      <c r="B1938" s="3"/>
+      <c r="C1938" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1938" s="3">
+        <v>6084850975</v>
+      </c>
+      <c r="E1938" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1938" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1938" s="3" t="s">
+        <v>4878</v>
+      </c>
+      <c r="H1938" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1938" s="3">
+        <v>60</v>
+      </c>
+      <c r="J1938" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1938" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1938" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1938" s="3" t="s">
+        <v>4870</v>
+      </c>
+      <c r="N1938" s="3"/>
+    </row>
+    <row r="1939" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1939" s="3" t="s">
+        <v>4879</v>
+      </c>
+      <c r="B1939" s="3"/>
+      <c r="C1939" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1939" s="3">
+        <v>6086016909</v>
+      </c>
+      <c r="E1939" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1939" s="3" t="s">
+        <v>3953</v>
+      </c>
+      <c r="G1939" s="3" t="s">
+        <v>4880</v>
+      </c>
+      <c r="H1939" s="3"/>
+      <c r="I1939" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1939" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1939" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1939" s="3"/>
+      <c r="M1939" s="3"/>
+      <c r="N1939" s="3"/>
+    </row>
+    <row r="1940" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1940" s="3" t="s">
+        <v>4881</v>
+      </c>
+      <c r="B1940" s="3"/>
+      <c r="C1940" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1940" s="3">
+        <v>6086042309</v>
+      </c>
+      <c r="E1940" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1940" s="3" t="s">
+        <v>4882</v>
+      </c>
+      <c r="G1940" s="3" t="s">
+        <v>4883</v>
+      </c>
+      <c r="H1940" s="3"/>
+      <c r="I1940" s="3">
+        <v>63</v>
+      </c>
+      <c r="J1940" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1940" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1940" s="3"/>
+      <c r="M1940" s="3"/>
+      <c r="N1940" s="3"/>
+    </row>
+    <row r="1941" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1941" s="3" t="s">
+        <v>4884</v>
+      </c>
+      <c r="B1941" s="3"/>
+      <c r="C1941" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1941" s="3">
+        <v>6086062009</v>
+      </c>
+      <c r="E1941" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1941" s="3" t="s">
+        <v>1665</v>
+      </c>
+      <c r="G1941" s="3" t="s">
+        <v>4885</v>
+      </c>
+      <c r="H1941" s="3"/>
+      <c r="I1941" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1941" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1941" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1941" s="3"/>
+      <c r="M1941" s="3"/>
+      <c r="N1941" s="3"/>
+    </row>
+    <row r="1942" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1942" s="3" t="s">
+        <v>4886</v>
+      </c>
+      <c r="B1942" s="3"/>
+      <c r="C1942" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1942" s="3">
+        <v>6086216191</v>
+      </c>
+      <c r="E1942" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1942" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1942" s="3" t="s">
+        <v>4887</v>
+      </c>
+      <c r="H1942" s="3"/>
+      <c r="I1942" s="3">
+        <v>16</v>
+      </c>
+      <c r="J1942" s="3"/>
+      <c r="K1942" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1942" s="3"/>
+      <c r="M1942" s="3"/>
+      <c r="N1942" s="3"/>
+    </row>
+    <row r="1943" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1943" s="3" t="s">
+        <v>4888</v>
+      </c>
+      <c r="B1943" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1943" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1943" s="3">
+        <v>6086407670</v>
+      </c>
+      <c r="E1943" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1943" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="G1943" s="3" t="s">
+        <v>4889</v>
+      </c>
+      <c r="H1943" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1943" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1943" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1943" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1943" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1943" s="3" t="s">
+        <v>4890</v>
+      </c>
+      <c r="N1943" s="3"/>
+    </row>
+    <row r="1944" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1944" s="3" t="s">
+        <v>4891</v>
+      </c>
+      <c r="B1944" s="3"/>
+      <c r="C1944" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1944" s="3">
+        <v>6086416063</v>
+      </c>
+      <c r="E1944" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1944" s="3" t="s">
+        <v>2044</v>
+      </c>
+      <c r="G1944" s="3" t="s">
+        <v>4892</v>
+      </c>
+      <c r="H1944" s="3"/>
+      <c r="I1944" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1944" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1944" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1944" s="3"/>
+      <c r="M1944" s="3"/>
+      <c r="N1944" s="3"/>
+    </row>
+    <row r="1945" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1945" s="3" t="s">
+        <v>4893</v>
+      </c>
+      <c r="B1945" s="3"/>
+      <c r="C1945" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1945" s="3">
+        <v>6089380492</v>
+      </c>
+      <c r="E1945" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1945" s="3" t="s">
+        <v>1948</v>
+      </c>
+      <c r="G1945" s="3" t="s">
+        <v>4894</v>
+      </c>
+      <c r="H1945" s="3"/>
+      <c r="I1945" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1945" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1945" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1945" s="3"/>
+      <c r="M1945" s="3"/>
+      <c r="N1945" s="3"/>
+    </row>
+    <row r="1946" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1946" s="3" t="s">
+        <v>4895</v>
+      </c>
+      <c r="B1946" s="3"/>
+      <c r="C1946" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1946" s="3">
+        <v>6089531929</v>
+      </c>
+      <c r="E1946" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1946" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="G1946" s="3" t="s">
+        <v>4896</v>
+      </c>
+      <c r="H1946" s="3"/>
+      <c r="I1946" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1946" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1946" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1946" s="3"/>
+      <c r="M1946" s="3"/>
+      <c r="N1946" s="3"/>
+    </row>
+    <row r="1947" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1947" s="3" t="s">
+        <v>4897</v>
+      </c>
+      <c r="B1947" s="3"/>
+      <c r="C1947" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1947" s="3">
+        <v>6090804445</v>
+      </c>
+      <c r="E1947" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1947" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1947" s="3" t="s">
+        <v>4898</v>
+      </c>
+      <c r="H1947" s="3"/>
+      <c r="I1947" s="3">
+        <v>36</v>
+      </c>
+      <c r="J1947" s="3"/>
+      <c r="K1947" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1947" s="3"/>
+      <c r="M1947" s="3"/>
+      <c r="N1947" s="3"/>
+    </row>
+    <row r="1948" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1948" s="3" t="s">
+        <v>4899</v>
+      </c>
+      <c r="B1948" s="3"/>
+      <c r="C1948" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1948" s="3">
+        <v>6090813684</v>
+      </c>
+      <c r="E1948" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1948" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G1948" s="3" t="s">
+        <v>4900</v>
+      </c>
+      <c r="H1948" s="3"/>
+      <c r="I1948" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1948" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1948" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1948" s="3"/>
+      <c r="M1948" s="3"/>
+      <c r="N1948" s="3"/>
+    </row>
+    <row r="1949" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1949" s="3" t="s">
+        <v>4901</v>
+      </c>
+      <c r="B1949" s="3"/>
+      <c r="C1949" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1949" s="3">
+        <v>6090816868</v>
+      </c>
+      <c r="E1949" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1949" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G1949" s="3" t="s">
+        <v>4902</v>
+      </c>
+      <c r="H1949" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1949" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1949" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1949" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1949" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1949" s="3" t="s">
+        <v>4903</v>
+      </c>
+      <c r="N1949" s="3"/>
+    </row>
+    <row r="1950" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1950" s="3" t="s">
+        <v>4904</v>
+      </c>
+      <c r="B1950" s="3"/>
+      <c r="C1950" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1950" s="3">
+        <v>6090846017</v>
+      </c>
+      <c r="E1950" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1950" s="3" t="s">
+        <v>1779</v>
+      </c>
+      <c r="G1950" s="3" t="s">
+        <v>4905</v>
+      </c>
+      <c r="H1950" s="3"/>
+      <c r="I1950" s="3">
+        <v>17</v>
+      </c>
+      <c r="J1950" s="3"/>
+      <c r="K1950" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1950" s="3"/>
+      <c r="M1950" s="3"/>
+      <c r="N1950" s="3"/>
+    </row>
+    <row r="1951" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1951" s="3" t="s">
+        <v>4906</v>
+      </c>
+      <c r="B1951" s="3"/>
+      <c r="C1951" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1951" s="3">
+        <v>6090862853</v>
+      </c>
+      <c r="E1951" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1951" s="3" t="s">
+        <v>4907</v>
+      </c>
+      <c r="G1951" s="3" t="s">
+        <v>4908</v>
+      </c>
+      <c r="H1951" s="3"/>
+      <c r="I1951" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1951" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1951" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1951" s="3"/>
+      <c r="M1951" s="3"/>
+      <c r="N1951" s="3"/>
+    </row>
+    <row r="1952" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1952" s="3" t="s">
+        <v>4909</v>
+      </c>
+      <c r="B1952" s="3"/>
+      <c r="C1952" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1952" s="3">
+        <v>6090961278</v>
+      </c>
+      <c r="E1952" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1952" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="G1952" s="3" t="s">
+        <v>4910</v>
+      </c>
+      <c r="H1952" s="3"/>
+      <c r="I1952" s="3">
+        <v>46</v>
+      </c>
+      <c r="J1952" s="3"/>
+      <c r="K1952" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1952" s="3"/>
+      <c r="M1952" s="3"/>
+      <c r="N1952" s="3"/>
+    </row>
+    <row r="1953" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1953" s="3" t="s">
+        <v>4911</v>
+      </c>
+      <c r="B1953" s="3"/>
+      <c r="C1953" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1953" s="3">
+        <v>6091145782</v>
+      </c>
+      <c r="E1953" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F1953" s="3" t="s">
+        <v>4133</v>
+      </c>
+      <c r="G1953" s="3" t="s">
+        <v>4912</v>
+      </c>
+      <c r="H1953" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1953" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1953" s="3"/>
+      <c r="K1953" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1953" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1953" s="3" t="s">
+        <v>4913</v>
+      </c>
+      <c r="N1953" s="3"/>
+    </row>
+    <row r="1954" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1954" s="3" t="s">
+        <v>4914</v>
+      </c>
+      <c r="B1954" s="3"/>
+      <c r="C1954" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1954" s="3">
+        <v>6091154245</v>
+      </c>
+      <c r="E1954" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1954" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="G1954" s="3" t="s">
+        <v>4915</v>
+      </c>
+      <c r="H1954" s="3"/>
+      <c r="I1954" s="3">
+        <v>57</v>
+      </c>
+      <c r="J1954" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1954" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1954" s="3"/>
+      <c r="M1954" s="3"/>
+      <c r="N1954" s="3"/>
+    </row>
+    <row r="1955" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1955" s="3" t="s">
+        <v>4916</v>
+      </c>
+      <c r="B1955" s="3"/>
+      <c r="C1955" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1955" s="3">
+        <v>6091194339</v>
+      </c>
+      <c r="E1955" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F1955" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="G1955" s="3" t="s">
+        <v>4917</v>
+      </c>
+      <c r="H1955" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1955" s="3">
+        <v>42</v>
+      </c>
+      <c r="J1955" s="3"/>
+      <c r="K1955" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1955" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1955" s="3" t="s">
+        <v>4918</v>
+      </c>
+      <c r="N1955" s="3"/>
+    </row>
+    <row r="1956" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1956" s="3" t="s">
+        <v>4919</v>
+      </c>
+      <c r="B1956" s="3"/>
+      <c r="C1956" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1956" s="3">
+        <v>6091979142</v>
+      </c>
+      <c r="E1956" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1956" s="3" t="s">
+        <v>4920</v>
+      </c>
+      <c r="G1956" s="3" t="s">
+        <v>4921</v>
+      </c>
+      <c r="H1956" s="3"/>
+      <c r="I1956" s="3">
+        <v>36</v>
+      </c>
+      <c r="J1956" s="3"/>
+      <c r="K1956" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1956" s="3"/>
+      <c r="M1956" s="3"/>
+      <c r="N1956" s="3"/>
+    </row>
+    <row r="1957" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1957" s="3" t="s">
+        <v>4922</v>
+      </c>
+      <c r="B1957" s="3"/>
+      <c r="C1957" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1957" s="3">
+        <v>6092971959</v>
+      </c>
+      <c r="E1957" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1957" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="G1957" s="3" t="s">
+        <v>4923</v>
+      </c>
+      <c r="H1957" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1957" s="3">
+        <v>71</v>
+      </c>
+      <c r="J1957" s="3"/>
+      <c r="K1957" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1957" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1957" s="3" t="s">
+        <v>4924</v>
+      </c>
+      <c r="N1957" s="3"/>
+    </row>
+    <row r="1958" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1958" s="3" t="s">
+        <v>4925</v>
+      </c>
+      <c r="B1958" s="3"/>
+      <c r="C1958" s="3">
+        <v>27</v>
+      </c>
+      <c r="D1958" s="3">
+        <v>6096171942</v>
+      </c>
+      <c r="E1958" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1958" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G1958" s="3" t="s">
+        <v>4926</v>
+      </c>
+      <c r="H1958" s="3"/>
+      <c r="I1958" s="3">
+        <v>47</v>
+      </c>
+      <c r="J1958" s="3"/>
+      <c r="K1958" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1958" s="3"/>
+      <c r="M1958" s="3"/>
+      <c r="N1958" s="3"/>
+    </row>
+    <row r="1959" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1959" s="3" t="s">
+        <v>4927</v>
+      </c>
+      <c r="B1959" s="3"/>
+      <c r="C1959" s="3">
+        <v>27</v>
+      </c>
+      <c r="D1959" s="3">
+        <v>6096195370</v>
+      </c>
+      <c r="E1959" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1959" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G1959" s="3" t="s">
+        <v>4928</v>
+      </c>
+      <c r="H1959" s="3"/>
+      <c r="I1959" s="3">
+        <v>48</v>
+      </c>
+      <c r="J1959" s="3"/>
+      <c r="K1959" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1959" s="3"/>
+      <c r="M1959" s="3"/>
+      <c r="N1959" s="3"/>
+    </row>
+    <row r="1960" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1960" s="3" t="s">
+        <v>4929</v>
+      </c>
+      <c r="B1960" s="3"/>
+      <c r="C1960" s="3">
+        <v>27</v>
+      </c>
+      <c r="D1960" s="3">
+        <v>6096227077</v>
+      </c>
+      <c r="E1960" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1960" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1960" s="3" t="s">
+        <v>4930</v>
+      </c>
+      <c r="H1960" s="3"/>
+      <c r="I1960" s="3">
+        <v>43</v>
+      </c>
+      <c r="J1960" s="3"/>
+      <c r="K1960" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1960" s="3"/>
+      <c r="M1960" s="3"/>
+      <c r="N1960" s="3"/>
+    </row>
+    <row r="1961" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1961" s="3" t="s">
+        <v>4931</v>
+      </c>
+      <c r="B1961" s="3"/>
+      <c r="C1961" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1961" s="3">
+        <v>6097982197</v>
+      </c>
+      <c r="E1961" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1961" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G1961" s="3" t="s">
+        <v>4932</v>
+      </c>
+      <c r="H1961" s="3"/>
+      <c r="I1961" s="3">
+        <v>25</v>
+      </c>
+      <c r="J1961" s="3"/>
+      <c r="K1961" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1961" s="3"/>
+      <c r="M1961" s="3"/>
+      <c r="N1961" s="3"/>
+    </row>
+    <row r="1962" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1962" s="3" t="s">
+        <v>4933</v>
+      </c>
+      <c r="B1962" s="3"/>
+      <c r="C1962" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1962" s="3">
+        <v>6097992517</v>
+      </c>
+      <c r="E1962" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1962" s="3" t="s">
+        <v>1600</v>
+      </c>
+      <c r="G1962" s="3" t="s">
+        <v>4934</v>
+      </c>
+      <c r="H1962" s="3"/>
+      <c r="I1962" s="3">
+        <v>59</v>
+      </c>
+      <c r="J1962" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1962" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1962" s="3"/>
+      <c r="M1962" s="3"/>
+      <c r="N1962" s="3"/>
+    </row>
+    <row r="1963" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1963" s="3" t="s">
+        <v>4935</v>
+      </c>
+      <c r="B1963" s="3"/>
+      <c r="C1963" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1963" s="3">
+        <v>6098097812</v>
+      </c>
+      <c r="E1963" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1963" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G1963" s="3" t="s">
+        <v>4936</v>
+      </c>
+      <c r="H1963" s="3"/>
+      <c r="I1963" s="3">
+        <v>33</v>
+      </c>
+      <c r="J1963" s="3"/>
+      <c r="K1963" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1963" s="3"/>
+      <c r="M1963" s="3"/>
+      <c r="N1963" s="3"/>
+    </row>
+    <row r="1964" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1964" s="3" t="s">
+        <v>4937</v>
+      </c>
+      <c r="B1964" s="3"/>
+      <c r="C1964" s="3">
+        <v>27</v>
+      </c>
+      <c r="D1964" s="3">
+        <v>6103236735</v>
+      </c>
+      <c r="E1964" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1964" s="3" t="s">
+        <v>1994</v>
+      </c>
+      <c r="G1964" s="3" t="s">
+        <v>4938</v>
+      </c>
+      <c r="H1964" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1964" s="3">
+        <v>77</v>
+      </c>
+      <c r="J1964" s="3">
+        <v>70</v>
+      </c>
+      <c r="K1964" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1964" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1964" s="3" t="s">
+        <v>4939</v>
+      </c>
+      <c r="N1964" s="3"/>
+    </row>
+    <row r="1965" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1965" s="3" t="s">
+        <v>4940</v>
+      </c>
+      <c r="B1965" s="3"/>
+      <c r="C1965" s="3">
+        <v>27</v>
+      </c>
+      <c r="D1965" s="3">
+        <v>6103890716</v>
+      </c>
+      <c r="E1965" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1965" s="3" t="s">
+        <v>2083</v>
+      </c>
+      <c r="G1965" s="3" t="s">
+        <v>4941</v>
+      </c>
+      <c r="H1965" s="3"/>
+      <c r="I1965" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1965" s="3"/>
+      <c r="K1965" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1965" s="3"/>
+      <c r="M1965" s="3"/>
+      <c r="N1965" s="3"/>
+    </row>
+    <row r="1966" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1966" s="3" t="s">
+        <v>4942</v>
+      </c>
+      <c r="B1966" s="3"/>
+      <c r="C1966" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1966" s="3">
+        <v>6104532511</v>
+      </c>
+      <c r="E1966" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1966" s="3" t="s">
+        <v>1636</v>
+      </c>
+      <c r="G1966" s="3" t="s">
+        <v>4943</v>
+      </c>
+      <c r="H1966" s="3"/>
+      <c r="I1966" s="3"/>
+      <c r="J1966" s="3"/>
+      <c r="K1966" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1966" s="3"/>
+      <c r="M1966" s="3"/>
+      <c r="N1966" s="3"/>
+    </row>
+    <row r="1967" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1967" s="3" t="s">
+        <v>4944</v>
+      </c>
+      <c r="B1967" s="3"/>
+      <c r="C1967" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1967" s="3">
+        <v>6104578107</v>
+      </c>
+      <c r="E1967" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1967" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1967" s="3" t="s">
+        <v>4945</v>
+      </c>
+      <c r="H1967" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1967" s="3">
+        <v>41</v>
+      </c>
+      <c r="J1967" s="3"/>
+      <c r="K1967" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1967" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1967" s="3" t="s">
+        <v>4939</v>
+      </c>
+      <c r="N1967" s="3"/>
+    </row>
+    <row r="1968" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1968" s="3" t="s">
+        <v>4946</v>
+      </c>
+      <c r="B1968" s="3"/>
+      <c r="C1968" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1968" s="3">
+        <v>6105965947</v>
+      </c>
+      <c r="E1968" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1968" s="3" t="s">
+        <v>2890</v>
+      </c>
+      <c r="G1968" s="3" t="s">
+        <v>4947</v>
+      </c>
+      <c r="H1968" s="3"/>
+      <c r="I1968" s="3">
+        <v>56</v>
+      </c>
+      <c r="J1968" s="3"/>
+      <c r="K1968" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1968" s="3"/>
+      <c r="M1968" s="3"/>
+      <c r="N1968" s="3"/>
+    </row>
+    <row r="1969" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1969" s="3" t="s">
+        <v>4948</v>
+      </c>
+      <c r="B1969" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1969" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1969" s="3">
+        <v>6105973964</v>
+      </c>
+      <c r="E1969" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1969" s="3" t="s">
+        <v>4949</v>
+      </c>
+      <c r="G1969" s="3" t="s">
+        <v>4950</v>
+      </c>
+      <c r="H1969" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1969" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1969" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1969" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1969" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1969" s="3" t="s">
+        <v>4951</v>
+      </c>
+      <c r="N1969" s="3" t="s">
+        <v>4952</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1970" s="3" t="s">
+        <v>4953</v>
+      </c>
+      <c r="B1970" s="3"/>
+      <c r="C1970" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1970" s="3">
+        <v>6105985751</v>
+      </c>
+      <c r="E1970" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1970" s="3" t="s">
+        <v>3281</v>
+      </c>
+      <c r="G1970" s="3" t="s">
+        <v>4954</v>
+      </c>
+      <c r="H1970" s="3"/>
+      <c r="I1970" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1970" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1970" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1970" s="3"/>
+      <c r="M1970" s="3"/>
+      <c r="N1970" s="3"/>
+    </row>
+    <row r="1971" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1971" s="3" t="s">
+        <v>4955</v>
+      </c>
+      <c r="B1971" s="3"/>
+      <c r="C1971" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1971" s="3">
+        <v>6105997212</v>
+      </c>
+      <c r="E1971" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1971" s="3" t="s">
+        <v>4070</v>
+      </c>
+      <c r="G1971" s="3" t="s">
+        <v>4956</v>
+      </c>
+      <c r="H1971" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1971" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1971" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1971" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1971" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1971" s="3" t="s">
+        <v>4957</v>
+      </c>
+      <c r="N1971" s="3"/>
+    </row>
+    <row r="1972" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1972" s="3" t="s">
+        <v>4958</v>
+      </c>
+      <c r="B1972" s="3"/>
+      <c r="C1972" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1972" s="3">
+        <v>6106005230</v>
+      </c>
+      <c r="E1972" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1972" s="3" t="s">
+        <v>4073</v>
+      </c>
+      <c r="G1972" s="3" t="s">
+        <v>4959</v>
+      </c>
+      <c r="H1972" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1972" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1972" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1972" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1972" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1972" s="3" t="s">
+        <v>4960</v>
+      </c>
+      <c r="N1972" s="3"/>
+    </row>
+    <row r="1973" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1973" s="3" t="s">
+        <v>4960</v>
+      </c>
+      <c r="B1973" s="3"/>
+      <c r="C1973" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1973" s="3">
+        <v>6106283360</v>
+      </c>
+      <c r="E1973" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1973" s="3" t="s">
+        <v>4961</v>
+      </c>
+      <c r="G1973" s="3" t="s">
+        <v>4962</v>
+      </c>
+      <c r="H1973" s="3"/>
+      <c r="I1973" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1973" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1973" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1973" s="3"/>
+      <c r="M1973" s="3"/>
+      <c r="N1973" s="3"/>
+    </row>
+    <row r="1974" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1974" s="3" t="s">
+        <v>4963</v>
+      </c>
+      <c r="B1974" s="3"/>
+      <c r="C1974" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1974" s="3">
+        <v>6106970663</v>
+      </c>
+      <c r="E1974" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1974" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G1974" s="3" t="s">
+        <v>4964</v>
+      </c>
+      <c r="H1974" s="3"/>
+      <c r="I1974" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1974" s="3"/>
+      <c r="K1974" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1974" s="3"/>
+      <c r="M1974" s="3"/>
+      <c r="N1974" s="3"/>
+    </row>
+    <row r="1975" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1975" s="3" t="s">
+        <v>4965</v>
+      </c>
+      <c r="B1975" s="3"/>
+      <c r="C1975" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1975" s="3">
+        <v>6107448784</v>
+      </c>
+      <c r="E1975" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1975" s="3" t="s">
+        <v>2344</v>
+      </c>
+      <c r="G1975" s="3" t="s">
+        <v>4966</v>
+      </c>
+      <c r="H1975" s="3"/>
+      <c r="I1975" s="3"/>
+      <c r="J1975" s="3"/>
+      <c r="K1975" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1975" s="3"/>
+      <c r="M1975" s="3"/>
+      <c r="N1975" s="3"/>
+    </row>
+    <row r="1976" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1976" s="3" t="s">
+        <v>4967</v>
+      </c>
+      <c r="B1976" s="3"/>
+      <c r="C1976" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1976" s="3">
+        <v>6107557921</v>
+      </c>
+      <c r="E1976" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1976" s="3" t="s">
+        <v>2555</v>
+      </c>
+      <c r="G1976" s="3" t="s">
+        <v>4968</v>
+      </c>
+      <c r="H1976" s="3"/>
+      <c r="I1976" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1976" s="3"/>
+      <c r="K1976" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1976" s="3"/>
+      <c r="M1976" s="3"/>
+      <c r="N1976" s="3"/>
+    </row>
+    <row r="1977" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1977" s="3" t="s">
+        <v>4969</v>
+      </c>
+      <c r="B1977" s="3"/>
+      <c r="C1977" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1977" s="3">
+        <v>6107733800</v>
+      </c>
+      <c r="E1977" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1977" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="G1977" s="3" t="s">
+        <v>4970</v>
+      </c>
+      <c r="H1977" s="3"/>
+      <c r="I1977" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1977" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1977" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1977" s="3"/>
+      <c r="M1977" s="3"/>
+      <c r="N1977" s="3"/>
+    </row>
+    <row r="1978" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1978" s="3" t="s">
+        <v>4971</v>
+      </c>
+      <c r="B1978" s="3"/>
+      <c r="C1978" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1978" s="3">
+        <v>6111023549</v>
+      </c>
+      <c r="E1978" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1978" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G1978" s="3" t="s">
+        <v>4972</v>
+      </c>
+      <c r="H1978" s="3"/>
+      <c r="I1978" s="3">
+        <v>46</v>
+      </c>
+      <c r="J1978" s="3"/>
+      <c r="K1978" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1978" s="3"/>
+      <c r="M1978" s="3"/>
+      <c r="N1978" s="3"/>
+    </row>
+    <row r="1979" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1979" s="3" t="s">
+        <v>4973</v>
+      </c>
+      <c r="B1979" s="3"/>
+      <c r="C1979" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1979" s="3">
+        <v>6111034641</v>
+      </c>
+      <c r="E1979" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1979" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="G1979" s="3" t="s">
+        <v>4974</v>
+      </c>
+      <c r="H1979" s="3"/>
+      <c r="I1979" s="3">
+        <v>38</v>
+      </c>
+      <c r="J1979" s="3"/>
+      <c r="K1979" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1979" s="3"/>
+      <c r="M1979" s="3"/>
+      <c r="N1979" s="3"/>
+    </row>
+    <row r="1980" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1980" s="3" t="s">
+        <v>4975</v>
+      </c>
+      <c r="B1980" s="3"/>
+      <c r="C1980" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1980" s="3">
+        <v>6111077595</v>
+      </c>
+      <c r="E1980" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1980" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="G1980" s="3" t="s">
+        <v>4976</v>
+      </c>
+      <c r="H1980" s="3"/>
+      <c r="I1980" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1980" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1980" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1980" s="3"/>
+      <c r="M1980" s="3"/>
+      <c r="N1980" s="3"/>
+    </row>
+    <row r="1981" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1981" s="3" t="s">
+        <v>4977</v>
+      </c>
+      <c r="B1981" s="3"/>
+      <c r="C1981" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1981" s="3">
+        <v>6111087947</v>
+      </c>
+      <c r="E1981" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1981" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1981" s="3" t="s">
+        <v>4978</v>
+      </c>
+      <c r="H1981" s="3"/>
+      <c r="I1981" s="3">
+        <v>71</v>
+      </c>
+      <c r="J1981" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1981" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1981" s="3"/>
+      <c r="M1981" s="3"/>
+      <c r="N1981" s="3"/>
+    </row>
+    <row r="1982" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1982" s="3" t="s">
+        <v>4977</v>
+      </c>
+      <c r="B1982" s="3"/>
+      <c r="C1982" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1982" s="3">
+        <v>6111087948</v>
+      </c>
+      <c r="E1982" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1982" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1982" s="3" t="s">
+        <v>4979</v>
+      </c>
+      <c r="H1982" s="3"/>
+      <c r="I1982" s="3">
+        <v>33</v>
+      </c>
+      <c r="J1982" s="3"/>
+      <c r="K1982" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1982" s="3"/>
+      <c r="M1982" s="3"/>
+      <c r="N1982" s="3"/>
+    </row>
+    <row r="1983" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1983" s="3" t="s">
+        <v>4980</v>
+      </c>
+      <c r="B1983" s="3"/>
+      <c r="C1983" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1983" s="3">
+        <v>6111124016</v>
+      </c>
+      <c r="E1983" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1983" s="3" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G1983" s="3" t="s">
+        <v>4981</v>
+      </c>
+      <c r="H1983" s="3"/>
+      <c r="I1983" s="3">
+        <v>56</v>
+      </c>
+      <c r="J1983" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1983" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1983" s="3"/>
+      <c r="M1983" s="3"/>
+      <c r="N1983" s="3"/>
+    </row>
+    <row r="1984" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1984" s="3" t="s">
+        <v>4982</v>
+      </c>
+      <c r="B1984" s="3"/>
+      <c r="C1984" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1984" s="3">
+        <v>6111134310</v>
+      </c>
+      <c r="E1984" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1984" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G1984" s="3" t="s">
+        <v>4983</v>
+      </c>
+      <c r="H1984" s="3"/>
+      <c r="I1984" s="3">
+        <v>57</v>
+      </c>
+      <c r="J1984" s="3"/>
+      <c r="K1984" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1984" s="3"/>
+      <c r="M1984" s="3"/>
+      <c r="N1984" s="3"/>
+    </row>
+    <row r="1985" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1985" s="3" t="s">
+        <v>4984</v>
+      </c>
+      <c r="B1985" s="3"/>
+      <c r="C1985" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1985" s="3">
+        <v>6111306453</v>
+      </c>
+      <c r="E1985" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1985" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="G1985" s="3" t="s">
+        <v>4985</v>
+      </c>
+      <c r="H1985" s="3"/>
+      <c r="I1985" s="3">
+        <v>36</v>
+      </c>
+      <c r="J1985" s="3"/>
+      <c r="K1985" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1985" s="3"/>
+      <c r="M1985" s="3"/>
+      <c r="N1985" s="3"/>
+    </row>
+    <row r="1986" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1986" s="3" t="s">
+        <v>4986</v>
+      </c>
+      <c r="B1986" s="3"/>
+      <c r="C1986" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1986" s="3">
+        <v>6113787059</v>
+      </c>
+      <c r="E1986" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1986" s="3" t="s">
+        <v>4987</v>
+      </c>
+      <c r="G1986" s="3" t="s">
+        <v>4988</v>
+      </c>
+      <c r="H1986" s="3"/>
+      <c r="I1986" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1986" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1986" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1986" s="3"/>
+      <c r="M1986" s="3"/>
+      <c r="N1986" s="3"/>
+    </row>
+    <row r="1987" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1987" s="3" t="s">
+        <v>4989</v>
+      </c>
+      <c r="B1987" s="3"/>
+      <c r="C1987" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1987" s="3">
+        <v>6113810211</v>
+      </c>
+      <c r="E1987" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1987" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G1987" s="3" t="s">
+        <v>4990</v>
+      </c>
+      <c r="H1987" s="3"/>
+      <c r="I1987" s="3">
+        <v>40</v>
+      </c>
+      <c r="J1987" s="3"/>
+      <c r="K1987" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1987" s="3"/>
+      <c r="M1987" s="3"/>
+      <c r="N1987" s="3"/>
+    </row>
+    <row r="1988" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1988" s="3" t="s">
+        <v>4991</v>
+      </c>
+      <c r="B1988" s="3"/>
+      <c r="C1988" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1988" s="3">
+        <v>6113908191</v>
+      </c>
+      <c r="E1988" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1988" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G1988" s="3" t="s">
+        <v>4992</v>
+      </c>
+      <c r="H1988" s="3"/>
+      <c r="I1988" s="3">
+        <v>57</v>
+      </c>
+      <c r="J1988" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1988" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1988" s="3"/>
+      <c r="M1988" s="3"/>
+      <c r="N1988" s="3"/>
+    </row>
+    <row r="1989" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1989" s="3" t="s">
+        <v>4993</v>
+      </c>
+      <c r="B1989" s="3"/>
+      <c r="C1989" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1989" s="3">
+        <v>6114629025</v>
+      </c>
+      <c r="E1989" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1989" s="3" t="s">
+        <v>3702</v>
+      </c>
+      <c r="G1989" s="3" t="s">
+        <v>4994</v>
+      </c>
+      <c r="H1989" s="3"/>
+      <c r="I1989" s="3">
+        <v>41</v>
+      </c>
+      <c r="J1989" s="3">
+        <v>35</v>
+      </c>
+      <c r="K1989" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1989" s="3"/>
+      <c r="M1989" s="3"/>
+      <c r="N1989" s="3"/>
+    </row>
+    <row r="1990" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1990" s="3" t="s">
+        <v>4995</v>
+      </c>
+      <c r="B1990" s="3"/>
+      <c r="C1990" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1990" s="3">
+        <v>6114898512</v>
+      </c>
+      <c r="E1990" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1990" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="G1990" s="3" t="s">
+        <v>4996</v>
+      </c>
+      <c r="H1990" s="3"/>
+      <c r="I1990" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1990" s="3"/>
+      <c r="K1990" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1990" s="3"/>
+      <c r="M1990" s="3"/>
+      <c r="N1990" s="3"/>
+    </row>
+    <row r="1991" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1991" s="3" t="s">
+        <v>4997</v>
+      </c>
+      <c r="B1991" s="3"/>
+      <c r="C1991" s="3">
+        <v>28</v>
+      </c>
+      <c r="D1991" s="3">
+        <v>6115084431</v>
+      </c>
+      <c r="E1991" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1991" s="3" t="s">
+        <v>4998</v>
+      </c>
+      <c r="G1991" s="3" t="s">
+        <v>4999</v>
+      </c>
+      <c r="H1991" s="3"/>
+      <c r="I1991" s="3">
+        <v>57</v>
+      </c>
+      <c r="J1991" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1991" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1991" s="3"/>
+      <c r="M1991" s="3"/>
+      <c r="N1991" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Curtis-Garage-Wrecker-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B9C3761-4076-49DC-B338-4963DABF5095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABE44531-A529-4D50-B6E5-17B1799D316C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12175" uniqueCount="5000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12619" uniqueCount="5186">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -15013,6 +15013,9 @@
     <t>39.567696, -86.637610</t>
   </si>
   <si>
+    <t>07/13/26 08:40 EDT</t>
+  </si>
+  <si>
     <t>07/11/26 17:05 EDT</t>
   </si>
   <si>
@@ -15020,6 +15023,561 @@
   </si>
   <si>
     <t>39.573490, -86.872110</t>
+  </si>
+  <si>
+    <t>07/12/26 14:23 EDT</t>
+  </si>
+  <si>
+    <t>5.4mi NE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.680000, -86.753140</t>
+  </si>
+  <si>
+    <t>07/13/26 08:49 EDT</t>
+  </si>
+  <si>
+    <t>07/13/26 09:39 EDT</t>
+  </si>
+  <si>
+    <t>07/12/26 14:31 EDT</t>
+  </si>
+  <si>
+    <t>0.9mi E of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.646255, -86.825270</t>
+  </si>
+  <si>
+    <t>07/13/26 06:29 EDT</t>
+  </si>
+  <si>
+    <t>39.589780, -86.629100</t>
+  </si>
+  <si>
+    <t>07/14/26 08:06 EDT</t>
+  </si>
+  <si>
+    <t>07/14/26 09:33 EDT</t>
+  </si>
+  <si>
+    <t>07/13/26 09:13 EDT</t>
+  </si>
+  <si>
+    <t>39.547630, -86.723680</t>
+  </si>
+  <si>
+    <t>07/13/26 09:52 EDT</t>
+  </si>
+  <si>
+    <t>12.1mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.468660, -86.862740</t>
+  </si>
+  <si>
+    <t>07/13/26 11:12 EDT</t>
+  </si>
+  <si>
+    <t>8.5mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.523040, -86.811360</t>
+  </si>
+  <si>
+    <t>07/14/26 10:29 EDT</t>
+  </si>
+  <si>
+    <t>07/13/26 12:48 EDT</t>
+  </si>
+  <si>
+    <t>39.579240, -86.540330</t>
+  </si>
+  <si>
+    <t>07/13/26 12:54 EDT</t>
+  </si>
+  <si>
+    <t>39.568302, -86.632500</t>
+  </si>
+  <si>
+    <t>07/13/26 13:07 EDT</t>
+  </si>
+  <si>
+    <t>39.515350, -86.794260</t>
+  </si>
+  <si>
+    <t>07/13/26 13:08 EDT</t>
+  </si>
+  <si>
+    <t>39.581326, -86.491776</t>
+  </si>
+  <si>
+    <t>07/14/26 07:54 EDT</t>
+  </si>
+  <si>
+    <t>07/13/26 13:46 EDT</t>
+  </si>
+  <si>
+    <t>39.539764, -86.755615</t>
+  </si>
+  <si>
+    <t>07/13/26 16:22 EDT</t>
+  </si>
+  <si>
+    <t>39.571670, -86.631900</t>
+  </si>
+  <si>
+    <t>07/14/26 07:55 EDT</t>
+  </si>
+  <si>
+    <t>07/13/26 17:19 EDT</t>
+  </si>
+  <si>
+    <t>39.534520, -86.564050</t>
+  </si>
+  <si>
+    <t>07/13/26 19:23 EDT</t>
+  </si>
+  <si>
+    <t>39.526928, -86.641510</t>
+  </si>
+  <si>
+    <t>07/13/26 21:42 EDT</t>
+  </si>
+  <si>
+    <t>39.579422, -86.632034</t>
+  </si>
+  <si>
+    <t>07/14/26 09:35 EDT</t>
+  </si>
+  <si>
+    <t>39.579037, -86.479480</t>
+  </si>
+  <si>
+    <t>07/14/26 10:33 EDT</t>
+  </si>
+  <si>
+    <t>07/14/26 10:49 EDT</t>
+  </si>
+  <si>
+    <t>07/14/26 15:05 EDT</t>
+  </si>
+  <si>
+    <t>39.568210, -86.632080</t>
+  </si>
+  <si>
+    <t>07/15/26 07:48 EDT</t>
+  </si>
+  <si>
+    <t>07/14/26 23:36 EDT</t>
+  </si>
+  <si>
+    <t>39.499380, -86.657900</t>
+  </si>
+  <si>
+    <t>07/15/26 00:06 EDT</t>
+  </si>
+  <si>
+    <t>39.580635, -86.593700</t>
+  </si>
+  <si>
+    <t>07/15/26 07:49 EDT</t>
+  </si>
+  <si>
+    <t>07/15/26 00:07 EDT</t>
+  </si>
+  <si>
+    <t>39.578682, -86.600620</t>
+  </si>
+  <si>
+    <t>07/15/26 00:22 EDT</t>
+  </si>
+  <si>
+    <t>39.564980, -86.631950</t>
+  </si>
+  <si>
+    <t>07/15/26 00:27 EDT</t>
+  </si>
+  <si>
+    <t>39.520680, -86.641540</t>
+  </si>
+  <si>
+    <t>07/15/26 05:59 EDT</t>
+  </si>
+  <si>
+    <t>39.613100, -86.622800</t>
+  </si>
+  <si>
+    <t>07/15/26 06:01 EDT</t>
+  </si>
+  <si>
+    <t>39.588830, -86.629620</t>
+  </si>
+  <si>
+    <t>07/15/26 07:55 EDT</t>
+  </si>
+  <si>
+    <t>07/15/26 08:02 EDT</t>
+  </si>
+  <si>
+    <t>07/15/26 09:01 EDT</t>
+  </si>
+  <si>
+    <t>39.533997, -86.787020</t>
+  </si>
+  <si>
+    <t>07/15/26 09:10 EDT</t>
+  </si>
+  <si>
+    <t>11.2mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.486610, -86.785330</t>
+  </si>
+  <si>
+    <t>07/15/26 10:04 EDT</t>
+  </si>
+  <si>
+    <t>07/15/26 09:45 EDT</t>
+  </si>
+  <si>
+    <t>3.8mi SW of Plainfield IN</t>
+  </si>
+  <si>
+    <t>39.648014, -86.408195</t>
+  </si>
+  <si>
+    <t>07/15/26 09:48 EDT</t>
+  </si>
+  <si>
+    <t>39.673110, -86.357330</t>
+  </si>
+  <si>
+    <t>07/16/26 07:39 EDT</t>
+  </si>
+  <si>
+    <t>07/15/26 10:34 EDT</t>
+  </si>
+  <si>
+    <t>39.579887, -86.595660</t>
+  </si>
+  <si>
+    <t>07/16/26 07:40 EDT</t>
+  </si>
+  <si>
+    <t>07/15/26 11:12 EDT</t>
+  </si>
+  <si>
+    <t>2.9mi W of Beech Grove IN</t>
+  </si>
+  <si>
+    <t>39.713474, -86.140880</t>
+  </si>
+  <si>
+    <t>07/15/26 11:29 EDT</t>
+  </si>
+  <si>
+    <t>39.758945, -86.264630</t>
+  </si>
+  <si>
+    <t>07/15/26 12:24 EDT</t>
+  </si>
+  <si>
+    <t>0.5mi NE of Westfield IN</t>
+  </si>
+  <si>
+    <t>40.039840, -86.146020</t>
+  </si>
+  <si>
+    <t>07/15/26 12:50 EDT</t>
+  </si>
+  <si>
+    <t>39.678980, -86.368965</t>
+  </si>
+  <si>
+    <t>07/15/26 15:02 EDT</t>
+  </si>
+  <si>
+    <t>39.532250, -86.800170</t>
+  </si>
+  <si>
+    <t>07/15/26 15:03 EDT</t>
+  </si>
+  <si>
+    <t>39.532696, -86.793060</t>
+  </si>
+  <si>
+    <t>07/16/26 07:41 EDT</t>
+  </si>
+  <si>
+    <t>07/16/26 00:13 EDT</t>
+  </si>
+  <si>
+    <t>39.557900, -86.731490</t>
+  </si>
+  <si>
+    <t>07/16/26 00:14 EDT</t>
+  </si>
+  <si>
+    <t>39.557670, -86.713110</t>
+  </si>
+  <si>
+    <t>07/16/26 08:59 EDT</t>
+  </si>
+  <si>
+    <t>39.662193, -86.384834</t>
+  </si>
+  <si>
+    <t>07/16/26 09:20 EDT</t>
+  </si>
+  <si>
+    <t>3.8mi E of Beech Grove IN</t>
+  </si>
+  <si>
+    <t>39.722630, -86.016740</t>
+  </si>
+  <si>
+    <t>07/16/26 09:54 EDT</t>
+  </si>
+  <si>
+    <t>0.9mi NW of Greensburg IN</t>
+  </si>
+  <si>
+    <t>39.360622, -85.516080</t>
+  </si>
+  <si>
+    <t>07/16/26 20:30 EDT</t>
+  </si>
+  <si>
+    <t>07/16/26 10:29 EDT</t>
+  </si>
+  <si>
+    <t>4.2mi E of Greensburg IN</t>
+  </si>
+  <si>
+    <t>39.341970, -85.424860</t>
+  </si>
+  <si>
+    <t>07/16/26 10:59 EDT</t>
+  </si>
+  <si>
+    <t>3.8mi W of Bright IN</t>
+  </si>
+  <si>
+    <t>39.205760, -84.928250</t>
+  </si>
+  <si>
+    <t>07/16/26 11:23 EDT</t>
+  </si>
+  <si>
+    <t>2mi SW of Villa Hills KY</t>
+  </si>
+  <si>
+    <t>39.052170, -84.627670</t>
+  </si>
+  <si>
+    <t>07/16/26 12:56 EDT</t>
+  </si>
+  <si>
+    <t>39.535310, -86.779550</t>
+  </si>
+  <si>
+    <t>07/16/26 13:02 EDT</t>
+  </si>
+  <si>
+    <t>39.561005, -86.653030</t>
+  </si>
+  <si>
+    <t>07/16/26 16:15 EDT</t>
+  </si>
+  <si>
+    <t>39.655952, -86.394165</t>
+  </si>
+  <si>
+    <t>07/16/26 18:14 EDT</t>
+  </si>
+  <si>
+    <t>39.709736, -86.669830</t>
+  </si>
+  <si>
+    <t>07/17/26 06:43 EDT</t>
+  </si>
+  <si>
+    <t>39.628080, -86.670135</t>
+  </si>
+  <si>
+    <t>07/17/26 06:51 EDT</t>
+  </si>
+  <si>
+    <t>39.583960, -86.631940</t>
+  </si>
+  <si>
+    <t>07/17/26 12:32 EDT</t>
+  </si>
+  <si>
+    <t>39.569960, -86.630226</t>
+  </si>
+  <si>
+    <t>07/17/26 13:30 EDT</t>
+  </si>
+  <si>
+    <t>39.578990, -86.511560</t>
+  </si>
+  <si>
+    <t>07/17/26 15:19 EDT</t>
+  </si>
+  <si>
+    <t>4.3mi N of Indianapolis IN</t>
+  </si>
+  <si>
+    <t>39.839962, -86.145280</t>
+  </si>
+  <si>
+    <t>07/17/26 15:27 EDT</t>
+  </si>
+  <si>
+    <t>39.564484, -86.643135</t>
+  </si>
+  <si>
+    <t>07/17/26 15:42 EDT</t>
+  </si>
+  <si>
+    <t>39.532850, -86.791794</t>
+  </si>
+  <si>
+    <t>39.534798, -86.781820</t>
+  </si>
+  <si>
+    <t>07/17/26 16:00 EDT</t>
+  </si>
+  <si>
+    <t>4.3mi S of Speedway IN</t>
+  </si>
+  <si>
+    <t>39.731960, -86.241700</t>
+  </si>
+  <si>
+    <t>07/17/26 17:55 EDT</t>
+  </si>
+  <si>
+    <t>10.7mi S of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.499740, -86.766690</t>
+  </si>
+  <si>
+    <t>07/17/26 18:07 EDT</t>
+  </si>
+  <si>
+    <t>11mi NW of Martinsville IN</t>
+  </si>
+  <si>
+    <t>39.521180, -86.586240</t>
+  </si>
+  <si>
+    <t>07/17/26 18:41 EDT</t>
+  </si>
+  <si>
+    <t>39.614770, -86.713650</t>
+  </si>
+  <si>
+    <t>07/17/26 19:17 EDT</t>
+  </si>
+  <si>
+    <t>9.7mi NE of Greencastle IN</t>
+  </si>
+  <si>
+    <t>39.738556, -86.706720</t>
+  </si>
+  <si>
+    <t>07/17/26 19:23 EDT</t>
+  </si>
+  <si>
+    <t>39.738800, -86.651150</t>
+  </si>
+  <si>
+    <t>07/18/26 06:33 EDT</t>
+  </si>
+  <si>
+    <t>39.572190, -86.669876</t>
+  </si>
+  <si>
+    <t>07/18/26 06:36 EDT</t>
+  </si>
+  <si>
+    <t>39.579390, -86.632034</t>
+  </si>
+  <si>
+    <t>07/18/26 07:42 EDT</t>
+  </si>
+  <si>
+    <t>39.564850, -86.613910</t>
+  </si>
+  <si>
+    <t>07/18/26 10:15 EDT</t>
+  </si>
+  <si>
+    <t>39.563583, -86.643620</t>
+  </si>
+  <si>
+    <t>07/18/26 11:50 EDT</t>
+  </si>
+  <si>
+    <t>39.568330, -86.632570</t>
+  </si>
+  <si>
+    <t>07/18/26 12:32 EDT</t>
+  </si>
+  <si>
+    <t>39.567616, -86.632416</t>
+  </si>
+  <si>
+    <t>07/18/26 12:49 EDT</t>
+  </si>
+  <si>
+    <t>39.532760, -86.564000</t>
+  </si>
+  <si>
+    <t>07/18/26 15:17 EDT</t>
+  </si>
+  <si>
+    <t>39.528477, -86.801830</t>
+  </si>
+  <si>
+    <t>07/18/26 15:26 EDT</t>
+  </si>
+  <si>
+    <t>39.569450, -86.632095</t>
+  </si>
+  <si>
+    <t>07/18/26 22:48 EDT</t>
+  </si>
+  <si>
+    <t>39.524920, -86.564030</t>
+  </si>
+  <si>
+    <t>07/19/26 06:36 EDT</t>
+  </si>
+  <si>
+    <t>39.571987, -86.626390</t>
+  </si>
+  <si>
+    <t>07/19/26 08:19 EDT</t>
+  </si>
+  <si>
+    <t>39.521280, -86.628850</t>
+  </si>
+  <si>
+    <t>07/19/26 08:34 EDT</t>
+  </si>
+  <si>
+    <t>39.568386, -86.632385</t>
+  </si>
+  <si>
+    <t>07/19/26 08:58 EDT</t>
+  </si>
+  <si>
+    <t>39.602610, -86.479600</t>
   </si>
 </sst>
 </file>
@@ -15381,7 +15939,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1991"/>
+  <dimension ref="A1:N2066"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -84433,21 +84991,27 @@
       <c r="G1990" s="3" t="s">
         <v>4996</v>
       </c>
-      <c r="H1990" s="3"/>
+      <c r="H1990" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="I1990" s="3">
         <v>62</v>
       </c>
       <c r="J1990" s="3"/>
       <c r="K1990" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1990" s="3"/>
-      <c r="M1990" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="L1990" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1990" s="3" t="s">
+        <v>4997</v>
+      </c>
       <c r="N1990" s="3"/>
     </row>
     <row r="1991" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1991" s="3" t="s">
-        <v>4997</v>
+        <v>4998</v>
       </c>
       <c r="B1991" s="3"/>
       <c r="C1991" s="3">
@@ -84460,10 +85024,10 @@
         <v>17</v>
       </c>
       <c r="F1991" s="3" t="s">
-        <v>4998</v>
+        <v>4999</v>
       </c>
       <c r="G1991" s="3" t="s">
-        <v>4999</v>
+        <v>5000</v>
       </c>
       <c r="H1991" s="3"/>
       <c r="I1991" s="3">
@@ -84478,6 +85042,2584 @@
       <c r="L1991" s="3"/>
       <c r="M1991" s="3"/>
       <c r="N1991" s="3"/>
+    </row>
+    <row r="1992" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1992" s="3" t="s">
+        <v>5001</v>
+      </c>
+      <c r="B1992" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1992" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1992" s="3">
+        <v>6118169535</v>
+      </c>
+      <c r="E1992" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1992" s="3" t="s">
+        <v>5002</v>
+      </c>
+      <c r="G1992" s="3" t="s">
+        <v>5003</v>
+      </c>
+      <c r="H1992" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1992" s="3">
+        <v>6</v>
+      </c>
+      <c r="J1992" s="3"/>
+      <c r="K1992" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1992" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1992" s="3" t="s">
+        <v>5004</v>
+      </c>
+      <c r="N1992" s="3" t="s">
+        <v>5005</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1993" s="3" t="s">
+        <v>5006</v>
+      </c>
+      <c r="B1993" s="3"/>
+      <c r="C1993" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1993" s="3">
+        <v>6118212915</v>
+      </c>
+      <c r="E1993" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F1993" s="3" t="s">
+        <v>5007</v>
+      </c>
+      <c r="G1993" s="3" t="s">
+        <v>5008</v>
+      </c>
+      <c r="H1993" s="3"/>
+      <c r="I1993" s="3">
+        <v>53</v>
+      </c>
+      <c r="J1993" s="3"/>
+      <c r="K1993" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1993" s="3"/>
+      <c r="M1993" s="3"/>
+      <c r="N1993" s="3"/>
+    </row>
+    <row r="1994" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1994" s="3" t="s">
+        <v>5009</v>
+      </c>
+      <c r="B1994" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1994" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1994" s="3">
+        <v>6120939324</v>
+      </c>
+      <c r="E1994" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1994" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G1994" s="3" t="s">
+        <v>5010</v>
+      </c>
+      <c r="H1994" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1994" s="3">
+        <v>61</v>
+      </c>
+      <c r="J1994" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1994" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1994" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1994" s="3" t="s">
+        <v>5011</v>
+      </c>
+      <c r="N1994" s="3" t="s">
+        <v>5012</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1995" s="3" t="s">
+        <v>5013</v>
+      </c>
+      <c r="B1995" s="3"/>
+      <c r="C1995" s="3">
+        <v>27</v>
+      </c>
+      <c r="D1995" s="3">
+        <v>6121645551</v>
+      </c>
+      <c r="E1995" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1995" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1995" s="3" t="s">
+        <v>5014</v>
+      </c>
+      <c r="H1995" s="3"/>
+      <c r="I1995" s="3">
+        <v>71</v>
+      </c>
+      <c r="J1995" s="3"/>
+      <c r="K1995" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1995" s="3"/>
+      <c r="M1995" s="3"/>
+      <c r="N1995" s="3"/>
+    </row>
+    <row r="1996" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1996" s="3" t="s">
+        <v>5015</v>
+      </c>
+      <c r="B1996" s="3"/>
+      <c r="C1996" s="3">
+        <v>26</v>
+      </c>
+      <c r="D1996" s="3">
+        <v>6121842486</v>
+      </c>
+      <c r="E1996" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1996" s="3" t="s">
+        <v>5016</v>
+      </c>
+      <c r="G1996" s="3" t="s">
+        <v>5017</v>
+      </c>
+      <c r="H1996" s="3"/>
+      <c r="I1996" s="3">
+        <v>23</v>
+      </c>
+      <c r="J1996" s="3"/>
+      <c r="K1996" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1996" s="3"/>
+      <c r="M1996" s="3"/>
+      <c r="N1996" s="3"/>
+    </row>
+    <row r="1997" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1997" s="3" t="s">
+        <v>5018</v>
+      </c>
+      <c r="B1997" s="3"/>
+      <c r="C1997" s="3">
+        <v>31</v>
+      </c>
+      <c r="D1997" s="3">
+        <v>6122332343</v>
+      </c>
+      <c r="E1997" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1997" s="3" t="s">
+        <v>5019</v>
+      </c>
+      <c r="G1997" s="3" t="s">
+        <v>5020</v>
+      </c>
+      <c r="H1997" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1997" s="3">
+        <v>14</v>
+      </c>
+      <c r="J1997" s="3"/>
+      <c r="K1997" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1997" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M1997" s="3" t="s">
+        <v>5021</v>
+      </c>
+      <c r="N1997" s="3"/>
+    </row>
+    <row r="1998" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1998" s="3" t="s">
+        <v>5022</v>
+      </c>
+      <c r="B1998" s="3"/>
+      <c r="C1998" s="3">
+        <v>27</v>
+      </c>
+      <c r="D1998" s="3">
+        <v>6123091703</v>
+      </c>
+      <c r="E1998" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1998" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1998" s="3" t="s">
+        <v>5023</v>
+      </c>
+      <c r="H1998" s="3"/>
+      <c r="I1998" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1998" s="3">
+        <v>-5</v>
+      </c>
+      <c r="K1998" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1998" s="3"/>
+      <c r="M1998" s="3"/>
+      <c r="N1998" s="3"/>
+    </row>
+    <row r="1999" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1999" s="3" t="s">
+        <v>5024</v>
+      </c>
+      <c r="B1999" s="3"/>
+      <c r="C1999" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1999" s="3">
+        <v>6123138356</v>
+      </c>
+      <c r="E1999" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F1999" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1999" s="3" t="s">
+        <v>5025</v>
+      </c>
+      <c r="H1999" s="3"/>
+      <c r="I1999" s="3">
+        <v>6</v>
+      </c>
+      <c r="J1999" s="3"/>
+      <c r="K1999" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1999" s="3"/>
+      <c r="M1999" s="3"/>
+      <c r="N1999" s="3"/>
+    </row>
+    <row r="2000" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2000" s="3" t="s">
+        <v>5026</v>
+      </c>
+      <c r="B2000" s="3"/>
+      <c r="C2000" s="3">
+        <v>2</v>
+      </c>
+      <c r="D2000" s="3">
+        <v>6123249884</v>
+      </c>
+      <c r="E2000" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2000" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="G2000" s="3" t="s">
+        <v>5027</v>
+      </c>
+      <c r="H2000" s="3"/>
+      <c r="I2000" s="3">
+        <v>26</v>
+      </c>
+      <c r="J2000" s="3"/>
+      <c r="K2000" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2000" s="3"/>
+      <c r="M2000" s="3"/>
+      <c r="N2000" s="3"/>
+    </row>
+    <row r="2001" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2001" s="3" t="s">
+        <v>5028</v>
+      </c>
+      <c r="B2001" s="3"/>
+      <c r="C2001" s="3">
+        <v>27</v>
+      </c>
+      <c r="D2001" s="3">
+        <v>6123259175</v>
+      </c>
+      <c r="E2001" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2001" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="G2001" s="3" t="s">
+        <v>5029</v>
+      </c>
+      <c r="H2001" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I2001" s="3">
+        <v>5</v>
+      </c>
+      <c r="J2001" s="3"/>
+      <c r="K2001" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2001" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M2001" s="3" t="s">
+        <v>5030</v>
+      </c>
+      <c r="N2001" s="3"/>
+    </row>
+    <row r="2002" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2002" s="3" t="s">
+        <v>5031</v>
+      </c>
+      <c r="B2002" s="3"/>
+      <c r="C2002" s="3">
+        <v>2</v>
+      </c>
+      <c r="D2002" s="3">
+        <v>6123579725</v>
+      </c>
+      <c r="E2002" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F2002" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="G2002" s="3" t="s">
+        <v>5032</v>
+      </c>
+      <c r="H2002" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I2002" s="3"/>
+      <c r="J2002" s="3">
+        <v>70</v>
+      </c>
+      <c r="K2002" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2002" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M2002" s="3" t="s">
+        <v>5030</v>
+      </c>
+      <c r="N2002" s="3"/>
+    </row>
+    <row r="2003" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2003" s="3" t="s">
+        <v>5033</v>
+      </c>
+      <c r="B2003" s="3"/>
+      <c r="C2003" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2003" s="3">
+        <v>6124890696</v>
+      </c>
+      <c r="E2003" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2003" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2003" s="3" t="s">
+        <v>5034</v>
+      </c>
+      <c r="H2003" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I2003" s="3">
+        <v>70</v>
+      </c>
+      <c r="J2003" s="3">
+        <v>70</v>
+      </c>
+      <c r="K2003" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2003" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M2003" s="3" t="s">
+        <v>5035</v>
+      </c>
+      <c r="N2003" s="3"/>
+    </row>
+    <row r="2004" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2004" s="3" t="s">
+        <v>5036</v>
+      </c>
+      <c r="B2004" s="3"/>
+      <c r="C2004" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2004" s="3">
+        <v>6125325634</v>
+      </c>
+      <c r="E2004" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2004" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="G2004" s="3" t="s">
+        <v>5037</v>
+      </c>
+      <c r="H2004" s="3"/>
+      <c r="I2004" s="3">
+        <v>56</v>
+      </c>
+      <c r="J2004" s="3">
+        <v>50</v>
+      </c>
+      <c r="K2004" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2004" s="3"/>
+      <c r="M2004" s="3"/>
+      <c r="N2004" s="3"/>
+    </row>
+    <row r="2005" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2005" s="3" t="s">
+        <v>5038</v>
+      </c>
+      <c r="B2005" s="3"/>
+      <c r="C2005" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2005" s="3">
+        <v>6126132845</v>
+      </c>
+      <c r="E2005" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2005" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="G2005" s="3" t="s">
+        <v>5039</v>
+      </c>
+      <c r="H2005" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I2005" s="3">
+        <v>22</v>
+      </c>
+      <c r="J2005" s="3"/>
+      <c r="K2005" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2005" s="3"/>
+      <c r="M2005" s="3"/>
+      <c r="N2005" s="3"/>
+    </row>
+    <row r="2006" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2006" s="3" t="s">
+        <v>5040</v>
+      </c>
+      <c r="B2006" s="3"/>
+      <c r="C2006" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2006" s="3">
+        <v>6126670319</v>
+      </c>
+      <c r="E2006" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2006" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2006" s="3" t="s">
+        <v>5041</v>
+      </c>
+      <c r="H2006" s="3"/>
+      <c r="I2006" s="3">
+        <v>32</v>
+      </c>
+      <c r="J2006" s="3"/>
+      <c r="K2006" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2006" s="3"/>
+      <c r="M2006" s="3"/>
+      <c r="N2006" s="3"/>
+    </row>
+    <row r="2007" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2007" s="3" t="s">
+        <v>5042</v>
+      </c>
+      <c r="B2007" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2007" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2007" s="3">
+        <v>6128503257</v>
+      </c>
+      <c r="E2007" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2007" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2007" s="3" t="s">
+        <v>5043</v>
+      </c>
+      <c r="H2007" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2007" s="3">
+        <v>28</v>
+      </c>
+      <c r="J2007" s="3"/>
+      <c r="K2007" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2007" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M2007" s="3" t="s">
+        <v>5044</v>
+      </c>
+      <c r="N2007" s="3" t="s">
+        <v>5045</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2008" s="3" t="s">
+        <v>5046</v>
+      </c>
+      <c r="B2008" s="3"/>
+      <c r="C2008" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2008" s="3">
+        <v>6131102680</v>
+      </c>
+      <c r="E2008" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2008" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G2008" s="3" t="s">
+        <v>5047</v>
+      </c>
+      <c r="H2008" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I2008" s="3">
+        <v>76</v>
+      </c>
+      <c r="J2008" s="3"/>
+      <c r="K2008" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2008" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M2008" s="3" t="s">
+        <v>5048</v>
+      </c>
+      <c r="N2008" s="3"/>
+    </row>
+    <row r="2009" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2009" s="3" t="s">
+        <v>5049</v>
+      </c>
+      <c r="B2009" s="3"/>
+      <c r="C2009" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2009" s="3">
+        <v>6133787127</v>
+      </c>
+      <c r="E2009" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2009" s="3" t="s">
+        <v>2360</v>
+      </c>
+      <c r="G2009" s="3" t="s">
+        <v>5050</v>
+      </c>
+      <c r="H2009" s="3"/>
+      <c r="I2009" s="3">
+        <v>58</v>
+      </c>
+      <c r="J2009" s="3"/>
+      <c r="K2009" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2009" s="3"/>
+      <c r="M2009" s="3"/>
+      <c r="N2009" s="3"/>
+    </row>
+    <row r="2010" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2010" s="3" t="s">
+        <v>5051</v>
+      </c>
+      <c r="B2010" s="3"/>
+      <c r="C2010" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2010" s="3">
+        <v>6133846491</v>
+      </c>
+      <c r="E2010" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2010" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="G2010" s="3" t="s">
+        <v>5052</v>
+      </c>
+      <c r="H2010" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I2010" s="3">
+        <v>83</v>
+      </c>
+      <c r="J2010" s="3"/>
+      <c r="K2010" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2010" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M2010" s="3" t="s">
+        <v>5053</v>
+      </c>
+      <c r="N2010" s="3"/>
+    </row>
+    <row r="2011" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2011" s="3" t="s">
+        <v>5054</v>
+      </c>
+      <c r="B2011" s="3"/>
+      <c r="C2011" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2011" s="3">
+        <v>6133848401</v>
+      </c>
+      <c r="E2011" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2011" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="G2011" s="3" t="s">
+        <v>5055</v>
+      </c>
+      <c r="H2011" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2011" s="3">
+        <v>72</v>
+      </c>
+      <c r="J2011" s="3"/>
+      <c r="K2011" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2011" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M2011" s="3" t="s">
+        <v>5053</v>
+      </c>
+      <c r="N2011" s="3"/>
+    </row>
+    <row r="2012" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2012" s="3" t="s">
+        <v>5056</v>
+      </c>
+      <c r="B2012" s="3"/>
+      <c r="C2012" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2012" s="3">
+        <v>6133874704</v>
+      </c>
+      <c r="E2012" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2012" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="G2012" s="3" t="s">
+        <v>5057</v>
+      </c>
+      <c r="H2012" s="3"/>
+      <c r="I2012" s="3">
+        <v>36</v>
+      </c>
+      <c r="J2012" s="3"/>
+      <c r="K2012" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2012" s="3"/>
+      <c r="M2012" s="3"/>
+      <c r="N2012" s="3"/>
+    </row>
+    <row r="2013" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2013" s="3" t="s">
+        <v>5058</v>
+      </c>
+      <c r="B2013" s="3"/>
+      <c r="C2013" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2013" s="3">
+        <v>6133883617</v>
+      </c>
+      <c r="E2013" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2013" s="3" t="s">
+        <v>2360</v>
+      </c>
+      <c r="G2013" s="3" t="s">
+        <v>5059</v>
+      </c>
+      <c r="H2013" s="3"/>
+      <c r="I2013" s="3">
+        <v>45</v>
+      </c>
+      <c r="J2013" s="3">
+        <v>35</v>
+      </c>
+      <c r="K2013" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2013" s="3"/>
+      <c r="M2013" s="3"/>
+      <c r="N2013" s="3"/>
+    </row>
+    <row r="2014" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2014" s="3" t="s">
+        <v>5060</v>
+      </c>
+      <c r="B2014" s="3"/>
+      <c r="C2014" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2014" s="3">
+        <v>6134480094</v>
+      </c>
+      <c r="E2014" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2014" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="G2014" s="3" t="s">
+        <v>5061</v>
+      </c>
+      <c r="H2014" s="3"/>
+      <c r="I2014" s="3">
+        <v>61</v>
+      </c>
+      <c r="J2014" s="3">
+        <v>55</v>
+      </c>
+      <c r="K2014" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2014" s="3"/>
+      <c r="M2014" s="3"/>
+      <c r="N2014" s="3"/>
+    </row>
+    <row r="2015" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2015" s="3" t="s">
+        <v>5062</v>
+      </c>
+      <c r="B2015" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2015" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2015" s="3">
+        <v>6134485640</v>
+      </c>
+      <c r="E2015" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2015" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G2015" s="3" t="s">
+        <v>5063</v>
+      </c>
+      <c r="H2015" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2015" s="3">
+        <v>60</v>
+      </c>
+      <c r="J2015" s="3">
+        <v>50</v>
+      </c>
+      <c r="K2015" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2015" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M2015" s="3" t="s">
+        <v>5064</v>
+      </c>
+      <c r="N2015" s="3" t="s">
+        <v>5065</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2016" s="3" t="s">
+        <v>5066</v>
+      </c>
+      <c r="B2016" s="3"/>
+      <c r="C2016" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2016" s="3">
+        <v>6135262753</v>
+      </c>
+      <c r="E2016" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2016" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G2016" s="3" t="s">
+        <v>5067</v>
+      </c>
+      <c r="H2016" s="3"/>
+      <c r="I2016" s="3">
+        <v>65</v>
+      </c>
+      <c r="J2016" s="3"/>
+      <c r="K2016" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2016" s="3"/>
+      <c r="M2016" s="3"/>
+      <c r="N2016" s="3"/>
+    </row>
+    <row r="2017" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2017" s="3" t="s">
+        <v>5068</v>
+      </c>
+      <c r="B2017" s="3"/>
+      <c r="C2017" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2017" s="3">
+        <v>6135309264</v>
+      </c>
+      <c r="E2017" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2017" s="3" t="s">
+        <v>5069</v>
+      </c>
+      <c r="G2017" s="3" t="s">
+        <v>5070</v>
+      </c>
+      <c r="H2017" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I2017" s="3">
+        <v>7</v>
+      </c>
+      <c r="J2017" s="3"/>
+      <c r="K2017" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2017" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M2017" s="3" t="s">
+        <v>5071</v>
+      </c>
+      <c r="N2017" s="3"/>
+    </row>
+    <row r="2018" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2018" s="3" t="s">
+        <v>5072</v>
+      </c>
+      <c r="B2018" s="3"/>
+      <c r="C2018" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2018" s="3">
+        <v>6135500949</v>
+      </c>
+      <c r="E2018" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2018" s="3" t="s">
+        <v>5073</v>
+      </c>
+      <c r="G2018" s="3" t="s">
+        <v>5074</v>
+      </c>
+      <c r="H2018" s="3"/>
+      <c r="I2018" s="3">
+        <v>52</v>
+      </c>
+      <c r="J2018" s="3"/>
+      <c r="K2018" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2018" s="3"/>
+      <c r="M2018" s="3"/>
+      <c r="N2018" s="3"/>
+    </row>
+    <row r="2019" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2019" s="3" t="s">
+        <v>5075</v>
+      </c>
+      <c r="B2019" s="3"/>
+      <c r="C2019" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2019" s="3">
+        <v>6135517554</v>
+      </c>
+      <c r="E2019" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2019" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="G2019" s="3" t="s">
+        <v>5076</v>
+      </c>
+      <c r="H2019" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I2019" s="3">
+        <v>76</v>
+      </c>
+      <c r="J2019" s="3">
+        <v>70</v>
+      </c>
+      <c r="K2019" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2019" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M2019" s="3" t="s">
+        <v>5077</v>
+      </c>
+      <c r="N2019" s="3"/>
+    </row>
+    <row r="2020" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2020" s="3" t="s">
+        <v>5078</v>
+      </c>
+      <c r="B2020" s="3"/>
+      <c r="C2020" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2020" s="3">
+        <v>6135789850</v>
+      </c>
+      <c r="E2020" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2020" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2020" s="3" t="s">
+        <v>5079</v>
+      </c>
+      <c r="H2020" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I2020" s="3">
+        <v>72</v>
+      </c>
+      <c r="J2020" s="3"/>
+      <c r="K2020" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2020" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M2020" s="3" t="s">
+        <v>5080</v>
+      </c>
+      <c r="N2020" s="3"/>
+    </row>
+    <row r="2021" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2021" s="3" t="s">
+        <v>5081</v>
+      </c>
+      <c r="B2021" s="3"/>
+      <c r="C2021" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2021" s="3">
+        <v>6136050326</v>
+      </c>
+      <c r="E2021" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2021" s="3" t="s">
+        <v>5082</v>
+      </c>
+      <c r="G2021" s="3" t="s">
+        <v>5083</v>
+      </c>
+      <c r="H2021" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I2021" s="3">
+        <v>6</v>
+      </c>
+      <c r="J2021" s="3"/>
+      <c r="K2021" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2021" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M2021" s="3" t="s">
+        <v>5080</v>
+      </c>
+      <c r="N2021" s="3"/>
+    </row>
+    <row r="2022" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2022" s="3" t="s">
+        <v>5084</v>
+      </c>
+      <c r="B2022" s="3"/>
+      <c r="C2022" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2022" s="3">
+        <v>6136181058</v>
+      </c>
+      <c r="E2022" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2022" s="3" t="s">
+        <v>1920</v>
+      </c>
+      <c r="G2022" s="3" t="s">
+        <v>5085</v>
+      </c>
+      <c r="H2022" s="3"/>
+      <c r="I2022" s="3">
+        <v>58</v>
+      </c>
+      <c r="J2022" s="3"/>
+      <c r="K2022" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2022" s="3"/>
+      <c r="M2022" s="3"/>
+      <c r="N2022" s="3"/>
+    </row>
+    <row r="2023" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2023" s="3" t="s">
+        <v>5086</v>
+      </c>
+      <c r="B2023" s="3"/>
+      <c r="C2023" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2023" s="3">
+        <v>6136624706</v>
+      </c>
+      <c r="E2023" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F2023" s="3" t="s">
+        <v>5087</v>
+      </c>
+      <c r="G2023" s="3" t="s">
+        <v>5088</v>
+      </c>
+      <c r="H2023" s="3"/>
+      <c r="I2023" s="3">
+        <v>40</v>
+      </c>
+      <c r="J2023" s="3"/>
+      <c r="K2023" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2023" s="3"/>
+      <c r="M2023" s="3"/>
+      <c r="N2023" s="3"/>
+    </row>
+    <row r="2024" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2024" s="3" t="s">
+        <v>5089</v>
+      </c>
+      <c r="B2024" s="3"/>
+      <c r="C2024" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2024" s="3">
+        <v>6136856984</v>
+      </c>
+      <c r="E2024" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2024" s="3" t="s">
+        <v>1804</v>
+      </c>
+      <c r="G2024" s="3" t="s">
+        <v>5090</v>
+      </c>
+      <c r="H2024" s="3"/>
+      <c r="I2024" s="3">
+        <v>5</v>
+      </c>
+      <c r="J2024" s="3"/>
+      <c r="K2024" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2024" s="3"/>
+      <c r="M2024" s="3"/>
+      <c r="N2024" s="3"/>
+    </row>
+    <row r="2025" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2025" s="3" t="s">
+        <v>5091</v>
+      </c>
+      <c r="B2025" s="3"/>
+      <c r="C2025" s="3">
+        <v>2</v>
+      </c>
+      <c r="D2025" s="3">
+        <v>6138027219</v>
+      </c>
+      <c r="E2025" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2025" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="G2025" s="3" t="s">
+        <v>5092</v>
+      </c>
+      <c r="H2025" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I2025" s="3">
+        <v>26</v>
+      </c>
+      <c r="J2025" s="3"/>
+      <c r="K2025" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2025" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M2025" s="3" t="s">
+        <v>5080</v>
+      </c>
+      <c r="N2025" s="3"/>
+    </row>
+    <row r="2026" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2026" s="3" t="s">
+        <v>5093</v>
+      </c>
+      <c r="B2026" s="3"/>
+      <c r="C2026" s="3">
+        <v>2</v>
+      </c>
+      <c r="D2026" s="3">
+        <v>6138036723</v>
+      </c>
+      <c r="E2026" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2026" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G2026" s="3" t="s">
+        <v>5094</v>
+      </c>
+      <c r="H2026" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I2026" s="3">
+        <v>52</v>
+      </c>
+      <c r="J2026" s="3"/>
+      <c r="K2026" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2026" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M2026" s="3" t="s">
+        <v>5095</v>
+      </c>
+      <c r="N2026" s="3"/>
+    </row>
+    <row r="2027" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2027" s="3" t="s">
+        <v>5096</v>
+      </c>
+      <c r="B2027" s="3"/>
+      <c r="C2027" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2027" s="3">
+        <v>6140801144</v>
+      </c>
+      <c r="E2027" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2027" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G2027" s="3" t="s">
+        <v>5097</v>
+      </c>
+      <c r="H2027" s="3"/>
+      <c r="I2027" s="3">
+        <v>57</v>
+      </c>
+      <c r="J2027" s="3">
+        <v>50</v>
+      </c>
+      <c r="K2027" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2027" s="3"/>
+      <c r="M2027" s="3"/>
+      <c r="N2027" s="3"/>
+    </row>
+    <row r="2028" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2028" s="3" t="s">
+        <v>5098</v>
+      </c>
+      <c r="B2028" s="3"/>
+      <c r="C2028" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2028" s="3">
+        <v>6140802948</v>
+      </c>
+      <c r="E2028" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2028" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="G2028" s="3" t="s">
+        <v>5099</v>
+      </c>
+      <c r="H2028" s="3"/>
+      <c r="I2028" s="3">
+        <v>59</v>
+      </c>
+      <c r="J2028" s="3">
+        <v>50</v>
+      </c>
+      <c r="K2028" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2028" s="3"/>
+      <c r="M2028" s="3"/>
+      <c r="N2028" s="3"/>
+    </row>
+    <row r="2029" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2029" s="3" t="s">
+        <v>5100</v>
+      </c>
+      <c r="B2029" s="3"/>
+      <c r="C2029" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2029" s="3">
+        <v>6142204222</v>
+      </c>
+      <c r="E2029" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2029" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2029" s="3" t="s">
+        <v>5101</v>
+      </c>
+      <c r="H2029" s="3"/>
+      <c r="I2029" s="3">
+        <v>74</v>
+      </c>
+      <c r="J2029" s="3"/>
+      <c r="K2029" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2029" s="3"/>
+      <c r="M2029" s="3"/>
+      <c r="N2029" s="3"/>
+    </row>
+    <row r="2030" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2030" s="3" t="s">
+        <v>5102</v>
+      </c>
+      <c r="B2030" s="3"/>
+      <c r="C2030" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2030" s="3">
+        <v>6142321674</v>
+      </c>
+      <c r="E2030" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2030" s="3" t="s">
+        <v>5103</v>
+      </c>
+      <c r="G2030" s="3" t="s">
+        <v>5104</v>
+      </c>
+      <c r="H2030" s="3"/>
+      <c r="I2030" s="3">
+        <v>74</v>
+      </c>
+      <c r="J2030" s="3">
+        <v>55</v>
+      </c>
+      <c r="K2030" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2030" s="3"/>
+      <c r="M2030" s="3"/>
+      <c r="N2030" s="3"/>
+    </row>
+    <row r="2031" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2031" s="3" t="s">
+        <v>5105</v>
+      </c>
+      <c r="B2031" s="3"/>
+      <c r="C2031" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2031" s="3">
+        <v>6142509106</v>
+      </c>
+      <c r="E2031" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2031" s="3" t="s">
+        <v>5106</v>
+      </c>
+      <c r="G2031" s="3" t="s">
+        <v>5107</v>
+      </c>
+      <c r="H2031" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I2031" s="3">
+        <v>40</v>
+      </c>
+      <c r="J2031" s="3"/>
+      <c r="K2031" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2031" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M2031" s="3" t="s">
+        <v>5108</v>
+      </c>
+      <c r="N2031" s="3"/>
+    </row>
+    <row r="2032" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2032" s="3" t="s">
+        <v>5109</v>
+      </c>
+      <c r="B2032" s="3"/>
+      <c r="C2032" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2032" s="3">
+        <v>6142709372</v>
+      </c>
+      <c r="E2032" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2032" s="3" t="s">
+        <v>5110</v>
+      </c>
+      <c r="G2032" s="3" t="s">
+        <v>5111</v>
+      </c>
+      <c r="H2032" s="3"/>
+      <c r="I2032" s="3">
+        <v>74</v>
+      </c>
+      <c r="J2032" s="3"/>
+      <c r="K2032" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2032" s="3"/>
+      <c r="M2032" s="3"/>
+      <c r="N2032" s="3"/>
+    </row>
+    <row r="2033" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2033" s="3" t="s">
+        <v>5112</v>
+      </c>
+      <c r="B2033" s="3"/>
+      <c r="C2033" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2033" s="3">
+        <v>6142915226</v>
+      </c>
+      <c r="E2033" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2033" s="3" t="s">
+        <v>5113</v>
+      </c>
+      <c r="G2033" s="3" t="s">
+        <v>5114</v>
+      </c>
+      <c r="H2033" s="3"/>
+      <c r="I2033" s="3">
+        <v>58</v>
+      </c>
+      <c r="J2033" s="3">
+        <v>50</v>
+      </c>
+      <c r="K2033" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2033" s="3"/>
+      <c r="M2033" s="3"/>
+      <c r="N2033" s="3"/>
+    </row>
+    <row r="2034" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2034" s="3" t="s">
+        <v>5115</v>
+      </c>
+      <c r="B2034" s="3"/>
+      <c r="C2034" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2034" s="3">
+        <v>6143088168</v>
+      </c>
+      <c r="E2034" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F2034" s="3" t="s">
+        <v>5116</v>
+      </c>
+      <c r="G2034" s="3" t="s">
+        <v>5117</v>
+      </c>
+      <c r="H2034" s="3"/>
+      <c r="I2034" s="3">
+        <v>20</v>
+      </c>
+      <c r="J2034" s="3"/>
+      <c r="K2034" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2034" s="3"/>
+      <c r="M2034" s="3"/>
+      <c r="N2034" s="3"/>
+    </row>
+    <row r="2035" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2035" s="3" t="s">
+        <v>5118</v>
+      </c>
+      <c r="B2035" s="3"/>
+      <c r="C2035" s="3">
+        <v>26</v>
+      </c>
+      <c r="D2035" s="3">
+        <v>6143839710</v>
+      </c>
+      <c r="E2035" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2035" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G2035" s="3" t="s">
+        <v>5119</v>
+      </c>
+      <c r="H2035" s="3"/>
+      <c r="I2035" s="3">
+        <v>69</v>
+      </c>
+      <c r="J2035" s="3"/>
+      <c r="K2035" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2035" s="3"/>
+      <c r="M2035" s="3"/>
+      <c r="N2035" s="3"/>
+    </row>
+    <row r="2036" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2036" s="3" t="s">
+        <v>5120</v>
+      </c>
+      <c r="B2036" s="3"/>
+      <c r="C2036" s="3">
+        <v>26</v>
+      </c>
+      <c r="D2036" s="3">
+        <v>6143899808</v>
+      </c>
+      <c r="E2036" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2036" s="3" t="s">
+        <v>3515</v>
+      </c>
+      <c r="G2036" s="3" t="s">
+        <v>5121</v>
+      </c>
+      <c r="H2036" s="3"/>
+      <c r="I2036" s="3">
+        <v>67</v>
+      </c>
+      <c r="J2036" s="3"/>
+      <c r="K2036" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2036" s="3"/>
+      <c r="M2036" s="3"/>
+      <c r="N2036" s="3"/>
+    </row>
+    <row r="2037" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2037" s="3" t="s">
+        <v>5122</v>
+      </c>
+      <c r="B2037" s="3"/>
+      <c r="C2037" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2037" s="3">
+        <v>6145544759</v>
+      </c>
+      <c r="E2037" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2037" s="3" t="s">
+        <v>1536</v>
+      </c>
+      <c r="G2037" s="3" t="s">
+        <v>5123</v>
+      </c>
+      <c r="H2037" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I2037" s="3">
+        <v>68</v>
+      </c>
+      <c r="J2037" s="3"/>
+      <c r="K2037" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2037" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M2037" s="3" t="s">
+        <v>5108</v>
+      </c>
+      <c r="N2037" s="3"/>
+    </row>
+    <row r="2038" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2038" s="3" t="s">
+        <v>5124</v>
+      </c>
+      <c r="B2038" s="3"/>
+      <c r="C2038" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2038" s="3">
+        <v>6146389623</v>
+      </c>
+      <c r="E2038" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2038" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G2038" s="3" t="s">
+        <v>5125</v>
+      </c>
+      <c r="H2038" s="3"/>
+      <c r="I2038" s="3">
+        <v>8</v>
+      </c>
+      <c r="J2038" s="3"/>
+      <c r="K2038" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2038" s="3"/>
+      <c r="M2038" s="3"/>
+      <c r="N2038" s="3"/>
+    </row>
+    <row r="2039" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2039" s="3" t="s">
+        <v>5126</v>
+      </c>
+      <c r="B2039" s="3"/>
+      <c r="C2039" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2039" s="3">
+        <v>6148401613</v>
+      </c>
+      <c r="E2039" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2039" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G2039" s="3" t="s">
+        <v>5127</v>
+      </c>
+      <c r="H2039" s="3"/>
+      <c r="I2039" s="3">
+        <v>33</v>
+      </c>
+      <c r="J2039" s="3"/>
+      <c r="K2039" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2039" s="3"/>
+      <c r="M2039" s="3"/>
+      <c r="N2039" s="3"/>
+    </row>
+    <row r="2040" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2040" s="3" t="s">
+        <v>5128</v>
+      </c>
+      <c r="B2040" s="3"/>
+      <c r="C2040" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2040" s="3">
+        <v>6148430541</v>
+      </c>
+      <c r="E2040" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2040" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G2040" s="3" t="s">
+        <v>5129</v>
+      </c>
+      <c r="H2040" s="3"/>
+      <c r="I2040" s="3">
+        <v>57</v>
+      </c>
+      <c r="J2040" s="3">
+        <v>50</v>
+      </c>
+      <c r="K2040" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2040" s="3"/>
+      <c r="M2040" s="3"/>
+      <c r="N2040" s="3"/>
+    </row>
+    <row r="2041" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2041" s="3" t="s">
+        <v>5130</v>
+      </c>
+      <c r="B2041" s="3"/>
+      <c r="C2041" s="3">
+        <v>26</v>
+      </c>
+      <c r="D2041" s="3">
+        <v>6150432924</v>
+      </c>
+      <c r="E2041" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2041" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G2041" s="3" t="s">
+        <v>5131</v>
+      </c>
+      <c r="H2041" s="3"/>
+      <c r="I2041" s="3">
+        <v>32</v>
+      </c>
+      <c r="J2041" s="3"/>
+      <c r="K2041" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2041" s="3"/>
+      <c r="M2041" s="3"/>
+      <c r="N2041" s="3"/>
+    </row>
+    <row r="2042" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2042" s="3" t="s">
+        <v>5132</v>
+      </c>
+      <c r="B2042" s="3"/>
+      <c r="C2042" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2042" s="3">
+        <v>6150915930</v>
+      </c>
+      <c r="E2042" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2042" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="G2042" s="3" t="s">
+        <v>5133</v>
+      </c>
+      <c r="H2042" s="3"/>
+      <c r="I2042" s="3">
+        <v>68</v>
+      </c>
+      <c r="J2042" s="3">
+        <v>60</v>
+      </c>
+      <c r="K2042" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2042" s="3"/>
+      <c r="M2042" s="3"/>
+      <c r="N2042" s="3"/>
+    </row>
+    <row r="2043" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2043" s="3" t="s">
+        <v>5134</v>
+      </c>
+      <c r="B2043" s="3"/>
+      <c r="C2043" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2043" s="3">
+        <v>6151831135</v>
+      </c>
+      <c r="E2043" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2043" s="3" t="s">
+        <v>5135</v>
+      </c>
+      <c r="G2043" s="3" t="s">
+        <v>5136</v>
+      </c>
+      <c r="H2043" s="3"/>
+      <c r="I2043" s="3">
+        <v>3</v>
+      </c>
+      <c r="J2043" s="3"/>
+      <c r="K2043" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2043" s="3"/>
+      <c r="M2043" s="3"/>
+      <c r="N2043" s="3"/>
+    </row>
+    <row r="2044" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2044" s="3" t="s">
+        <v>5137</v>
+      </c>
+      <c r="B2044" s="3"/>
+      <c r="C2044" s="3">
+        <v>2</v>
+      </c>
+      <c r="D2044" s="3">
+        <v>6151896627</v>
+      </c>
+      <c r="E2044" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2044" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="G2044" s="3" t="s">
+        <v>5138</v>
+      </c>
+      <c r="H2044" s="3"/>
+      <c r="I2044" s="3">
+        <v>68</v>
+      </c>
+      <c r="J2044" s="3"/>
+      <c r="K2044" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2044" s="3"/>
+      <c r="M2044" s="3"/>
+      <c r="N2044" s="3"/>
+    </row>
+    <row r="2045" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2045" s="3" t="s">
+        <v>5139</v>
+      </c>
+      <c r="B2045" s="3"/>
+      <c r="C2045" s="3">
+        <v>2</v>
+      </c>
+      <c r="D2045" s="3">
+        <v>6152018036</v>
+      </c>
+      <c r="E2045" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2045" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G2045" s="3" t="s">
+        <v>5140</v>
+      </c>
+      <c r="H2045" s="3"/>
+      <c r="I2045" s="3">
+        <v>57</v>
+      </c>
+      <c r="J2045" s="3"/>
+      <c r="K2045" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2045" s="3"/>
+      <c r="M2045" s="3"/>
+      <c r="N2045" s="3"/>
+    </row>
+    <row r="2046" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2046" s="3" t="s">
+        <v>5139</v>
+      </c>
+      <c r="B2046" s="3"/>
+      <c r="C2046" s="3">
+        <v>2</v>
+      </c>
+      <c r="D2046" s="3">
+        <v>6152026819</v>
+      </c>
+      <c r="E2046" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2046" s="3" t="s">
+        <v>1951</v>
+      </c>
+      <c r="G2046" s="3" t="s">
+        <v>5141</v>
+      </c>
+      <c r="H2046" s="3"/>
+      <c r="I2046" s="3">
+        <v>61</v>
+      </c>
+      <c r="J2046" s="3"/>
+      <c r="K2046" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2046" s="3"/>
+      <c r="M2046" s="3"/>
+      <c r="N2046" s="3"/>
+    </row>
+    <row r="2047" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2047" s="3" t="s">
+        <v>5142</v>
+      </c>
+      <c r="B2047" s="3"/>
+      <c r="C2047" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2047" s="3">
+        <v>6152166593</v>
+      </c>
+      <c r="E2047" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2047" s="3" t="s">
+        <v>5143</v>
+      </c>
+      <c r="G2047" s="3" t="s">
+        <v>5144</v>
+      </c>
+      <c r="H2047" s="3"/>
+      <c r="I2047" s="3">
+        <v>66</v>
+      </c>
+      <c r="J2047" s="3">
+        <v>60</v>
+      </c>
+      <c r="K2047" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2047" s="3"/>
+      <c r="M2047" s="3"/>
+      <c r="N2047" s="3"/>
+    </row>
+    <row r="2048" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2048" s="3" t="s">
+        <v>5145</v>
+      </c>
+      <c r="B2048" s="3"/>
+      <c r="C2048" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2048" s="3">
+        <v>6152973065</v>
+      </c>
+      <c r="E2048" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2048" s="3" t="s">
+        <v>5146</v>
+      </c>
+      <c r="G2048" s="3" t="s">
+        <v>5147</v>
+      </c>
+      <c r="H2048" s="3"/>
+      <c r="I2048" s="3">
+        <v>69</v>
+      </c>
+      <c r="J2048" s="3">
+        <v>60</v>
+      </c>
+      <c r="K2048" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2048" s="3"/>
+      <c r="M2048" s="3"/>
+      <c r="N2048" s="3"/>
+    </row>
+    <row r="2049" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2049" s="3" t="s">
+        <v>5148</v>
+      </c>
+      <c r="B2049" s="3"/>
+      <c r="C2049" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2049" s="3">
+        <v>6153048232</v>
+      </c>
+      <c r="E2049" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2049" s="3" t="s">
+        <v>5149</v>
+      </c>
+      <c r="G2049" s="3" t="s">
+        <v>5150</v>
+      </c>
+      <c r="H2049" s="3"/>
+      <c r="I2049" s="3">
+        <v>67</v>
+      </c>
+      <c r="J2049" s="3">
+        <v>60</v>
+      </c>
+      <c r="K2049" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2049" s="3"/>
+      <c r="M2049" s="3"/>
+      <c r="N2049" s="3"/>
+    </row>
+    <row r="2050" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2050" s="3" t="s">
+        <v>5151</v>
+      </c>
+      <c r="B2050" s="3"/>
+      <c r="C2050" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2050" s="3">
+        <v>6153249219</v>
+      </c>
+      <c r="E2050" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2050" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G2050" s="3" t="s">
+        <v>5152</v>
+      </c>
+      <c r="H2050" s="3"/>
+      <c r="I2050" s="3">
+        <v>67</v>
+      </c>
+      <c r="J2050" s="3">
+        <v>60</v>
+      </c>
+      <c r="K2050" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2050" s="3"/>
+      <c r="M2050" s="3"/>
+      <c r="N2050" s="3"/>
+    </row>
+    <row r="2051" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2051" s="3" t="s">
+        <v>5153</v>
+      </c>
+      <c r="B2051" s="3"/>
+      <c r="C2051" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2051" s="3">
+        <v>6153447794</v>
+      </c>
+      <c r="E2051" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2051" s="3" t="s">
+        <v>5154</v>
+      </c>
+      <c r="G2051" s="3" t="s">
+        <v>5155</v>
+      </c>
+      <c r="H2051" s="3"/>
+      <c r="I2051" s="3">
+        <v>32</v>
+      </c>
+      <c r="J2051" s="3"/>
+      <c r="K2051" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2051" s="3"/>
+      <c r="M2051" s="3"/>
+      <c r="N2051" s="3"/>
+    </row>
+    <row r="2052" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2052" s="3" t="s">
+        <v>5156</v>
+      </c>
+      <c r="B2052" s="3"/>
+      <c r="C2052" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2052" s="3">
+        <v>6153478861</v>
+      </c>
+      <c r="E2052" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2052" s="3" t="s">
+        <v>4025</v>
+      </c>
+      <c r="G2052" s="3" t="s">
+        <v>5157</v>
+      </c>
+      <c r="H2052" s="3"/>
+      <c r="I2052" s="3">
+        <v>13</v>
+      </c>
+      <c r="J2052" s="3"/>
+      <c r="K2052" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2052" s="3"/>
+      <c r="M2052" s="3"/>
+      <c r="N2052" s="3"/>
+    </row>
+    <row r="2053" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2053" s="3" t="s">
+        <v>5158</v>
+      </c>
+      <c r="B2053" s="3"/>
+      <c r="C2053" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2053" s="3">
+        <v>6154811052</v>
+      </c>
+      <c r="E2053" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2053" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G2053" s="3" t="s">
+        <v>5159</v>
+      </c>
+      <c r="H2053" s="3"/>
+      <c r="I2053" s="3">
+        <v>17</v>
+      </c>
+      <c r="J2053" s="3"/>
+      <c r="K2053" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2053" s="3"/>
+      <c r="M2053" s="3"/>
+      <c r="N2053" s="3"/>
+    </row>
+    <row r="2054" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2054" s="3" t="s">
+        <v>5160</v>
+      </c>
+      <c r="B2054" s="3"/>
+      <c r="C2054" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2054" s="3">
+        <v>6154819224</v>
+      </c>
+      <c r="E2054" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2054" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2054" s="3" t="s">
+        <v>5161</v>
+      </c>
+      <c r="H2054" s="3"/>
+      <c r="I2054" s="3">
+        <v>18</v>
+      </c>
+      <c r="J2054" s="3"/>
+      <c r="K2054" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2054" s="3"/>
+      <c r="M2054" s="3"/>
+      <c r="N2054" s="3"/>
+    </row>
+    <row r="2055" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2055" s="3" t="s">
+        <v>5162</v>
+      </c>
+      <c r="B2055" s="3"/>
+      <c r="C2055" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2055" s="3">
+        <v>6154968653</v>
+      </c>
+      <c r="E2055" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2055" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="G2055" s="3" t="s">
+        <v>5163</v>
+      </c>
+      <c r="H2055" s="3"/>
+      <c r="I2055" s="3">
+        <v>68</v>
+      </c>
+      <c r="J2055" s="3">
+        <v>60</v>
+      </c>
+      <c r="K2055" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2055" s="3"/>
+      <c r="M2055" s="3"/>
+      <c r="N2055" s="3"/>
+    </row>
+    <row r="2056" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2056" s="3" t="s">
+        <v>5164</v>
+      </c>
+      <c r="B2056" s="3"/>
+      <c r="C2056" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2056" s="3">
+        <v>6155390223</v>
+      </c>
+      <c r="E2056" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2056" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="G2056" s="3" t="s">
+        <v>5165</v>
+      </c>
+      <c r="H2056" s="3"/>
+      <c r="I2056" s="3">
+        <v>33</v>
+      </c>
+      <c r="J2056" s="3">
+        <v>70</v>
+      </c>
+      <c r="K2056" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2056" s="3"/>
+      <c r="M2056" s="3"/>
+      <c r="N2056" s="3"/>
+    </row>
+    <row r="2057" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2057" s="3" t="s">
+        <v>5166</v>
+      </c>
+      <c r="B2057" s="3"/>
+      <c r="C2057" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2057" s="3">
+        <v>6155788780</v>
+      </c>
+      <c r="E2057" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2057" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G2057" s="3" t="s">
+        <v>5167</v>
+      </c>
+      <c r="H2057" s="3"/>
+      <c r="I2057" s="3">
+        <v>16</v>
+      </c>
+      <c r="J2057" s="3"/>
+      <c r="K2057" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2057" s="3"/>
+      <c r="M2057" s="3"/>
+      <c r="N2057" s="3"/>
+    </row>
+    <row r="2058" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2058" s="3" t="s">
+        <v>5168</v>
+      </c>
+      <c r="B2058" s="3"/>
+      <c r="C2058" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2058" s="3">
+        <v>6156010546</v>
+      </c>
+      <c r="E2058" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2058" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G2058" s="3" t="s">
+        <v>5169</v>
+      </c>
+      <c r="H2058" s="3"/>
+      <c r="I2058" s="3">
+        <v>4</v>
+      </c>
+      <c r="J2058" s="3"/>
+      <c r="K2058" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2058" s="3"/>
+      <c r="M2058" s="3"/>
+      <c r="N2058" s="3"/>
+    </row>
+    <row r="2059" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2059" s="3" t="s">
+        <v>5170</v>
+      </c>
+      <c r="B2059" s="3"/>
+      <c r="C2059" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2059" s="3">
+        <v>6156108947</v>
+      </c>
+      <c r="E2059" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2059" s="3" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G2059" s="3" t="s">
+        <v>5171</v>
+      </c>
+      <c r="H2059" s="3"/>
+      <c r="I2059" s="3">
+        <v>58</v>
+      </c>
+      <c r="J2059" s="3">
+        <v>50</v>
+      </c>
+      <c r="K2059" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2059" s="3"/>
+      <c r="M2059" s="3"/>
+      <c r="N2059" s="3"/>
+    </row>
+    <row r="2060" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2060" s="3" t="s">
+        <v>5172</v>
+      </c>
+      <c r="B2060" s="3"/>
+      <c r="C2060" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2060" s="3">
+        <v>6156954665</v>
+      </c>
+      <c r="E2060" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2060" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G2060" s="3" t="s">
+        <v>5173</v>
+      </c>
+      <c r="H2060" s="3"/>
+      <c r="I2060" s="3">
+        <v>32</v>
+      </c>
+      <c r="J2060" s="3"/>
+      <c r="K2060" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2060" s="3"/>
+      <c r="M2060" s="3"/>
+      <c r="N2060" s="3"/>
+    </row>
+    <row r="2061" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2061" s="3" t="s">
+        <v>5174</v>
+      </c>
+      <c r="B2061" s="3"/>
+      <c r="C2061" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2061" s="3">
+        <v>6157004351</v>
+      </c>
+      <c r="E2061" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2061" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G2061" s="3" t="s">
+        <v>5175</v>
+      </c>
+      <c r="H2061" s="3"/>
+      <c r="I2061" s="3">
+        <v>46</v>
+      </c>
+      <c r="J2061" s="3"/>
+      <c r="K2061" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2061" s="3"/>
+      <c r="M2061" s="3"/>
+      <c r="N2061" s="3"/>
+    </row>
+    <row r="2062" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2062" s="3" t="s">
+        <v>5176</v>
+      </c>
+      <c r="B2062" s="3"/>
+      <c r="C2062" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2062" s="3">
+        <v>6158660859</v>
+      </c>
+      <c r="E2062" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2062" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G2062" s="3" t="s">
+        <v>5177</v>
+      </c>
+      <c r="H2062" s="3"/>
+      <c r="I2062" s="3">
+        <v>61</v>
+      </c>
+      <c r="J2062" s="3">
+        <v>50</v>
+      </c>
+      <c r="K2062" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2062" s="3"/>
+      <c r="M2062" s="3"/>
+      <c r="N2062" s="3"/>
+    </row>
+    <row r="2063" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2063" s="3" t="s">
+        <v>5178</v>
+      </c>
+      <c r="B2063" s="3"/>
+      <c r="C2063" s="3">
+        <v>28</v>
+      </c>
+      <c r="D2063" s="3">
+        <v>6159171154</v>
+      </c>
+      <c r="E2063" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F2063" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="G2063" s="3" t="s">
+        <v>5179</v>
+      </c>
+      <c r="H2063" s="3"/>
+      <c r="I2063" s="3"/>
+      <c r="J2063" s="3"/>
+      <c r="K2063" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2063" s="3"/>
+      <c r="M2063" s="3"/>
+      <c r="N2063" s="3"/>
+    </row>
+    <row r="2064" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2064" s="3" t="s">
+        <v>5180</v>
+      </c>
+      <c r="B2064" s="3"/>
+      <c r="C2064" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2064" s="3">
+        <v>6159334416</v>
+      </c>
+      <c r="E2064" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2064" s="3" t="s">
+        <v>2113</v>
+      </c>
+      <c r="G2064" s="3" t="s">
+        <v>5181</v>
+      </c>
+      <c r="H2064" s="3"/>
+      <c r="I2064" s="3">
+        <v>67</v>
+      </c>
+      <c r="J2064" s="3">
+        <v>60</v>
+      </c>
+      <c r="K2064" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2064" s="3"/>
+      <c r="M2064" s="3"/>
+      <c r="N2064" s="3"/>
+    </row>
+    <row r="2065" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2065" s="3" t="s">
+        <v>5182</v>
+      </c>
+      <c r="B2065" s="3"/>
+      <c r="C2065" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2065" s="3">
+        <v>6159359181</v>
+      </c>
+      <c r="E2065" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2065" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G2065" s="3" t="s">
+        <v>5183</v>
+      </c>
+      <c r="H2065" s="3"/>
+      <c r="I2065" s="3">
+        <v>9</v>
+      </c>
+      <c r="J2065" s="3"/>
+      <c r="K2065" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2065" s="3"/>
+      <c r="M2065" s="3"/>
+      <c r="N2065" s="3"/>
+    </row>
+    <row r="2066" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2066" s="3" t="s">
+        <v>5184</v>
+      </c>
+      <c r="B2066" s="3"/>
+      <c r="C2066" s="3">
+        <v>31</v>
+      </c>
+      <c r="D2066" s="3">
+        <v>6159403615</v>
+      </c>
+      <c r="E2066" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2066" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="G2066" s="3" t="s">
+        <v>5185</v>
+      </c>
+      <c r="H2066" s="3"/>
+      <c r="I2066" s="3">
+        <v>65</v>
+      </c>
+      <c r="J2066" s="3">
+        <v>50</v>
+      </c>
+      <c r="K2066" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2066" s="3"/>
+      <c r="M2066" s="3"/>
+      <c r="N2066" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
